--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie "O que mexer primeiro" e use o prompt "Retomar proposta parada" da biblioteca para escrever a mensagem ao cliente; copie "Motivos de perda" e use "Revisar a proposta de honorários". A proposta fechada vira caso na planilha 13 (Carteira).</t>
+          <t>Copie "O que mexer primeiro" e use o prompt "Clientes 06 · Por que as propostas não fecham" da biblioteca para escrever a mensagem ao cliente; copie "Motivos de perda" e use "Revisar a proposta de honorários". A proposta fechada vira caso na planilha 13 (Carteira).</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
@@ -826,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -927,77 +927,89 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie "O que mexer primeiro" e use o prompt "Clientes 06 · Por que as propostas não fecham" da biblioteca para escrever a mensagem ao cliente; copie "Motivos de perda" e use "Revisar a proposta de honorários". A proposta fechada vira caso na planilha 13 (Carteira).</t>
+          <t>Copie "Motivos de perda" e use o prompt "Clientes 06 · Por que as propostas não fecham" da biblioteca; para uma proposta parada, "Honorários 02 · Revisar a proposta pela margem" antes de retomar o contato. A proposta fechada vira caso na planilha 13 (Carteira).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Legenda</t>
+          <t>Exemplo</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
+          <t>O funil traz 20 propostas de junho a setembro de 2026: as 7 fechadas viraram casos na planilha 13 (abertura no mês do fechamento) e as 10 mais recentes já enviadas são as mesmas do Registro da planilha 07.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Proteção</t>
+          <t>Legenda</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
+          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>Proteção</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1033,9 +1045,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Funil de propostas · "&amp;TEXT(DAY(Config!$B$5),"00")&amp;"/"&amp;TEXT(MONTH(Config!$B$5),"00")&amp;"/"&amp;YEAR(Config!$B$5)</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Funil de propostas · 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1086,32 +1098,32 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13">
         <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;")</f>
-        <v/>
+        <v>72900</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="14">
         <f>SUMIFS(Propostas!$N$5:$N$304,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;")</f>
-        <v/>
+        <v>30805</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="15">
         <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,"Fechada",Propostas!$K$5:$K$304,"&gt;="&amp;DATE(YEAR(Config!$B$5),3*INT((MONTH(Config!$B$5)-1)/3)+1,1))</f>
-        <v/>
+        <v>53000</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="16">
         <f>IFERROR(E5/Config!$B$6,0)</f>
-        <v/>
+        <v>0.883333333333333</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="17">
         <f>IFERROR(COUNTIFS(Propostas!$G$5:$G$304,"Fechada")/(COUNTIFS(Propostas!$G$5:$G$304,"Fechada")+COUNTIFS(Propostas!$G$5:$G$304,"Perdida")),0)</f>
-        <v/>
+        <v>0.636363636363636</v>
       </c>
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="18">
         <f>IFERROR(AVERAGEIFS(Propostas!$P$5:$P$304,Propostas!$G$5:$G$304,"Fechada"),0)</f>
-        <v/>
+        <v>19.5714285714286</v>
       </c>
       <c r="L5" s="8" t="n"/>
     </row>
@@ -1164,113 +1176,113 @@
       <c r="H10" s="23" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="24">
+      <c r="A11" s="24" t="str">
         <f>Config!$A$10</f>
-        <v/>
+        <v>Contato</v>
       </c>
       <c r="B11" s="25">
         <f>COUNTIFS(Propostas!$G$5:$G$304,A11)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C11" s="26">
         <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,A11)</f>
-        <v/>
+        <v>18800</v>
       </c>
       <c r="D11" s="26">
         <f>SUMIFS(Propostas!$N$5:$N$304,Propostas!$G$5:$G$304,A11)</f>
-        <v/>
+        <v>1880</v>
       </c>
       <c r="E11" s="27">
         <f>IFERROR((COUNTIFS(Propostas!$G$5:$G$304,Config!$A$11)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$12)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$13)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$14)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$15))/(B11+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$11)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$12)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$13)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$14)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$15)),0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="28">
+        <v>0.9</v>
+      </c>
+      <c r="F11" s="28" t="str">
         <f>REPT("█",ROUND(IFERROR(C11/MAX($C$11:$C$14),0)*30,0))</f>
-        <v/>
+        <v>███████████████████████████</v>
       </c>
       <c r="G11" s="22" t="n"/>
       <c r="H11" s="23" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="24">
+      <c r="A12" s="24" t="str">
         <f>Config!$A$11</f>
-        <v/>
+        <v>Reunião feita</v>
       </c>
       <c r="B12" s="25">
         <f>COUNTIFS(Propostas!$G$5:$G$304,A12)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C12" s="26">
         <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,A12)</f>
-        <v/>
+        <v>13700</v>
       </c>
       <c r="D12" s="26">
         <f>SUMIFS(Propostas!$N$5:$N$304,Propostas!$G$5:$G$304,A12)</f>
-        <v/>
+        <v>3425</v>
       </c>
       <c r="E12" s="27">
         <f>IFERROR((COUNTIFS(Propostas!$G$5:$G$304,Config!$A$12)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$13)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$14)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$15))/(B12+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$12)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$13)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$14)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$15)),0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
+        <v>0.888888888888889</v>
+      </c>
+      <c r="F12" s="28" t="str">
         <f>REPT("█",ROUND(IFERROR(C12/MAX($C$11:$C$14),0)*30,0))</f>
-        <v/>
+        <v>███████████████████</v>
       </c>
       <c r="G12" s="22" t="n"/>
       <c r="H12" s="23" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="24">
+      <c r="A13" s="24" t="str">
         <f>Config!$A$12</f>
-        <v/>
+        <v>Proposta enviada</v>
       </c>
       <c r="B13" s="25">
         <f>COUNTIFS(Propostas!$G$5:$G$304,A13)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C13" s="26">
         <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,A13)</f>
-        <v/>
+        <v>19200</v>
       </c>
       <c r="D13" s="26">
         <f>SUMIFS(Propostas!$N$5:$N$304,Propostas!$G$5:$G$304,A13)</f>
-        <v/>
+        <v>9600</v>
       </c>
       <c r="E13" s="27">
         <f>IFERROR((COUNTIFS(Propostas!$G$5:$G$304,Config!$A$13)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$14)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$15))/(B13+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$13)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$14)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$15)),0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="28">
+        <v>0.8125</v>
+      </c>
+      <c r="F13" s="28" t="str">
         <f>REPT("█",ROUND(IFERROR(C13/MAX($C$11:$C$14),0)*30,0))</f>
-        <v/>
+        <v>███████████████████████████</v>
       </c>
       <c r="G13" s="22" t="n"/>
       <c r="H13" s="23" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="24">
+      <c r="A14" s="24" t="str">
         <f>Config!$A$13</f>
-        <v/>
+        <v>Negociação</v>
       </c>
       <c r="B14" s="25">
         <f>COUNTIFS(Propostas!$G$5:$G$304,A14)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C14" s="26">
         <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,A14)</f>
-        <v/>
+        <v>21200</v>
       </c>
       <c r="D14" s="26">
         <f>SUMIFS(Propostas!$N$5:$N$304,Propostas!$G$5:$G$304,A14)</f>
-        <v/>
+        <v>15900</v>
       </c>
       <c r="E14" s="27">
         <f>IFERROR((COUNTIFS(Propostas!$G$5:$G$304,Config!$A$14)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$15))/(B14+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$14)+COUNTIFS(Propostas!$G$5:$G$304,Config!$A$15)),0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="28">
+        <v>0.846153846153846</v>
+      </c>
+      <c r="F14" s="28" t="str">
         <f>REPT("█",ROUND(IFERROR(C14/MAX($C$11:$C$14),0)*30,0))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="G14" s="22" t="n"/>
       <c r="H14" s="23" t="n"/>
@@ -1283,11 +1295,11 @@
       </c>
       <c r="B15" s="25">
         <f>COUNTIFS(Propostas!$G$5:$G$304,"Fechada")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C15" s="26">
         <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,"Fechada")</f>
-        <v/>
+        <v>71000</v>
       </c>
     </row>
     <row r="16">
@@ -1298,11 +1310,11 @@
       </c>
       <c r="B16" s="25">
         <f>COUNTIFS(Propostas!$G$5:$G$304,"Perdida")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C16" s="26">
         <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,"Perdida")</f>
-        <v/>
+        <v>27100</v>
       </c>
     </row>
     <row r="17">
@@ -1313,7 +1325,7 @@
       </c>
       <c r="B17" s="26">
         <f>IFERROR(C15/B15,0)</f>
-        <v/>
+        <v>10142.8571428571</v>
       </c>
       <c r="C17" s="26" t="n"/>
     </row>
@@ -1384,264 +1396,264 @@
       <c r="A23" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,1)&gt;0,INDEX(Propostas!$A$5:$A$304,MATCH(LARGE(Propostas!$R$5:$R$304,1),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C23" s="24">
+        <v>Clínica Bem-Estar</v>
+      </c>
+      <c r="C23" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,1)&gt;0,INDEX(Propostas!$C$5:$C$304,MATCH(LARGE(Propostas!$R$5:$R$304,1),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="25">
+        <v>Contratos com convênios</v>
+      </c>
+      <c r="D23" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,1)&gt;0,INDEX(Propostas!$G$5:$G$304,MATCH(LARGE(Propostas!$R$5:$R$304,1),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Negociação</v>
       </c>
       <c r="E23" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,1)&gt;0,INDEX(Propostas!$F$5:$F$304,MATCH(LARGE(Propostas!$R$5:$R$304,1),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>6800</v>
       </c>
       <c r="F23" s="29">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,1)&gt;0,INDEX(Propostas!$O$5:$O$304,MATCH(LARGE(Propostas!$R$5:$R$304,1),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="25">
+        <v>17</v>
+      </c>
+      <c r="G23" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,1)&gt;0,INDEX(Propostas!$Q$5:$Q$304,MATCH(LARGE(Propostas!$R$5:$R$304,1),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="25">
+        <v>Previsão vencida</v>
+      </c>
+      <c r="H23" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,1)&gt;0,INDEX(Propostas!$E$5:$E$304,MATCH(LARGE(Propostas!$R$5:$R$304,1),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,2)&gt;0,INDEX(Propostas!$A$5:$A$304,MATCH(LARGE(Propostas!$R$5:$R$304,2),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="24">
+        <v>José Antônio Ribeiro</v>
+      </c>
+      <c r="C24" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,2)&gt;0,INDEX(Propostas!$C$5:$C$304,MATCH(LARGE(Propostas!$R$5:$R$304,2),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="25">
+        <v>Revisão de benefício</v>
+      </c>
+      <c r="D24" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,2)&gt;0,INDEX(Propostas!$G$5:$G$304,MATCH(LARGE(Propostas!$R$5:$R$304,2),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Proposta enviada</v>
       </c>
       <c r="E24" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,2)&gt;0,INDEX(Propostas!$F$5:$F$304,MATCH(LARGE(Propostas!$R$5:$R$304,2),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>4200</v>
       </c>
       <c r="F24" s="29">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,2)&gt;0,INDEX(Propostas!$O$5:$O$304,MATCH(LARGE(Propostas!$R$5:$R$304,2),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="25">
+        <v>14</v>
+      </c>
+      <c r="G24" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,2)&gt;0,INDEX(Propostas!$Q$5:$Q$304,MATCH(LARGE(Propostas!$R$5:$R$304,2),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="25">
+        <v>Previsão vencida</v>
+      </c>
+      <c r="H24" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,2)&gt;0,INDEX(Propostas!$E$5:$E$304,MATCH(LARGE(Propostas!$R$5:$R$304,2),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,3)&gt;0,INDEX(Propostas!$A$5:$A$304,MATCH(LARGE(Propostas!$R$5:$R$304,3),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C25" s="24">
+        <v>Patrícia Gomes</v>
+      </c>
+      <c r="C25" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,3)&gt;0,INDEX(Propostas!$C$5:$C$304,MATCH(LARGE(Propostas!$R$5:$R$304,3),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="25">
+        <v>Inventário</v>
+      </c>
+      <c r="D25" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,3)&gt;0,INDEX(Propostas!$G$5:$G$304,MATCH(LARGE(Propostas!$R$5:$R$304,3),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Proposta enviada</v>
       </c>
       <c r="E25" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,3)&gt;0,INDEX(Propostas!$F$5:$F$304,MATCH(LARGE(Propostas!$R$5:$R$304,3),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>10500</v>
       </c>
       <c r="F25" s="29">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,3)&gt;0,INDEX(Propostas!$O$5:$O$304,MATCH(LARGE(Propostas!$R$5:$R$304,3),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="25">
+        <v>16</v>
+      </c>
+      <c r="G25" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,3)&gt;0,INDEX(Propostas!$Q$5:$Q$304,MATCH(LARGE(Propostas!$R$5:$R$304,3),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="25">
+        <v>Parada</v>
+      </c>
+      <c r="H25" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,3)&gt;0,INDEX(Propostas!$E$5:$E$304,MATCH(LARGE(Propostas!$R$5:$R$304,3),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,4)&gt;0,INDEX(Propostas!$A$5:$A$304,MATCH(LARGE(Propostas!$R$5:$R$304,4),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C26" s="24">
+        <v>Transportadora Rota Sul</v>
+      </c>
+      <c r="C26" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,4)&gt;0,INDEX(Propostas!$C$5:$C$304,MATCH(LARGE(Propostas!$R$5:$R$304,4),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="25">
+        <v>Assessoria mensal (12 meses)</v>
+      </c>
+      <c r="D26" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,4)&gt;0,INDEX(Propostas!$G$5:$G$304,MATCH(LARGE(Propostas!$R$5:$R$304,4),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Negociação</v>
       </c>
       <c r="E26" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,4)&gt;0,INDEX(Propostas!$F$5:$F$304,MATCH(LARGE(Propostas!$R$5:$R$304,4),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>14400</v>
       </c>
       <c r="F26" s="29">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,4)&gt;0,INDEX(Propostas!$O$5:$O$304,MATCH(LARGE(Propostas!$R$5:$R$304,4),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="25">
+        <v>4</v>
+      </c>
+      <c r="G26" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,4)&gt;0,INDEX(Propostas!$Q$5:$Q$304,MATCH(LARGE(Propostas!$R$5:$R$304,4),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="25">
+        <v>Ativa</v>
+      </c>
+      <c r="H26" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,4)&gt;0,INDEX(Propostas!$E$5:$E$304,MATCH(LARGE(Propostas!$R$5:$R$304,4),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,5)&gt;0,INDEX(Propostas!$A$5:$A$304,MATCH(LARGE(Propostas!$R$5:$R$304,5),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C27" s="24">
+        <v>Helena Duarte</v>
+      </c>
+      <c r="C27" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,5)&gt;0,INDEX(Propostas!$C$5:$C$304,MATCH(LARGE(Propostas!$R$5:$R$304,5),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="25">
+        <v>Ação trabalhista</v>
+      </c>
+      <c r="D27" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,5)&gt;0,INDEX(Propostas!$G$5:$G$304,MATCH(LARGE(Propostas!$R$5:$R$304,5),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Reunião feita</v>
       </c>
       <c r="E27" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,5)&gt;0,INDEX(Propostas!$F$5:$F$304,MATCH(LARGE(Propostas!$R$5:$R$304,5),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>5800</v>
       </c>
       <c r="F27" s="29">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,5)&gt;0,INDEX(Propostas!$O$5:$O$304,MATCH(LARGE(Propostas!$R$5:$R$304,5),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="25">
+        <v>3</v>
+      </c>
+      <c r="G27" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,5)&gt;0,INDEX(Propostas!$Q$5:$Q$304,MATCH(LARGE(Propostas!$R$5:$R$304,5),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="25">
+        <v>Ativa</v>
+      </c>
+      <c r="H27" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,5)&gt;0,INDEX(Propostas!$E$5:$E$304,MATCH(LARGE(Propostas!$R$5:$R$304,5),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,6)&gt;0,INDEX(Propostas!$A$5:$A$304,MATCH(LARGE(Propostas!$R$5:$R$304,6),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="24">
+        <v>Marcos Vinícius Teles</v>
+      </c>
+      <c r="C28" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,6)&gt;0,INDEX(Propostas!$C$5:$C$304,MATCH(LARGE(Propostas!$R$5:$R$304,6),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="25">
+        <v>Divórcio e partilha</v>
+      </c>
+      <c r="D28" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,6)&gt;0,INDEX(Propostas!$G$5:$G$304,MATCH(LARGE(Propostas!$R$5:$R$304,6),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Contato</v>
       </c>
       <c r="E28" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,6)&gt;0,INDEX(Propostas!$F$5:$F$304,MATCH(LARGE(Propostas!$R$5:$R$304,6),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>5600</v>
       </c>
       <c r="F28" s="29">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,6)&gt;0,INDEX(Propostas!$O$5:$O$304,MATCH(LARGE(Propostas!$R$5:$R$304,6),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="25">
+        <v>3</v>
+      </c>
+      <c r="G28" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,6)&gt;0,INDEX(Propostas!$Q$5:$Q$304,MATCH(LARGE(Propostas!$R$5:$R$304,6),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="25">
+        <v>Ativa</v>
+      </c>
+      <c r="H28" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,6)&gt;0,INDEX(Propostas!$E$5:$E$304,MATCH(LARGE(Propostas!$R$5:$R$304,6),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,7)&gt;0,INDEX(Propostas!$A$5:$A$304,MATCH(LARGE(Propostas!$R$5:$R$304,7),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="24">
+        <v>Luciana Farias</v>
+      </c>
+      <c r="C29" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,7)&gt;0,INDEX(Propostas!$C$5:$C$304,MATCH(LARGE(Propostas!$R$5:$R$304,7),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="25">
+        <v>Cobrança judicial</v>
+      </c>
+      <c r="D29" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,7)&gt;0,INDEX(Propostas!$G$5:$G$304,MATCH(LARGE(Propostas!$R$5:$R$304,7),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Reunião feita</v>
       </c>
       <c r="E29" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,7)&gt;0,INDEX(Propostas!$F$5:$F$304,MATCH(LARGE(Propostas!$R$5:$R$304,7),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>7900</v>
       </c>
       <c r="F29" s="29">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,7)&gt;0,INDEX(Propostas!$O$5:$O$304,MATCH(LARGE(Propostas!$R$5:$R$304,7),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="25">
+        <v>2</v>
+      </c>
+      <c r="G29" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,7)&gt;0,INDEX(Propostas!$Q$5:$Q$304,MATCH(LARGE(Propostas!$R$5:$R$304,7),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="25">
+        <v>Ativa</v>
+      </c>
+      <c r="H29" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,7)&gt;0,INDEX(Propostas!$E$5:$E$304,MATCH(LARGE(Propostas!$R$5:$R$304,7),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,8)&gt;0,INDEX(Propostas!$A$5:$A$304,MATCH(LARGE(Propostas!$R$5:$R$304,8),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="24">
+        <v>Construtora Horizonte</v>
+      </c>
+      <c r="C30" s="24" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,8)&gt;0,INDEX(Propostas!$C$5:$C$304,MATCH(LARGE(Propostas!$R$5:$R$304,8),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="25">
+        <v>Assessoria mensal (12 meses)</v>
+      </c>
+      <c r="D30" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,8)&gt;0,INDEX(Propostas!$G$5:$G$304,MATCH(LARGE(Propostas!$R$5:$R$304,8),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Contato</v>
       </c>
       <c r="E30" s="26">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,8)&gt;0,INDEX(Propostas!$F$5:$F$304,MATCH(LARGE(Propostas!$R$5:$R$304,8),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>13200</v>
       </c>
       <c r="F30" s="29">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,8)&gt;0,INDEX(Propostas!$O$5:$O$304,MATCH(LARGE(Propostas!$R$5:$R$304,8),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="25">
+        <v>1</v>
+      </c>
+      <c r="G30" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,8)&gt;0,INDEX(Propostas!$Q$5:$Q$304,MATCH(LARGE(Propostas!$R$5:$R$304,8),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="25">
+        <v>Ativa</v>
+      </c>
+      <c r="H30" s="25" t="str">
         <f>IFERROR(IF(LARGE(Propostas!$R$5:$R$304,8)&gt;0,INDEX(Propostas!$E$5:$E$304,MATCH(LARGE(Propostas!$R$5:$R$304,8),Propostas!$R$5:$R$304,0)),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="32">
@@ -1689,153 +1701,153 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24">
+      <c r="A34" s="24" t="str">
         <f>IF(Config!$A$18="","",Config!$A$18)</f>
-        <v/>
+        <v>Cível</v>
       </c>
       <c r="B34" s="25">
         <f>IF(Config!$A$18="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$18))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C34" s="25">
         <f>IF(Config!$A$18="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$18,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D34" s="25">
         <f>IF(Config!$A$18="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$18,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E34" s="27">
         <f>IF(Config!$A$18="","",IFERROR(C34/(C34+D34),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F34" s="26">
         <f>IF(Config!$A$18="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$18,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>28700</v>
       </c>
       <c r="G34" s="26">
         <f>IF(Config!$A$18="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$18,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
-        <v/>
+        <v>12400</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24">
+      <c r="A35" s="24" t="str">
         <f>IF(Config!$A$19="","",Config!$A$19)</f>
-        <v/>
+        <v>Trabalhista</v>
       </c>
       <c r="B35" s="25">
         <f>IF(Config!$A$19="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$19))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C35" s="25">
         <f>IF(Config!$A$19="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$19,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D35" s="25">
         <f>IF(Config!$A$19="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$19,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E35" s="27">
         <f>IF(Config!$A$19="","",IFERROR(C35/(C35+D35),0))</f>
-        <v/>
+        <v>0.333333333333333</v>
       </c>
       <c r="F35" s="26">
         <f>IF(Config!$A$19="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$19,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="G35" s="26">
         <f>IF(Config!$A$19="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$19,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
-        <v/>
+        <v>20200</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24">
+      <c r="A36" s="24" t="str">
         <f>IF(Config!$A$20="","",Config!$A$20)</f>
-        <v/>
+        <v>Previdenciário</v>
       </c>
       <c r="B36" s="25">
         <f>IF(Config!$A$20="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$20))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C36" s="25">
         <f>IF(Config!$A$20="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$20,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D36" s="25">
         <f>IF(Config!$A$20="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$20,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E36" s="27">
         <f>IF(Config!$A$20="","",IFERROR(C36/(C36+D36),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F36" s="26">
         <f>IF(Config!$A$20="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$20,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>9900</v>
       </c>
       <c r="G36" s="26">
         <f>IF(Config!$A$20="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$20,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
-        <v/>
+        <v>4200</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24">
+      <c r="A37" s="24" t="str">
         <f>IF(Config!$A$21="","",Config!$A$21)</f>
-        <v/>
+        <v>Empresarial</v>
       </c>
       <c r="B37" s="25">
         <f>IF(Config!$A$21="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$21))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C37" s="25">
         <f>IF(Config!$A$21="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$21,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D37" s="25">
         <f>IF(Config!$A$21="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$21,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E37" s="27">
         <f>IF(Config!$A$21="","",IFERROR(C37/(C37+D37),0))</f>
-        <v/>
+        <v>0.666666666666667</v>
       </c>
       <c r="F37" s="26">
         <f>IF(Config!$A$21="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$21,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>26400</v>
       </c>
       <c r="G37" s="26">
         <f>IF(Config!$A$21="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$21,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
-        <v/>
+        <v>20000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24">
+      <c r="A38" s="24" t="str">
         <f>IF(Config!$A$22="","",Config!$A$22)</f>
-        <v/>
+        <v>Família</v>
       </c>
       <c r="B38" s="25">
         <f>IF(Config!$A$22="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$22))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C38" s="25">
         <f>IF(Config!$A$22="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$22,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D38" s="25">
         <f>IF(Config!$A$22="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$22,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E38" s="27">
         <f>IF(Config!$A$22="","",IFERROR(C38/(C38+D38),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F38" s="26">
         <f>IF(Config!$A$22="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$22,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="26">
         <f>IF(Config!$A$22="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$22,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
-        <v/>
+        <v>16100</v>
       </c>
     </row>
     <row r="39">
@@ -2043,231 +2055,231 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="24">
+      <c r="A47" s="24" t="str">
         <f>IF(Config!$E$18="","",Config!$E$18)</f>
-        <v/>
+        <v>Preço</v>
       </c>
       <c r="B47" s="25">
         <f>IF(Config!$E$18="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$18,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C47" s="26">
         <f>IF(Config!$E$18="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$18,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>16200</v>
       </c>
       <c r="D47" s="27">
         <f>IF(Config!$E$18="","",IFERROR(B47/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F47" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="F47" s="24" t="str">
         <f>IF(Config!$C$18="","",Config!$C$18)</f>
-        <v/>
+        <v>Indicação de cliente</v>
       </c>
       <c r="G47" s="25">
         <f>IF(Config!$C$18="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$18))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="H47" s="25">
         <f>IF(Config!$C$18="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$18,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I47" s="27">
         <f>IF(Config!$C$18="","",IFERROR(H47/(H47+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$18,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="J47" s="26">
         <f>IF(Config!$C$18="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$18,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>6000</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24">
+      <c r="A48" s="24" t="str">
         <f>IF(Config!$E$19="","",Config!$E$19)</f>
-        <v/>
+        <v>Fechou com outro escritório</v>
       </c>
       <c r="B48" s="25">
         <f>IF(Config!$E$19="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$19,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C48" s="26">
         <f>IF(Config!$E$19="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$19,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>6500</v>
       </c>
       <c r="D48" s="27">
         <f>IF(Config!$E$19="","",IFERROR(B48/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F48" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="F48" s="24" t="str">
         <f>IF(Config!$C$19="","",Config!$C$19)</f>
-        <v/>
+        <v>Site e Google</v>
       </c>
       <c r="G48" s="25">
         <f>IF(Config!$C$19="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$19))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H48" s="25">
         <f>IF(Config!$C$19="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$19,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I48" s="27">
         <f>IF(Config!$C$19="","",IFERROR(H48/(H48+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$19,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="J48" s="26">
         <f>IF(Config!$C$19="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$19,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>5400</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="24">
+      <c r="A49" s="24" t="str">
         <f>IF(Config!$E$20="","",Config!$E$20)</f>
-        <v/>
+        <v>Desistiu da demanda</v>
       </c>
       <c r="B49" s="25">
         <f>IF(Config!$E$20="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$20,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C49" s="26">
         <f>IF(Config!$E$20="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$20,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D49" s="27">
         <f>IF(Config!$E$20="","",IFERROR(B49/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F49" s="24">
+        <v>0</v>
+      </c>
+      <c r="F49" s="24" t="str">
         <f>IF(Config!$C$20="","",Config!$C$20)</f>
-        <v/>
+        <v>Instagram</v>
       </c>
       <c r="G49" s="25">
         <f>IF(Config!$C$20="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$20))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H49" s="25">
         <f>IF(Config!$C$20="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$20,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I49" s="27">
         <f>IF(Config!$C$20="","",IFERROR(H49/(H49+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$20,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="J49" s="26">
         <f>IF(Config!$C$20="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$20,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>4500</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24">
+      <c r="A50" s="24" t="str">
         <f>IF(Config!$E$21="","",Config!$E$21)</f>
-        <v/>
+        <v>Sem resposta</v>
       </c>
       <c r="B50" s="25">
         <f>IF(Config!$E$21="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$21,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C50" s="26">
         <f>IF(Config!$E$21="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$21,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>4400</v>
       </c>
       <c r="D50" s="27">
         <f>IF(Config!$E$21="","",IFERROR(B50/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F50" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="F50" s="24" t="str">
         <f>IF(Config!$C$21="","",Config!$C$21)</f>
-        <v/>
+        <v>Cliente antigo</v>
       </c>
       <c r="G50" s="25">
         <f>IF(Config!$C$21="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$21))</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="H50" s="25">
         <f>IF(Config!$C$21="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$21,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="I50" s="27">
         <f>IF(Config!$C$21="","",IFERROR(H50/(H50+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$21,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J50" s="26">
         <f>IF(Config!$C$21="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$21,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>46700</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24">
+      <c r="A51" s="24" t="str">
         <f>IF(Config!$E$22="","",Config!$E$22)</f>
-        <v/>
+        <v>Fora da área de atuação</v>
       </c>
       <c r="B51" s="25">
         <f>IF(Config!$E$22="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$22,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C51" s="26">
         <f>IF(Config!$E$22="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$22,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D51" s="27">
         <f>IF(Config!$E$22="","",IFERROR(B51/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F51" s="24">
+        <v>0</v>
+      </c>
+      <c r="F51" s="24" t="str">
         <f>IF(Config!$C$22="","",Config!$C$22)</f>
-        <v/>
+        <v>Parceria (contador, imobiliária)</v>
       </c>
       <c r="G51" s="25">
         <f>IF(Config!$C$22="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$22))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H51" s="25">
         <f>IF(Config!$C$22="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$22,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I51" s="27">
         <f>IF(Config!$C$22="","",IFERROR(H51/(H51+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$22,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J51" s="26">
         <f>IF(Config!$C$22="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$22,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>8400</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24">
+      <c r="A52" s="24" t="str">
         <f>IF(Config!$E$23="","",Config!$E$23)</f>
-        <v/>
+        <v>Prazo de atendimento</v>
       </c>
       <c r="B52" s="25">
         <f>IF(Config!$E$23="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$23,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C52" s="26">
         <f>IF(Config!$E$23="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$23,Propostas!$G$5:$G$304,"Perdida"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="D52" s="27">
         <f>IF(Config!$E$23="","",IFERROR(B52/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F52" s="24">
+        <v>0</v>
+      </c>
+      <c r="F52" s="24" t="str">
         <f>IF(Config!$C$23="","",Config!$C$23)</f>
-        <v/>
+        <v>Evento ou palestra</v>
       </c>
       <c r="G52" s="25">
         <f>IF(Config!$C$23="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$23))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H52" s="25">
         <f>IF(Config!$C$23="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$23,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I52" s="27">
         <f>IF(Config!$C$23="","",IFERROR(H52/(H52+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$23,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J52" s="26">
         <f>IF(Config!$C$23="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$23,Propostas!$G$5:$G$304,"Fechada"))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2522,7 +2534,7 @@
       </c>
       <c r="B5" s="32">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
     </row>
     <row r="6">
@@ -2674,7 +2686,7 @@
       </c>
       <c r="I18" s="31" t="inlineStr">
         <is>
-          <t>Assessoria mensal</t>
+          <t>Assessoria mensal (12 meses)</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2823,7 @@
       <c r="G25" s="31" t="n"/>
       <c r="I25" s="31" t="inlineStr">
         <is>
-          <t>Divórcio e partilha</t>
+          <t>Contratos com convênios</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2834,7 @@
       <c r="G26" s="31" t="n"/>
       <c r="I26" s="31" t="inlineStr">
         <is>
-          <t>Inventário</t>
+          <t>Divórcio e partilha</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2845,7 @@
       <c r="G27" s="31" t="n"/>
       <c r="I27" s="31" t="inlineStr">
         <is>
-          <t>Recuperação de crédito</t>
+          <t>Inventário</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3009,7 @@
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>Assessoria mensal</t>
+          <t>Assessoria mensal (12 meses)</t>
         </is>
       </c>
       <c r="D5" s="34" t="inlineStr">
@@ -3011,7 +3023,7 @@
         </is>
       </c>
       <c r="F5" s="33" t="n">
-        <v>9600</v>
+        <v>18000</v>
       </c>
       <c r="G5" s="34" t="inlineStr">
         <is>
@@ -3033,11 +3045,11 @@
       <c r="L5" s="31" t="n"/>
       <c r="M5" s="27">
         <f>IF(G5="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G5,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N5" s="26">
         <f>IF(OR(G5="",F5=""),"",F5*M5)</f>
-        <v/>
+        <v>18000</v>
       </c>
       <c r="O5" s="29">
         <f>IF(OR(G5="",G5="Fechada",G5="Perdida",AND(H5="",I5="")),"",Config!$B$5-IF(I5="",H5,I5))</f>
@@ -3045,15 +3057,15 @@
       </c>
       <c r="P5" s="29">
         <f>IF(AND(G5="Fechada",K5&lt;&gt;"",H5&lt;&gt;""),K5-H5,"")</f>
-        <v/>
-      </c>
-      <c r="Q5" s="25">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="25" t="str">
         <f>IF(G5="","",IF(G5="Fechada","Fechada",IF(G5="Perdida","Perdida",IF(AND(J5&lt;&gt;"",J5&lt;Config!$B$5),"Previsão vencida",IF(AND(O5&lt;&gt;"",O5&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Fechada</v>
       </c>
       <c r="R5" s="37">
         <f>IF(OR(G5="",Q5="Fechada",Q5="Perdida"),0,IF(Q5="Previsão vencida",3000,IF(Q5="Parada",2000,1000))+MIN(N(O5),500)+N(F5)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3105,11 +3117,11 @@
       <c r="L6" s="31" t="n"/>
       <c r="M6" s="27">
         <f>IF(G6="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G6,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N6" s="26">
         <f>IF(OR(G6="",F6=""),"",F6*M6)</f>
-        <v/>
+        <v>6000</v>
       </c>
       <c r="O6" s="29">
         <f>IF(OR(G6="",G6="Fechada",G6="Perdida",AND(H6="",I6="")),"",Config!$B$5-IF(I6="",H6,I6))</f>
@@ -3117,15 +3129,15 @@
       </c>
       <c r="P6" s="29">
         <f>IF(AND(G6="Fechada",K6&lt;&gt;"",H6&lt;&gt;""),K6-H6,"")</f>
-        <v/>
-      </c>
-      <c r="Q6" s="25">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="25" t="str">
         <f>IF(G6="","",IF(G6="Fechada","Fechada",IF(G6="Perdida","Perdida",IF(AND(J6&lt;&gt;"",J6&lt;Config!$B$5),"Previsão vencida",IF(AND(O6&lt;&gt;"",O6&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Fechada</v>
       </c>
       <c r="R6" s="37">
         <f>IF(OR(G6="",Q6="Fechada",Q6="Perdida"),0,IF(Q6="Previsão vencida",3000,IF(Q6="Parada",2000,1000))+MIN(N(O6),500)+N(F6)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3155,7 +3167,7 @@
         </is>
       </c>
       <c r="F7" s="33" t="n">
-        <v>12500</v>
+        <v>15500</v>
       </c>
       <c r="G7" s="34" t="inlineStr">
         <is>
@@ -3177,11 +3189,11 @@
       <c r="L7" s="31" t="n"/>
       <c r="M7" s="27">
         <f>IF(G7="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G7,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N7" s="26">
         <f>IF(OR(G7="",F7=""),"",F7*M7)</f>
-        <v/>
+        <v>15500</v>
       </c>
       <c r="O7" s="29">
         <f>IF(OR(G7="",G7="Fechada",G7="Perdida",AND(H7="",I7="")),"",Config!$B$5-IF(I7="",H7,I7))</f>
@@ -3189,15 +3201,15 @@
       </c>
       <c r="P7" s="29">
         <f>IF(AND(G7="Fechada",K7&lt;&gt;"",H7&lt;&gt;""),K7-H7,"")</f>
-        <v/>
-      </c>
-      <c r="Q7" s="25">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="25" t="str">
         <f>IF(G7="","",IF(G7="Fechada","Fechada",IF(G7="Perdida","Perdida",IF(AND(J7&lt;&gt;"",J7&lt;Config!$B$5),"Previsão vencida",IF(AND(O7&lt;&gt;"",O7&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Fechada</v>
       </c>
       <c r="R7" s="37">
         <f>IF(OR(G7="",Q7="Fechada",Q7="Perdida"),0,IF(Q7="Previsão vencida",3000,IF(Q7="Parada",2000,1000))+MIN(N(O7),500)+N(F7)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3227,7 +3239,7 @@
         </is>
       </c>
       <c r="F8" s="33" t="n">
-        <v>4800</v>
+        <v>5400</v>
       </c>
       <c r="G8" s="34" t="inlineStr">
         <is>
@@ -3249,11 +3261,11 @@
       <c r="L8" s="31" t="n"/>
       <c r="M8" s="27">
         <f>IF(G8="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G8,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N8" s="26">
         <f>IF(OR(G8="",F8=""),"",F8*M8)</f>
-        <v/>
+        <v>5400</v>
       </c>
       <c r="O8" s="29">
         <f>IF(OR(G8="",G8="Fechada",G8="Perdida",AND(H8="",I8="")),"",Config!$B$5-IF(I8="",H8,I8))</f>
@@ -3261,36 +3273,36 @@
       </c>
       <c r="P8" s="29">
         <f>IF(AND(G8="Fechada",K8&lt;&gt;"",H8&lt;&gt;""),K8-H8,"")</f>
-        <v/>
-      </c>
-      <c r="Q8" s="25">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="25" t="str">
         <f>IF(G8="","",IF(G8="Fechada","Fechada",IF(G8="Perdida","Perdida",IF(AND(J8&lt;&gt;"",J8&lt;Config!$B$5),"Previsão vencida",IF(AND(O8&lt;&gt;"",O8&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Fechada</v>
       </c>
       <c r="R8" s="37">
         <f>IF(OR(G8="",Q8="Fechada",Q8="Perdida"),0,IF(Q8="Previsão vencida",3000,IF(Q8="Parada",2000,1000))+MIN(N(O8),500)+N(F8)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>Loja Verde Comércio</t>
+          <t>Escola Aurora</t>
         </is>
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>Contratos e consultoria</t>
+          <t>Assessoria mensal (12 meses)</t>
         </is>
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>Parceria (contador, imobiliária)</t>
+          <t>Cliente antigo</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -3299,7 +3311,7 @@
         </is>
       </c>
       <c r="F9" s="33" t="n">
-        <v>7200</v>
+        <v>13200</v>
       </c>
       <c r="G9" s="34" t="inlineStr">
         <is>
@@ -3307,25 +3319,25 @@
         </is>
       </c>
       <c r="H9" s="36" t="n">
-        <v>46223</v>
+        <v>46217</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>46248</v>
+        <v>46241</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="L9" s="31" t="n"/>
       <c r="M9" s="27">
         <f>IF(G9="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G9,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N9" s="26">
         <f>IF(OR(G9="",F9=""),"",F9*M9)</f>
-        <v/>
+        <v>13200</v>
       </c>
       <c r="O9" s="29">
         <f>IF(OR(G9="",G9="Fechada",G9="Perdida",AND(H9="",I9="")),"",Config!$B$5-IF(I9="",H9,I9))</f>
@@ -3333,36 +3345,36 @@
       </c>
       <c r="P9" s="29">
         <f>IF(AND(G9="Fechada",K9&lt;&gt;"",H9&lt;&gt;""),K9-H9,"")</f>
-        <v/>
-      </c>
-      <c r="Q9" s="25">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="25" t="str">
         <f>IF(G9="","",IF(G9="Fechada","Fechada",IF(G9="Perdida","Perdida",IF(AND(J9&lt;&gt;"",J9&lt;Config!$B$5),"Previsão vencida",IF(AND(O9&lt;&gt;"",O9&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Fechada</v>
       </c>
       <c r="R9" s="37">
         <f>IF(OR(G9="",Q9="Fechada",Q9="Perdida"),0,IF(Q9="Previsão vencida",3000,IF(Q9="Parada",2000,1000))+MIN(N(O9),500)+N(F9)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>Planejamento previdenciário</t>
+          <t>Defesa em reclamação trabalhista</t>
         </is>
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Indicação de cliente</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
@@ -3371,33 +3383,37 @@
         </is>
       </c>
       <c r="F10" s="33" t="n">
-        <v>3900</v>
+        <v>5200</v>
       </c>
       <c r="G10" s="34" t="inlineStr">
         <is>
-          <t>Fechada</t>
+          <t>Perdida</t>
         </is>
       </c>
       <c r="H10" s="36" t="n">
-        <v>46237</v>
+        <v>46195</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>46253</v>
+        <v>46217</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>46262</v>
+        <v>46220</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>46253</v>
-      </c>
-      <c r="L10" s="31" t="n"/>
+        <v>46217</v>
+      </c>
+      <c r="L10" s="31" t="inlineStr">
+        <is>
+          <t>Preço</t>
+        </is>
+      </c>
       <c r="M10" s="27">
         <f>IF(G10="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G10,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N10" s="26">
         <f>IF(OR(G10="",F10=""),"",F10*M10)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O10" s="29">
         <f>IF(OR(G10="",G10="Fechada",G10="Perdida",AND(H10="",I10="")),"",Config!$B$5-IF(I10="",H10,I10))</f>
@@ -3407,34 +3423,34 @@
         <f>IF(AND(G10="Fechada",K10&lt;&gt;"",H10&lt;&gt;""),K10-H10,"")</f>
         <v/>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q10" s="25" t="str">
         <f>IF(G10="","",IF(G10="Fechada","Fechada",IF(G10="Perdida","Perdida",IF(AND(J10&lt;&gt;"",J10&lt;Config!$B$5),"Previsão vencida",IF(AND(O10&lt;&gt;"",O10&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Perdida</v>
       </c>
       <c r="R10" s="37">
         <f>IF(OR(G10="",Q10="Fechada",Q10="Perdida"),0,IF(Q10="Previsão vencida",3000,IF(Q10="Parada",2000,1000))+MIN(N(O10),500)+N(F10)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Fernanda Castro</t>
         </is>
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
-          <t>Assessoria mensal</t>
+          <t>Divórcio e partilha</t>
         </is>
       </c>
       <c r="D11" s="34" t="inlineStr">
         <is>
-          <t>Cliente antigo</t>
+          <t>Site e Google</t>
         </is>
       </c>
       <c r="E11" s="34" t="inlineStr">
@@ -3443,33 +3459,37 @@
         </is>
       </c>
       <c r="F11" s="33" t="n">
-        <v>8400</v>
+        <v>6500</v>
       </c>
       <c r="G11" s="34" t="inlineStr">
         <is>
-          <t>Fechada</t>
+          <t>Perdida</t>
         </is>
       </c>
       <c r="H11" s="36" t="n">
-        <v>46244</v>
+        <v>46209</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>46266</v>
+        <v>46230</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>46269</v>
+        <v>46234</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>46266</v>
-      </c>
-      <c r="L11" s="31" t="n"/>
+        <v>46230</v>
+      </c>
+      <c r="L11" s="31" t="inlineStr">
+        <is>
+          <t>Fechou com outro escritório</t>
+        </is>
+      </c>
       <c r="M11" s="27">
         <f>IF(G11="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G11,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N11" s="26">
         <f>IF(OR(G11="",F11=""),"",F11*M11)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O11" s="29">
         <f>IF(OR(G11="",G11="Fechada",G11="Perdida",AND(H11="",I11="")),"",Config!$B$5-IF(I11="",H11,I11))</f>
@@ -3479,73 +3499,69 @@
         <f>IF(AND(G11="Fechada",K11&lt;&gt;"",H11&lt;&gt;""),K11-H11,"")</f>
         <v/>
       </c>
-      <c r="Q11" s="25">
+      <c r="Q11" s="25" t="str">
         <f>IF(G11="","",IF(G11="Fechada","Fechada",IF(G11="Perdida","Perdida",IF(AND(J11&lt;&gt;"",J11&lt;Config!$B$5),"Previsão vencida",IF(AND(O11&lt;&gt;"",O11&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Perdida</v>
       </c>
       <c r="R11" s="37">
         <f>IF(OR(G11="",Q11="Fechada",Q11="Perdida"),0,IF(Q11="Previsão vencida",3000,IF(Q11="Parada",2000,1000))+MIN(N(O11),500)+N(F11)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
+          <t>Loja Verde Comércio</t>
         </is>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>Defesa em reclamação trabalhista</t>
+          <t>Contratos e consultoria</t>
         </is>
       </c>
       <c r="D12" s="34" t="inlineStr">
         <is>
-          <t>Indicação de cliente</t>
+          <t>Parceria (contador, imobiliária)</t>
         </is>
       </c>
       <c r="E12" s="34" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F12" s="33" t="n">
-        <v>5200</v>
+        <v>8400</v>
       </c>
       <c r="G12" s="34" t="inlineStr">
         <is>
-          <t>Perdida</t>
+          <t>Fechada</t>
         </is>
       </c>
       <c r="H12" s="36" t="n">
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>46217</v>
+        <v>46245</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>46220</v>
+        <v>46248</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>46217</v>
-      </c>
-      <c r="L12" s="31" t="inlineStr">
-        <is>
-          <t>Preço</t>
-        </is>
-      </c>
+        <v>46245</v>
+      </c>
+      <c r="L12" s="31" t="n"/>
       <c r="M12" s="27">
         <f>IF(G12="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G12,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N12" s="26">
         <f>IF(OR(G12="",F12=""),"",F12*M12)</f>
-        <v/>
+        <v>8400</v>
       </c>
       <c r="O12" s="29">
         <f>IF(OR(G12="",G12="Fechada",G12="Perdida",AND(H12="",I12="")),"",Config!$B$5-IF(I12="",H12,I12))</f>
@@ -3553,75 +3569,71 @@
       </c>
       <c r="P12" s="29">
         <f>IF(AND(G12="Fechada",K12&lt;&gt;"",H12&lt;&gt;""),K12-H12,"")</f>
-        <v/>
-      </c>
-      <c r="Q12" s="25">
+        <v>22</v>
+      </c>
+      <c r="Q12" s="25" t="str">
         <f>IF(G12="","",IF(G12="Fechada","Fechada",IF(G12="Perdida","Perdida",IF(AND(J12&lt;&gt;"",J12&lt;Config!$B$5),"Previsão vencida",IF(AND(O12&lt;&gt;"",O12&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Fechada</v>
       </c>
       <c r="R12" s="37">
         <f>IF(OR(G12="",Q12="Fechada",Q12="Perdida"),0,IF(Q12="Previsão vencida",3000,IF(Q12="Parada",2000,1000))+MIN(N(O12),500)+N(F12)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>Fernanda Castro</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>Divórcio e partilha</t>
+          <t>Planejamento previdenciário</t>
         </is>
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>Site e Google</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E13" s="34" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F13" s="33" t="n">
-        <v>6500</v>
+        <v>4500</v>
       </c>
       <c r="G13" s="34" t="inlineStr">
         <is>
-          <t>Perdida</t>
+          <t>Fechada</t>
         </is>
       </c>
       <c r="H13" s="36" t="n">
-        <v>46209</v>
+        <v>46237</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>46230</v>
+        <v>46253</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>46234</v>
+        <v>46262</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>46230</v>
-      </c>
-      <c r="L13" s="31" t="inlineStr">
-        <is>
-          <t>Fechou com outro escritório</t>
-        </is>
-      </c>
+        <v>46253</v>
+      </c>
+      <c r="L13" s="31" t="n"/>
       <c r="M13" s="27">
         <f>IF(G13="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G13,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N13" s="26">
         <f>IF(OR(G13="",F13=""),"",F13*M13)</f>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="O13" s="29">
         <f>IF(OR(G13="",G13="Fechada",G13="Perdida",AND(H13="",I13="")),"",Config!$B$5-IF(I13="",H13,I13))</f>
@@ -3629,45 +3641,45 @@
       </c>
       <c r="P13" s="29">
         <f>IF(AND(G13="Fechada",K13&lt;&gt;"",H13&lt;&gt;""),K13-H13,"")</f>
-        <v/>
-      </c>
-      <c r="Q13" s="25">
+        <v>16</v>
+      </c>
+      <c r="Q13" s="25" t="str">
         <f>IF(G13="","",IF(G13="Fechada","Fechada",IF(G13="Perdida","Perdida",IF(AND(J13&lt;&gt;"",J13&lt;Config!$B$5),"Previsão vencida",IF(AND(O13&lt;&gt;"",O13&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Fechada</v>
       </c>
       <c r="R13" s="37">
         <f>IF(OR(G13="",Q13="Fechada",Q13="Perdida"),0,IF(Q13="Previsão vencida",3000,IF(Q13="Parada",2000,1000))+MIN(N(O13),500)+N(F13)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>Recuperação de crédito</t>
+          <t>Ação trabalhista</t>
         </is>
       </c>
       <c r="D14" s="34" t="inlineStr">
         <is>
-          <t>Cliente antigo</t>
+          <t>Evento ou palestra</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F14" s="33" t="n">
-        <v>9800</v>
+        <v>4400</v>
       </c>
       <c r="G14" s="34" t="inlineStr">
         <is>
@@ -3675,29 +3687,29 @@
         </is>
       </c>
       <c r="H14" s="36" t="n">
-        <v>46218</v>
+        <v>46238</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="L14" s="31" t="inlineStr">
         <is>
-          <t>Desistiu da demanda</t>
+          <t>Sem resposta</t>
         </is>
       </c>
       <c r="M14" s="27">
         <f>IF(G14="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G14,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N14" s="26">
         <f>IF(OR(G14="",F14=""),"",F14*M14)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O14" s="29">
         <f>IF(OR(G14="",G14="Fechada",G14="Perdida",AND(H14="",I14="")),"",Config!$B$5-IF(I14="",H14,I14))</f>
@@ -3707,43 +3719,43 @@
         <f>IF(AND(G14="Fechada",K14&lt;&gt;"",H14&lt;&gt;""),K14-H14,"")</f>
         <v/>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="25" t="str">
         <f>IF(G14="","",IF(G14="Fechada","Fechada",IF(G14="Perdida","Perdida",IF(AND(J14&lt;&gt;"",J14&lt;Config!$B$5),"Previsão vencida",IF(AND(O14&lt;&gt;"",O14&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Perdida</v>
       </c>
       <c r="R14" s="37">
         <f>IF(OR(G14="",Q14="Fechada",Q14="Perdida"),0,IF(Q14="Previsão vencida",3000,IF(Q14="Parada",2000,1000))+MIN(N(O14),500)+N(F14)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
-          <t>Ação trabalhista</t>
+          <t>Contratos e consultoria</t>
         </is>
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>Evento ou palestra</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F15" s="33" t="n">
-        <v>4400</v>
+        <v>11000</v>
       </c>
       <c r="G15" s="34" t="inlineStr">
         <is>
@@ -3751,29 +3763,29 @@
         </is>
       </c>
       <c r="H15" s="36" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="L15" s="31" t="inlineStr">
         <is>
-          <t>Sem resposta</t>
+          <t>Preço</t>
         </is>
       </c>
       <c r="M15" s="27">
         <f>IF(G15="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G15,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N15" s="26">
         <f>IF(OR(G15="",F15=""),"",F15*M15)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O15" s="29">
         <f>IF(OR(G15="",G15="Fechada",G15="Perdida",AND(H15="",I15="")),"",Config!$B$5-IF(I15="",H15,I15))</f>
@@ -3783,105 +3795,101 @@
         <f>IF(AND(G15="Fechada",K15&lt;&gt;"",H15&lt;&gt;""),K15-H15,"")</f>
         <v/>
       </c>
-      <c r="Q15" s="25">
+      <c r="Q15" s="25" t="str">
         <f>IF(G15="","",IF(G15="Fechada","Fechada",IF(G15="Perdida","Perdida",IF(AND(J15&lt;&gt;"",J15&lt;Config!$B$5),"Previsão vencida",IF(AND(O15&lt;&gt;"",O15&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Perdida</v>
       </c>
       <c r="R15" s="37">
         <f>IF(OR(G15="",Q15="Fechada",Q15="Perdida"),0,IF(Q15="Previsão vencida",3000,IF(Q15="Parada",2000,1000))+MIN(N(O15),500)+N(F15)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="C16" s="31" t="inlineStr">
         <is>
-          <t>Contratos e consultoria</t>
+          <t>Assessoria mensal (12 meses)</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Cliente antigo</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F16" s="33" t="n">
-        <v>11000</v>
+        <v>14400</v>
       </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
-          <t>Perdida</t>
+          <t>Negociação</t>
         </is>
       </c>
       <c r="H16" s="36" t="n">
-        <v>46246</v>
-      </c>
-      <c r="I16" s="36" t="n">
-        <v>46267</v>
-      </c>
-      <c r="J16" s="36" t="n">
-        <v>46269</v>
-      </c>
-      <c r="K16" s="36" t="n">
-        <v>46267</v>
-      </c>
-      <c r="L16" s="31" t="inlineStr">
-        <is>
-          <t>Preço</t>
-        </is>
-      </c>
+        <v>46251</v>
+      </c>
+      <c r="I16" s="36">
+        <f>TODAY()-4</f>
+        <v>46275.0</v>
+      </c>
+      <c r="J16" s="36">
+        <f>TODAY()+6</f>
+        <v>46285.0</v>
+      </c>
+      <c r="K16" s="36" t="n"/>
+      <c r="L16" s="31" t="n"/>
       <c r="M16" s="27">
         <f>IF(G16="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G16,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="N16" s="26">
         <f>IF(OR(G16="",F16=""),"",F16*M16)</f>
-        <v/>
+        <v>10800</v>
       </c>
       <c r="O16" s="29">
         <f>IF(OR(G16="",G16="Fechada",G16="Perdida",AND(H16="",I16="")),"",Config!$B$5-IF(I16="",H16,I16))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="P16" s="29">
         <f>IF(AND(G16="Fechada",K16&lt;&gt;"",H16&lt;&gt;""),K16-H16,"")</f>
         <v/>
       </c>
-      <c r="Q16" s="25">
+      <c r="Q16" s="25" t="str">
         <f>IF(G16="","",IF(G16="Fechada","Fechada",IF(G16="Perdida","Perdida",IF(AND(J16&lt;&gt;"",J16&lt;Config!$B$5),"Previsão vencida",IF(AND(O16&lt;&gt;"",O16&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Ativa</v>
       </c>
       <c r="R16" s="37">
         <f>IF(OR(G16="",Q16="Fechada",Q16="Perdida"),0,IF(Q16="Previsão vencida",3000,IF(Q16="Parada",2000,1000))+MIN(N(O16),500)+N(F16)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>1004.01424</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>Assessoria mensal</t>
+          <t>Contratos com convênios</t>
         </is>
       </c>
       <c r="D17" s="34" t="inlineStr">
@@ -3891,11 +3899,11 @@
       </c>
       <c r="E17" s="34" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F17" s="33" t="n">
-        <v>14400</v>
+        <v>6800</v>
       </c>
       <c r="G17" s="34" t="inlineStr">
         <is>
@@ -3903,62 +3911,62 @@
         </is>
       </c>
       <c r="H17" s="36" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="I17" s="36">
-        <f>TODAY()-4</f>
-        <v/>
+        <f>TODAY()-17</f>
+        <v>46262.0</v>
       </c>
       <c r="J17" s="36">
-        <f>TODAY()+6</f>
-        <v/>
+        <f>TODAY()-2</f>
+        <v>46277.0</v>
       </c>
       <c r="K17" s="36" t="n"/>
       <c r="L17" s="31" t="n"/>
       <c r="M17" s="27">
         <f>IF(G17="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G17,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="N17" s="26">
         <f>IF(OR(G17="",F17=""),"",F17*M17)</f>
-        <v/>
+        <v>5100</v>
       </c>
       <c r="O17" s="29">
         <f>IF(OR(G17="",G17="Fechada",G17="Perdida",AND(H17="",I17="")),"",Config!$B$5-IF(I17="",H17,I17))</f>
-        <v/>
+        <v>17</v>
       </c>
       <c r="P17" s="29">
         <f>IF(AND(G17="Fechada",K17&lt;&gt;"",H17&lt;&gt;""),K17-H17,"")</f>
         <v/>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="25" t="str">
         <f>IF(G17="","",IF(G17="Fechada","Fechada",IF(G17="Perdida","Perdida",IF(AND(J17&lt;&gt;"",J17&lt;Config!$B$5),"Previsão vencida",IF(AND(O17&lt;&gt;"",O17&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Previsão vencida</v>
       </c>
       <c r="R17" s="37">
         <f>IF(OR(G17="",Q17="Fechada",Q17="Perdida"),0,IF(Q17="Previsão vencida",3000,IF(Q17="Parada",2000,1000))+MIN(N(O17),500)+N(F17)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>3017.00663</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
-          <t>Contratos e consultoria</t>
+          <t>Inventário</t>
         </is>
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>Cliente antigo</t>
+          <t>Indicação de cliente</t>
         </is>
       </c>
       <c r="E18" s="34" t="inlineStr">
@@ -3967,79 +3975,79 @@
         </is>
       </c>
       <c r="F18" s="33" t="n">
-        <v>6800</v>
+        <v>10500</v>
       </c>
       <c r="G18" s="34" t="inlineStr">
         <is>
-          <t>Negociação</t>
+          <t>Proposta enviada</t>
         </is>
       </c>
       <c r="H18" s="36" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="I18" s="36">
-        <f>TODAY()-17</f>
-        <v/>
+        <f>TODAY()-16</f>
+        <v>46263.0</v>
       </c>
       <c r="J18" s="36">
-        <f>TODAY()-2</f>
-        <v/>
+        <f>TODAY()+12</f>
+        <v>46291.0</v>
       </c>
       <c r="K18" s="36" t="n"/>
       <c r="L18" s="31" t="n"/>
       <c r="M18" s="27">
         <f>IF(G18="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G18,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="N18" s="26">
         <f>IF(OR(G18="",F18=""),"",F18*M18)</f>
-        <v/>
+        <v>5250</v>
       </c>
       <c r="O18" s="29">
         <f>IF(OR(G18="",G18="Fechada",G18="Perdida",AND(H18="",I18="")),"",Config!$B$5-IF(I18="",H18,I18))</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="P18" s="29">
         <f>IF(AND(G18="Fechada",K18&lt;&gt;"",H18&lt;&gt;""),K18-H18,"")</f>
         <v/>
       </c>
-      <c r="Q18" s="25">
+      <c r="Q18" s="25" t="str">
         <f>IF(G18="","",IF(G18="Fechada","Fechada",IF(G18="Perdida","Perdida",IF(AND(J18&lt;&gt;"",J18&lt;Config!$B$5),"Previsão vencida",IF(AND(O18&lt;&gt;"",O18&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Parada</v>
       </c>
       <c r="R18" s="37">
         <f>IF(OR(G18="",Q18="Fechada",Q18="Perdida"),0,IF(Q18="Previsão vencida",3000,IF(Q18="Parada",2000,1000))+MIN(N(O18),500)+N(F18)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>2016.01032</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>José Antônio Ribeiro</t>
         </is>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>Inventário</t>
+          <t>Revisão de benefício</t>
         </is>
       </c>
       <c r="D19" s="34" t="inlineStr">
         <is>
-          <t>Indicação de cliente</t>
+          <t>Site e Google</t>
         </is>
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F19" s="33" t="n">
-        <v>10500</v>
+        <v>4200</v>
       </c>
       <c r="G19" s="34" t="inlineStr">
         <is>
@@ -4047,62 +4055,62 @@
         </is>
       </c>
       <c r="H19" s="36" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="I19" s="36">
-        <f>TODAY()-16</f>
-        <v/>
+        <f>TODAY()-14</f>
+        <v>46265.0</v>
       </c>
       <c r="J19" s="36">
-        <f>TODAY()+12</f>
-        <v/>
+        <f>TODAY()-6</f>
+        <v>46273.0</v>
       </c>
       <c r="K19" s="36" t="n"/>
       <c r="L19" s="31" t="n"/>
       <c r="M19" s="27">
         <f>IF(G19="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G19,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="N19" s="26">
         <f>IF(OR(G19="",F19=""),"",F19*M19)</f>
-        <v/>
+        <v>2100</v>
       </c>
       <c r="O19" s="29">
         <f>IF(OR(G19="",G19="Fechada",G19="Perdida",AND(H19="",I19="")),"",Config!$B$5-IF(I19="",H19,I19))</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="P19" s="29">
         <f>IF(AND(G19="Fechada",K19&lt;&gt;"",H19&lt;&gt;""),K19-H19,"")</f>
         <v/>
       </c>
-      <c r="Q19" s="25">
+      <c r="Q19" s="25" t="str">
         <f>IF(G19="","",IF(G19="Fechada","Fechada",IF(G19="Perdida","Perdida",IF(AND(J19&lt;&gt;"",J19&lt;Config!$B$5),"Previsão vencida",IF(AND(O19&lt;&gt;"",O19&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Previsão vencida</v>
       </c>
       <c r="R19" s="37">
         <f>IF(OR(G19="",Q19="Fechada",Q19="Perdida"),0,IF(Q19="Previsão vencida",3000,IF(Q19="Parada",2000,1000))+MIN(N(O19),500)+N(F19)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>3014.00401</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
         <is>
-          <t>José Antônio Ribeiro</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>Revisão de benefício</t>
+          <t>Ação trabalhista</t>
         </is>
       </c>
       <c r="D20" s="34" t="inlineStr">
         <is>
-          <t>Site e Google</t>
+          <t>Indicação de cliente</t>
         </is>
       </c>
       <c r="E20" s="34" t="inlineStr">
@@ -4111,79 +4119,79 @@
         </is>
       </c>
       <c r="F20" s="33" t="n">
-        <v>4200</v>
+        <v>5800</v>
       </c>
       <c r="G20" s="34" t="inlineStr">
         <is>
-          <t>Proposta enviada</t>
+          <t>Reunião feita</t>
         </is>
       </c>
       <c r="H20" s="36" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="I20" s="36">
-        <f>TODAY()-20</f>
-        <v/>
+        <f>TODAY()-3</f>
+        <v>46276.0</v>
       </c>
       <c r="J20" s="36">
-        <f>TODAY()-6</f>
-        <v/>
+        <f>TODAY()+20</f>
+        <v>46299.0</v>
       </c>
       <c r="K20" s="36" t="n"/>
       <c r="L20" s="31" t="n"/>
       <c r="M20" s="27">
         <f>IF(G20="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G20,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0.25</v>
       </c>
       <c r="N20" s="26">
         <f>IF(OR(G20="",F20=""),"",F20*M20)</f>
-        <v/>
+        <v>1450</v>
       </c>
       <c r="O20" s="29">
         <f>IF(OR(G20="",G20="Fechada",G20="Perdida",AND(H20="",I20="")),"",Config!$B$5-IF(I20="",H20,I20))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="P20" s="29">
         <f>IF(AND(G20="Fechada",K20&lt;&gt;"",H20&lt;&gt;""),K20-H20,"")</f>
         <v/>
       </c>
-      <c r="Q20" s="25">
+      <c r="Q20" s="25" t="str">
         <f>IF(G20="","",IF(G20="Fechada","Fechada",IF(G20="Perdida","Perdida",IF(AND(J20&lt;&gt;"",J20&lt;Config!$B$5),"Previsão vencida",IF(AND(O20&lt;&gt;"",O20&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Ativa</v>
       </c>
       <c r="R20" s="37">
         <f>IF(OR(G20="",Q20="Fechada",Q20="Perdida"),0,IF(Q20="Previsão vencida",3000,IF(Q20="Parada",2000,1000))+MIN(N(O20),500)+N(F20)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>1003.0056</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>Ação trabalhista</t>
+          <t>Cobrança judicial</t>
         </is>
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>Indicação de cliente</t>
+          <t>Parceria (contador, imobiliária)</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F21" s="33" t="n">
-        <v>5800</v>
+        <v>7900</v>
       </c>
       <c r="G21" s="34" t="inlineStr">
         <is>
@@ -4191,62 +4199,62 @@
         </is>
       </c>
       <c r="H21" s="36" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="I21" s="36">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()-2</f>
+        <v>46277.0</v>
       </c>
       <c r="J21" s="36">
-        <f>TODAY()+20</f>
-        <v/>
+        <f>TODAY()+25</f>
+        <v>46304.0</v>
       </c>
       <c r="K21" s="36" t="n"/>
       <c r="L21" s="31" t="n"/>
       <c r="M21" s="27">
         <f>IF(G21="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G21,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0.25</v>
       </c>
       <c r="N21" s="26">
         <f>IF(OR(G21="",F21=""),"",F21*M21)</f>
-        <v/>
+        <v>1975</v>
       </c>
       <c r="O21" s="29">
         <f>IF(OR(G21="",G21="Fechada",G21="Perdida",AND(H21="",I21="")),"",Config!$B$5-IF(I21="",H21,I21))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="P21" s="29">
         <f>IF(AND(G21="Fechada",K21&lt;&gt;"",H21&lt;&gt;""),K21-H21,"")</f>
         <v/>
       </c>
-      <c r="Q21" s="25">
+      <c r="Q21" s="25" t="str">
         <f>IF(G21="","",IF(G21="Fechada","Fechada",IF(G21="Perdida","Perdida",IF(AND(J21&lt;&gt;"",J21&lt;Config!$B$5),"Previsão vencida",IF(AND(O21&lt;&gt;"",O21&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Ativa</v>
       </c>
       <c r="R21" s="37">
         <f>IF(OR(G21="",Q21="Fechada",Q21="Perdida"),0,IF(Q21="Previsão vencida",3000,IF(Q21="Parada",2000,1000))+MIN(N(O21),500)+N(F21)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>1002.00769</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Construtora Horizonte</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>Cobrança judicial</t>
+          <t>Assessoria mensal (12 meses)</t>
         </is>
       </c>
       <c r="D22" s="34" t="inlineStr">
         <is>
-          <t>Parceria (contador, imobiliária)</t>
+          <t>Cliente antigo</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
@@ -4255,65 +4263,65 @@
         </is>
       </c>
       <c r="F22" s="33" t="n">
-        <v>7900</v>
+        <v>13200</v>
       </c>
       <c r="G22" s="34" t="inlineStr">
         <is>
-          <t>Reunião feita</t>
+          <t>Contato</t>
         </is>
       </c>
       <c r="H22" s="36" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="I22" s="36">
-        <f>TODAY()-2</f>
-        <v/>
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
       </c>
       <c r="J22" s="36">
-        <f>TODAY()+25</f>
-        <v/>
+        <f>TODAY()+30</f>
+        <v>46309.0</v>
       </c>
       <c r="K22" s="36" t="n"/>
       <c r="L22" s="31" t="n"/>
       <c r="M22" s="27">
         <f>IF(G22="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G22,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="N22" s="26">
         <f>IF(OR(G22="",F22=""),"",F22*M22)</f>
-        <v/>
+        <v>1320</v>
       </c>
       <c r="O22" s="29">
         <f>IF(OR(G22="",G22="Fechada",G22="Perdida",AND(H22="",I22="")),"",Config!$B$5-IF(I22="",H22,I22))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P22" s="29">
         <f>IF(AND(G22="Fechada",K22&lt;&gt;"",H22&lt;&gt;""),K22-H22,"")</f>
         <v/>
       </c>
-      <c r="Q22" s="25">
+      <c r="Q22" s="25" t="str">
         <f>IF(G22="","",IF(G22="Fechada","Fechada",IF(G22="Perdida","Perdida",IF(AND(J22&lt;&gt;"",J22&lt;Config!$B$5),"Previsão vencida",IF(AND(O22&lt;&gt;"",O22&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Ativa</v>
       </c>
       <c r="R22" s="37">
         <f>IF(OR(G22="",Q22="Fechada",Q22="Perdida"),0,IF(Q22="Previsão vencida",3000,IF(Q22="Parada",2000,1000))+MIN(N(O22),500)+N(F22)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>1001.01298</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>Assessoria mensal</t>
+          <t>Discussão de contrato de prestação de serviços</t>
         </is>
       </c>
       <c r="D23" s="34" t="inlineStr">
@@ -4327,49 +4335,49 @@
         </is>
       </c>
       <c r="F23" s="33" t="n">
-        <v>13200</v>
+        <v>4500</v>
       </c>
       <c r="G23" s="34" t="inlineStr">
         <is>
-          <t>Contato</t>
+          <t>Proposta enviada</t>
         </is>
       </c>
       <c r="H23" s="36" t="n">
         <v>46274</v>
       </c>
       <c r="I23" s="36">
-        <f>TODAY()-1</f>
-        <v/>
+        <f>TODAY()</f>
+        <v>46279.0</v>
       </c>
       <c r="J23" s="36">
-        <f>TODAY()+30</f>
-        <v/>
+        <f>TODAY()+15</f>
+        <v>46294.0</v>
       </c>
       <c r="K23" s="36" t="n"/>
       <c r="L23" s="31" t="n"/>
       <c r="M23" s="27">
         <f>IF(G23="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G23,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="N23" s="26">
         <f>IF(OR(G23="",F23=""),"",F23*M23)</f>
-        <v/>
+        <v>2250</v>
       </c>
       <c r="O23" s="29">
         <f>IF(OR(G23="",G23="Fechada",G23="Perdida",AND(H23="",I23="")),"",Config!$B$5-IF(I23="",H23,I23))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="P23" s="29">
         <f>IF(AND(G23="Fechada",K23&lt;&gt;"",H23&lt;&gt;""),K23-H23,"")</f>
         <v/>
       </c>
-      <c r="Q23" s="25">
+      <c r="Q23" s="25" t="str">
         <f>IF(G23="","",IF(G23="Fechada","Fechada",IF(G23="Perdida","Perdida",IF(AND(J23&lt;&gt;"",J23&lt;Config!$B$5),"Previsão vencida",IF(AND(O23&lt;&gt;"",O23&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Ativa</v>
       </c>
       <c r="R23" s="37">
         <f>IF(OR(G23="",Q23="Fechada",Q23="Perdida"),0,IF(Q23="Previsão vencida",3000,IF(Q23="Parada",2000,1000))+MIN(N(O23),500)+N(F23)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>1000.00427</v>
       </c>
     </row>
     <row r="24">
@@ -4409,36 +4417,39 @@
       <c r="H24" s="36" t="n">
         <v>46276</v>
       </c>
-      <c r="I24" s="36" t="n"/>
+      <c r="I24" s="36">
+        <f>TODAY()-3</f>
+        <v>46276.0</v>
+      </c>
       <c r="J24" s="36">
         <f>TODAY()+35</f>
-        <v/>
+        <v>46314.0</v>
       </c>
       <c r="K24" s="36" t="n"/>
       <c r="L24" s="31" t="n"/>
       <c r="M24" s="27">
         <f>IF(G24="","",IFERROR(INDEX(Config!$B$10:$B$15,MATCH(G24,Config!$A$10:$A$15,0)),0))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="N24" s="26">
         <f>IF(OR(G24="",F24=""),"",F24*M24)</f>
-        <v/>
+        <v>560</v>
       </c>
       <c r="O24" s="29">
         <f>IF(OR(G24="",G24="Fechada",G24="Perdida",AND(H24="",I24="")),"",Config!$B$5-IF(I24="",H24,I24))</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="P24" s="29">
         <f>IF(AND(G24="Fechada",K24&lt;&gt;"",H24&lt;&gt;""),K24-H24,"")</f>
         <v/>
       </c>
-      <c r="Q24" s="25">
+      <c r="Q24" s="25" t="str">
         <f>IF(G24="","",IF(G24="Fechada","Fechada",IF(G24="Perdida","Perdida",IF(AND(J24&lt;&gt;"",J24&lt;Config!$B$5),"Previsão vencida",IF(AND(O24&lt;&gt;"",O24&gt;Config!$B$7),"Parada","Ativa")))))</f>
-        <v/>
+        <v>Ativa</v>
       </c>
       <c r="R24" s="37">
         <f>IF(OR(G24="",Q24="Fechada",Q24="Perdida"),0,IF(Q24="Previsão vencida",3000,IF(Q24="Parada",2000,1000))+MIN(N(O24),500)+N(F24)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>1003.00536</v>
       </c>
     </row>
     <row r="25">
@@ -4476,7 +4487,7 @@
       </c>
       <c r="R25" s="37">
         <f>IF(OR(G25="",Q25="Fechada",Q25="Perdida"),0,IF(Q25="Previsão vencida",3000,IF(Q25="Parada",2000,1000))+MIN(N(O25),500)+N(F25)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -4514,7 +4525,7 @@
       </c>
       <c r="R26" s="37">
         <f>IF(OR(G26="",Q26="Fechada",Q26="Perdida"),0,IF(Q26="Previsão vencida",3000,IF(Q26="Parada",2000,1000))+MIN(N(O26),500)+N(F26)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4552,7 +4563,7 @@
       </c>
       <c r="R27" s="37">
         <f>IF(OR(G27="",Q27="Fechada",Q27="Perdida"),0,IF(Q27="Previsão vencida",3000,IF(Q27="Parada",2000,1000))+MIN(N(O27),500)+N(F27)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4590,7 +4601,7 @@
       </c>
       <c r="R28" s="37">
         <f>IF(OR(G28="",Q28="Fechada",Q28="Perdida"),0,IF(Q28="Previsão vencida",3000,IF(Q28="Parada",2000,1000))+MIN(N(O28),500)+N(F28)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4628,7 +4639,7 @@
       </c>
       <c r="R29" s="37">
         <f>IF(OR(G29="",Q29="Fechada",Q29="Perdida"),0,IF(Q29="Previsão vencida",3000,IF(Q29="Parada",2000,1000))+MIN(N(O29),500)+N(F29)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -4666,7 +4677,7 @@
       </c>
       <c r="R30" s="37">
         <f>IF(OR(G30="",Q30="Fechada",Q30="Perdida"),0,IF(Q30="Previsão vencida",3000,IF(Q30="Parada",2000,1000))+MIN(N(O30),500)+N(F30)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4704,7 +4715,7 @@
       </c>
       <c r="R31" s="37">
         <f>IF(OR(G31="",Q31="Fechada",Q31="Perdida"),0,IF(Q31="Previsão vencida",3000,IF(Q31="Parada",2000,1000))+MIN(N(O31),500)+N(F31)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4742,7 +4753,7 @@
       </c>
       <c r="R32" s="37">
         <f>IF(OR(G32="",Q32="Fechada",Q32="Perdida"),0,IF(Q32="Previsão vencida",3000,IF(Q32="Parada",2000,1000))+MIN(N(O32),500)+N(F32)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4780,7 +4791,7 @@
       </c>
       <c r="R33" s="37">
         <f>IF(OR(G33="",Q33="Fechada",Q33="Perdida"),0,IF(Q33="Previsão vencida",3000,IF(Q33="Parada",2000,1000))+MIN(N(O33),500)+N(F33)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4818,7 +4829,7 @@
       </c>
       <c r="R34" s="37">
         <f>IF(OR(G34="",Q34="Fechada",Q34="Perdida"),0,IF(Q34="Previsão vencida",3000,IF(Q34="Parada",2000,1000))+MIN(N(O34),500)+N(F34)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4856,7 +4867,7 @@
       </c>
       <c r="R35" s="37">
         <f>IF(OR(G35="",Q35="Fechada",Q35="Perdida"),0,IF(Q35="Previsão vencida",3000,IF(Q35="Parada",2000,1000))+MIN(N(O35),500)+N(F35)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4894,7 +4905,7 @@
       </c>
       <c r="R36" s="37">
         <f>IF(OR(G36="",Q36="Fechada",Q36="Perdida"),0,IF(Q36="Previsão vencida",3000,IF(Q36="Parada",2000,1000))+MIN(N(O36),500)+N(F36)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4932,7 +4943,7 @@
       </c>
       <c r="R37" s="37">
         <f>IF(OR(G37="",Q37="Fechada",Q37="Perdida"),0,IF(Q37="Previsão vencida",3000,IF(Q37="Parada",2000,1000))+MIN(N(O37),500)+N(F37)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4970,7 +4981,7 @@
       </c>
       <c r="R38" s="37">
         <f>IF(OR(G38="",Q38="Fechada",Q38="Perdida"),0,IF(Q38="Previsão vencida",3000,IF(Q38="Parada",2000,1000))+MIN(N(O38),500)+N(F38)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -5008,7 +5019,7 @@
       </c>
       <c r="R39" s="37">
         <f>IF(OR(G39="",Q39="Fechada",Q39="Perdida"),0,IF(Q39="Previsão vencida",3000,IF(Q39="Parada",2000,1000))+MIN(N(O39),500)+N(F39)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -5046,7 +5057,7 @@
       </c>
       <c r="R40" s="37">
         <f>IF(OR(G40="",Q40="Fechada",Q40="Perdida"),0,IF(Q40="Previsão vencida",3000,IF(Q40="Parada",2000,1000))+MIN(N(O40),500)+N(F40)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -5084,7 +5095,7 @@
       </c>
       <c r="R41" s="37">
         <f>IF(OR(G41="",Q41="Fechada",Q41="Perdida"),0,IF(Q41="Previsão vencida",3000,IF(Q41="Parada",2000,1000))+MIN(N(O41),500)+N(F41)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -5122,7 +5133,7 @@
       </c>
       <c r="R42" s="37">
         <f>IF(OR(G42="",Q42="Fechada",Q42="Perdida"),0,IF(Q42="Previsão vencida",3000,IF(Q42="Parada",2000,1000))+MIN(N(O42),500)+N(F42)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5160,7 +5171,7 @@
       </c>
       <c r="R43" s="37">
         <f>IF(OR(G43="",Q43="Fechada",Q43="Perdida"),0,IF(Q43="Previsão vencida",3000,IF(Q43="Parada",2000,1000))+MIN(N(O43),500)+N(F43)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5198,7 +5209,7 @@
       </c>
       <c r="R44" s="37">
         <f>IF(OR(G44="",Q44="Fechada",Q44="Perdida"),0,IF(Q44="Previsão vencida",3000,IF(Q44="Parada",2000,1000))+MIN(N(O44),500)+N(F44)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5236,7 +5247,7 @@
       </c>
       <c r="R45" s="37">
         <f>IF(OR(G45="",Q45="Fechada",Q45="Perdida"),0,IF(Q45="Previsão vencida",3000,IF(Q45="Parada",2000,1000))+MIN(N(O45),500)+N(F45)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5274,7 +5285,7 @@
       </c>
       <c r="R46" s="37">
         <f>IF(OR(G46="",Q46="Fechada",Q46="Perdida"),0,IF(Q46="Previsão vencida",3000,IF(Q46="Parada",2000,1000))+MIN(N(O46),500)+N(F46)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5312,7 +5323,7 @@
       </c>
       <c r="R47" s="37">
         <f>IF(OR(G47="",Q47="Fechada",Q47="Perdida"),0,IF(Q47="Previsão vencida",3000,IF(Q47="Parada",2000,1000))+MIN(N(O47),500)+N(F47)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5350,7 +5361,7 @@
       </c>
       <c r="R48" s="37">
         <f>IF(OR(G48="",Q48="Fechada",Q48="Perdida"),0,IF(Q48="Previsão vencida",3000,IF(Q48="Parada",2000,1000))+MIN(N(O48),500)+N(F48)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5388,7 +5399,7 @@
       </c>
       <c r="R49" s="37">
         <f>IF(OR(G49="",Q49="Fechada",Q49="Perdida"),0,IF(Q49="Previsão vencida",3000,IF(Q49="Parada",2000,1000))+MIN(N(O49),500)+N(F49)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5426,7 +5437,7 @@
       </c>
       <c r="R50" s="37">
         <f>IF(OR(G50="",Q50="Fechada",Q50="Perdida"),0,IF(Q50="Previsão vencida",3000,IF(Q50="Parada",2000,1000))+MIN(N(O50),500)+N(F50)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -5464,7 +5475,7 @@
       </c>
       <c r="R51" s="37">
         <f>IF(OR(G51="",Q51="Fechada",Q51="Perdida"),0,IF(Q51="Previsão vencida",3000,IF(Q51="Parada",2000,1000))+MIN(N(O51),500)+N(F51)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -5502,7 +5513,7 @@
       </c>
       <c r="R52" s="37">
         <f>IF(OR(G52="",Q52="Fechada",Q52="Perdida"),0,IF(Q52="Previsão vencida",3000,IF(Q52="Parada",2000,1000))+MIN(N(O52),500)+N(F52)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5540,7 +5551,7 @@
       </c>
       <c r="R53" s="37">
         <f>IF(OR(G53="",Q53="Fechada",Q53="Perdida"),0,IF(Q53="Previsão vencida",3000,IF(Q53="Parada",2000,1000))+MIN(N(O53),500)+N(F53)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -5578,7 +5589,7 @@
       </c>
       <c r="R54" s="37">
         <f>IF(OR(G54="",Q54="Fechada",Q54="Perdida"),0,IF(Q54="Previsão vencida",3000,IF(Q54="Parada",2000,1000))+MIN(N(O54),500)+N(F54)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5616,7 +5627,7 @@
       </c>
       <c r="R55" s="37">
         <f>IF(OR(G55="",Q55="Fechada",Q55="Perdida"),0,IF(Q55="Previsão vencida",3000,IF(Q55="Parada",2000,1000))+MIN(N(O55),500)+N(F55)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5654,7 +5665,7 @@
       </c>
       <c r="R56" s="37">
         <f>IF(OR(G56="",Q56="Fechada",Q56="Perdida"),0,IF(Q56="Previsão vencida",3000,IF(Q56="Parada",2000,1000))+MIN(N(O56),500)+N(F56)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5692,7 +5703,7 @@
       </c>
       <c r="R57" s="37">
         <f>IF(OR(G57="",Q57="Fechada",Q57="Perdida"),0,IF(Q57="Previsão vencida",3000,IF(Q57="Parada",2000,1000))+MIN(N(O57),500)+N(F57)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5730,7 +5741,7 @@
       </c>
       <c r="R58" s="37">
         <f>IF(OR(G58="",Q58="Fechada",Q58="Perdida"),0,IF(Q58="Previsão vencida",3000,IF(Q58="Parada",2000,1000))+MIN(N(O58),500)+N(F58)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5768,7 +5779,7 @@
       </c>
       <c r="R59" s="37">
         <f>IF(OR(G59="",Q59="Fechada",Q59="Perdida"),0,IF(Q59="Previsão vencida",3000,IF(Q59="Parada",2000,1000))+MIN(N(O59),500)+N(F59)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5806,7 +5817,7 @@
       </c>
       <c r="R60" s="37">
         <f>IF(OR(G60="",Q60="Fechada",Q60="Perdida"),0,IF(Q60="Previsão vencida",3000,IF(Q60="Parada",2000,1000))+MIN(N(O60),500)+N(F60)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5844,7 +5855,7 @@
       </c>
       <c r="R61" s="37">
         <f>IF(OR(G61="",Q61="Fechada",Q61="Perdida"),0,IF(Q61="Previsão vencida",3000,IF(Q61="Parada",2000,1000))+MIN(N(O61),500)+N(F61)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5882,7 +5893,7 @@
       </c>
       <c r="R62" s="37">
         <f>IF(OR(G62="",Q62="Fechada",Q62="Perdida"),0,IF(Q62="Previsão vencida",3000,IF(Q62="Parada",2000,1000))+MIN(N(O62),500)+N(F62)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5920,7 +5931,7 @@
       </c>
       <c r="R63" s="37">
         <f>IF(OR(G63="",Q63="Fechada",Q63="Perdida"),0,IF(Q63="Previsão vencida",3000,IF(Q63="Parada",2000,1000))+MIN(N(O63),500)+N(F63)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5958,7 +5969,7 @@
       </c>
       <c r="R64" s="37">
         <f>IF(OR(G64="",Q64="Fechada",Q64="Perdida"),0,IF(Q64="Previsão vencida",3000,IF(Q64="Parada",2000,1000))+MIN(N(O64),500)+N(F64)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5996,7 +6007,7 @@
       </c>
       <c r="R65" s="37">
         <f>IF(OR(G65="",Q65="Fechada",Q65="Perdida"),0,IF(Q65="Previsão vencida",3000,IF(Q65="Parada",2000,1000))+MIN(N(O65),500)+N(F65)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -6034,7 +6045,7 @@
       </c>
       <c r="R66" s="37">
         <f>IF(OR(G66="",Q66="Fechada",Q66="Perdida"),0,IF(Q66="Previsão vencida",3000,IF(Q66="Parada",2000,1000))+MIN(N(O66),500)+N(F66)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -6072,7 +6083,7 @@
       </c>
       <c r="R67" s="37">
         <f>IF(OR(G67="",Q67="Fechada",Q67="Perdida"),0,IF(Q67="Previsão vencida",3000,IF(Q67="Parada",2000,1000))+MIN(N(O67),500)+N(F67)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -6110,7 +6121,7 @@
       </c>
       <c r="R68" s="37">
         <f>IF(OR(G68="",Q68="Fechada",Q68="Perdida"),0,IF(Q68="Previsão vencida",3000,IF(Q68="Parada",2000,1000))+MIN(N(O68),500)+N(F68)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6148,7 +6159,7 @@
       </c>
       <c r="R69" s="37">
         <f>IF(OR(G69="",Q69="Fechada",Q69="Perdida"),0,IF(Q69="Previsão vencida",3000,IF(Q69="Parada",2000,1000))+MIN(N(O69),500)+N(F69)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6186,7 +6197,7 @@
       </c>
       <c r="R70" s="37">
         <f>IF(OR(G70="",Q70="Fechada",Q70="Perdida"),0,IF(Q70="Previsão vencida",3000,IF(Q70="Parada",2000,1000))+MIN(N(O70),500)+N(F70)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6224,7 +6235,7 @@
       </c>
       <c r="R71" s="37">
         <f>IF(OR(G71="",Q71="Fechada",Q71="Perdida"),0,IF(Q71="Previsão vencida",3000,IF(Q71="Parada",2000,1000))+MIN(N(O71),500)+N(F71)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6262,7 +6273,7 @@
       </c>
       <c r="R72" s="37">
         <f>IF(OR(G72="",Q72="Fechada",Q72="Perdida"),0,IF(Q72="Previsão vencida",3000,IF(Q72="Parada",2000,1000))+MIN(N(O72),500)+N(F72)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6300,7 +6311,7 @@
       </c>
       <c r="R73" s="37">
         <f>IF(OR(G73="",Q73="Fechada",Q73="Perdida"),0,IF(Q73="Previsão vencida",3000,IF(Q73="Parada",2000,1000))+MIN(N(O73),500)+N(F73)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6338,7 +6349,7 @@
       </c>
       <c r="R74" s="37">
         <f>IF(OR(G74="",Q74="Fechada",Q74="Perdida"),0,IF(Q74="Previsão vencida",3000,IF(Q74="Parada",2000,1000))+MIN(N(O74),500)+N(F74)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6376,7 +6387,7 @@
       </c>
       <c r="R75" s="37">
         <f>IF(OR(G75="",Q75="Fechada",Q75="Perdida"),0,IF(Q75="Previsão vencida",3000,IF(Q75="Parada",2000,1000))+MIN(N(O75),500)+N(F75)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6414,7 +6425,7 @@
       </c>
       <c r="R76" s="37">
         <f>IF(OR(G76="",Q76="Fechada",Q76="Perdida"),0,IF(Q76="Previsão vencida",3000,IF(Q76="Parada",2000,1000))+MIN(N(O76),500)+N(F76)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6452,7 +6463,7 @@
       </c>
       <c r="R77" s="37">
         <f>IF(OR(G77="",Q77="Fechada",Q77="Perdida"),0,IF(Q77="Previsão vencida",3000,IF(Q77="Parada",2000,1000))+MIN(N(O77),500)+N(F77)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6490,7 +6501,7 @@
       </c>
       <c r="R78" s="37">
         <f>IF(OR(G78="",Q78="Fechada",Q78="Perdida"),0,IF(Q78="Previsão vencida",3000,IF(Q78="Parada",2000,1000))+MIN(N(O78),500)+N(F78)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6528,7 +6539,7 @@
       </c>
       <c r="R79" s="37">
         <f>IF(OR(G79="",Q79="Fechada",Q79="Perdida"),0,IF(Q79="Previsão vencida",3000,IF(Q79="Parada",2000,1000))+MIN(N(O79),500)+N(F79)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6566,7 +6577,7 @@
       </c>
       <c r="R80" s="37">
         <f>IF(OR(G80="",Q80="Fechada",Q80="Perdida"),0,IF(Q80="Previsão vencida",3000,IF(Q80="Parada",2000,1000))+MIN(N(O80),500)+N(F80)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6604,7 +6615,7 @@
       </c>
       <c r="R81" s="37">
         <f>IF(OR(G81="",Q81="Fechada",Q81="Perdida"),0,IF(Q81="Previsão vencida",3000,IF(Q81="Parada",2000,1000))+MIN(N(O81),500)+N(F81)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -6642,7 +6653,7 @@
       </c>
       <c r="R82" s="37">
         <f>IF(OR(G82="",Q82="Fechada",Q82="Perdida"),0,IF(Q82="Previsão vencida",3000,IF(Q82="Parada",2000,1000))+MIN(N(O82),500)+N(F82)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -6680,7 +6691,7 @@
       </c>
       <c r="R83" s="37">
         <f>IF(OR(G83="",Q83="Fechada",Q83="Perdida"),0,IF(Q83="Previsão vencida",3000,IF(Q83="Parada",2000,1000))+MIN(N(O83),500)+N(F83)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -6718,7 +6729,7 @@
       </c>
       <c r="R84" s="37">
         <f>IF(OR(G84="",Q84="Fechada",Q84="Perdida"),0,IF(Q84="Previsão vencida",3000,IF(Q84="Parada",2000,1000))+MIN(N(O84),500)+N(F84)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -6756,7 +6767,7 @@
       </c>
       <c r="R85" s="37">
         <f>IF(OR(G85="",Q85="Fechada",Q85="Perdida"),0,IF(Q85="Previsão vencida",3000,IF(Q85="Parada",2000,1000))+MIN(N(O85),500)+N(F85)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6794,7 +6805,7 @@
       </c>
       <c r="R86" s="37">
         <f>IF(OR(G86="",Q86="Fechada",Q86="Perdida"),0,IF(Q86="Previsão vencida",3000,IF(Q86="Parada",2000,1000))+MIN(N(O86),500)+N(F86)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -6832,7 +6843,7 @@
       </c>
       <c r="R87" s="37">
         <f>IF(OR(G87="",Q87="Fechada",Q87="Perdida"),0,IF(Q87="Previsão vencida",3000,IF(Q87="Parada",2000,1000))+MIN(N(O87),500)+N(F87)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -6870,7 +6881,7 @@
       </c>
       <c r="R88" s="37">
         <f>IF(OR(G88="",Q88="Fechada",Q88="Perdida"),0,IF(Q88="Previsão vencida",3000,IF(Q88="Parada",2000,1000))+MIN(N(O88),500)+N(F88)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -6908,7 +6919,7 @@
       </c>
       <c r="R89" s="37">
         <f>IF(OR(G89="",Q89="Fechada",Q89="Perdida"),0,IF(Q89="Previsão vencida",3000,IF(Q89="Parada",2000,1000))+MIN(N(O89),500)+N(F89)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -6946,7 +6957,7 @@
       </c>
       <c r="R90" s="37">
         <f>IF(OR(G90="",Q90="Fechada",Q90="Perdida"),0,IF(Q90="Previsão vencida",3000,IF(Q90="Parada",2000,1000))+MIN(N(O90),500)+N(F90)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -6984,7 +6995,7 @@
       </c>
       <c r="R91" s="37">
         <f>IF(OR(G91="",Q91="Fechada",Q91="Perdida"),0,IF(Q91="Previsão vencida",3000,IF(Q91="Parada",2000,1000))+MIN(N(O91),500)+N(F91)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7022,7 +7033,7 @@
       </c>
       <c r="R92" s="37">
         <f>IF(OR(G92="",Q92="Fechada",Q92="Perdida"),0,IF(Q92="Previsão vencida",3000,IF(Q92="Parada",2000,1000))+MIN(N(O92),500)+N(F92)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -7060,7 +7071,7 @@
       </c>
       <c r="R93" s="37">
         <f>IF(OR(G93="",Q93="Fechada",Q93="Perdida"),0,IF(Q93="Previsão vencida",3000,IF(Q93="Parada",2000,1000))+MIN(N(O93),500)+N(F93)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -7098,7 +7109,7 @@
       </c>
       <c r="R94" s="37">
         <f>IF(OR(G94="",Q94="Fechada",Q94="Perdida"),0,IF(Q94="Previsão vencida",3000,IF(Q94="Parada",2000,1000))+MIN(N(O94),500)+N(F94)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -7136,7 +7147,7 @@
       </c>
       <c r="R95" s="37">
         <f>IF(OR(G95="",Q95="Fechada",Q95="Perdida"),0,IF(Q95="Previsão vencida",3000,IF(Q95="Parada",2000,1000))+MIN(N(O95),500)+N(F95)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7174,7 +7185,7 @@
       </c>
       <c r="R96" s="37">
         <f>IF(OR(G96="",Q96="Fechada",Q96="Perdida"),0,IF(Q96="Previsão vencida",3000,IF(Q96="Parada",2000,1000))+MIN(N(O96),500)+N(F96)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -7212,7 +7223,7 @@
       </c>
       <c r="R97" s="37">
         <f>IF(OR(G97="",Q97="Fechada",Q97="Perdida"),0,IF(Q97="Previsão vencida",3000,IF(Q97="Parada",2000,1000))+MIN(N(O97),500)+N(F97)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -7250,7 +7261,7 @@
       </c>
       <c r="R98" s="37">
         <f>IF(OR(G98="",Q98="Fechada",Q98="Perdida"),0,IF(Q98="Previsão vencida",3000,IF(Q98="Parada",2000,1000))+MIN(N(O98),500)+N(F98)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -7288,7 +7299,7 @@
       </c>
       <c r="R99" s="37">
         <f>IF(OR(G99="",Q99="Fechada",Q99="Perdida"),0,IF(Q99="Previsão vencida",3000,IF(Q99="Parada",2000,1000))+MIN(N(O99),500)+N(F99)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -7326,7 +7337,7 @@
       </c>
       <c r="R100" s="37">
         <f>IF(OR(G100="",Q100="Fechada",Q100="Perdida"),0,IF(Q100="Previsão vencida",3000,IF(Q100="Parada",2000,1000))+MIN(N(O100),500)+N(F100)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -7364,7 +7375,7 @@
       </c>
       <c r="R101" s="37">
         <f>IF(OR(G101="",Q101="Fechada",Q101="Perdida"),0,IF(Q101="Previsão vencida",3000,IF(Q101="Parada",2000,1000))+MIN(N(O101),500)+N(F101)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -7402,7 +7413,7 @@
       </c>
       <c r="R102" s="37">
         <f>IF(OR(G102="",Q102="Fechada",Q102="Perdida"),0,IF(Q102="Previsão vencida",3000,IF(Q102="Parada",2000,1000))+MIN(N(O102),500)+N(F102)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -7440,7 +7451,7 @@
       </c>
       <c r="R103" s="37">
         <f>IF(OR(G103="",Q103="Fechada",Q103="Perdida"),0,IF(Q103="Previsão vencida",3000,IF(Q103="Parada",2000,1000))+MIN(N(O103),500)+N(F103)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -7478,7 +7489,7 @@
       </c>
       <c r="R104" s="37">
         <f>IF(OR(G104="",Q104="Fechada",Q104="Perdida"),0,IF(Q104="Previsão vencida",3000,IF(Q104="Parada",2000,1000))+MIN(N(O104),500)+N(F104)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -7516,7 +7527,7 @@
       </c>
       <c r="R105" s="37">
         <f>IF(OR(G105="",Q105="Fechada",Q105="Perdida"),0,IF(Q105="Previsão vencida",3000,IF(Q105="Parada",2000,1000))+MIN(N(O105),500)+N(F105)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -7554,7 +7565,7 @@
       </c>
       <c r="R106" s="37">
         <f>IF(OR(G106="",Q106="Fechada",Q106="Perdida"),0,IF(Q106="Previsão vencida",3000,IF(Q106="Parada",2000,1000))+MIN(N(O106),500)+N(F106)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -7592,7 +7603,7 @@
       </c>
       <c r="R107" s="37">
         <f>IF(OR(G107="",Q107="Fechada",Q107="Perdida"),0,IF(Q107="Previsão vencida",3000,IF(Q107="Parada",2000,1000))+MIN(N(O107),500)+N(F107)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -7630,7 +7641,7 @@
       </c>
       <c r="R108" s="37">
         <f>IF(OR(G108="",Q108="Fechada",Q108="Perdida"),0,IF(Q108="Previsão vencida",3000,IF(Q108="Parada",2000,1000))+MIN(N(O108),500)+N(F108)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -7668,7 +7679,7 @@
       </c>
       <c r="R109" s="37">
         <f>IF(OR(G109="",Q109="Fechada",Q109="Perdida"),0,IF(Q109="Previsão vencida",3000,IF(Q109="Parada",2000,1000))+MIN(N(O109),500)+N(F109)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -7706,7 +7717,7 @@
       </c>
       <c r="R110" s="37">
         <f>IF(OR(G110="",Q110="Fechada",Q110="Perdida"),0,IF(Q110="Previsão vencida",3000,IF(Q110="Parada",2000,1000))+MIN(N(O110),500)+N(F110)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -7744,7 +7755,7 @@
       </c>
       <c r="R111" s="37">
         <f>IF(OR(G111="",Q111="Fechada",Q111="Perdida"),0,IF(Q111="Previsão vencida",3000,IF(Q111="Parada",2000,1000))+MIN(N(O111),500)+N(F111)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -7782,7 +7793,7 @@
       </c>
       <c r="R112" s="37">
         <f>IF(OR(G112="",Q112="Fechada",Q112="Perdida"),0,IF(Q112="Previsão vencida",3000,IF(Q112="Parada",2000,1000))+MIN(N(O112),500)+N(F112)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -7820,7 +7831,7 @@
       </c>
       <c r="R113" s="37">
         <f>IF(OR(G113="",Q113="Fechada",Q113="Perdida"),0,IF(Q113="Previsão vencida",3000,IF(Q113="Parada",2000,1000))+MIN(N(O113),500)+N(F113)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -7858,7 +7869,7 @@
       </c>
       <c r="R114" s="37">
         <f>IF(OR(G114="",Q114="Fechada",Q114="Perdida"),0,IF(Q114="Previsão vencida",3000,IF(Q114="Parada",2000,1000))+MIN(N(O114),500)+N(F114)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -7896,7 +7907,7 @@
       </c>
       <c r="R115" s="37">
         <f>IF(OR(G115="",Q115="Fechada",Q115="Perdida"),0,IF(Q115="Previsão vencida",3000,IF(Q115="Parada",2000,1000))+MIN(N(O115),500)+N(F115)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -7934,7 +7945,7 @@
       </c>
       <c r="R116" s="37">
         <f>IF(OR(G116="",Q116="Fechada",Q116="Perdida"),0,IF(Q116="Previsão vencida",3000,IF(Q116="Parada",2000,1000))+MIN(N(O116),500)+N(F116)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -7972,7 +7983,7 @@
       </c>
       <c r="R117" s="37">
         <f>IF(OR(G117="",Q117="Fechada",Q117="Perdida"),0,IF(Q117="Previsão vencida",3000,IF(Q117="Parada",2000,1000))+MIN(N(O117),500)+N(F117)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -8010,7 +8021,7 @@
       </c>
       <c r="R118" s="37">
         <f>IF(OR(G118="",Q118="Fechada",Q118="Perdida"),0,IF(Q118="Previsão vencida",3000,IF(Q118="Parada",2000,1000))+MIN(N(O118),500)+N(F118)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -8048,7 +8059,7 @@
       </c>
       <c r="R119" s="37">
         <f>IF(OR(G119="",Q119="Fechada",Q119="Perdida"),0,IF(Q119="Previsão vencida",3000,IF(Q119="Parada",2000,1000))+MIN(N(O119),500)+N(F119)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -8086,7 +8097,7 @@
       </c>
       <c r="R120" s="37">
         <f>IF(OR(G120="",Q120="Fechada",Q120="Perdida"),0,IF(Q120="Previsão vencida",3000,IF(Q120="Parada",2000,1000))+MIN(N(O120),500)+N(F120)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -8124,7 +8135,7 @@
       </c>
       <c r="R121" s="37">
         <f>IF(OR(G121="",Q121="Fechada",Q121="Perdida"),0,IF(Q121="Previsão vencida",3000,IF(Q121="Parada",2000,1000))+MIN(N(O121),500)+N(F121)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -8162,7 +8173,7 @@
       </c>
       <c r="R122" s="37">
         <f>IF(OR(G122="",Q122="Fechada",Q122="Perdida"),0,IF(Q122="Previsão vencida",3000,IF(Q122="Parada",2000,1000))+MIN(N(O122),500)+N(F122)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -8200,7 +8211,7 @@
       </c>
       <c r="R123" s="37">
         <f>IF(OR(G123="",Q123="Fechada",Q123="Perdida"),0,IF(Q123="Previsão vencida",3000,IF(Q123="Parada",2000,1000))+MIN(N(O123),500)+N(F123)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -8238,7 +8249,7 @@
       </c>
       <c r="R124" s="37">
         <f>IF(OR(G124="",Q124="Fechada",Q124="Perdida"),0,IF(Q124="Previsão vencida",3000,IF(Q124="Parada",2000,1000))+MIN(N(O124),500)+N(F124)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -8276,7 +8287,7 @@
       </c>
       <c r="R125" s="37">
         <f>IF(OR(G125="",Q125="Fechada",Q125="Perdida"),0,IF(Q125="Previsão vencida",3000,IF(Q125="Parada",2000,1000))+MIN(N(O125),500)+N(F125)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -8314,7 +8325,7 @@
       </c>
       <c r="R126" s="37">
         <f>IF(OR(G126="",Q126="Fechada",Q126="Perdida"),0,IF(Q126="Previsão vencida",3000,IF(Q126="Parada",2000,1000))+MIN(N(O126),500)+N(F126)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -8352,7 +8363,7 @@
       </c>
       <c r="R127" s="37">
         <f>IF(OR(G127="",Q127="Fechada",Q127="Perdida"),0,IF(Q127="Previsão vencida",3000,IF(Q127="Parada",2000,1000))+MIN(N(O127),500)+N(F127)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -8390,7 +8401,7 @@
       </c>
       <c r="R128" s="37">
         <f>IF(OR(G128="",Q128="Fechada",Q128="Perdida"),0,IF(Q128="Previsão vencida",3000,IF(Q128="Parada",2000,1000))+MIN(N(O128),500)+N(F128)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -8428,7 +8439,7 @@
       </c>
       <c r="R129" s="37">
         <f>IF(OR(G129="",Q129="Fechada",Q129="Perdida"),0,IF(Q129="Previsão vencida",3000,IF(Q129="Parada",2000,1000))+MIN(N(O129),500)+N(F129)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -8466,7 +8477,7 @@
       </c>
       <c r="R130" s="37">
         <f>IF(OR(G130="",Q130="Fechada",Q130="Perdida"),0,IF(Q130="Previsão vencida",3000,IF(Q130="Parada",2000,1000))+MIN(N(O130),500)+N(F130)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -8504,7 +8515,7 @@
       </c>
       <c r="R131" s="37">
         <f>IF(OR(G131="",Q131="Fechada",Q131="Perdida"),0,IF(Q131="Previsão vencida",3000,IF(Q131="Parada",2000,1000))+MIN(N(O131),500)+N(F131)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -8542,7 +8553,7 @@
       </c>
       <c r="R132" s="37">
         <f>IF(OR(G132="",Q132="Fechada",Q132="Perdida"),0,IF(Q132="Previsão vencida",3000,IF(Q132="Parada",2000,1000))+MIN(N(O132),500)+N(F132)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -8580,7 +8591,7 @@
       </c>
       <c r="R133" s="37">
         <f>IF(OR(G133="",Q133="Fechada",Q133="Perdida"),0,IF(Q133="Previsão vencida",3000,IF(Q133="Parada",2000,1000))+MIN(N(O133),500)+N(F133)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -8618,7 +8629,7 @@
       </c>
       <c r="R134" s="37">
         <f>IF(OR(G134="",Q134="Fechada",Q134="Perdida"),0,IF(Q134="Previsão vencida",3000,IF(Q134="Parada",2000,1000))+MIN(N(O134),500)+N(F134)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -8656,7 +8667,7 @@
       </c>
       <c r="R135" s="37">
         <f>IF(OR(G135="",Q135="Fechada",Q135="Perdida"),0,IF(Q135="Previsão vencida",3000,IF(Q135="Parada",2000,1000))+MIN(N(O135),500)+N(F135)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -8694,7 +8705,7 @@
       </c>
       <c r="R136" s="37">
         <f>IF(OR(G136="",Q136="Fechada",Q136="Perdida"),0,IF(Q136="Previsão vencida",3000,IF(Q136="Parada",2000,1000))+MIN(N(O136),500)+N(F136)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -8732,7 +8743,7 @@
       </c>
       <c r="R137" s="37">
         <f>IF(OR(G137="",Q137="Fechada",Q137="Perdida"),0,IF(Q137="Previsão vencida",3000,IF(Q137="Parada",2000,1000))+MIN(N(O137),500)+N(F137)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -8770,7 +8781,7 @@
       </c>
       <c r="R138" s="37">
         <f>IF(OR(G138="",Q138="Fechada",Q138="Perdida"),0,IF(Q138="Previsão vencida",3000,IF(Q138="Parada",2000,1000))+MIN(N(O138),500)+N(F138)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -8808,7 +8819,7 @@
       </c>
       <c r="R139" s="37">
         <f>IF(OR(G139="",Q139="Fechada",Q139="Perdida"),0,IF(Q139="Previsão vencida",3000,IF(Q139="Parada",2000,1000))+MIN(N(O139),500)+N(F139)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -8846,7 +8857,7 @@
       </c>
       <c r="R140" s="37">
         <f>IF(OR(G140="",Q140="Fechada",Q140="Perdida"),0,IF(Q140="Previsão vencida",3000,IF(Q140="Parada",2000,1000))+MIN(N(O140),500)+N(F140)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -8884,7 +8895,7 @@
       </c>
       <c r="R141" s="37">
         <f>IF(OR(G141="",Q141="Fechada",Q141="Perdida"),0,IF(Q141="Previsão vencida",3000,IF(Q141="Parada",2000,1000))+MIN(N(O141),500)+N(F141)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -8922,7 +8933,7 @@
       </c>
       <c r="R142" s="37">
         <f>IF(OR(G142="",Q142="Fechada",Q142="Perdida"),0,IF(Q142="Previsão vencida",3000,IF(Q142="Parada",2000,1000))+MIN(N(O142),500)+N(F142)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -8960,7 +8971,7 @@
       </c>
       <c r="R143" s="37">
         <f>IF(OR(G143="",Q143="Fechada",Q143="Perdida"),0,IF(Q143="Previsão vencida",3000,IF(Q143="Parada",2000,1000))+MIN(N(O143),500)+N(F143)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -8998,7 +9009,7 @@
       </c>
       <c r="R144" s="37">
         <f>IF(OR(G144="",Q144="Fechada",Q144="Perdida"),0,IF(Q144="Previsão vencida",3000,IF(Q144="Parada",2000,1000))+MIN(N(O144),500)+N(F144)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -9036,7 +9047,7 @@
       </c>
       <c r="R145" s="37">
         <f>IF(OR(G145="",Q145="Fechada",Q145="Perdida"),0,IF(Q145="Previsão vencida",3000,IF(Q145="Parada",2000,1000))+MIN(N(O145),500)+N(F145)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -9074,7 +9085,7 @@
       </c>
       <c r="R146" s="37">
         <f>IF(OR(G146="",Q146="Fechada",Q146="Perdida"),0,IF(Q146="Previsão vencida",3000,IF(Q146="Parada",2000,1000))+MIN(N(O146),500)+N(F146)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -9112,7 +9123,7 @@
       </c>
       <c r="R147" s="37">
         <f>IF(OR(G147="",Q147="Fechada",Q147="Perdida"),0,IF(Q147="Previsão vencida",3000,IF(Q147="Parada",2000,1000))+MIN(N(O147),500)+N(F147)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -9150,7 +9161,7 @@
       </c>
       <c r="R148" s="37">
         <f>IF(OR(G148="",Q148="Fechada",Q148="Perdida"),0,IF(Q148="Previsão vencida",3000,IF(Q148="Parada",2000,1000))+MIN(N(O148),500)+N(F148)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -9188,7 +9199,7 @@
       </c>
       <c r="R149" s="37">
         <f>IF(OR(G149="",Q149="Fechada",Q149="Perdida"),0,IF(Q149="Previsão vencida",3000,IF(Q149="Parada",2000,1000))+MIN(N(O149),500)+N(F149)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -9226,7 +9237,7 @@
       </c>
       <c r="R150" s="37">
         <f>IF(OR(G150="",Q150="Fechada",Q150="Perdida"),0,IF(Q150="Previsão vencida",3000,IF(Q150="Parada",2000,1000))+MIN(N(O150),500)+N(F150)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -9264,7 +9275,7 @@
       </c>
       <c r="R151" s="37">
         <f>IF(OR(G151="",Q151="Fechada",Q151="Perdida"),0,IF(Q151="Previsão vencida",3000,IF(Q151="Parada",2000,1000))+MIN(N(O151),500)+N(F151)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -9302,7 +9313,7 @@
       </c>
       <c r="R152" s="37">
         <f>IF(OR(G152="",Q152="Fechada",Q152="Perdida"),0,IF(Q152="Previsão vencida",3000,IF(Q152="Parada",2000,1000))+MIN(N(O152),500)+N(F152)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -9340,7 +9351,7 @@
       </c>
       <c r="R153" s="37">
         <f>IF(OR(G153="",Q153="Fechada",Q153="Perdida"),0,IF(Q153="Previsão vencida",3000,IF(Q153="Parada",2000,1000))+MIN(N(O153),500)+N(F153)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -9378,7 +9389,7 @@
       </c>
       <c r="R154" s="37">
         <f>IF(OR(G154="",Q154="Fechada",Q154="Perdida"),0,IF(Q154="Previsão vencida",3000,IF(Q154="Parada",2000,1000))+MIN(N(O154),500)+N(F154)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -9416,7 +9427,7 @@
       </c>
       <c r="R155" s="37">
         <f>IF(OR(G155="",Q155="Fechada",Q155="Perdida"),0,IF(Q155="Previsão vencida",3000,IF(Q155="Parada",2000,1000))+MIN(N(O155),500)+N(F155)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -9454,7 +9465,7 @@
       </c>
       <c r="R156" s="37">
         <f>IF(OR(G156="",Q156="Fechada",Q156="Perdida"),0,IF(Q156="Previsão vencida",3000,IF(Q156="Parada",2000,1000))+MIN(N(O156),500)+N(F156)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -9492,7 +9503,7 @@
       </c>
       <c r="R157" s="37">
         <f>IF(OR(G157="",Q157="Fechada",Q157="Perdida"),0,IF(Q157="Previsão vencida",3000,IF(Q157="Parada",2000,1000))+MIN(N(O157),500)+N(F157)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -9530,7 +9541,7 @@
       </c>
       <c r="R158" s="37">
         <f>IF(OR(G158="",Q158="Fechada",Q158="Perdida"),0,IF(Q158="Previsão vencida",3000,IF(Q158="Parada",2000,1000))+MIN(N(O158),500)+N(F158)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -9568,7 +9579,7 @@
       </c>
       <c r="R159" s="37">
         <f>IF(OR(G159="",Q159="Fechada",Q159="Perdida"),0,IF(Q159="Previsão vencida",3000,IF(Q159="Parada",2000,1000))+MIN(N(O159),500)+N(F159)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -9606,7 +9617,7 @@
       </c>
       <c r="R160" s="37">
         <f>IF(OR(G160="",Q160="Fechada",Q160="Perdida"),0,IF(Q160="Previsão vencida",3000,IF(Q160="Parada",2000,1000))+MIN(N(O160),500)+N(F160)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -9644,7 +9655,7 @@
       </c>
       <c r="R161" s="37">
         <f>IF(OR(G161="",Q161="Fechada",Q161="Perdida"),0,IF(Q161="Previsão vencida",3000,IF(Q161="Parada",2000,1000))+MIN(N(O161),500)+N(F161)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -9682,7 +9693,7 @@
       </c>
       <c r="R162" s="37">
         <f>IF(OR(G162="",Q162="Fechada",Q162="Perdida"),0,IF(Q162="Previsão vencida",3000,IF(Q162="Parada",2000,1000))+MIN(N(O162),500)+N(F162)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -9720,7 +9731,7 @@
       </c>
       <c r="R163" s="37">
         <f>IF(OR(G163="",Q163="Fechada",Q163="Perdida"),0,IF(Q163="Previsão vencida",3000,IF(Q163="Parada",2000,1000))+MIN(N(O163),500)+N(F163)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -9758,7 +9769,7 @@
       </c>
       <c r="R164" s="37">
         <f>IF(OR(G164="",Q164="Fechada",Q164="Perdida"),0,IF(Q164="Previsão vencida",3000,IF(Q164="Parada",2000,1000))+MIN(N(O164),500)+N(F164)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -9796,7 +9807,7 @@
       </c>
       <c r="R165" s="37">
         <f>IF(OR(G165="",Q165="Fechada",Q165="Perdida"),0,IF(Q165="Previsão vencida",3000,IF(Q165="Parada",2000,1000))+MIN(N(O165),500)+N(F165)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -9834,7 +9845,7 @@
       </c>
       <c r="R166" s="37">
         <f>IF(OR(G166="",Q166="Fechada",Q166="Perdida"),0,IF(Q166="Previsão vencida",3000,IF(Q166="Parada",2000,1000))+MIN(N(O166),500)+N(F166)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -9872,7 +9883,7 @@
       </c>
       <c r="R167" s="37">
         <f>IF(OR(G167="",Q167="Fechada",Q167="Perdida"),0,IF(Q167="Previsão vencida",3000,IF(Q167="Parada",2000,1000))+MIN(N(O167),500)+N(F167)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -9910,7 +9921,7 @@
       </c>
       <c r="R168" s="37">
         <f>IF(OR(G168="",Q168="Fechada",Q168="Perdida"),0,IF(Q168="Previsão vencida",3000,IF(Q168="Parada",2000,1000))+MIN(N(O168),500)+N(F168)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -9948,7 +9959,7 @@
       </c>
       <c r="R169" s="37">
         <f>IF(OR(G169="",Q169="Fechada",Q169="Perdida"),0,IF(Q169="Previsão vencida",3000,IF(Q169="Parada",2000,1000))+MIN(N(O169),500)+N(F169)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -9986,7 +9997,7 @@
       </c>
       <c r="R170" s="37">
         <f>IF(OR(G170="",Q170="Fechada",Q170="Perdida"),0,IF(Q170="Previsão vencida",3000,IF(Q170="Parada",2000,1000))+MIN(N(O170),500)+N(F170)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -10024,7 +10035,7 @@
       </c>
       <c r="R171" s="37">
         <f>IF(OR(G171="",Q171="Fechada",Q171="Perdida"),0,IF(Q171="Previsão vencida",3000,IF(Q171="Parada",2000,1000))+MIN(N(O171),500)+N(F171)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -10062,7 +10073,7 @@
       </c>
       <c r="R172" s="37">
         <f>IF(OR(G172="",Q172="Fechada",Q172="Perdida"),0,IF(Q172="Previsão vencida",3000,IF(Q172="Parada",2000,1000))+MIN(N(O172),500)+N(F172)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -10100,7 +10111,7 @@
       </c>
       <c r="R173" s="37">
         <f>IF(OR(G173="",Q173="Fechada",Q173="Perdida"),0,IF(Q173="Previsão vencida",3000,IF(Q173="Parada",2000,1000))+MIN(N(O173),500)+N(F173)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -10138,7 +10149,7 @@
       </c>
       <c r="R174" s="37">
         <f>IF(OR(G174="",Q174="Fechada",Q174="Perdida"),0,IF(Q174="Previsão vencida",3000,IF(Q174="Parada",2000,1000))+MIN(N(O174),500)+N(F174)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -10176,7 +10187,7 @@
       </c>
       <c r="R175" s="37">
         <f>IF(OR(G175="",Q175="Fechada",Q175="Perdida"),0,IF(Q175="Previsão vencida",3000,IF(Q175="Parada",2000,1000))+MIN(N(O175),500)+N(F175)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -10214,7 +10225,7 @@
       </c>
       <c r="R176" s="37">
         <f>IF(OR(G176="",Q176="Fechada",Q176="Perdida"),0,IF(Q176="Previsão vencida",3000,IF(Q176="Parada",2000,1000))+MIN(N(O176),500)+N(F176)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -10252,7 +10263,7 @@
       </c>
       <c r="R177" s="37">
         <f>IF(OR(G177="",Q177="Fechada",Q177="Perdida"),0,IF(Q177="Previsão vencida",3000,IF(Q177="Parada",2000,1000))+MIN(N(O177),500)+N(F177)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -10290,7 +10301,7 @@
       </c>
       <c r="R178" s="37">
         <f>IF(OR(G178="",Q178="Fechada",Q178="Perdida"),0,IF(Q178="Previsão vencida",3000,IF(Q178="Parada",2000,1000))+MIN(N(O178),500)+N(F178)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -10328,7 +10339,7 @@
       </c>
       <c r="R179" s="37">
         <f>IF(OR(G179="",Q179="Fechada",Q179="Perdida"),0,IF(Q179="Previsão vencida",3000,IF(Q179="Parada",2000,1000))+MIN(N(O179),500)+N(F179)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -10366,7 +10377,7 @@
       </c>
       <c r="R180" s="37">
         <f>IF(OR(G180="",Q180="Fechada",Q180="Perdida"),0,IF(Q180="Previsão vencida",3000,IF(Q180="Parada",2000,1000))+MIN(N(O180),500)+N(F180)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -10404,7 +10415,7 @@
       </c>
       <c r="R181" s="37">
         <f>IF(OR(G181="",Q181="Fechada",Q181="Perdida"),0,IF(Q181="Previsão vencida",3000,IF(Q181="Parada",2000,1000))+MIN(N(O181),500)+N(F181)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -10442,7 +10453,7 @@
       </c>
       <c r="R182" s="37">
         <f>IF(OR(G182="",Q182="Fechada",Q182="Perdida"),0,IF(Q182="Previsão vencida",3000,IF(Q182="Parada",2000,1000))+MIN(N(O182),500)+N(F182)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -10480,7 +10491,7 @@
       </c>
       <c r="R183" s="37">
         <f>IF(OR(G183="",Q183="Fechada",Q183="Perdida"),0,IF(Q183="Previsão vencida",3000,IF(Q183="Parada",2000,1000))+MIN(N(O183),500)+N(F183)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -10518,7 +10529,7 @@
       </c>
       <c r="R184" s="37">
         <f>IF(OR(G184="",Q184="Fechada",Q184="Perdida"),0,IF(Q184="Previsão vencida",3000,IF(Q184="Parada",2000,1000))+MIN(N(O184),500)+N(F184)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -10556,7 +10567,7 @@
       </c>
       <c r="R185" s="37">
         <f>IF(OR(G185="",Q185="Fechada",Q185="Perdida"),0,IF(Q185="Previsão vencida",3000,IF(Q185="Parada",2000,1000))+MIN(N(O185),500)+N(F185)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -10594,7 +10605,7 @@
       </c>
       <c r="R186" s="37">
         <f>IF(OR(G186="",Q186="Fechada",Q186="Perdida"),0,IF(Q186="Previsão vencida",3000,IF(Q186="Parada",2000,1000))+MIN(N(O186),500)+N(F186)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -10632,7 +10643,7 @@
       </c>
       <c r="R187" s="37">
         <f>IF(OR(G187="",Q187="Fechada",Q187="Perdida"),0,IF(Q187="Previsão vencida",3000,IF(Q187="Parada",2000,1000))+MIN(N(O187),500)+N(F187)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -10670,7 +10681,7 @@
       </c>
       <c r="R188" s="37">
         <f>IF(OR(G188="",Q188="Fechada",Q188="Perdida"),0,IF(Q188="Previsão vencida",3000,IF(Q188="Parada",2000,1000))+MIN(N(O188),500)+N(F188)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -10708,7 +10719,7 @@
       </c>
       <c r="R189" s="37">
         <f>IF(OR(G189="",Q189="Fechada",Q189="Perdida"),0,IF(Q189="Previsão vencida",3000,IF(Q189="Parada",2000,1000))+MIN(N(O189),500)+N(F189)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -10746,7 +10757,7 @@
       </c>
       <c r="R190" s="37">
         <f>IF(OR(G190="",Q190="Fechada",Q190="Perdida"),0,IF(Q190="Previsão vencida",3000,IF(Q190="Parada",2000,1000))+MIN(N(O190),500)+N(F190)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -10784,7 +10795,7 @@
       </c>
       <c r="R191" s="37">
         <f>IF(OR(G191="",Q191="Fechada",Q191="Perdida"),0,IF(Q191="Previsão vencida",3000,IF(Q191="Parada",2000,1000))+MIN(N(O191),500)+N(F191)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -10822,7 +10833,7 @@
       </c>
       <c r="R192" s="37">
         <f>IF(OR(G192="",Q192="Fechada",Q192="Perdida"),0,IF(Q192="Previsão vencida",3000,IF(Q192="Parada",2000,1000))+MIN(N(O192),500)+N(F192)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -10860,7 +10871,7 @@
       </c>
       <c r="R193" s="37">
         <f>IF(OR(G193="",Q193="Fechada",Q193="Perdida"),0,IF(Q193="Previsão vencida",3000,IF(Q193="Parada",2000,1000))+MIN(N(O193),500)+N(F193)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -10898,7 +10909,7 @@
       </c>
       <c r="R194" s="37">
         <f>IF(OR(G194="",Q194="Fechada",Q194="Perdida"),0,IF(Q194="Previsão vencida",3000,IF(Q194="Parada",2000,1000))+MIN(N(O194),500)+N(F194)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -10936,7 +10947,7 @@
       </c>
       <c r="R195" s="37">
         <f>IF(OR(G195="",Q195="Fechada",Q195="Perdida"),0,IF(Q195="Previsão vencida",3000,IF(Q195="Parada",2000,1000))+MIN(N(O195),500)+N(F195)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -10974,7 +10985,7 @@
       </c>
       <c r="R196" s="37">
         <f>IF(OR(G196="",Q196="Fechada",Q196="Perdida"),0,IF(Q196="Previsão vencida",3000,IF(Q196="Parada",2000,1000))+MIN(N(O196),500)+N(F196)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -11012,7 +11023,7 @@
       </c>
       <c r="R197" s="37">
         <f>IF(OR(G197="",Q197="Fechada",Q197="Perdida"),0,IF(Q197="Previsão vencida",3000,IF(Q197="Parada",2000,1000))+MIN(N(O197),500)+N(F197)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -11050,7 +11061,7 @@
       </c>
       <c r="R198" s="37">
         <f>IF(OR(G198="",Q198="Fechada",Q198="Perdida"),0,IF(Q198="Previsão vencida",3000,IF(Q198="Parada",2000,1000))+MIN(N(O198),500)+N(F198)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -11088,7 +11099,7 @@
       </c>
       <c r="R199" s="37">
         <f>IF(OR(G199="",Q199="Fechada",Q199="Perdida"),0,IF(Q199="Previsão vencida",3000,IF(Q199="Parada",2000,1000))+MIN(N(O199),500)+N(F199)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -11126,7 +11137,7 @@
       </c>
       <c r="R200" s="37">
         <f>IF(OR(G200="",Q200="Fechada",Q200="Perdida"),0,IF(Q200="Previsão vencida",3000,IF(Q200="Parada",2000,1000))+MIN(N(O200),500)+N(F200)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -11164,7 +11175,7 @@
       </c>
       <c r="R201" s="37">
         <f>IF(OR(G201="",Q201="Fechada",Q201="Perdida"),0,IF(Q201="Previsão vencida",3000,IF(Q201="Parada",2000,1000))+MIN(N(O201),500)+N(F201)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -11202,7 +11213,7 @@
       </c>
       <c r="R202" s="37">
         <f>IF(OR(G202="",Q202="Fechada",Q202="Perdida"),0,IF(Q202="Previsão vencida",3000,IF(Q202="Parada",2000,1000))+MIN(N(O202),500)+N(F202)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -11240,7 +11251,7 @@
       </c>
       <c r="R203" s="37">
         <f>IF(OR(G203="",Q203="Fechada",Q203="Perdida"),0,IF(Q203="Previsão vencida",3000,IF(Q203="Parada",2000,1000))+MIN(N(O203),500)+N(F203)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -11278,7 +11289,7 @@
       </c>
       <c r="R204" s="37">
         <f>IF(OR(G204="",Q204="Fechada",Q204="Perdida"),0,IF(Q204="Previsão vencida",3000,IF(Q204="Parada",2000,1000))+MIN(N(O204),500)+N(F204)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -11316,7 +11327,7 @@
       </c>
       <c r="R205" s="37">
         <f>IF(OR(G205="",Q205="Fechada",Q205="Perdida"),0,IF(Q205="Previsão vencida",3000,IF(Q205="Parada",2000,1000))+MIN(N(O205),500)+N(F205)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -11354,7 +11365,7 @@
       </c>
       <c r="R206" s="37">
         <f>IF(OR(G206="",Q206="Fechada",Q206="Perdida"),0,IF(Q206="Previsão vencida",3000,IF(Q206="Parada",2000,1000))+MIN(N(O206),500)+N(F206)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -11392,7 +11403,7 @@
       </c>
       <c r="R207" s="37">
         <f>IF(OR(G207="",Q207="Fechada",Q207="Perdida"),0,IF(Q207="Previsão vencida",3000,IF(Q207="Parada",2000,1000))+MIN(N(O207),500)+N(F207)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -11430,7 +11441,7 @@
       </c>
       <c r="R208" s="37">
         <f>IF(OR(G208="",Q208="Fechada",Q208="Perdida"),0,IF(Q208="Previsão vencida",3000,IF(Q208="Parada",2000,1000))+MIN(N(O208),500)+N(F208)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -11468,7 +11479,7 @@
       </c>
       <c r="R209" s="37">
         <f>IF(OR(G209="",Q209="Fechada",Q209="Perdida"),0,IF(Q209="Previsão vencida",3000,IF(Q209="Parada",2000,1000))+MIN(N(O209),500)+N(F209)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -11506,7 +11517,7 @@
       </c>
       <c r="R210" s="37">
         <f>IF(OR(G210="",Q210="Fechada",Q210="Perdida"),0,IF(Q210="Previsão vencida",3000,IF(Q210="Parada",2000,1000))+MIN(N(O210),500)+N(F210)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -11544,7 +11555,7 @@
       </c>
       <c r="R211" s="37">
         <f>IF(OR(G211="",Q211="Fechada",Q211="Perdida"),0,IF(Q211="Previsão vencida",3000,IF(Q211="Parada",2000,1000))+MIN(N(O211),500)+N(F211)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -11582,7 +11593,7 @@
       </c>
       <c r="R212" s="37">
         <f>IF(OR(G212="",Q212="Fechada",Q212="Perdida"),0,IF(Q212="Previsão vencida",3000,IF(Q212="Parada",2000,1000))+MIN(N(O212),500)+N(F212)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -11620,7 +11631,7 @@
       </c>
       <c r="R213" s="37">
         <f>IF(OR(G213="",Q213="Fechada",Q213="Perdida"),0,IF(Q213="Previsão vencida",3000,IF(Q213="Parada",2000,1000))+MIN(N(O213),500)+N(F213)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -11658,7 +11669,7 @@
       </c>
       <c r="R214" s="37">
         <f>IF(OR(G214="",Q214="Fechada",Q214="Perdida"),0,IF(Q214="Previsão vencida",3000,IF(Q214="Parada",2000,1000))+MIN(N(O214),500)+N(F214)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -11696,7 +11707,7 @@
       </c>
       <c r="R215" s="37">
         <f>IF(OR(G215="",Q215="Fechada",Q215="Perdida"),0,IF(Q215="Previsão vencida",3000,IF(Q215="Parada",2000,1000))+MIN(N(O215),500)+N(F215)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -11734,7 +11745,7 @@
       </c>
       <c r="R216" s="37">
         <f>IF(OR(G216="",Q216="Fechada",Q216="Perdida"),0,IF(Q216="Previsão vencida",3000,IF(Q216="Parada",2000,1000))+MIN(N(O216),500)+N(F216)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -11772,7 +11783,7 @@
       </c>
       <c r="R217" s="37">
         <f>IF(OR(G217="",Q217="Fechada",Q217="Perdida"),0,IF(Q217="Previsão vencida",3000,IF(Q217="Parada",2000,1000))+MIN(N(O217),500)+N(F217)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -11810,7 +11821,7 @@
       </c>
       <c r="R218" s="37">
         <f>IF(OR(G218="",Q218="Fechada",Q218="Perdida"),0,IF(Q218="Previsão vencida",3000,IF(Q218="Parada",2000,1000))+MIN(N(O218),500)+N(F218)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -11848,7 +11859,7 @@
       </c>
       <c r="R219" s="37">
         <f>IF(OR(G219="",Q219="Fechada",Q219="Perdida"),0,IF(Q219="Previsão vencida",3000,IF(Q219="Parada",2000,1000))+MIN(N(O219),500)+N(F219)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -11886,7 +11897,7 @@
       </c>
       <c r="R220" s="37">
         <f>IF(OR(G220="",Q220="Fechada",Q220="Perdida"),0,IF(Q220="Previsão vencida",3000,IF(Q220="Parada",2000,1000))+MIN(N(O220),500)+N(F220)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -11924,7 +11935,7 @@
       </c>
       <c r="R221" s="37">
         <f>IF(OR(G221="",Q221="Fechada",Q221="Perdida"),0,IF(Q221="Previsão vencida",3000,IF(Q221="Parada",2000,1000))+MIN(N(O221),500)+N(F221)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -11962,7 +11973,7 @@
       </c>
       <c r="R222" s="37">
         <f>IF(OR(G222="",Q222="Fechada",Q222="Perdida"),0,IF(Q222="Previsão vencida",3000,IF(Q222="Parada",2000,1000))+MIN(N(O222),500)+N(F222)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -12000,7 +12011,7 @@
       </c>
       <c r="R223" s="37">
         <f>IF(OR(G223="",Q223="Fechada",Q223="Perdida"),0,IF(Q223="Previsão vencida",3000,IF(Q223="Parada",2000,1000))+MIN(N(O223),500)+N(F223)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -12038,7 +12049,7 @@
       </c>
       <c r="R224" s="37">
         <f>IF(OR(G224="",Q224="Fechada",Q224="Perdida"),0,IF(Q224="Previsão vencida",3000,IF(Q224="Parada",2000,1000))+MIN(N(O224),500)+N(F224)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -12076,7 +12087,7 @@
       </c>
       <c r="R225" s="37">
         <f>IF(OR(G225="",Q225="Fechada",Q225="Perdida"),0,IF(Q225="Previsão vencida",3000,IF(Q225="Parada",2000,1000))+MIN(N(O225),500)+N(F225)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -12114,7 +12125,7 @@
       </c>
       <c r="R226" s="37">
         <f>IF(OR(G226="",Q226="Fechada",Q226="Perdida"),0,IF(Q226="Previsão vencida",3000,IF(Q226="Parada",2000,1000))+MIN(N(O226),500)+N(F226)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -12152,7 +12163,7 @@
       </c>
       <c r="R227" s="37">
         <f>IF(OR(G227="",Q227="Fechada",Q227="Perdida"),0,IF(Q227="Previsão vencida",3000,IF(Q227="Parada",2000,1000))+MIN(N(O227),500)+N(F227)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -12190,7 +12201,7 @@
       </c>
       <c r="R228" s="37">
         <f>IF(OR(G228="",Q228="Fechada",Q228="Perdida"),0,IF(Q228="Previsão vencida",3000,IF(Q228="Parada",2000,1000))+MIN(N(O228),500)+N(F228)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -12228,7 +12239,7 @@
       </c>
       <c r="R229" s="37">
         <f>IF(OR(G229="",Q229="Fechada",Q229="Perdida"),0,IF(Q229="Previsão vencida",3000,IF(Q229="Parada",2000,1000))+MIN(N(O229),500)+N(F229)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -12266,7 +12277,7 @@
       </c>
       <c r="R230" s="37">
         <f>IF(OR(G230="",Q230="Fechada",Q230="Perdida"),0,IF(Q230="Previsão vencida",3000,IF(Q230="Parada",2000,1000))+MIN(N(O230),500)+N(F230)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -12304,7 +12315,7 @@
       </c>
       <c r="R231" s="37">
         <f>IF(OR(G231="",Q231="Fechada",Q231="Perdida"),0,IF(Q231="Previsão vencida",3000,IF(Q231="Parada",2000,1000))+MIN(N(O231),500)+N(F231)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -12342,7 +12353,7 @@
       </c>
       <c r="R232" s="37">
         <f>IF(OR(G232="",Q232="Fechada",Q232="Perdida"),0,IF(Q232="Previsão vencida",3000,IF(Q232="Parada",2000,1000))+MIN(N(O232),500)+N(F232)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -12380,7 +12391,7 @@
       </c>
       <c r="R233" s="37">
         <f>IF(OR(G233="",Q233="Fechada",Q233="Perdida"),0,IF(Q233="Previsão vencida",3000,IF(Q233="Parada",2000,1000))+MIN(N(O233),500)+N(F233)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -12418,7 +12429,7 @@
       </c>
       <c r="R234" s="37">
         <f>IF(OR(G234="",Q234="Fechada",Q234="Perdida"),0,IF(Q234="Previsão vencida",3000,IF(Q234="Parada",2000,1000))+MIN(N(O234),500)+N(F234)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -12456,7 +12467,7 @@
       </c>
       <c r="R235" s="37">
         <f>IF(OR(G235="",Q235="Fechada",Q235="Perdida"),0,IF(Q235="Previsão vencida",3000,IF(Q235="Parada",2000,1000))+MIN(N(O235),500)+N(F235)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -12494,7 +12505,7 @@
       </c>
       <c r="R236" s="37">
         <f>IF(OR(G236="",Q236="Fechada",Q236="Perdida"),0,IF(Q236="Previsão vencida",3000,IF(Q236="Parada",2000,1000))+MIN(N(O236),500)+N(F236)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -12532,7 +12543,7 @@
       </c>
       <c r="R237" s="37">
         <f>IF(OR(G237="",Q237="Fechada",Q237="Perdida"),0,IF(Q237="Previsão vencida",3000,IF(Q237="Parada",2000,1000))+MIN(N(O237),500)+N(F237)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -12570,7 +12581,7 @@
       </c>
       <c r="R238" s="37">
         <f>IF(OR(G238="",Q238="Fechada",Q238="Perdida"),0,IF(Q238="Previsão vencida",3000,IF(Q238="Parada",2000,1000))+MIN(N(O238),500)+N(F238)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -12608,7 +12619,7 @@
       </c>
       <c r="R239" s="37">
         <f>IF(OR(G239="",Q239="Fechada",Q239="Perdida"),0,IF(Q239="Previsão vencida",3000,IF(Q239="Parada",2000,1000))+MIN(N(O239),500)+N(F239)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -12646,7 +12657,7 @@
       </c>
       <c r="R240" s="37">
         <f>IF(OR(G240="",Q240="Fechada",Q240="Perdida"),0,IF(Q240="Previsão vencida",3000,IF(Q240="Parada",2000,1000))+MIN(N(O240),500)+N(F240)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -12684,7 +12695,7 @@
       </c>
       <c r="R241" s="37">
         <f>IF(OR(G241="",Q241="Fechada",Q241="Perdida"),0,IF(Q241="Previsão vencida",3000,IF(Q241="Parada",2000,1000))+MIN(N(O241),500)+N(F241)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -12722,7 +12733,7 @@
       </c>
       <c r="R242" s="37">
         <f>IF(OR(G242="",Q242="Fechada",Q242="Perdida"),0,IF(Q242="Previsão vencida",3000,IF(Q242="Parada",2000,1000))+MIN(N(O242),500)+N(F242)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -12760,7 +12771,7 @@
       </c>
       <c r="R243" s="37">
         <f>IF(OR(G243="",Q243="Fechada",Q243="Perdida"),0,IF(Q243="Previsão vencida",3000,IF(Q243="Parada",2000,1000))+MIN(N(O243),500)+N(F243)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -12798,7 +12809,7 @@
       </c>
       <c r="R244" s="37">
         <f>IF(OR(G244="",Q244="Fechada",Q244="Perdida"),0,IF(Q244="Previsão vencida",3000,IF(Q244="Parada",2000,1000))+MIN(N(O244),500)+N(F244)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -12836,7 +12847,7 @@
       </c>
       <c r="R245" s="37">
         <f>IF(OR(G245="",Q245="Fechada",Q245="Perdida"),0,IF(Q245="Previsão vencida",3000,IF(Q245="Parada",2000,1000))+MIN(N(O245),500)+N(F245)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -12874,7 +12885,7 @@
       </c>
       <c r="R246" s="37">
         <f>IF(OR(G246="",Q246="Fechada",Q246="Perdida"),0,IF(Q246="Previsão vencida",3000,IF(Q246="Parada",2000,1000))+MIN(N(O246),500)+N(F246)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -12912,7 +12923,7 @@
       </c>
       <c r="R247" s="37">
         <f>IF(OR(G247="",Q247="Fechada",Q247="Perdida"),0,IF(Q247="Previsão vencida",3000,IF(Q247="Parada",2000,1000))+MIN(N(O247),500)+N(F247)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -12950,7 +12961,7 @@
       </c>
       <c r="R248" s="37">
         <f>IF(OR(G248="",Q248="Fechada",Q248="Perdida"),0,IF(Q248="Previsão vencida",3000,IF(Q248="Parada",2000,1000))+MIN(N(O248),500)+N(F248)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -12988,7 +12999,7 @@
       </c>
       <c r="R249" s="37">
         <f>IF(OR(G249="",Q249="Fechada",Q249="Perdida"),0,IF(Q249="Previsão vencida",3000,IF(Q249="Parada",2000,1000))+MIN(N(O249),500)+N(F249)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -13026,7 +13037,7 @@
       </c>
       <c r="R250" s="37">
         <f>IF(OR(G250="",Q250="Fechada",Q250="Perdida"),0,IF(Q250="Previsão vencida",3000,IF(Q250="Parada",2000,1000))+MIN(N(O250),500)+N(F250)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -13064,7 +13075,7 @@
       </c>
       <c r="R251" s="37">
         <f>IF(OR(G251="",Q251="Fechada",Q251="Perdida"),0,IF(Q251="Previsão vencida",3000,IF(Q251="Parada",2000,1000))+MIN(N(O251),500)+N(F251)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -13102,7 +13113,7 @@
       </c>
       <c r="R252" s="37">
         <f>IF(OR(G252="",Q252="Fechada",Q252="Perdida"),0,IF(Q252="Previsão vencida",3000,IF(Q252="Parada",2000,1000))+MIN(N(O252),500)+N(F252)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -13140,7 +13151,7 @@
       </c>
       <c r="R253" s="37">
         <f>IF(OR(G253="",Q253="Fechada",Q253="Perdida"),0,IF(Q253="Previsão vencida",3000,IF(Q253="Parada",2000,1000))+MIN(N(O253),500)+N(F253)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -13178,7 +13189,7 @@
       </c>
       <c r="R254" s="37">
         <f>IF(OR(G254="",Q254="Fechada",Q254="Perdida"),0,IF(Q254="Previsão vencida",3000,IF(Q254="Parada",2000,1000))+MIN(N(O254),500)+N(F254)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -13216,7 +13227,7 @@
       </c>
       <c r="R255" s="37">
         <f>IF(OR(G255="",Q255="Fechada",Q255="Perdida"),0,IF(Q255="Previsão vencida",3000,IF(Q255="Parada",2000,1000))+MIN(N(O255),500)+N(F255)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -13254,7 +13265,7 @@
       </c>
       <c r="R256" s="37">
         <f>IF(OR(G256="",Q256="Fechada",Q256="Perdida"),0,IF(Q256="Previsão vencida",3000,IF(Q256="Parada",2000,1000))+MIN(N(O256),500)+N(F256)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -13292,7 +13303,7 @@
       </c>
       <c r="R257" s="37">
         <f>IF(OR(G257="",Q257="Fechada",Q257="Perdida"),0,IF(Q257="Previsão vencida",3000,IF(Q257="Parada",2000,1000))+MIN(N(O257),500)+N(F257)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -13330,7 +13341,7 @@
       </c>
       <c r="R258" s="37">
         <f>IF(OR(G258="",Q258="Fechada",Q258="Perdida"),0,IF(Q258="Previsão vencida",3000,IF(Q258="Parada",2000,1000))+MIN(N(O258),500)+N(F258)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -13368,7 +13379,7 @@
       </c>
       <c r="R259" s="37">
         <f>IF(OR(G259="",Q259="Fechada",Q259="Perdida"),0,IF(Q259="Previsão vencida",3000,IF(Q259="Parada",2000,1000))+MIN(N(O259),500)+N(F259)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -13406,7 +13417,7 @@
       </c>
       <c r="R260" s="37">
         <f>IF(OR(G260="",Q260="Fechada",Q260="Perdida"),0,IF(Q260="Previsão vencida",3000,IF(Q260="Parada",2000,1000))+MIN(N(O260),500)+N(F260)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -13444,7 +13455,7 @@
       </c>
       <c r="R261" s="37">
         <f>IF(OR(G261="",Q261="Fechada",Q261="Perdida"),0,IF(Q261="Previsão vencida",3000,IF(Q261="Parada",2000,1000))+MIN(N(O261),500)+N(F261)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -13482,7 +13493,7 @@
       </c>
       <c r="R262" s="37">
         <f>IF(OR(G262="",Q262="Fechada",Q262="Perdida"),0,IF(Q262="Previsão vencida",3000,IF(Q262="Parada",2000,1000))+MIN(N(O262),500)+N(F262)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -13520,7 +13531,7 @@
       </c>
       <c r="R263" s="37">
         <f>IF(OR(G263="",Q263="Fechada",Q263="Perdida"),0,IF(Q263="Previsão vencida",3000,IF(Q263="Parada",2000,1000))+MIN(N(O263),500)+N(F263)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -13558,7 +13569,7 @@
       </c>
       <c r="R264" s="37">
         <f>IF(OR(G264="",Q264="Fechada",Q264="Perdida"),0,IF(Q264="Previsão vencida",3000,IF(Q264="Parada",2000,1000))+MIN(N(O264),500)+N(F264)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -13596,7 +13607,7 @@
       </c>
       <c r="R265" s="37">
         <f>IF(OR(G265="",Q265="Fechada",Q265="Perdida"),0,IF(Q265="Previsão vencida",3000,IF(Q265="Parada",2000,1000))+MIN(N(O265),500)+N(F265)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -13634,7 +13645,7 @@
       </c>
       <c r="R266" s="37">
         <f>IF(OR(G266="",Q266="Fechada",Q266="Perdida"),0,IF(Q266="Previsão vencida",3000,IF(Q266="Parada",2000,1000))+MIN(N(O266),500)+N(F266)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -13672,7 +13683,7 @@
       </c>
       <c r="R267" s="37">
         <f>IF(OR(G267="",Q267="Fechada",Q267="Perdida"),0,IF(Q267="Previsão vencida",3000,IF(Q267="Parada",2000,1000))+MIN(N(O267),500)+N(F267)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -13710,7 +13721,7 @@
       </c>
       <c r="R268" s="37">
         <f>IF(OR(G268="",Q268="Fechada",Q268="Perdida"),0,IF(Q268="Previsão vencida",3000,IF(Q268="Parada",2000,1000))+MIN(N(O268),500)+N(F268)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -13748,7 +13759,7 @@
       </c>
       <c r="R269" s="37">
         <f>IF(OR(G269="",Q269="Fechada",Q269="Perdida"),0,IF(Q269="Previsão vencida",3000,IF(Q269="Parada",2000,1000))+MIN(N(O269),500)+N(F269)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -13786,7 +13797,7 @@
       </c>
       <c r="R270" s="37">
         <f>IF(OR(G270="",Q270="Fechada",Q270="Perdida"),0,IF(Q270="Previsão vencida",3000,IF(Q270="Parada",2000,1000))+MIN(N(O270),500)+N(F270)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -13824,7 +13835,7 @@
       </c>
       <c r="R271" s="37">
         <f>IF(OR(G271="",Q271="Fechada",Q271="Perdida"),0,IF(Q271="Previsão vencida",3000,IF(Q271="Parada",2000,1000))+MIN(N(O271),500)+N(F271)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -13862,7 +13873,7 @@
       </c>
       <c r="R272" s="37">
         <f>IF(OR(G272="",Q272="Fechada",Q272="Perdida"),0,IF(Q272="Previsão vencida",3000,IF(Q272="Parada",2000,1000))+MIN(N(O272),500)+N(F272)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -13900,7 +13911,7 @@
       </c>
       <c r="R273" s="37">
         <f>IF(OR(G273="",Q273="Fechada",Q273="Perdida"),0,IF(Q273="Previsão vencida",3000,IF(Q273="Parada",2000,1000))+MIN(N(O273),500)+N(F273)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -13938,7 +13949,7 @@
       </c>
       <c r="R274" s="37">
         <f>IF(OR(G274="",Q274="Fechada",Q274="Perdida"),0,IF(Q274="Previsão vencida",3000,IF(Q274="Parada",2000,1000))+MIN(N(O274),500)+N(F274)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -13976,7 +13987,7 @@
       </c>
       <c r="R275" s="37">
         <f>IF(OR(G275="",Q275="Fechada",Q275="Perdida"),0,IF(Q275="Previsão vencida",3000,IF(Q275="Parada",2000,1000))+MIN(N(O275),500)+N(F275)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -14014,7 +14025,7 @@
       </c>
       <c r="R276" s="37">
         <f>IF(OR(G276="",Q276="Fechada",Q276="Perdida"),0,IF(Q276="Previsão vencida",3000,IF(Q276="Parada",2000,1000))+MIN(N(O276),500)+N(F276)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -14052,7 +14063,7 @@
       </c>
       <c r="R277" s="37">
         <f>IF(OR(G277="",Q277="Fechada",Q277="Perdida"),0,IF(Q277="Previsão vencida",3000,IF(Q277="Parada",2000,1000))+MIN(N(O277),500)+N(F277)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -14090,7 +14101,7 @@
       </c>
       <c r="R278" s="37">
         <f>IF(OR(G278="",Q278="Fechada",Q278="Perdida"),0,IF(Q278="Previsão vencida",3000,IF(Q278="Parada",2000,1000))+MIN(N(O278),500)+N(F278)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -14128,7 +14139,7 @@
       </c>
       <c r="R279" s="37">
         <f>IF(OR(G279="",Q279="Fechada",Q279="Perdida"),0,IF(Q279="Previsão vencida",3000,IF(Q279="Parada",2000,1000))+MIN(N(O279),500)+N(F279)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -14166,7 +14177,7 @@
       </c>
       <c r="R280" s="37">
         <f>IF(OR(G280="",Q280="Fechada",Q280="Perdida"),0,IF(Q280="Previsão vencida",3000,IF(Q280="Parada",2000,1000))+MIN(N(O280),500)+N(F280)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -14204,7 +14215,7 @@
       </c>
       <c r="R281" s="37">
         <f>IF(OR(G281="",Q281="Fechada",Q281="Perdida"),0,IF(Q281="Previsão vencida",3000,IF(Q281="Parada",2000,1000))+MIN(N(O281),500)+N(F281)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -14242,7 +14253,7 @@
       </c>
       <c r="R282" s="37">
         <f>IF(OR(G282="",Q282="Fechada",Q282="Perdida"),0,IF(Q282="Previsão vencida",3000,IF(Q282="Parada",2000,1000))+MIN(N(O282),500)+N(F282)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -14280,7 +14291,7 @@
       </c>
       <c r="R283" s="37">
         <f>IF(OR(G283="",Q283="Fechada",Q283="Perdida"),0,IF(Q283="Previsão vencida",3000,IF(Q283="Parada",2000,1000))+MIN(N(O283),500)+N(F283)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -14318,7 +14329,7 @@
       </c>
       <c r="R284" s="37">
         <f>IF(OR(G284="",Q284="Fechada",Q284="Perdida"),0,IF(Q284="Previsão vencida",3000,IF(Q284="Parada",2000,1000))+MIN(N(O284),500)+N(F284)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -14356,7 +14367,7 @@
       </c>
       <c r="R285" s="37">
         <f>IF(OR(G285="",Q285="Fechada",Q285="Perdida"),0,IF(Q285="Previsão vencida",3000,IF(Q285="Parada",2000,1000))+MIN(N(O285),500)+N(F285)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -14394,7 +14405,7 @@
       </c>
       <c r="R286" s="37">
         <f>IF(OR(G286="",Q286="Fechada",Q286="Perdida"),0,IF(Q286="Previsão vencida",3000,IF(Q286="Parada",2000,1000))+MIN(N(O286),500)+N(F286)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -14432,7 +14443,7 @@
       </c>
       <c r="R287" s="37">
         <f>IF(OR(G287="",Q287="Fechada",Q287="Perdida"),0,IF(Q287="Previsão vencida",3000,IF(Q287="Parada",2000,1000))+MIN(N(O287),500)+N(F287)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -14470,7 +14481,7 @@
       </c>
       <c r="R288" s="37">
         <f>IF(OR(G288="",Q288="Fechada",Q288="Perdida"),0,IF(Q288="Previsão vencida",3000,IF(Q288="Parada",2000,1000))+MIN(N(O288),500)+N(F288)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -14508,7 +14519,7 @@
       </c>
       <c r="R289" s="37">
         <f>IF(OR(G289="",Q289="Fechada",Q289="Perdida"),0,IF(Q289="Previsão vencida",3000,IF(Q289="Parada",2000,1000))+MIN(N(O289),500)+N(F289)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -14546,7 +14557,7 @@
       </c>
       <c r="R290" s="37">
         <f>IF(OR(G290="",Q290="Fechada",Q290="Perdida"),0,IF(Q290="Previsão vencida",3000,IF(Q290="Parada",2000,1000))+MIN(N(O290),500)+N(F290)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -14584,7 +14595,7 @@
       </c>
       <c r="R291" s="37">
         <f>IF(OR(G291="",Q291="Fechada",Q291="Perdida"),0,IF(Q291="Previsão vencida",3000,IF(Q291="Parada",2000,1000))+MIN(N(O291),500)+N(F291)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -14622,7 +14633,7 @@
       </c>
       <c r="R292" s="37">
         <f>IF(OR(G292="",Q292="Fechada",Q292="Perdida"),0,IF(Q292="Previsão vencida",3000,IF(Q292="Parada",2000,1000))+MIN(N(O292),500)+N(F292)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -14660,7 +14671,7 @@
       </c>
       <c r="R293" s="37">
         <f>IF(OR(G293="",Q293="Fechada",Q293="Perdida"),0,IF(Q293="Previsão vencida",3000,IF(Q293="Parada",2000,1000))+MIN(N(O293),500)+N(F293)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -14698,7 +14709,7 @@
       </c>
       <c r="R294" s="37">
         <f>IF(OR(G294="",Q294="Fechada",Q294="Perdida"),0,IF(Q294="Previsão vencida",3000,IF(Q294="Parada",2000,1000))+MIN(N(O294),500)+N(F294)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -14736,7 +14747,7 @@
       </c>
       <c r="R295" s="37">
         <f>IF(OR(G295="",Q295="Fechada",Q295="Perdida"),0,IF(Q295="Previsão vencida",3000,IF(Q295="Parada",2000,1000))+MIN(N(O295),500)+N(F295)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -14774,7 +14785,7 @@
       </c>
       <c r="R296" s="37">
         <f>IF(OR(G296="",Q296="Fechada",Q296="Perdida"),0,IF(Q296="Previsão vencida",3000,IF(Q296="Parada",2000,1000))+MIN(N(O296),500)+N(F296)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -14812,7 +14823,7 @@
       </c>
       <c r="R297" s="37">
         <f>IF(OR(G297="",Q297="Fechada",Q297="Perdida"),0,IF(Q297="Previsão vencida",3000,IF(Q297="Parada",2000,1000))+MIN(N(O297),500)+N(F297)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -14850,7 +14861,7 @@
       </c>
       <c r="R298" s="37">
         <f>IF(OR(G298="",Q298="Fechada",Q298="Perdida"),0,IF(Q298="Previsão vencida",3000,IF(Q298="Parada",2000,1000))+MIN(N(O298),500)+N(F298)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -14888,7 +14899,7 @@
       </c>
       <c r="R299" s="37">
         <f>IF(OR(G299="",Q299="Fechada",Q299="Perdida"),0,IF(Q299="Previsão vencida",3000,IF(Q299="Parada",2000,1000))+MIN(N(O299),500)+N(F299)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -14926,7 +14937,7 @@
       </c>
       <c r="R300" s="37">
         <f>IF(OR(G300="",Q300="Fechada",Q300="Perdida"),0,IF(Q300="Previsão vencida",3000,IF(Q300="Parada",2000,1000))+MIN(N(O300),500)+N(F300)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -14964,7 +14975,7 @@
       </c>
       <c r="R301" s="37">
         <f>IF(OR(G301="",Q301="Fechada",Q301="Perdida"),0,IF(Q301="Previsão vencida",3000,IF(Q301="Parada",2000,1000))+MIN(N(O301),500)+N(F301)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -15002,7 +15013,7 @@
       </c>
       <c r="R302" s="37">
         <f>IF(OR(G302="",Q302="Fechada",Q302="Perdida"),0,IF(Q302="Previsão vencida",3000,IF(Q302="Parada",2000,1000))+MIN(N(O302),500)+N(F302)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -15040,7 +15051,7 @@
       </c>
       <c r="R303" s="37">
         <f>IF(OR(G303="",Q303="Fechada",Q303="Perdida"),0,IF(Q303="Previsão vencida",3000,IF(Q303="Parada",2000,1000))+MIN(N(O303),500)+N(F303)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -15078,7 +15089,7 @@
       </c>
       <c r="R304" s="37">
         <f>IF(OR(G304="",Q304="Fechada",Q304="Perdida"),0,IF(Q304="Previsão vencida",3000,IF(Q304="Parada",2000,1000))+MIN(N(O304),500)+N(F304)/1000000-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="306">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
@@ -21,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -246,13 +247,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -275,7 +276,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,10 +290,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -303,7 +304,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -826,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -999,17 +1000,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1107,7 +1120,7 @@
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="15">
-        <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,"Fechada",Propostas!$K$5:$K$304,"&gt;="&amp;DATE(YEAR(Config!$B$5),3*INT((MONTH(Config!$B$5)-1)/3)+1,1))</f>
+        <f>SUMIFS(Propostas!$F$5:$F$304,Propostas!$G$5:$G$304,"Fechada",Propostas!$K$5:$K$304,"&gt;="&amp;DATE(YEAR(Config!$B$5),3*INT((MONTH(Config!$B$5)-1)/3)+1,1),Propostas!$K$5:$K$304,"&lt;"&amp;DATE(YEAR(Config!$B$5)+(3*INT((MONTH(Config!$B$5)-1)/3)+4&gt;12),IF(3*INT((MONTH(Config!$B$5)-1)/3)+4&gt;12,1,3*INT((MONTH(Config!$B$5)-1)/3)+4),1))</f>
         <v>53000</v>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -2532,9 +2545,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="32">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B5" s="32" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="6">
@@ -3841,13 +3853,11 @@
       <c r="H16" s="36" t="n">
         <v>46251</v>
       </c>
-      <c r="I16" s="36">
-        <f>TODAY()-4</f>
-        <v>46275.0</v>
-      </c>
-      <c r="J16" s="36">
-        <f>TODAY()+6</f>
-        <v>46285.0</v>
+      <c r="I16" s="36" t="n">
+        <v>46275</v>
+      </c>
+      <c r="J16" s="36" t="n">
+        <v>46285</v>
       </c>
       <c r="K16" s="36" t="n"/>
       <c r="L16" s="31" t="n"/>
@@ -3913,13 +3923,11 @@
       <c r="H17" s="36" t="n">
         <v>46258</v>
       </c>
-      <c r="I17" s="36">
-        <f>TODAY()-17</f>
-        <v>46262.0</v>
-      </c>
-      <c r="J17" s="36">
-        <f>TODAY()-2</f>
-        <v>46277.0</v>
+      <c r="I17" s="36" t="n">
+        <v>46262</v>
+      </c>
+      <c r="J17" s="36" t="n">
+        <v>46277</v>
       </c>
       <c r="K17" s="36" t="n"/>
       <c r="L17" s="31" t="n"/>
@@ -3985,13 +3993,11 @@
       <c r="H18" s="36" t="n">
         <v>46260</v>
       </c>
-      <c r="I18" s="36">
-        <f>TODAY()-16</f>
-        <v>46263.0</v>
-      </c>
-      <c r="J18" s="36">
-        <f>TODAY()+12</f>
-        <v>46291.0</v>
+      <c r="I18" s="36" t="n">
+        <v>46263</v>
+      </c>
+      <c r="J18" s="36" t="n">
+        <v>46291</v>
       </c>
       <c r="K18" s="36" t="n"/>
       <c r="L18" s="31" t="n"/>
@@ -4057,13 +4063,11 @@
       <c r="H19" s="36" t="n">
         <v>46262</v>
       </c>
-      <c r="I19" s="36">
-        <f>TODAY()-14</f>
-        <v>46265.0</v>
-      </c>
-      <c r="J19" s="36">
-        <f>TODAY()-6</f>
-        <v>46273.0</v>
+      <c r="I19" s="36" t="n">
+        <v>46265</v>
+      </c>
+      <c r="J19" s="36" t="n">
+        <v>46273</v>
       </c>
       <c r="K19" s="36" t="n"/>
       <c r="L19" s="31" t="n"/>
@@ -4129,13 +4133,11 @@
       <c r="H20" s="36" t="n">
         <v>46267</v>
       </c>
-      <c r="I20" s="36">
-        <f>TODAY()-3</f>
-        <v>46276.0</v>
-      </c>
-      <c r="J20" s="36">
-        <f>TODAY()+20</f>
-        <v>46299.0</v>
+      <c r="I20" s="36" t="n">
+        <v>46276</v>
+      </c>
+      <c r="J20" s="36" t="n">
+        <v>46299</v>
       </c>
       <c r="K20" s="36" t="n"/>
       <c r="L20" s="31" t="n"/>
@@ -4201,13 +4203,11 @@
       <c r="H21" s="36" t="n">
         <v>46269</v>
       </c>
-      <c r="I21" s="36">
-        <f>TODAY()-2</f>
-        <v>46277.0</v>
-      </c>
-      <c r="J21" s="36">
-        <f>TODAY()+25</f>
-        <v>46304.0</v>
+      <c r="I21" s="36" t="n">
+        <v>46277</v>
+      </c>
+      <c r="J21" s="36" t="n">
+        <v>46304</v>
       </c>
       <c r="K21" s="36" t="n"/>
       <c r="L21" s="31" t="n"/>
@@ -4273,13 +4273,11 @@
       <c r="H22" s="36" t="n">
         <v>46274</v>
       </c>
-      <c r="I22" s="36">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
-      </c>
-      <c r="J22" s="36">
-        <f>TODAY()+30</f>
-        <v>46309.0</v>
+      <c r="I22" s="36" t="n">
+        <v>46278</v>
+      </c>
+      <c r="J22" s="36" t="n">
+        <v>46309</v>
       </c>
       <c r="K22" s="36" t="n"/>
       <c r="L22" s="31" t="n"/>
@@ -4345,13 +4343,11 @@
       <c r="H23" s="36" t="n">
         <v>46274</v>
       </c>
-      <c r="I23" s="36">
-        <f>TODAY()</f>
-        <v>46279.0</v>
-      </c>
-      <c r="J23" s="36">
-        <f>TODAY()+15</f>
-        <v>46294.0</v>
+      <c r="I23" s="36" t="n">
+        <v>46279</v>
+      </c>
+      <c r="J23" s="36" t="n">
+        <v>46294</v>
       </c>
       <c r="K23" s="36" t="n"/>
       <c r="L23" s="31" t="n"/>
@@ -4417,13 +4413,11 @@
       <c r="H24" s="36" t="n">
         <v>46276</v>
       </c>
-      <c r="I24" s="36">
-        <f>TODAY()-3</f>
-        <v>46276.0</v>
-      </c>
-      <c r="J24" s="36">
-        <f>TODAY()+35</f>
-        <v>46314.0</v>
+      <c r="I24" s="36" t="n">
+        <v>46276</v>
+      </c>
+      <c r="J24" s="36" t="n">
+        <v>46314</v>
       </c>
       <c r="K24" s="36" t="n"/>
       <c r="L24" s="31" t="n"/>
@@ -15129,10 +15123,10 @@
     <dataValidation sqref="B5:B304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$A$18,0,0,MAX(1,COUNTA(Config!$A$18:$A$27)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$I$18,0,0,MAX(1,COUNTA(Config!$I$18:$I$27)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$C$18,0,0,MAX(1,COUNTA(Config!$C$18:$C$27)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -15141,13 +15135,13 @@
     <dataValidation sqref="G5:G304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$A$10:$A$15</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L5:L304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$E$18,0,0,MAX(1,COUNTA(Config!$E$18:$E$27)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:K304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:K304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5:F304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
@@ -988,7 +988,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2861,6 +2861,13 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Discussão de contrato de prestação de serviços</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
@@ -3076,7 +3083,7 @@
         <v>Fechada</v>
       </c>
       <c r="R5" s="37">
-        <f>IF(OR(G5="",Q5="Fechada",Q5="Perdida"),0,IF(Q5="Previsão vencida",3000,IF(Q5="Parada",2000,1000))+MIN(N(O5),500)+N(F5)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G5="",Q5="Fechada",Q5="Perdida"),0,IF(Q5="Previsão vencida",3,IF(Q5="Parada",2,1))*1E+13+MIN(N(O5),500)*1E+10+MIN(ROUND(N(F5),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3148,7 +3155,7 @@
         <v>Fechada</v>
       </c>
       <c r="R6" s="37">
-        <f>IF(OR(G6="",Q6="Fechada",Q6="Perdida"),0,IF(Q6="Previsão vencida",3000,IF(Q6="Parada",2000,1000))+MIN(N(O6),500)+N(F6)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G6="",Q6="Fechada",Q6="Perdida"),0,IF(Q6="Previsão vencida",3,IF(Q6="Parada",2,1))*1E+13+MIN(N(O6),500)*1E+10+MIN(ROUND(N(F6),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3220,7 +3227,7 @@
         <v>Fechada</v>
       </c>
       <c r="R7" s="37">
-        <f>IF(OR(G7="",Q7="Fechada",Q7="Perdida"),0,IF(Q7="Previsão vencida",3000,IF(Q7="Parada",2000,1000))+MIN(N(O7),500)+N(F7)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G7="",Q7="Fechada",Q7="Perdida"),0,IF(Q7="Previsão vencida",3,IF(Q7="Parada",2,1))*1E+13+MIN(N(O7),500)*1E+10+MIN(ROUND(N(F7),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3292,7 +3299,7 @@
         <v>Fechada</v>
       </c>
       <c r="R8" s="37">
-        <f>IF(OR(G8="",Q8="Fechada",Q8="Perdida"),0,IF(Q8="Previsão vencida",3000,IF(Q8="Parada",2000,1000))+MIN(N(O8),500)+N(F8)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G8="",Q8="Fechada",Q8="Perdida"),0,IF(Q8="Previsão vencida",3,IF(Q8="Parada",2,1))*1E+13+MIN(N(O8),500)*1E+10+MIN(ROUND(N(F8),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3364,7 +3371,7 @@
         <v>Fechada</v>
       </c>
       <c r="R9" s="37">
-        <f>IF(OR(G9="",Q9="Fechada",Q9="Perdida"),0,IF(Q9="Previsão vencida",3000,IF(Q9="Parada",2000,1000))+MIN(N(O9),500)+N(F9)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G9="",Q9="Fechada",Q9="Perdida"),0,IF(Q9="Previsão vencida",3,IF(Q9="Parada",2,1))*1E+13+MIN(N(O9),500)*1E+10+MIN(ROUND(N(F9),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3440,7 +3447,7 @@
         <v>Perdida</v>
       </c>
       <c r="R10" s="37">
-        <f>IF(OR(G10="",Q10="Fechada",Q10="Perdida"),0,IF(Q10="Previsão vencida",3000,IF(Q10="Parada",2000,1000))+MIN(N(O10),500)+N(F10)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G10="",Q10="Fechada",Q10="Perdida"),0,IF(Q10="Previsão vencida",3,IF(Q10="Parada",2,1))*1E+13+MIN(N(O10),500)*1E+10+MIN(ROUND(N(F10),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3516,7 +3523,7 @@
         <v>Perdida</v>
       </c>
       <c r="R11" s="37">
-        <f>IF(OR(G11="",Q11="Fechada",Q11="Perdida"),0,IF(Q11="Previsão vencida",3000,IF(Q11="Parada",2000,1000))+MIN(N(O11),500)+N(F11)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G11="",Q11="Fechada",Q11="Perdida"),0,IF(Q11="Previsão vencida",3,IF(Q11="Parada",2,1))*1E+13+MIN(N(O11),500)*1E+10+MIN(ROUND(N(F11),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3588,7 +3595,7 @@
         <v>Fechada</v>
       </c>
       <c r="R12" s="37">
-        <f>IF(OR(G12="",Q12="Fechada",Q12="Perdida"),0,IF(Q12="Previsão vencida",3000,IF(Q12="Parada",2000,1000))+MIN(N(O12),500)+N(F12)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G12="",Q12="Fechada",Q12="Perdida"),0,IF(Q12="Previsão vencida",3,IF(Q12="Parada",2,1))*1E+13+MIN(N(O12),500)*1E+10+MIN(ROUND(N(F12),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3660,7 +3667,7 @@
         <v>Fechada</v>
       </c>
       <c r="R13" s="37">
-        <f>IF(OR(G13="",Q13="Fechada",Q13="Perdida"),0,IF(Q13="Previsão vencida",3000,IF(Q13="Parada",2000,1000))+MIN(N(O13),500)+N(F13)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G13="",Q13="Fechada",Q13="Perdida"),0,IF(Q13="Previsão vencida",3,IF(Q13="Parada",2,1))*1E+13+MIN(N(O13),500)*1E+10+MIN(ROUND(N(F13),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3736,7 +3743,7 @@
         <v>Perdida</v>
       </c>
       <c r="R14" s="37">
-        <f>IF(OR(G14="",Q14="Fechada",Q14="Perdida"),0,IF(Q14="Previsão vencida",3000,IF(Q14="Parada",2000,1000))+MIN(N(O14),500)+N(F14)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G14="",Q14="Fechada",Q14="Perdida"),0,IF(Q14="Previsão vencida",3,IF(Q14="Parada",2,1))*1E+13+MIN(N(O14),500)*1E+10+MIN(ROUND(N(F14),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3812,7 +3819,7 @@
         <v>Perdida</v>
       </c>
       <c r="R15" s="37">
-        <f>IF(OR(G15="",Q15="Fechada",Q15="Perdida"),0,IF(Q15="Previsão vencida",3000,IF(Q15="Parada",2000,1000))+MIN(N(O15),500)+N(F15)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G15="",Q15="Fechada",Q15="Perdida"),0,IF(Q15="Previsão vencida",3,IF(Q15="Parada",2,1))*1E+13+MIN(N(O15),500)*1E+10+MIN(ROUND(N(F15),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3882,8 +3889,8 @@
         <v>Ativa</v>
       </c>
       <c r="R16" s="37">
-        <f>IF(OR(G16="",Q16="Fechada",Q16="Perdida"),0,IF(Q16="Previsão vencida",3000,IF(Q16="Parada",2000,1000))+MIN(N(O16),500)+N(F16)/1000000-ROW()/100000)</f>
-        <v>1004.01424</v>
+        <f>IF(OR(G16="",Q16="Fechada",Q16="Perdida"),0,IF(Q16="Previsão vencida",3,IF(Q16="Parada",2,1))*1E+13+MIN(N(O16),500)*1E+10+MIN(ROUND(N(F16),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10040144000289</v>
       </c>
     </row>
     <row r="17">
@@ -3952,8 +3959,8 @@
         <v>Previsão vencida</v>
       </c>
       <c r="R17" s="37">
-        <f>IF(OR(G17="",Q17="Fechada",Q17="Perdida"),0,IF(Q17="Previsão vencida",3000,IF(Q17="Parada",2000,1000))+MIN(N(O17),500)+N(F17)/1000000-ROW()/100000)</f>
-        <v>3017.00663</v>
+        <f>IF(OR(G17="",Q17="Fechada",Q17="Perdida"),0,IF(Q17="Previsão vencida",3,IF(Q17="Parada",2,1))*1E+13+MIN(N(O17),500)*1E+10+MIN(ROUND(N(F17),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>30170068000288</v>
       </c>
     </row>
     <row r="18">
@@ -4022,8 +4029,8 @@
         <v>Parada</v>
       </c>
       <c r="R18" s="37">
-        <f>IF(OR(G18="",Q18="Fechada",Q18="Perdida"),0,IF(Q18="Previsão vencida",3000,IF(Q18="Parada",2000,1000))+MIN(N(O18),500)+N(F18)/1000000-ROW()/100000)</f>
-        <v>2016.01032</v>
+        <f>IF(OR(G18="",Q18="Fechada",Q18="Perdida"),0,IF(Q18="Previsão vencida",3,IF(Q18="Parada",2,1))*1E+13+MIN(N(O18),500)*1E+10+MIN(ROUND(N(F18),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>20160105000287</v>
       </c>
     </row>
     <row r="19">
@@ -4092,8 +4099,8 @@
         <v>Previsão vencida</v>
       </c>
       <c r="R19" s="37">
-        <f>IF(OR(G19="",Q19="Fechada",Q19="Perdida"),0,IF(Q19="Previsão vencida",3000,IF(Q19="Parada",2000,1000))+MIN(N(O19),500)+N(F19)/1000000-ROW()/100000)</f>
-        <v>3014.00401</v>
+        <f>IF(OR(G19="",Q19="Fechada",Q19="Perdida"),0,IF(Q19="Previsão vencida",3,IF(Q19="Parada",2,1))*1E+13+MIN(N(O19),500)*1E+10+MIN(ROUND(N(F19),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>30140042000286</v>
       </c>
     </row>
     <row r="20">
@@ -4162,8 +4169,8 @@
         <v>Ativa</v>
       </c>
       <c r="R20" s="37">
-        <f>IF(OR(G20="",Q20="Fechada",Q20="Perdida"),0,IF(Q20="Previsão vencida",3000,IF(Q20="Parada",2000,1000))+MIN(N(O20),500)+N(F20)/1000000-ROW()/100000)</f>
-        <v>1003.0056</v>
+        <f>IF(OR(G20="",Q20="Fechada",Q20="Perdida"),0,IF(Q20="Previsão vencida",3,IF(Q20="Parada",2,1))*1E+13+MIN(N(O20),500)*1E+10+MIN(ROUND(N(F20),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10030058000285</v>
       </c>
     </row>
     <row r="21">
@@ -4232,8 +4239,8 @@
         <v>Ativa</v>
       </c>
       <c r="R21" s="37">
-        <f>IF(OR(G21="",Q21="Fechada",Q21="Perdida"),0,IF(Q21="Previsão vencida",3000,IF(Q21="Parada",2000,1000))+MIN(N(O21),500)+N(F21)/1000000-ROW()/100000)</f>
-        <v>1002.00769</v>
+        <f>IF(OR(G21="",Q21="Fechada",Q21="Perdida"),0,IF(Q21="Previsão vencida",3,IF(Q21="Parada",2,1))*1E+13+MIN(N(O21),500)*1E+10+MIN(ROUND(N(F21),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10020079000284</v>
       </c>
     </row>
     <row r="22">
@@ -4302,8 +4309,8 @@
         <v>Ativa</v>
       </c>
       <c r="R22" s="37">
-        <f>IF(OR(G22="",Q22="Fechada",Q22="Perdida"),0,IF(Q22="Previsão vencida",3000,IF(Q22="Parada",2000,1000))+MIN(N(O22),500)+N(F22)/1000000-ROW()/100000)</f>
-        <v>1001.01298</v>
+        <f>IF(OR(G22="",Q22="Fechada",Q22="Perdida"),0,IF(Q22="Previsão vencida",3,IF(Q22="Parada",2,1))*1E+13+MIN(N(O22),500)*1E+10+MIN(ROUND(N(F22),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10010132000283</v>
       </c>
     </row>
     <row r="23">
@@ -4372,8 +4379,8 @@
         <v>Ativa</v>
       </c>
       <c r="R23" s="37">
-        <f>IF(OR(G23="",Q23="Fechada",Q23="Perdida"),0,IF(Q23="Previsão vencida",3000,IF(Q23="Parada",2000,1000))+MIN(N(O23),500)+N(F23)/1000000-ROW()/100000)</f>
-        <v>1000.00427</v>
+        <f>IF(OR(G23="",Q23="Fechada",Q23="Perdida"),0,IF(Q23="Previsão vencida",3,IF(Q23="Parada",2,1))*1E+13+MIN(N(O23),500)*1E+10+MIN(ROUND(N(F23),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10000045000282</v>
       </c>
     </row>
     <row r="24">
@@ -4442,8 +4449,8 @@
         <v>Ativa</v>
       </c>
       <c r="R24" s="37">
-        <f>IF(OR(G24="",Q24="Fechada",Q24="Perdida"),0,IF(Q24="Previsão vencida",3000,IF(Q24="Parada",2000,1000))+MIN(N(O24),500)+N(F24)/1000000-ROW()/100000)</f>
-        <v>1003.00536</v>
+        <f>IF(OR(G24="",Q24="Fechada",Q24="Perdida"),0,IF(Q24="Previsão vencida",3,IF(Q24="Parada",2,1))*1E+13+MIN(N(O24),500)*1E+10+MIN(ROUND(N(F24),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10030056000281</v>
       </c>
     </row>
     <row r="25">
@@ -4480,7 +4487,7 @@
         <v/>
       </c>
       <c r="R25" s="37">
-        <f>IF(OR(G25="",Q25="Fechada",Q25="Perdida"),0,IF(Q25="Previsão vencida",3000,IF(Q25="Parada",2000,1000))+MIN(N(O25),500)+N(F25)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G25="",Q25="Fechada",Q25="Perdida"),0,IF(Q25="Previsão vencida",3,IF(Q25="Parada",2,1))*1E+13+MIN(N(O25),500)*1E+10+MIN(ROUND(N(F25),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4518,7 +4525,7 @@
         <v/>
       </c>
       <c r="R26" s="37">
-        <f>IF(OR(G26="",Q26="Fechada",Q26="Perdida"),0,IF(Q26="Previsão vencida",3000,IF(Q26="Parada",2000,1000))+MIN(N(O26),500)+N(F26)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G26="",Q26="Fechada",Q26="Perdida"),0,IF(Q26="Previsão vencida",3,IF(Q26="Parada",2,1))*1E+13+MIN(N(O26),500)*1E+10+MIN(ROUND(N(F26),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4556,7 +4563,7 @@
         <v/>
       </c>
       <c r="R27" s="37">
-        <f>IF(OR(G27="",Q27="Fechada",Q27="Perdida"),0,IF(Q27="Previsão vencida",3000,IF(Q27="Parada",2000,1000))+MIN(N(O27),500)+N(F27)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G27="",Q27="Fechada",Q27="Perdida"),0,IF(Q27="Previsão vencida",3,IF(Q27="Parada",2,1))*1E+13+MIN(N(O27),500)*1E+10+MIN(ROUND(N(F27),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4594,7 +4601,7 @@
         <v/>
       </c>
       <c r="R28" s="37">
-        <f>IF(OR(G28="",Q28="Fechada",Q28="Perdida"),0,IF(Q28="Previsão vencida",3000,IF(Q28="Parada",2000,1000))+MIN(N(O28),500)+N(F28)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G28="",Q28="Fechada",Q28="Perdida"),0,IF(Q28="Previsão vencida",3,IF(Q28="Parada",2,1))*1E+13+MIN(N(O28),500)*1E+10+MIN(ROUND(N(F28),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4632,7 +4639,7 @@
         <v/>
       </c>
       <c r="R29" s="37">
-        <f>IF(OR(G29="",Q29="Fechada",Q29="Perdida"),0,IF(Q29="Previsão vencida",3000,IF(Q29="Parada",2000,1000))+MIN(N(O29),500)+N(F29)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G29="",Q29="Fechada",Q29="Perdida"),0,IF(Q29="Previsão vencida",3,IF(Q29="Parada",2,1))*1E+13+MIN(N(O29),500)*1E+10+MIN(ROUND(N(F29),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4670,7 +4677,7 @@
         <v/>
       </c>
       <c r="R30" s="37">
-        <f>IF(OR(G30="",Q30="Fechada",Q30="Perdida"),0,IF(Q30="Previsão vencida",3000,IF(Q30="Parada",2000,1000))+MIN(N(O30),500)+N(F30)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G30="",Q30="Fechada",Q30="Perdida"),0,IF(Q30="Previsão vencida",3,IF(Q30="Parada",2,1))*1E+13+MIN(N(O30),500)*1E+10+MIN(ROUND(N(F30),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4708,7 +4715,7 @@
         <v/>
       </c>
       <c r="R31" s="37">
-        <f>IF(OR(G31="",Q31="Fechada",Q31="Perdida"),0,IF(Q31="Previsão vencida",3000,IF(Q31="Parada",2000,1000))+MIN(N(O31),500)+N(F31)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G31="",Q31="Fechada",Q31="Perdida"),0,IF(Q31="Previsão vencida",3,IF(Q31="Parada",2,1))*1E+13+MIN(N(O31),500)*1E+10+MIN(ROUND(N(F31),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4746,7 +4753,7 @@
         <v/>
       </c>
       <c r="R32" s="37">
-        <f>IF(OR(G32="",Q32="Fechada",Q32="Perdida"),0,IF(Q32="Previsão vencida",3000,IF(Q32="Parada",2000,1000))+MIN(N(O32),500)+N(F32)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G32="",Q32="Fechada",Q32="Perdida"),0,IF(Q32="Previsão vencida",3,IF(Q32="Parada",2,1))*1E+13+MIN(N(O32),500)*1E+10+MIN(ROUND(N(F32),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4784,7 +4791,7 @@
         <v/>
       </c>
       <c r="R33" s="37">
-        <f>IF(OR(G33="",Q33="Fechada",Q33="Perdida"),0,IF(Q33="Previsão vencida",3000,IF(Q33="Parada",2000,1000))+MIN(N(O33),500)+N(F33)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G33="",Q33="Fechada",Q33="Perdida"),0,IF(Q33="Previsão vencida",3,IF(Q33="Parada",2,1))*1E+13+MIN(N(O33),500)*1E+10+MIN(ROUND(N(F33),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4822,7 +4829,7 @@
         <v/>
       </c>
       <c r="R34" s="37">
-        <f>IF(OR(G34="",Q34="Fechada",Q34="Perdida"),0,IF(Q34="Previsão vencida",3000,IF(Q34="Parada",2000,1000))+MIN(N(O34),500)+N(F34)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G34="",Q34="Fechada",Q34="Perdida"),0,IF(Q34="Previsão vencida",3,IF(Q34="Parada",2,1))*1E+13+MIN(N(O34),500)*1E+10+MIN(ROUND(N(F34),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4860,7 +4867,7 @@
         <v/>
       </c>
       <c r="R35" s="37">
-        <f>IF(OR(G35="",Q35="Fechada",Q35="Perdida"),0,IF(Q35="Previsão vencida",3000,IF(Q35="Parada",2000,1000))+MIN(N(O35),500)+N(F35)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G35="",Q35="Fechada",Q35="Perdida"),0,IF(Q35="Previsão vencida",3,IF(Q35="Parada",2,1))*1E+13+MIN(N(O35),500)*1E+10+MIN(ROUND(N(F35),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4898,7 +4905,7 @@
         <v/>
       </c>
       <c r="R36" s="37">
-        <f>IF(OR(G36="",Q36="Fechada",Q36="Perdida"),0,IF(Q36="Previsão vencida",3000,IF(Q36="Parada",2000,1000))+MIN(N(O36),500)+N(F36)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G36="",Q36="Fechada",Q36="Perdida"),0,IF(Q36="Previsão vencida",3,IF(Q36="Parada",2,1))*1E+13+MIN(N(O36),500)*1E+10+MIN(ROUND(N(F36),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4936,7 +4943,7 @@
         <v/>
       </c>
       <c r="R37" s="37">
-        <f>IF(OR(G37="",Q37="Fechada",Q37="Perdida"),0,IF(Q37="Previsão vencida",3000,IF(Q37="Parada",2000,1000))+MIN(N(O37),500)+N(F37)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G37="",Q37="Fechada",Q37="Perdida"),0,IF(Q37="Previsão vencida",3,IF(Q37="Parada",2,1))*1E+13+MIN(N(O37),500)*1E+10+MIN(ROUND(N(F37),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4974,7 +4981,7 @@
         <v/>
       </c>
       <c r="R38" s="37">
-        <f>IF(OR(G38="",Q38="Fechada",Q38="Perdida"),0,IF(Q38="Previsão vencida",3000,IF(Q38="Parada",2000,1000))+MIN(N(O38),500)+N(F38)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G38="",Q38="Fechada",Q38="Perdida"),0,IF(Q38="Previsão vencida",3,IF(Q38="Parada",2,1))*1E+13+MIN(N(O38),500)*1E+10+MIN(ROUND(N(F38),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5012,7 +5019,7 @@
         <v/>
       </c>
       <c r="R39" s="37">
-        <f>IF(OR(G39="",Q39="Fechada",Q39="Perdida"),0,IF(Q39="Previsão vencida",3000,IF(Q39="Parada",2000,1000))+MIN(N(O39),500)+N(F39)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G39="",Q39="Fechada",Q39="Perdida"),0,IF(Q39="Previsão vencida",3,IF(Q39="Parada",2,1))*1E+13+MIN(N(O39),500)*1E+10+MIN(ROUND(N(F39),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5050,7 +5057,7 @@
         <v/>
       </c>
       <c r="R40" s="37">
-        <f>IF(OR(G40="",Q40="Fechada",Q40="Perdida"),0,IF(Q40="Previsão vencida",3000,IF(Q40="Parada",2000,1000))+MIN(N(O40),500)+N(F40)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G40="",Q40="Fechada",Q40="Perdida"),0,IF(Q40="Previsão vencida",3,IF(Q40="Parada",2,1))*1E+13+MIN(N(O40),500)*1E+10+MIN(ROUND(N(F40),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5088,7 +5095,7 @@
         <v/>
       </c>
       <c r="R41" s="37">
-        <f>IF(OR(G41="",Q41="Fechada",Q41="Perdida"),0,IF(Q41="Previsão vencida",3000,IF(Q41="Parada",2000,1000))+MIN(N(O41),500)+N(F41)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G41="",Q41="Fechada",Q41="Perdida"),0,IF(Q41="Previsão vencida",3,IF(Q41="Parada",2,1))*1E+13+MIN(N(O41),500)*1E+10+MIN(ROUND(N(F41),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5126,7 +5133,7 @@
         <v/>
       </c>
       <c r="R42" s="37">
-        <f>IF(OR(G42="",Q42="Fechada",Q42="Perdida"),0,IF(Q42="Previsão vencida",3000,IF(Q42="Parada",2000,1000))+MIN(N(O42),500)+N(F42)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G42="",Q42="Fechada",Q42="Perdida"),0,IF(Q42="Previsão vencida",3,IF(Q42="Parada",2,1))*1E+13+MIN(N(O42),500)*1E+10+MIN(ROUND(N(F42),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5164,7 +5171,7 @@
         <v/>
       </c>
       <c r="R43" s="37">
-        <f>IF(OR(G43="",Q43="Fechada",Q43="Perdida"),0,IF(Q43="Previsão vencida",3000,IF(Q43="Parada",2000,1000))+MIN(N(O43),500)+N(F43)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G43="",Q43="Fechada",Q43="Perdida"),0,IF(Q43="Previsão vencida",3,IF(Q43="Parada",2,1))*1E+13+MIN(N(O43),500)*1E+10+MIN(ROUND(N(F43),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5202,7 +5209,7 @@
         <v/>
       </c>
       <c r="R44" s="37">
-        <f>IF(OR(G44="",Q44="Fechada",Q44="Perdida"),0,IF(Q44="Previsão vencida",3000,IF(Q44="Parada",2000,1000))+MIN(N(O44),500)+N(F44)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G44="",Q44="Fechada",Q44="Perdida"),0,IF(Q44="Previsão vencida",3,IF(Q44="Parada",2,1))*1E+13+MIN(N(O44),500)*1E+10+MIN(ROUND(N(F44),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5240,7 +5247,7 @@
         <v/>
       </c>
       <c r="R45" s="37">
-        <f>IF(OR(G45="",Q45="Fechada",Q45="Perdida"),0,IF(Q45="Previsão vencida",3000,IF(Q45="Parada",2000,1000))+MIN(N(O45),500)+N(F45)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G45="",Q45="Fechada",Q45="Perdida"),0,IF(Q45="Previsão vencida",3,IF(Q45="Parada",2,1))*1E+13+MIN(N(O45),500)*1E+10+MIN(ROUND(N(F45),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5278,7 +5285,7 @@
         <v/>
       </c>
       <c r="R46" s="37">
-        <f>IF(OR(G46="",Q46="Fechada",Q46="Perdida"),0,IF(Q46="Previsão vencida",3000,IF(Q46="Parada",2000,1000))+MIN(N(O46),500)+N(F46)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G46="",Q46="Fechada",Q46="Perdida"),0,IF(Q46="Previsão vencida",3,IF(Q46="Parada",2,1))*1E+13+MIN(N(O46),500)*1E+10+MIN(ROUND(N(F46),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5316,7 +5323,7 @@
         <v/>
       </c>
       <c r="R47" s="37">
-        <f>IF(OR(G47="",Q47="Fechada",Q47="Perdida"),0,IF(Q47="Previsão vencida",3000,IF(Q47="Parada",2000,1000))+MIN(N(O47),500)+N(F47)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G47="",Q47="Fechada",Q47="Perdida"),0,IF(Q47="Previsão vencida",3,IF(Q47="Parada",2,1))*1E+13+MIN(N(O47),500)*1E+10+MIN(ROUND(N(F47),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5354,7 +5361,7 @@
         <v/>
       </c>
       <c r="R48" s="37">
-        <f>IF(OR(G48="",Q48="Fechada",Q48="Perdida"),0,IF(Q48="Previsão vencida",3000,IF(Q48="Parada",2000,1000))+MIN(N(O48),500)+N(F48)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G48="",Q48="Fechada",Q48="Perdida"),0,IF(Q48="Previsão vencida",3,IF(Q48="Parada",2,1))*1E+13+MIN(N(O48),500)*1E+10+MIN(ROUND(N(F48),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5392,7 +5399,7 @@
         <v/>
       </c>
       <c r="R49" s="37">
-        <f>IF(OR(G49="",Q49="Fechada",Q49="Perdida"),0,IF(Q49="Previsão vencida",3000,IF(Q49="Parada",2000,1000))+MIN(N(O49),500)+N(F49)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G49="",Q49="Fechada",Q49="Perdida"),0,IF(Q49="Previsão vencida",3,IF(Q49="Parada",2,1))*1E+13+MIN(N(O49),500)*1E+10+MIN(ROUND(N(F49),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5430,7 +5437,7 @@
         <v/>
       </c>
       <c r="R50" s="37">
-        <f>IF(OR(G50="",Q50="Fechada",Q50="Perdida"),0,IF(Q50="Previsão vencida",3000,IF(Q50="Parada",2000,1000))+MIN(N(O50),500)+N(F50)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G50="",Q50="Fechada",Q50="Perdida"),0,IF(Q50="Previsão vencida",3,IF(Q50="Parada",2,1))*1E+13+MIN(N(O50),500)*1E+10+MIN(ROUND(N(F50),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5468,7 +5475,7 @@
         <v/>
       </c>
       <c r="R51" s="37">
-        <f>IF(OR(G51="",Q51="Fechada",Q51="Perdida"),0,IF(Q51="Previsão vencida",3000,IF(Q51="Parada",2000,1000))+MIN(N(O51),500)+N(F51)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G51="",Q51="Fechada",Q51="Perdida"),0,IF(Q51="Previsão vencida",3,IF(Q51="Parada",2,1))*1E+13+MIN(N(O51),500)*1E+10+MIN(ROUND(N(F51),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5506,7 +5513,7 @@
         <v/>
       </c>
       <c r="R52" s="37">
-        <f>IF(OR(G52="",Q52="Fechada",Q52="Perdida"),0,IF(Q52="Previsão vencida",3000,IF(Q52="Parada",2000,1000))+MIN(N(O52),500)+N(F52)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G52="",Q52="Fechada",Q52="Perdida"),0,IF(Q52="Previsão vencida",3,IF(Q52="Parada",2,1))*1E+13+MIN(N(O52),500)*1E+10+MIN(ROUND(N(F52),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5544,7 +5551,7 @@
         <v/>
       </c>
       <c r="R53" s="37">
-        <f>IF(OR(G53="",Q53="Fechada",Q53="Perdida"),0,IF(Q53="Previsão vencida",3000,IF(Q53="Parada",2000,1000))+MIN(N(O53),500)+N(F53)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G53="",Q53="Fechada",Q53="Perdida"),0,IF(Q53="Previsão vencida",3,IF(Q53="Parada",2,1))*1E+13+MIN(N(O53),500)*1E+10+MIN(ROUND(N(F53),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5582,7 +5589,7 @@
         <v/>
       </c>
       <c r="R54" s="37">
-        <f>IF(OR(G54="",Q54="Fechada",Q54="Perdida"),0,IF(Q54="Previsão vencida",3000,IF(Q54="Parada",2000,1000))+MIN(N(O54),500)+N(F54)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G54="",Q54="Fechada",Q54="Perdida"),0,IF(Q54="Previsão vencida",3,IF(Q54="Parada",2,1))*1E+13+MIN(N(O54),500)*1E+10+MIN(ROUND(N(F54),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5620,7 +5627,7 @@
         <v/>
       </c>
       <c r="R55" s="37">
-        <f>IF(OR(G55="",Q55="Fechada",Q55="Perdida"),0,IF(Q55="Previsão vencida",3000,IF(Q55="Parada",2000,1000))+MIN(N(O55),500)+N(F55)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G55="",Q55="Fechada",Q55="Perdida"),0,IF(Q55="Previsão vencida",3,IF(Q55="Parada",2,1))*1E+13+MIN(N(O55),500)*1E+10+MIN(ROUND(N(F55),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5658,7 +5665,7 @@
         <v/>
       </c>
       <c r="R56" s="37">
-        <f>IF(OR(G56="",Q56="Fechada",Q56="Perdida"),0,IF(Q56="Previsão vencida",3000,IF(Q56="Parada",2000,1000))+MIN(N(O56),500)+N(F56)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G56="",Q56="Fechada",Q56="Perdida"),0,IF(Q56="Previsão vencida",3,IF(Q56="Parada",2,1))*1E+13+MIN(N(O56),500)*1E+10+MIN(ROUND(N(F56),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5696,7 +5703,7 @@
         <v/>
       </c>
       <c r="R57" s="37">
-        <f>IF(OR(G57="",Q57="Fechada",Q57="Perdida"),0,IF(Q57="Previsão vencida",3000,IF(Q57="Parada",2000,1000))+MIN(N(O57),500)+N(F57)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G57="",Q57="Fechada",Q57="Perdida"),0,IF(Q57="Previsão vencida",3,IF(Q57="Parada",2,1))*1E+13+MIN(N(O57),500)*1E+10+MIN(ROUND(N(F57),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5734,7 +5741,7 @@
         <v/>
       </c>
       <c r="R58" s="37">
-        <f>IF(OR(G58="",Q58="Fechada",Q58="Perdida"),0,IF(Q58="Previsão vencida",3000,IF(Q58="Parada",2000,1000))+MIN(N(O58),500)+N(F58)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G58="",Q58="Fechada",Q58="Perdida"),0,IF(Q58="Previsão vencida",3,IF(Q58="Parada",2,1))*1E+13+MIN(N(O58),500)*1E+10+MIN(ROUND(N(F58),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5772,7 +5779,7 @@
         <v/>
       </c>
       <c r="R59" s="37">
-        <f>IF(OR(G59="",Q59="Fechada",Q59="Perdida"),0,IF(Q59="Previsão vencida",3000,IF(Q59="Parada",2000,1000))+MIN(N(O59),500)+N(F59)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G59="",Q59="Fechada",Q59="Perdida"),0,IF(Q59="Previsão vencida",3,IF(Q59="Parada",2,1))*1E+13+MIN(N(O59),500)*1E+10+MIN(ROUND(N(F59),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5810,7 +5817,7 @@
         <v/>
       </c>
       <c r="R60" s="37">
-        <f>IF(OR(G60="",Q60="Fechada",Q60="Perdida"),0,IF(Q60="Previsão vencida",3000,IF(Q60="Parada",2000,1000))+MIN(N(O60),500)+N(F60)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G60="",Q60="Fechada",Q60="Perdida"),0,IF(Q60="Previsão vencida",3,IF(Q60="Parada",2,1))*1E+13+MIN(N(O60),500)*1E+10+MIN(ROUND(N(F60),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5848,7 +5855,7 @@
         <v/>
       </c>
       <c r="R61" s="37">
-        <f>IF(OR(G61="",Q61="Fechada",Q61="Perdida"),0,IF(Q61="Previsão vencida",3000,IF(Q61="Parada",2000,1000))+MIN(N(O61),500)+N(F61)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G61="",Q61="Fechada",Q61="Perdida"),0,IF(Q61="Previsão vencida",3,IF(Q61="Parada",2,1))*1E+13+MIN(N(O61),500)*1E+10+MIN(ROUND(N(F61),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5886,7 +5893,7 @@
         <v/>
       </c>
       <c r="R62" s="37">
-        <f>IF(OR(G62="",Q62="Fechada",Q62="Perdida"),0,IF(Q62="Previsão vencida",3000,IF(Q62="Parada",2000,1000))+MIN(N(O62),500)+N(F62)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G62="",Q62="Fechada",Q62="Perdida"),0,IF(Q62="Previsão vencida",3,IF(Q62="Parada",2,1))*1E+13+MIN(N(O62),500)*1E+10+MIN(ROUND(N(F62),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5924,7 +5931,7 @@
         <v/>
       </c>
       <c r="R63" s="37">
-        <f>IF(OR(G63="",Q63="Fechada",Q63="Perdida"),0,IF(Q63="Previsão vencida",3000,IF(Q63="Parada",2000,1000))+MIN(N(O63),500)+N(F63)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G63="",Q63="Fechada",Q63="Perdida"),0,IF(Q63="Previsão vencida",3,IF(Q63="Parada",2,1))*1E+13+MIN(N(O63),500)*1E+10+MIN(ROUND(N(F63),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5962,7 +5969,7 @@
         <v/>
       </c>
       <c r="R64" s="37">
-        <f>IF(OR(G64="",Q64="Fechada",Q64="Perdida"),0,IF(Q64="Previsão vencida",3000,IF(Q64="Parada",2000,1000))+MIN(N(O64),500)+N(F64)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G64="",Q64="Fechada",Q64="Perdida"),0,IF(Q64="Previsão vencida",3,IF(Q64="Parada",2,1))*1E+13+MIN(N(O64),500)*1E+10+MIN(ROUND(N(F64),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6000,7 +6007,7 @@
         <v/>
       </c>
       <c r="R65" s="37">
-        <f>IF(OR(G65="",Q65="Fechada",Q65="Perdida"),0,IF(Q65="Previsão vencida",3000,IF(Q65="Parada",2000,1000))+MIN(N(O65),500)+N(F65)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G65="",Q65="Fechada",Q65="Perdida"),0,IF(Q65="Previsão vencida",3,IF(Q65="Parada",2,1))*1E+13+MIN(N(O65),500)*1E+10+MIN(ROUND(N(F65),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6038,7 +6045,7 @@
         <v/>
       </c>
       <c r="R66" s="37">
-        <f>IF(OR(G66="",Q66="Fechada",Q66="Perdida"),0,IF(Q66="Previsão vencida",3000,IF(Q66="Parada",2000,1000))+MIN(N(O66),500)+N(F66)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G66="",Q66="Fechada",Q66="Perdida"),0,IF(Q66="Previsão vencida",3,IF(Q66="Parada",2,1))*1E+13+MIN(N(O66),500)*1E+10+MIN(ROUND(N(F66),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6076,7 +6083,7 @@
         <v/>
       </c>
       <c r="R67" s="37">
-        <f>IF(OR(G67="",Q67="Fechada",Q67="Perdida"),0,IF(Q67="Previsão vencida",3000,IF(Q67="Parada",2000,1000))+MIN(N(O67),500)+N(F67)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G67="",Q67="Fechada",Q67="Perdida"),0,IF(Q67="Previsão vencida",3,IF(Q67="Parada",2,1))*1E+13+MIN(N(O67),500)*1E+10+MIN(ROUND(N(F67),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6114,7 +6121,7 @@
         <v/>
       </c>
       <c r="R68" s="37">
-        <f>IF(OR(G68="",Q68="Fechada",Q68="Perdida"),0,IF(Q68="Previsão vencida",3000,IF(Q68="Parada",2000,1000))+MIN(N(O68),500)+N(F68)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G68="",Q68="Fechada",Q68="Perdida"),0,IF(Q68="Previsão vencida",3,IF(Q68="Parada",2,1))*1E+13+MIN(N(O68),500)*1E+10+MIN(ROUND(N(F68),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6152,7 +6159,7 @@
         <v/>
       </c>
       <c r="R69" s="37">
-        <f>IF(OR(G69="",Q69="Fechada",Q69="Perdida"),0,IF(Q69="Previsão vencida",3000,IF(Q69="Parada",2000,1000))+MIN(N(O69),500)+N(F69)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G69="",Q69="Fechada",Q69="Perdida"),0,IF(Q69="Previsão vencida",3,IF(Q69="Parada",2,1))*1E+13+MIN(N(O69),500)*1E+10+MIN(ROUND(N(F69),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6190,7 +6197,7 @@
         <v/>
       </c>
       <c r="R70" s="37">
-        <f>IF(OR(G70="",Q70="Fechada",Q70="Perdida"),0,IF(Q70="Previsão vencida",3000,IF(Q70="Parada",2000,1000))+MIN(N(O70),500)+N(F70)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G70="",Q70="Fechada",Q70="Perdida"),0,IF(Q70="Previsão vencida",3,IF(Q70="Parada",2,1))*1E+13+MIN(N(O70),500)*1E+10+MIN(ROUND(N(F70),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6228,7 +6235,7 @@
         <v/>
       </c>
       <c r="R71" s="37">
-        <f>IF(OR(G71="",Q71="Fechada",Q71="Perdida"),0,IF(Q71="Previsão vencida",3000,IF(Q71="Parada",2000,1000))+MIN(N(O71),500)+N(F71)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G71="",Q71="Fechada",Q71="Perdida"),0,IF(Q71="Previsão vencida",3,IF(Q71="Parada",2,1))*1E+13+MIN(N(O71),500)*1E+10+MIN(ROUND(N(F71),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6266,7 +6273,7 @@
         <v/>
       </c>
       <c r="R72" s="37">
-        <f>IF(OR(G72="",Q72="Fechada",Q72="Perdida"),0,IF(Q72="Previsão vencida",3000,IF(Q72="Parada",2000,1000))+MIN(N(O72),500)+N(F72)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G72="",Q72="Fechada",Q72="Perdida"),0,IF(Q72="Previsão vencida",3,IF(Q72="Parada",2,1))*1E+13+MIN(N(O72),500)*1E+10+MIN(ROUND(N(F72),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6304,7 +6311,7 @@
         <v/>
       </c>
       <c r="R73" s="37">
-        <f>IF(OR(G73="",Q73="Fechada",Q73="Perdida"),0,IF(Q73="Previsão vencida",3000,IF(Q73="Parada",2000,1000))+MIN(N(O73),500)+N(F73)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G73="",Q73="Fechada",Q73="Perdida"),0,IF(Q73="Previsão vencida",3,IF(Q73="Parada",2,1))*1E+13+MIN(N(O73),500)*1E+10+MIN(ROUND(N(F73),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6342,7 +6349,7 @@
         <v/>
       </c>
       <c r="R74" s="37">
-        <f>IF(OR(G74="",Q74="Fechada",Q74="Perdida"),0,IF(Q74="Previsão vencida",3000,IF(Q74="Parada",2000,1000))+MIN(N(O74),500)+N(F74)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G74="",Q74="Fechada",Q74="Perdida"),0,IF(Q74="Previsão vencida",3,IF(Q74="Parada",2,1))*1E+13+MIN(N(O74),500)*1E+10+MIN(ROUND(N(F74),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6380,7 +6387,7 @@
         <v/>
       </c>
       <c r="R75" s="37">
-        <f>IF(OR(G75="",Q75="Fechada",Q75="Perdida"),0,IF(Q75="Previsão vencida",3000,IF(Q75="Parada",2000,1000))+MIN(N(O75),500)+N(F75)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G75="",Q75="Fechada",Q75="Perdida"),0,IF(Q75="Previsão vencida",3,IF(Q75="Parada",2,1))*1E+13+MIN(N(O75),500)*1E+10+MIN(ROUND(N(F75),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6418,7 +6425,7 @@
         <v/>
       </c>
       <c r="R76" s="37">
-        <f>IF(OR(G76="",Q76="Fechada",Q76="Perdida"),0,IF(Q76="Previsão vencida",3000,IF(Q76="Parada",2000,1000))+MIN(N(O76),500)+N(F76)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G76="",Q76="Fechada",Q76="Perdida"),0,IF(Q76="Previsão vencida",3,IF(Q76="Parada",2,1))*1E+13+MIN(N(O76),500)*1E+10+MIN(ROUND(N(F76),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6456,7 +6463,7 @@
         <v/>
       </c>
       <c r="R77" s="37">
-        <f>IF(OR(G77="",Q77="Fechada",Q77="Perdida"),0,IF(Q77="Previsão vencida",3000,IF(Q77="Parada",2000,1000))+MIN(N(O77),500)+N(F77)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G77="",Q77="Fechada",Q77="Perdida"),0,IF(Q77="Previsão vencida",3,IF(Q77="Parada",2,1))*1E+13+MIN(N(O77),500)*1E+10+MIN(ROUND(N(F77),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6494,7 +6501,7 @@
         <v/>
       </c>
       <c r="R78" s="37">
-        <f>IF(OR(G78="",Q78="Fechada",Q78="Perdida"),0,IF(Q78="Previsão vencida",3000,IF(Q78="Parada",2000,1000))+MIN(N(O78),500)+N(F78)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G78="",Q78="Fechada",Q78="Perdida"),0,IF(Q78="Previsão vencida",3,IF(Q78="Parada",2,1))*1E+13+MIN(N(O78),500)*1E+10+MIN(ROUND(N(F78),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6532,7 +6539,7 @@
         <v/>
       </c>
       <c r="R79" s="37">
-        <f>IF(OR(G79="",Q79="Fechada",Q79="Perdida"),0,IF(Q79="Previsão vencida",3000,IF(Q79="Parada",2000,1000))+MIN(N(O79),500)+N(F79)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G79="",Q79="Fechada",Q79="Perdida"),0,IF(Q79="Previsão vencida",3,IF(Q79="Parada",2,1))*1E+13+MIN(N(O79),500)*1E+10+MIN(ROUND(N(F79),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6570,7 +6577,7 @@
         <v/>
       </c>
       <c r="R80" s="37">
-        <f>IF(OR(G80="",Q80="Fechada",Q80="Perdida"),0,IF(Q80="Previsão vencida",3000,IF(Q80="Parada",2000,1000))+MIN(N(O80),500)+N(F80)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G80="",Q80="Fechada",Q80="Perdida"),0,IF(Q80="Previsão vencida",3,IF(Q80="Parada",2,1))*1E+13+MIN(N(O80),500)*1E+10+MIN(ROUND(N(F80),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6608,7 +6615,7 @@
         <v/>
       </c>
       <c r="R81" s="37">
-        <f>IF(OR(G81="",Q81="Fechada",Q81="Perdida"),0,IF(Q81="Previsão vencida",3000,IF(Q81="Parada",2000,1000))+MIN(N(O81),500)+N(F81)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G81="",Q81="Fechada",Q81="Perdida"),0,IF(Q81="Previsão vencida",3,IF(Q81="Parada",2,1))*1E+13+MIN(N(O81),500)*1E+10+MIN(ROUND(N(F81),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6646,7 +6653,7 @@
         <v/>
       </c>
       <c r="R82" s="37">
-        <f>IF(OR(G82="",Q82="Fechada",Q82="Perdida"),0,IF(Q82="Previsão vencida",3000,IF(Q82="Parada",2000,1000))+MIN(N(O82),500)+N(F82)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G82="",Q82="Fechada",Q82="Perdida"),0,IF(Q82="Previsão vencida",3,IF(Q82="Parada",2,1))*1E+13+MIN(N(O82),500)*1E+10+MIN(ROUND(N(F82),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6684,7 +6691,7 @@
         <v/>
       </c>
       <c r="R83" s="37">
-        <f>IF(OR(G83="",Q83="Fechada",Q83="Perdida"),0,IF(Q83="Previsão vencida",3000,IF(Q83="Parada",2000,1000))+MIN(N(O83),500)+N(F83)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G83="",Q83="Fechada",Q83="Perdida"),0,IF(Q83="Previsão vencida",3,IF(Q83="Parada",2,1))*1E+13+MIN(N(O83),500)*1E+10+MIN(ROUND(N(F83),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6722,7 +6729,7 @@
         <v/>
       </c>
       <c r="R84" s="37">
-        <f>IF(OR(G84="",Q84="Fechada",Q84="Perdida"),0,IF(Q84="Previsão vencida",3000,IF(Q84="Parada",2000,1000))+MIN(N(O84),500)+N(F84)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G84="",Q84="Fechada",Q84="Perdida"),0,IF(Q84="Previsão vencida",3,IF(Q84="Parada",2,1))*1E+13+MIN(N(O84),500)*1E+10+MIN(ROUND(N(F84),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6760,7 +6767,7 @@
         <v/>
       </c>
       <c r="R85" s="37">
-        <f>IF(OR(G85="",Q85="Fechada",Q85="Perdida"),0,IF(Q85="Previsão vencida",3000,IF(Q85="Parada",2000,1000))+MIN(N(O85),500)+N(F85)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G85="",Q85="Fechada",Q85="Perdida"),0,IF(Q85="Previsão vencida",3,IF(Q85="Parada",2,1))*1E+13+MIN(N(O85),500)*1E+10+MIN(ROUND(N(F85),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6798,7 +6805,7 @@
         <v/>
       </c>
       <c r="R86" s="37">
-        <f>IF(OR(G86="",Q86="Fechada",Q86="Perdida"),0,IF(Q86="Previsão vencida",3000,IF(Q86="Parada",2000,1000))+MIN(N(O86),500)+N(F86)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G86="",Q86="Fechada",Q86="Perdida"),0,IF(Q86="Previsão vencida",3,IF(Q86="Parada",2,1))*1E+13+MIN(N(O86),500)*1E+10+MIN(ROUND(N(F86),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6836,7 +6843,7 @@
         <v/>
       </c>
       <c r="R87" s="37">
-        <f>IF(OR(G87="",Q87="Fechada",Q87="Perdida"),0,IF(Q87="Previsão vencida",3000,IF(Q87="Parada",2000,1000))+MIN(N(O87),500)+N(F87)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G87="",Q87="Fechada",Q87="Perdida"),0,IF(Q87="Previsão vencida",3,IF(Q87="Parada",2,1))*1E+13+MIN(N(O87),500)*1E+10+MIN(ROUND(N(F87),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6874,7 +6881,7 @@
         <v/>
       </c>
       <c r="R88" s="37">
-        <f>IF(OR(G88="",Q88="Fechada",Q88="Perdida"),0,IF(Q88="Previsão vencida",3000,IF(Q88="Parada",2000,1000))+MIN(N(O88),500)+N(F88)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G88="",Q88="Fechada",Q88="Perdida"),0,IF(Q88="Previsão vencida",3,IF(Q88="Parada",2,1))*1E+13+MIN(N(O88),500)*1E+10+MIN(ROUND(N(F88),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6912,7 +6919,7 @@
         <v/>
       </c>
       <c r="R89" s="37">
-        <f>IF(OR(G89="",Q89="Fechada",Q89="Perdida"),0,IF(Q89="Previsão vencida",3000,IF(Q89="Parada",2000,1000))+MIN(N(O89),500)+N(F89)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G89="",Q89="Fechada",Q89="Perdida"),0,IF(Q89="Previsão vencida",3,IF(Q89="Parada",2,1))*1E+13+MIN(N(O89),500)*1E+10+MIN(ROUND(N(F89),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6950,7 +6957,7 @@
         <v/>
       </c>
       <c r="R90" s="37">
-        <f>IF(OR(G90="",Q90="Fechada",Q90="Perdida"),0,IF(Q90="Previsão vencida",3000,IF(Q90="Parada",2000,1000))+MIN(N(O90),500)+N(F90)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G90="",Q90="Fechada",Q90="Perdida"),0,IF(Q90="Previsão vencida",3,IF(Q90="Parada",2,1))*1E+13+MIN(N(O90),500)*1E+10+MIN(ROUND(N(F90),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6988,7 +6995,7 @@
         <v/>
       </c>
       <c r="R91" s="37">
-        <f>IF(OR(G91="",Q91="Fechada",Q91="Perdida"),0,IF(Q91="Previsão vencida",3000,IF(Q91="Parada",2000,1000))+MIN(N(O91),500)+N(F91)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G91="",Q91="Fechada",Q91="Perdida"),0,IF(Q91="Previsão vencida",3,IF(Q91="Parada",2,1))*1E+13+MIN(N(O91),500)*1E+10+MIN(ROUND(N(F91),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7026,7 +7033,7 @@
         <v/>
       </c>
       <c r="R92" s="37">
-        <f>IF(OR(G92="",Q92="Fechada",Q92="Perdida"),0,IF(Q92="Previsão vencida",3000,IF(Q92="Parada",2000,1000))+MIN(N(O92),500)+N(F92)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G92="",Q92="Fechada",Q92="Perdida"),0,IF(Q92="Previsão vencida",3,IF(Q92="Parada",2,1))*1E+13+MIN(N(O92),500)*1E+10+MIN(ROUND(N(F92),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7064,7 +7071,7 @@
         <v/>
       </c>
       <c r="R93" s="37">
-        <f>IF(OR(G93="",Q93="Fechada",Q93="Perdida"),0,IF(Q93="Previsão vencida",3000,IF(Q93="Parada",2000,1000))+MIN(N(O93),500)+N(F93)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G93="",Q93="Fechada",Q93="Perdida"),0,IF(Q93="Previsão vencida",3,IF(Q93="Parada",2,1))*1E+13+MIN(N(O93),500)*1E+10+MIN(ROUND(N(F93),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7102,7 +7109,7 @@
         <v/>
       </c>
       <c r="R94" s="37">
-        <f>IF(OR(G94="",Q94="Fechada",Q94="Perdida"),0,IF(Q94="Previsão vencida",3000,IF(Q94="Parada",2000,1000))+MIN(N(O94),500)+N(F94)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G94="",Q94="Fechada",Q94="Perdida"),0,IF(Q94="Previsão vencida",3,IF(Q94="Parada",2,1))*1E+13+MIN(N(O94),500)*1E+10+MIN(ROUND(N(F94),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7140,7 +7147,7 @@
         <v/>
       </c>
       <c r="R95" s="37">
-        <f>IF(OR(G95="",Q95="Fechada",Q95="Perdida"),0,IF(Q95="Previsão vencida",3000,IF(Q95="Parada",2000,1000))+MIN(N(O95),500)+N(F95)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G95="",Q95="Fechada",Q95="Perdida"),0,IF(Q95="Previsão vencida",3,IF(Q95="Parada",2,1))*1E+13+MIN(N(O95),500)*1E+10+MIN(ROUND(N(F95),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7178,7 +7185,7 @@
         <v/>
       </c>
       <c r="R96" s="37">
-        <f>IF(OR(G96="",Q96="Fechada",Q96="Perdida"),0,IF(Q96="Previsão vencida",3000,IF(Q96="Parada",2000,1000))+MIN(N(O96),500)+N(F96)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G96="",Q96="Fechada",Q96="Perdida"),0,IF(Q96="Previsão vencida",3,IF(Q96="Parada",2,1))*1E+13+MIN(N(O96),500)*1E+10+MIN(ROUND(N(F96),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7216,7 +7223,7 @@
         <v/>
       </c>
       <c r="R97" s="37">
-        <f>IF(OR(G97="",Q97="Fechada",Q97="Perdida"),0,IF(Q97="Previsão vencida",3000,IF(Q97="Parada",2000,1000))+MIN(N(O97),500)+N(F97)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G97="",Q97="Fechada",Q97="Perdida"),0,IF(Q97="Previsão vencida",3,IF(Q97="Parada",2,1))*1E+13+MIN(N(O97),500)*1E+10+MIN(ROUND(N(F97),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7254,7 +7261,7 @@
         <v/>
       </c>
       <c r="R98" s="37">
-        <f>IF(OR(G98="",Q98="Fechada",Q98="Perdida"),0,IF(Q98="Previsão vencida",3000,IF(Q98="Parada",2000,1000))+MIN(N(O98),500)+N(F98)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G98="",Q98="Fechada",Q98="Perdida"),0,IF(Q98="Previsão vencida",3,IF(Q98="Parada",2,1))*1E+13+MIN(N(O98),500)*1E+10+MIN(ROUND(N(F98),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7292,7 +7299,7 @@
         <v/>
       </c>
       <c r="R99" s="37">
-        <f>IF(OR(G99="",Q99="Fechada",Q99="Perdida"),0,IF(Q99="Previsão vencida",3000,IF(Q99="Parada",2000,1000))+MIN(N(O99),500)+N(F99)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G99="",Q99="Fechada",Q99="Perdida"),0,IF(Q99="Previsão vencida",3,IF(Q99="Parada",2,1))*1E+13+MIN(N(O99),500)*1E+10+MIN(ROUND(N(F99),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7330,7 +7337,7 @@
         <v/>
       </c>
       <c r="R100" s="37">
-        <f>IF(OR(G100="",Q100="Fechada",Q100="Perdida"),0,IF(Q100="Previsão vencida",3000,IF(Q100="Parada",2000,1000))+MIN(N(O100),500)+N(F100)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G100="",Q100="Fechada",Q100="Perdida"),0,IF(Q100="Previsão vencida",3,IF(Q100="Parada",2,1))*1E+13+MIN(N(O100),500)*1E+10+MIN(ROUND(N(F100),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7368,7 +7375,7 @@
         <v/>
       </c>
       <c r="R101" s="37">
-        <f>IF(OR(G101="",Q101="Fechada",Q101="Perdida"),0,IF(Q101="Previsão vencida",3000,IF(Q101="Parada",2000,1000))+MIN(N(O101),500)+N(F101)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G101="",Q101="Fechada",Q101="Perdida"),0,IF(Q101="Previsão vencida",3,IF(Q101="Parada",2,1))*1E+13+MIN(N(O101),500)*1E+10+MIN(ROUND(N(F101),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7406,7 +7413,7 @@
         <v/>
       </c>
       <c r="R102" s="37">
-        <f>IF(OR(G102="",Q102="Fechada",Q102="Perdida"),0,IF(Q102="Previsão vencida",3000,IF(Q102="Parada",2000,1000))+MIN(N(O102),500)+N(F102)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G102="",Q102="Fechada",Q102="Perdida"),0,IF(Q102="Previsão vencida",3,IF(Q102="Parada",2,1))*1E+13+MIN(N(O102),500)*1E+10+MIN(ROUND(N(F102),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7444,7 +7451,7 @@
         <v/>
       </c>
       <c r="R103" s="37">
-        <f>IF(OR(G103="",Q103="Fechada",Q103="Perdida"),0,IF(Q103="Previsão vencida",3000,IF(Q103="Parada",2000,1000))+MIN(N(O103),500)+N(F103)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G103="",Q103="Fechada",Q103="Perdida"),0,IF(Q103="Previsão vencida",3,IF(Q103="Parada",2,1))*1E+13+MIN(N(O103),500)*1E+10+MIN(ROUND(N(F103),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7482,7 +7489,7 @@
         <v/>
       </c>
       <c r="R104" s="37">
-        <f>IF(OR(G104="",Q104="Fechada",Q104="Perdida"),0,IF(Q104="Previsão vencida",3000,IF(Q104="Parada",2000,1000))+MIN(N(O104),500)+N(F104)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G104="",Q104="Fechada",Q104="Perdida"),0,IF(Q104="Previsão vencida",3,IF(Q104="Parada",2,1))*1E+13+MIN(N(O104),500)*1E+10+MIN(ROUND(N(F104),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7520,7 +7527,7 @@
         <v/>
       </c>
       <c r="R105" s="37">
-        <f>IF(OR(G105="",Q105="Fechada",Q105="Perdida"),0,IF(Q105="Previsão vencida",3000,IF(Q105="Parada",2000,1000))+MIN(N(O105),500)+N(F105)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G105="",Q105="Fechada",Q105="Perdida"),0,IF(Q105="Previsão vencida",3,IF(Q105="Parada",2,1))*1E+13+MIN(N(O105),500)*1E+10+MIN(ROUND(N(F105),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7558,7 +7565,7 @@
         <v/>
       </c>
       <c r="R106" s="37">
-        <f>IF(OR(G106="",Q106="Fechada",Q106="Perdida"),0,IF(Q106="Previsão vencida",3000,IF(Q106="Parada",2000,1000))+MIN(N(O106),500)+N(F106)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G106="",Q106="Fechada",Q106="Perdida"),0,IF(Q106="Previsão vencida",3,IF(Q106="Parada",2,1))*1E+13+MIN(N(O106),500)*1E+10+MIN(ROUND(N(F106),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7596,7 +7603,7 @@
         <v/>
       </c>
       <c r="R107" s="37">
-        <f>IF(OR(G107="",Q107="Fechada",Q107="Perdida"),0,IF(Q107="Previsão vencida",3000,IF(Q107="Parada",2000,1000))+MIN(N(O107),500)+N(F107)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G107="",Q107="Fechada",Q107="Perdida"),0,IF(Q107="Previsão vencida",3,IF(Q107="Parada",2,1))*1E+13+MIN(N(O107),500)*1E+10+MIN(ROUND(N(F107),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7634,7 +7641,7 @@
         <v/>
       </c>
       <c r="R108" s="37">
-        <f>IF(OR(G108="",Q108="Fechada",Q108="Perdida"),0,IF(Q108="Previsão vencida",3000,IF(Q108="Parada",2000,1000))+MIN(N(O108),500)+N(F108)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G108="",Q108="Fechada",Q108="Perdida"),0,IF(Q108="Previsão vencida",3,IF(Q108="Parada",2,1))*1E+13+MIN(N(O108),500)*1E+10+MIN(ROUND(N(F108),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7672,7 +7679,7 @@
         <v/>
       </c>
       <c r="R109" s="37">
-        <f>IF(OR(G109="",Q109="Fechada",Q109="Perdida"),0,IF(Q109="Previsão vencida",3000,IF(Q109="Parada",2000,1000))+MIN(N(O109),500)+N(F109)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G109="",Q109="Fechada",Q109="Perdida"),0,IF(Q109="Previsão vencida",3,IF(Q109="Parada",2,1))*1E+13+MIN(N(O109),500)*1E+10+MIN(ROUND(N(F109),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7710,7 +7717,7 @@
         <v/>
       </c>
       <c r="R110" s="37">
-        <f>IF(OR(G110="",Q110="Fechada",Q110="Perdida"),0,IF(Q110="Previsão vencida",3000,IF(Q110="Parada",2000,1000))+MIN(N(O110),500)+N(F110)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G110="",Q110="Fechada",Q110="Perdida"),0,IF(Q110="Previsão vencida",3,IF(Q110="Parada",2,1))*1E+13+MIN(N(O110),500)*1E+10+MIN(ROUND(N(F110),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7748,7 +7755,7 @@
         <v/>
       </c>
       <c r="R111" s="37">
-        <f>IF(OR(G111="",Q111="Fechada",Q111="Perdida"),0,IF(Q111="Previsão vencida",3000,IF(Q111="Parada",2000,1000))+MIN(N(O111),500)+N(F111)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G111="",Q111="Fechada",Q111="Perdida"),0,IF(Q111="Previsão vencida",3,IF(Q111="Parada",2,1))*1E+13+MIN(N(O111),500)*1E+10+MIN(ROUND(N(F111),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7786,7 +7793,7 @@
         <v/>
       </c>
       <c r="R112" s="37">
-        <f>IF(OR(G112="",Q112="Fechada",Q112="Perdida"),0,IF(Q112="Previsão vencida",3000,IF(Q112="Parada",2000,1000))+MIN(N(O112),500)+N(F112)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G112="",Q112="Fechada",Q112="Perdida"),0,IF(Q112="Previsão vencida",3,IF(Q112="Parada",2,1))*1E+13+MIN(N(O112),500)*1E+10+MIN(ROUND(N(F112),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7824,7 +7831,7 @@
         <v/>
       </c>
       <c r="R113" s="37">
-        <f>IF(OR(G113="",Q113="Fechada",Q113="Perdida"),0,IF(Q113="Previsão vencida",3000,IF(Q113="Parada",2000,1000))+MIN(N(O113),500)+N(F113)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G113="",Q113="Fechada",Q113="Perdida"),0,IF(Q113="Previsão vencida",3,IF(Q113="Parada",2,1))*1E+13+MIN(N(O113),500)*1E+10+MIN(ROUND(N(F113),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7862,7 +7869,7 @@
         <v/>
       </c>
       <c r="R114" s="37">
-        <f>IF(OR(G114="",Q114="Fechada",Q114="Perdida"),0,IF(Q114="Previsão vencida",3000,IF(Q114="Parada",2000,1000))+MIN(N(O114),500)+N(F114)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G114="",Q114="Fechada",Q114="Perdida"),0,IF(Q114="Previsão vencida",3,IF(Q114="Parada",2,1))*1E+13+MIN(N(O114),500)*1E+10+MIN(ROUND(N(F114),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7900,7 +7907,7 @@
         <v/>
       </c>
       <c r="R115" s="37">
-        <f>IF(OR(G115="",Q115="Fechada",Q115="Perdida"),0,IF(Q115="Previsão vencida",3000,IF(Q115="Parada",2000,1000))+MIN(N(O115),500)+N(F115)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G115="",Q115="Fechada",Q115="Perdida"),0,IF(Q115="Previsão vencida",3,IF(Q115="Parada",2,1))*1E+13+MIN(N(O115),500)*1E+10+MIN(ROUND(N(F115),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7938,7 +7945,7 @@
         <v/>
       </c>
       <c r="R116" s="37">
-        <f>IF(OR(G116="",Q116="Fechada",Q116="Perdida"),0,IF(Q116="Previsão vencida",3000,IF(Q116="Parada",2000,1000))+MIN(N(O116),500)+N(F116)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G116="",Q116="Fechada",Q116="Perdida"),0,IF(Q116="Previsão vencida",3,IF(Q116="Parada",2,1))*1E+13+MIN(N(O116),500)*1E+10+MIN(ROUND(N(F116),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7976,7 +7983,7 @@
         <v/>
       </c>
       <c r="R117" s="37">
-        <f>IF(OR(G117="",Q117="Fechada",Q117="Perdida"),0,IF(Q117="Previsão vencida",3000,IF(Q117="Parada",2000,1000))+MIN(N(O117),500)+N(F117)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G117="",Q117="Fechada",Q117="Perdida"),0,IF(Q117="Previsão vencida",3,IF(Q117="Parada",2,1))*1E+13+MIN(N(O117),500)*1E+10+MIN(ROUND(N(F117),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8014,7 +8021,7 @@
         <v/>
       </c>
       <c r="R118" s="37">
-        <f>IF(OR(G118="",Q118="Fechada",Q118="Perdida"),0,IF(Q118="Previsão vencida",3000,IF(Q118="Parada",2000,1000))+MIN(N(O118),500)+N(F118)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G118="",Q118="Fechada",Q118="Perdida"),0,IF(Q118="Previsão vencida",3,IF(Q118="Parada",2,1))*1E+13+MIN(N(O118),500)*1E+10+MIN(ROUND(N(F118),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8052,7 +8059,7 @@
         <v/>
       </c>
       <c r="R119" s="37">
-        <f>IF(OR(G119="",Q119="Fechada",Q119="Perdida"),0,IF(Q119="Previsão vencida",3000,IF(Q119="Parada",2000,1000))+MIN(N(O119),500)+N(F119)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G119="",Q119="Fechada",Q119="Perdida"),0,IF(Q119="Previsão vencida",3,IF(Q119="Parada",2,1))*1E+13+MIN(N(O119),500)*1E+10+MIN(ROUND(N(F119),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8090,7 +8097,7 @@
         <v/>
       </c>
       <c r="R120" s="37">
-        <f>IF(OR(G120="",Q120="Fechada",Q120="Perdida"),0,IF(Q120="Previsão vencida",3000,IF(Q120="Parada",2000,1000))+MIN(N(O120),500)+N(F120)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G120="",Q120="Fechada",Q120="Perdida"),0,IF(Q120="Previsão vencida",3,IF(Q120="Parada",2,1))*1E+13+MIN(N(O120),500)*1E+10+MIN(ROUND(N(F120),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8128,7 +8135,7 @@
         <v/>
       </c>
       <c r="R121" s="37">
-        <f>IF(OR(G121="",Q121="Fechada",Q121="Perdida"),0,IF(Q121="Previsão vencida",3000,IF(Q121="Parada",2000,1000))+MIN(N(O121),500)+N(F121)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G121="",Q121="Fechada",Q121="Perdida"),0,IF(Q121="Previsão vencida",3,IF(Q121="Parada",2,1))*1E+13+MIN(N(O121),500)*1E+10+MIN(ROUND(N(F121),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8166,7 +8173,7 @@
         <v/>
       </c>
       <c r="R122" s="37">
-        <f>IF(OR(G122="",Q122="Fechada",Q122="Perdida"),0,IF(Q122="Previsão vencida",3000,IF(Q122="Parada",2000,1000))+MIN(N(O122),500)+N(F122)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G122="",Q122="Fechada",Q122="Perdida"),0,IF(Q122="Previsão vencida",3,IF(Q122="Parada",2,1))*1E+13+MIN(N(O122),500)*1E+10+MIN(ROUND(N(F122),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8204,7 +8211,7 @@
         <v/>
       </c>
       <c r="R123" s="37">
-        <f>IF(OR(G123="",Q123="Fechada",Q123="Perdida"),0,IF(Q123="Previsão vencida",3000,IF(Q123="Parada",2000,1000))+MIN(N(O123),500)+N(F123)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G123="",Q123="Fechada",Q123="Perdida"),0,IF(Q123="Previsão vencida",3,IF(Q123="Parada",2,1))*1E+13+MIN(N(O123),500)*1E+10+MIN(ROUND(N(F123),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8242,7 +8249,7 @@
         <v/>
       </c>
       <c r="R124" s="37">
-        <f>IF(OR(G124="",Q124="Fechada",Q124="Perdida"),0,IF(Q124="Previsão vencida",3000,IF(Q124="Parada",2000,1000))+MIN(N(O124),500)+N(F124)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G124="",Q124="Fechada",Q124="Perdida"),0,IF(Q124="Previsão vencida",3,IF(Q124="Parada",2,1))*1E+13+MIN(N(O124),500)*1E+10+MIN(ROUND(N(F124),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8280,7 +8287,7 @@
         <v/>
       </c>
       <c r="R125" s="37">
-        <f>IF(OR(G125="",Q125="Fechada",Q125="Perdida"),0,IF(Q125="Previsão vencida",3000,IF(Q125="Parada",2000,1000))+MIN(N(O125),500)+N(F125)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G125="",Q125="Fechada",Q125="Perdida"),0,IF(Q125="Previsão vencida",3,IF(Q125="Parada",2,1))*1E+13+MIN(N(O125),500)*1E+10+MIN(ROUND(N(F125),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8318,7 +8325,7 @@
         <v/>
       </c>
       <c r="R126" s="37">
-        <f>IF(OR(G126="",Q126="Fechada",Q126="Perdida"),0,IF(Q126="Previsão vencida",3000,IF(Q126="Parada",2000,1000))+MIN(N(O126),500)+N(F126)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G126="",Q126="Fechada",Q126="Perdida"),0,IF(Q126="Previsão vencida",3,IF(Q126="Parada",2,1))*1E+13+MIN(N(O126),500)*1E+10+MIN(ROUND(N(F126),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8356,7 +8363,7 @@
         <v/>
       </c>
       <c r="R127" s="37">
-        <f>IF(OR(G127="",Q127="Fechada",Q127="Perdida"),0,IF(Q127="Previsão vencida",3000,IF(Q127="Parada",2000,1000))+MIN(N(O127),500)+N(F127)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G127="",Q127="Fechada",Q127="Perdida"),0,IF(Q127="Previsão vencida",3,IF(Q127="Parada",2,1))*1E+13+MIN(N(O127),500)*1E+10+MIN(ROUND(N(F127),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8394,7 +8401,7 @@
         <v/>
       </c>
       <c r="R128" s="37">
-        <f>IF(OR(G128="",Q128="Fechada",Q128="Perdida"),0,IF(Q128="Previsão vencida",3000,IF(Q128="Parada",2000,1000))+MIN(N(O128),500)+N(F128)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G128="",Q128="Fechada",Q128="Perdida"),0,IF(Q128="Previsão vencida",3,IF(Q128="Parada",2,1))*1E+13+MIN(N(O128),500)*1E+10+MIN(ROUND(N(F128),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8432,7 +8439,7 @@
         <v/>
       </c>
       <c r="R129" s="37">
-        <f>IF(OR(G129="",Q129="Fechada",Q129="Perdida"),0,IF(Q129="Previsão vencida",3000,IF(Q129="Parada",2000,1000))+MIN(N(O129),500)+N(F129)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G129="",Q129="Fechada",Q129="Perdida"),0,IF(Q129="Previsão vencida",3,IF(Q129="Parada",2,1))*1E+13+MIN(N(O129),500)*1E+10+MIN(ROUND(N(F129),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8470,7 +8477,7 @@
         <v/>
       </c>
       <c r="R130" s="37">
-        <f>IF(OR(G130="",Q130="Fechada",Q130="Perdida"),0,IF(Q130="Previsão vencida",3000,IF(Q130="Parada",2000,1000))+MIN(N(O130),500)+N(F130)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G130="",Q130="Fechada",Q130="Perdida"),0,IF(Q130="Previsão vencida",3,IF(Q130="Parada",2,1))*1E+13+MIN(N(O130),500)*1E+10+MIN(ROUND(N(F130),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8508,7 +8515,7 @@
         <v/>
       </c>
       <c r="R131" s="37">
-        <f>IF(OR(G131="",Q131="Fechada",Q131="Perdida"),0,IF(Q131="Previsão vencida",3000,IF(Q131="Parada",2000,1000))+MIN(N(O131),500)+N(F131)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G131="",Q131="Fechada",Q131="Perdida"),0,IF(Q131="Previsão vencida",3,IF(Q131="Parada",2,1))*1E+13+MIN(N(O131),500)*1E+10+MIN(ROUND(N(F131),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8546,7 +8553,7 @@
         <v/>
       </c>
       <c r="R132" s="37">
-        <f>IF(OR(G132="",Q132="Fechada",Q132="Perdida"),0,IF(Q132="Previsão vencida",3000,IF(Q132="Parada",2000,1000))+MIN(N(O132),500)+N(F132)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G132="",Q132="Fechada",Q132="Perdida"),0,IF(Q132="Previsão vencida",3,IF(Q132="Parada",2,1))*1E+13+MIN(N(O132),500)*1E+10+MIN(ROUND(N(F132),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8584,7 +8591,7 @@
         <v/>
       </c>
       <c r="R133" s="37">
-        <f>IF(OR(G133="",Q133="Fechada",Q133="Perdida"),0,IF(Q133="Previsão vencida",3000,IF(Q133="Parada",2000,1000))+MIN(N(O133),500)+N(F133)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G133="",Q133="Fechada",Q133="Perdida"),0,IF(Q133="Previsão vencida",3,IF(Q133="Parada",2,1))*1E+13+MIN(N(O133),500)*1E+10+MIN(ROUND(N(F133),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8622,7 +8629,7 @@
         <v/>
       </c>
       <c r="R134" s="37">
-        <f>IF(OR(G134="",Q134="Fechada",Q134="Perdida"),0,IF(Q134="Previsão vencida",3000,IF(Q134="Parada",2000,1000))+MIN(N(O134),500)+N(F134)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G134="",Q134="Fechada",Q134="Perdida"),0,IF(Q134="Previsão vencida",3,IF(Q134="Parada",2,1))*1E+13+MIN(N(O134),500)*1E+10+MIN(ROUND(N(F134),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8660,7 +8667,7 @@
         <v/>
       </c>
       <c r="R135" s="37">
-        <f>IF(OR(G135="",Q135="Fechada",Q135="Perdida"),0,IF(Q135="Previsão vencida",3000,IF(Q135="Parada",2000,1000))+MIN(N(O135),500)+N(F135)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G135="",Q135="Fechada",Q135="Perdida"),0,IF(Q135="Previsão vencida",3,IF(Q135="Parada",2,1))*1E+13+MIN(N(O135),500)*1E+10+MIN(ROUND(N(F135),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8698,7 +8705,7 @@
         <v/>
       </c>
       <c r="R136" s="37">
-        <f>IF(OR(G136="",Q136="Fechada",Q136="Perdida"),0,IF(Q136="Previsão vencida",3000,IF(Q136="Parada",2000,1000))+MIN(N(O136),500)+N(F136)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G136="",Q136="Fechada",Q136="Perdida"),0,IF(Q136="Previsão vencida",3,IF(Q136="Parada",2,1))*1E+13+MIN(N(O136),500)*1E+10+MIN(ROUND(N(F136),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8736,7 +8743,7 @@
         <v/>
       </c>
       <c r="R137" s="37">
-        <f>IF(OR(G137="",Q137="Fechada",Q137="Perdida"),0,IF(Q137="Previsão vencida",3000,IF(Q137="Parada",2000,1000))+MIN(N(O137),500)+N(F137)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G137="",Q137="Fechada",Q137="Perdida"),0,IF(Q137="Previsão vencida",3,IF(Q137="Parada",2,1))*1E+13+MIN(N(O137),500)*1E+10+MIN(ROUND(N(F137),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8774,7 +8781,7 @@
         <v/>
       </c>
       <c r="R138" s="37">
-        <f>IF(OR(G138="",Q138="Fechada",Q138="Perdida"),0,IF(Q138="Previsão vencida",3000,IF(Q138="Parada",2000,1000))+MIN(N(O138),500)+N(F138)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G138="",Q138="Fechada",Q138="Perdida"),0,IF(Q138="Previsão vencida",3,IF(Q138="Parada",2,1))*1E+13+MIN(N(O138),500)*1E+10+MIN(ROUND(N(F138),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8812,7 +8819,7 @@
         <v/>
       </c>
       <c r="R139" s="37">
-        <f>IF(OR(G139="",Q139="Fechada",Q139="Perdida"),0,IF(Q139="Previsão vencida",3000,IF(Q139="Parada",2000,1000))+MIN(N(O139),500)+N(F139)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G139="",Q139="Fechada",Q139="Perdida"),0,IF(Q139="Previsão vencida",3,IF(Q139="Parada",2,1))*1E+13+MIN(N(O139),500)*1E+10+MIN(ROUND(N(F139),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8850,7 +8857,7 @@
         <v/>
       </c>
       <c r="R140" s="37">
-        <f>IF(OR(G140="",Q140="Fechada",Q140="Perdida"),0,IF(Q140="Previsão vencida",3000,IF(Q140="Parada",2000,1000))+MIN(N(O140),500)+N(F140)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G140="",Q140="Fechada",Q140="Perdida"),0,IF(Q140="Previsão vencida",3,IF(Q140="Parada",2,1))*1E+13+MIN(N(O140),500)*1E+10+MIN(ROUND(N(F140),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8888,7 +8895,7 @@
         <v/>
       </c>
       <c r="R141" s="37">
-        <f>IF(OR(G141="",Q141="Fechada",Q141="Perdida"),0,IF(Q141="Previsão vencida",3000,IF(Q141="Parada",2000,1000))+MIN(N(O141),500)+N(F141)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G141="",Q141="Fechada",Q141="Perdida"),0,IF(Q141="Previsão vencida",3,IF(Q141="Parada",2,1))*1E+13+MIN(N(O141),500)*1E+10+MIN(ROUND(N(F141),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8926,7 +8933,7 @@
         <v/>
       </c>
       <c r="R142" s="37">
-        <f>IF(OR(G142="",Q142="Fechada",Q142="Perdida"),0,IF(Q142="Previsão vencida",3000,IF(Q142="Parada",2000,1000))+MIN(N(O142),500)+N(F142)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G142="",Q142="Fechada",Q142="Perdida"),0,IF(Q142="Previsão vencida",3,IF(Q142="Parada",2,1))*1E+13+MIN(N(O142),500)*1E+10+MIN(ROUND(N(F142),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8964,7 +8971,7 @@
         <v/>
       </c>
       <c r="R143" s="37">
-        <f>IF(OR(G143="",Q143="Fechada",Q143="Perdida"),0,IF(Q143="Previsão vencida",3000,IF(Q143="Parada",2000,1000))+MIN(N(O143),500)+N(F143)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G143="",Q143="Fechada",Q143="Perdida"),0,IF(Q143="Previsão vencida",3,IF(Q143="Parada",2,1))*1E+13+MIN(N(O143),500)*1E+10+MIN(ROUND(N(F143),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9002,7 +9009,7 @@
         <v/>
       </c>
       <c r="R144" s="37">
-        <f>IF(OR(G144="",Q144="Fechada",Q144="Perdida"),0,IF(Q144="Previsão vencida",3000,IF(Q144="Parada",2000,1000))+MIN(N(O144),500)+N(F144)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G144="",Q144="Fechada",Q144="Perdida"),0,IF(Q144="Previsão vencida",3,IF(Q144="Parada",2,1))*1E+13+MIN(N(O144),500)*1E+10+MIN(ROUND(N(F144),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9040,7 +9047,7 @@
         <v/>
       </c>
       <c r="R145" s="37">
-        <f>IF(OR(G145="",Q145="Fechada",Q145="Perdida"),0,IF(Q145="Previsão vencida",3000,IF(Q145="Parada",2000,1000))+MIN(N(O145),500)+N(F145)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G145="",Q145="Fechada",Q145="Perdida"),0,IF(Q145="Previsão vencida",3,IF(Q145="Parada",2,1))*1E+13+MIN(N(O145),500)*1E+10+MIN(ROUND(N(F145),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9078,7 +9085,7 @@
         <v/>
       </c>
       <c r="R146" s="37">
-        <f>IF(OR(G146="",Q146="Fechada",Q146="Perdida"),0,IF(Q146="Previsão vencida",3000,IF(Q146="Parada",2000,1000))+MIN(N(O146),500)+N(F146)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G146="",Q146="Fechada",Q146="Perdida"),0,IF(Q146="Previsão vencida",3,IF(Q146="Parada",2,1))*1E+13+MIN(N(O146),500)*1E+10+MIN(ROUND(N(F146),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9116,7 +9123,7 @@
         <v/>
       </c>
       <c r="R147" s="37">
-        <f>IF(OR(G147="",Q147="Fechada",Q147="Perdida"),0,IF(Q147="Previsão vencida",3000,IF(Q147="Parada",2000,1000))+MIN(N(O147),500)+N(F147)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G147="",Q147="Fechada",Q147="Perdida"),0,IF(Q147="Previsão vencida",3,IF(Q147="Parada",2,1))*1E+13+MIN(N(O147),500)*1E+10+MIN(ROUND(N(F147),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9154,7 +9161,7 @@
         <v/>
       </c>
       <c r="R148" s="37">
-        <f>IF(OR(G148="",Q148="Fechada",Q148="Perdida"),0,IF(Q148="Previsão vencida",3000,IF(Q148="Parada",2000,1000))+MIN(N(O148),500)+N(F148)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G148="",Q148="Fechada",Q148="Perdida"),0,IF(Q148="Previsão vencida",3,IF(Q148="Parada",2,1))*1E+13+MIN(N(O148),500)*1E+10+MIN(ROUND(N(F148),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9192,7 +9199,7 @@
         <v/>
       </c>
       <c r="R149" s="37">
-        <f>IF(OR(G149="",Q149="Fechada",Q149="Perdida"),0,IF(Q149="Previsão vencida",3000,IF(Q149="Parada",2000,1000))+MIN(N(O149),500)+N(F149)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G149="",Q149="Fechada",Q149="Perdida"),0,IF(Q149="Previsão vencida",3,IF(Q149="Parada",2,1))*1E+13+MIN(N(O149),500)*1E+10+MIN(ROUND(N(F149),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9230,7 +9237,7 @@
         <v/>
       </c>
       <c r="R150" s="37">
-        <f>IF(OR(G150="",Q150="Fechada",Q150="Perdida"),0,IF(Q150="Previsão vencida",3000,IF(Q150="Parada",2000,1000))+MIN(N(O150),500)+N(F150)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G150="",Q150="Fechada",Q150="Perdida"),0,IF(Q150="Previsão vencida",3,IF(Q150="Parada",2,1))*1E+13+MIN(N(O150),500)*1E+10+MIN(ROUND(N(F150),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9268,7 +9275,7 @@
         <v/>
       </c>
       <c r="R151" s="37">
-        <f>IF(OR(G151="",Q151="Fechada",Q151="Perdida"),0,IF(Q151="Previsão vencida",3000,IF(Q151="Parada",2000,1000))+MIN(N(O151),500)+N(F151)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G151="",Q151="Fechada",Q151="Perdida"),0,IF(Q151="Previsão vencida",3,IF(Q151="Parada",2,1))*1E+13+MIN(N(O151),500)*1E+10+MIN(ROUND(N(F151),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9306,7 +9313,7 @@
         <v/>
       </c>
       <c r="R152" s="37">
-        <f>IF(OR(G152="",Q152="Fechada",Q152="Perdida"),0,IF(Q152="Previsão vencida",3000,IF(Q152="Parada",2000,1000))+MIN(N(O152),500)+N(F152)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G152="",Q152="Fechada",Q152="Perdida"),0,IF(Q152="Previsão vencida",3,IF(Q152="Parada",2,1))*1E+13+MIN(N(O152),500)*1E+10+MIN(ROUND(N(F152),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9344,7 +9351,7 @@
         <v/>
       </c>
       <c r="R153" s="37">
-        <f>IF(OR(G153="",Q153="Fechada",Q153="Perdida"),0,IF(Q153="Previsão vencida",3000,IF(Q153="Parada",2000,1000))+MIN(N(O153),500)+N(F153)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G153="",Q153="Fechada",Q153="Perdida"),0,IF(Q153="Previsão vencida",3,IF(Q153="Parada",2,1))*1E+13+MIN(N(O153),500)*1E+10+MIN(ROUND(N(F153),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9382,7 +9389,7 @@
         <v/>
       </c>
       <c r="R154" s="37">
-        <f>IF(OR(G154="",Q154="Fechada",Q154="Perdida"),0,IF(Q154="Previsão vencida",3000,IF(Q154="Parada",2000,1000))+MIN(N(O154),500)+N(F154)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G154="",Q154="Fechada",Q154="Perdida"),0,IF(Q154="Previsão vencida",3,IF(Q154="Parada",2,1))*1E+13+MIN(N(O154),500)*1E+10+MIN(ROUND(N(F154),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9420,7 +9427,7 @@
         <v/>
       </c>
       <c r="R155" s="37">
-        <f>IF(OR(G155="",Q155="Fechada",Q155="Perdida"),0,IF(Q155="Previsão vencida",3000,IF(Q155="Parada",2000,1000))+MIN(N(O155),500)+N(F155)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G155="",Q155="Fechada",Q155="Perdida"),0,IF(Q155="Previsão vencida",3,IF(Q155="Parada",2,1))*1E+13+MIN(N(O155),500)*1E+10+MIN(ROUND(N(F155),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9458,7 +9465,7 @@
         <v/>
       </c>
       <c r="R156" s="37">
-        <f>IF(OR(G156="",Q156="Fechada",Q156="Perdida"),0,IF(Q156="Previsão vencida",3000,IF(Q156="Parada",2000,1000))+MIN(N(O156),500)+N(F156)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G156="",Q156="Fechada",Q156="Perdida"),0,IF(Q156="Previsão vencida",3,IF(Q156="Parada",2,1))*1E+13+MIN(N(O156),500)*1E+10+MIN(ROUND(N(F156),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9496,7 +9503,7 @@
         <v/>
       </c>
       <c r="R157" s="37">
-        <f>IF(OR(G157="",Q157="Fechada",Q157="Perdida"),0,IF(Q157="Previsão vencida",3000,IF(Q157="Parada",2000,1000))+MIN(N(O157),500)+N(F157)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G157="",Q157="Fechada",Q157="Perdida"),0,IF(Q157="Previsão vencida",3,IF(Q157="Parada",2,1))*1E+13+MIN(N(O157),500)*1E+10+MIN(ROUND(N(F157),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9534,7 +9541,7 @@
         <v/>
       </c>
       <c r="R158" s="37">
-        <f>IF(OR(G158="",Q158="Fechada",Q158="Perdida"),0,IF(Q158="Previsão vencida",3000,IF(Q158="Parada",2000,1000))+MIN(N(O158),500)+N(F158)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G158="",Q158="Fechada",Q158="Perdida"),0,IF(Q158="Previsão vencida",3,IF(Q158="Parada",2,1))*1E+13+MIN(N(O158),500)*1E+10+MIN(ROUND(N(F158),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9572,7 +9579,7 @@
         <v/>
       </c>
       <c r="R159" s="37">
-        <f>IF(OR(G159="",Q159="Fechada",Q159="Perdida"),0,IF(Q159="Previsão vencida",3000,IF(Q159="Parada",2000,1000))+MIN(N(O159),500)+N(F159)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G159="",Q159="Fechada",Q159="Perdida"),0,IF(Q159="Previsão vencida",3,IF(Q159="Parada",2,1))*1E+13+MIN(N(O159),500)*1E+10+MIN(ROUND(N(F159),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9610,7 +9617,7 @@
         <v/>
       </c>
       <c r="R160" s="37">
-        <f>IF(OR(G160="",Q160="Fechada",Q160="Perdida"),0,IF(Q160="Previsão vencida",3000,IF(Q160="Parada",2000,1000))+MIN(N(O160),500)+N(F160)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G160="",Q160="Fechada",Q160="Perdida"),0,IF(Q160="Previsão vencida",3,IF(Q160="Parada",2,1))*1E+13+MIN(N(O160),500)*1E+10+MIN(ROUND(N(F160),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9648,7 +9655,7 @@
         <v/>
       </c>
       <c r="R161" s="37">
-        <f>IF(OR(G161="",Q161="Fechada",Q161="Perdida"),0,IF(Q161="Previsão vencida",3000,IF(Q161="Parada",2000,1000))+MIN(N(O161),500)+N(F161)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G161="",Q161="Fechada",Q161="Perdida"),0,IF(Q161="Previsão vencida",3,IF(Q161="Parada",2,1))*1E+13+MIN(N(O161),500)*1E+10+MIN(ROUND(N(F161),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9686,7 +9693,7 @@
         <v/>
       </c>
       <c r="R162" s="37">
-        <f>IF(OR(G162="",Q162="Fechada",Q162="Perdida"),0,IF(Q162="Previsão vencida",3000,IF(Q162="Parada",2000,1000))+MIN(N(O162),500)+N(F162)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G162="",Q162="Fechada",Q162="Perdida"),0,IF(Q162="Previsão vencida",3,IF(Q162="Parada",2,1))*1E+13+MIN(N(O162),500)*1E+10+MIN(ROUND(N(F162),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9724,7 +9731,7 @@
         <v/>
       </c>
       <c r="R163" s="37">
-        <f>IF(OR(G163="",Q163="Fechada",Q163="Perdida"),0,IF(Q163="Previsão vencida",3000,IF(Q163="Parada",2000,1000))+MIN(N(O163),500)+N(F163)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G163="",Q163="Fechada",Q163="Perdida"),0,IF(Q163="Previsão vencida",3,IF(Q163="Parada",2,1))*1E+13+MIN(N(O163),500)*1E+10+MIN(ROUND(N(F163),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9762,7 +9769,7 @@
         <v/>
       </c>
       <c r="R164" s="37">
-        <f>IF(OR(G164="",Q164="Fechada",Q164="Perdida"),0,IF(Q164="Previsão vencida",3000,IF(Q164="Parada",2000,1000))+MIN(N(O164),500)+N(F164)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G164="",Q164="Fechada",Q164="Perdida"),0,IF(Q164="Previsão vencida",3,IF(Q164="Parada",2,1))*1E+13+MIN(N(O164),500)*1E+10+MIN(ROUND(N(F164),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9800,7 +9807,7 @@
         <v/>
       </c>
       <c r="R165" s="37">
-        <f>IF(OR(G165="",Q165="Fechada",Q165="Perdida"),0,IF(Q165="Previsão vencida",3000,IF(Q165="Parada",2000,1000))+MIN(N(O165),500)+N(F165)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G165="",Q165="Fechada",Q165="Perdida"),0,IF(Q165="Previsão vencida",3,IF(Q165="Parada",2,1))*1E+13+MIN(N(O165),500)*1E+10+MIN(ROUND(N(F165),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9838,7 +9845,7 @@
         <v/>
       </c>
       <c r="R166" s="37">
-        <f>IF(OR(G166="",Q166="Fechada",Q166="Perdida"),0,IF(Q166="Previsão vencida",3000,IF(Q166="Parada",2000,1000))+MIN(N(O166),500)+N(F166)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G166="",Q166="Fechada",Q166="Perdida"),0,IF(Q166="Previsão vencida",3,IF(Q166="Parada",2,1))*1E+13+MIN(N(O166),500)*1E+10+MIN(ROUND(N(F166),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9876,7 +9883,7 @@
         <v/>
       </c>
       <c r="R167" s="37">
-        <f>IF(OR(G167="",Q167="Fechada",Q167="Perdida"),0,IF(Q167="Previsão vencida",3000,IF(Q167="Parada",2000,1000))+MIN(N(O167),500)+N(F167)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G167="",Q167="Fechada",Q167="Perdida"),0,IF(Q167="Previsão vencida",3,IF(Q167="Parada",2,1))*1E+13+MIN(N(O167),500)*1E+10+MIN(ROUND(N(F167),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9914,7 +9921,7 @@
         <v/>
       </c>
       <c r="R168" s="37">
-        <f>IF(OR(G168="",Q168="Fechada",Q168="Perdida"),0,IF(Q168="Previsão vencida",3000,IF(Q168="Parada",2000,1000))+MIN(N(O168),500)+N(F168)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G168="",Q168="Fechada",Q168="Perdida"),0,IF(Q168="Previsão vencida",3,IF(Q168="Parada",2,1))*1E+13+MIN(N(O168),500)*1E+10+MIN(ROUND(N(F168),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9952,7 +9959,7 @@
         <v/>
       </c>
       <c r="R169" s="37">
-        <f>IF(OR(G169="",Q169="Fechada",Q169="Perdida"),0,IF(Q169="Previsão vencida",3000,IF(Q169="Parada",2000,1000))+MIN(N(O169),500)+N(F169)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G169="",Q169="Fechada",Q169="Perdida"),0,IF(Q169="Previsão vencida",3,IF(Q169="Parada",2,1))*1E+13+MIN(N(O169),500)*1E+10+MIN(ROUND(N(F169),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9990,7 +9997,7 @@
         <v/>
       </c>
       <c r="R170" s="37">
-        <f>IF(OR(G170="",Q170="Fechada",Q170="Perdida"),0,IF(Q170="Previsão vencida",3000,IF(Q170="Parada",2000,1000))+MIN(N(O170),500)+N(F170)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G170="",Q170="Fechada",Q170="Perdida"),0,IF(Q170="Previsão vencida",3,IF(Q170="Parada",2,1))*1E+13+MIN(N(O170),500)*1E+10+MIN(ROUND(N(F170),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10028,7 +10035,7 @@
         <v/>
       </c>
       <c r="R171" s="37">
-        <f>IF(OR(G171="",Q171="Fechada",Q171="Perdida"),0,IF(Q171="Previsão vencida",3000,IF(Q171="Parada",2000,1000))+MIN(N(O171),500)+N(F171)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G171="",Q171="Fechada",Q171="Perdida"),0,IF(Q171="Previsão vencida",3,IF(Q171="Parada",2,1))*1E+13+MIN(N(O171),500)*1E+10+MIN(ROUND(N(F171),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10066,7 +10073,7 @@
         <v/>
       </c>
       <c r="R172" s="37">
-        <f>IF(OR(G172="",Q172="Fechada",Q172="Perdida"),0,IF(Q172="Previsão vencida",3000,IF(Q172="Parada",2000,1000))+MIN(N(O172),500)+N(F172)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G172="",Q172="Fechada",Q172="Perdida"),0,IF(Q172="Previsão vencida",3,IF(Q172="Parada",2,1))*1E+13+MIN(N(O172),500)*1E+10+MIN(ROUND(N(F172),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10104,7 +10111,7 @@
         <v/>
       </c>
       <c r="R173" s="37">
-        <f>IF(OR(G173="",Q173="Fechada",Q173="Perdida"),0,IF(Q173="Previsão vencida",3000,IF(Q173="Parada",2000,1000))+MIN(N(O173),500)+N(F173)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G173="",Q173="Fechada",Q173="Perdida"),0,IF(Q173="Previsão vencida",3,IF(Q173="Parada",2,1))*1E+13+MIN(N(O173),500)*1E+10+MIN(ROUND(N(F173),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10142,7 +10149,7 @@
         <v/>
       </c>
       <c r="R174" s="37">
-        <f>IF(OR(G174="",Q174="Fechada",Q174="Perdida"),0,IF(Q174="Previsão vencida",3000,IF(Q174="Parada",2000,1000))+MIN(N(O174),500)+N(F174)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G174="",Q174="Fechada",Q174="Perdida"),0,IF(Q174="Previsão vencida",3,IF(Q174="Parada",2,1))*1E+13+MIN(N(O174),500)*1E+10+MIN(ROUND(N(F174),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10180,7 +10187,7 @@
         <v/>
       </c>
       <c r="R175" s="37">
-        <f>IF(OR(G175="",Q175="Fechada",Q175="Perdida"),0,IF(Q175="Previsão vencida",3000,IF(Q175="Parada",2000,1000))+MIN(N(O175),500)+N(F175)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G175="",Q175="Fechada",Q175="Perdida"),0,IF(Q175="Previsão vencida",3,IF(Q175="Parada",2,1))*1E+13+MIN(N(O175),500)*1E+10+MIN(ROUND(N(F175),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10218,7 +10225,7 @@
         <v/>
       </c>
       <c r="R176" s="37">
-        <f>IF(OR(G176="",Q176="Fechada",Q176="Perdida"),0,IF(Q176="Previsão vencida",3000,IF(Q176="Parada",2000,1000))+MIN(N(O176),500)+N(F176)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G176="",Q176="Fechada",Q176="Perdida"),0,IF(Q176="Previsão vencida",3,IF(Q176="Parada",2,1))*1E+13+MIN(N(O176),500)*1E+10+MIN(ROUND(N(F176),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10256,7 +10263,7 @@
         <v/>
       </c>
       <c r="R177" s="37">
-        <f>IF(OR(G177="",Q177="Fechada",Q177="Perdida"),0,IF(Q177="Previsão vencida",3000,IF(Q177="Parada",2000,1000))+MIN(N(O177),500)+N(F177)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G177="",Q177="Fechada",Q177="Perdida"),0,IF(Q177="Previsão vencida",3,IF(Q177="Parada",2,1))*1E+13+MIN(N(O177),500)*1E+10+MIN(ROUND(N(F177),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10294,7 +10301,7 @@
         <v/>
       </c>
       <c r="R178" s="37">
-        <f>IF(OR(G178="",Q178="Fechada",Q178="Perdida"),0,IF(Q178="Previsão vencida",3000,IF(Q178="Parada",2000,1000))+MIN(N(O178),500)+N(F178)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G178="",Q178="Fechada",Q178="Perdida"),0,IF(Q178="Previsão vencida",3,IF(Q178="Parada",2,1))*1E+13+MIN(N(O178),500)*1E+10+MIN(ROUND(N(F178),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10332,7 +10339,7 @@
         <v/>
       </c>
       <c r="R179" s="37">
-        <f>IF(OR(G179="",Q179="Fechada",Q179="Perdida"),0,IF(Q179="Previsão vencida",3000,IF(Q179="Parada",2000,1000))+MIN(N(O179),500)+N(F179)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G179="",Q179="Fechada",Q179="Perdida"),0,IF(Q179="Previsão vencida",3,IF(Q179="Parada",2,1))*1E+13+MIN(N(O179),500)*1E+10+MIN(ROUND(N(F179),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10370,7 +10377,7 @@
         <v/>
       </c>
       <c r="R180" s="37">
-        <f>IF(OR(G180="",Q180="Fechada",Q180="Perdida"),0,IF(Q180="Previsão vencida",3000,IF(Q180="Parada",2000,1000))+MIN(N(O180),500)+N(F180)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G180="",Q180="Fechada",Q180="Perdida"),0,IF(Q180="Previsão vencida",3,IF(Q180="Parada",2,1))*1E+13+MIN(N(O180),500)*1E+10+MIN(ROUND(N(F180),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10408,7 +10415,7 @@
         <v/>
       </c>
       <c r="R181" s="37">
-        <f>IF(OR(G181="",Q181="Fechada",Q181="Perdida"),0,IF(Q181="Previsão vencida",3000,IF(Q181="Parada",2000,1000))+MIN(N(O181),500)+N(F181)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G181="",Q181="Fechada",Q181="Perdida"),0,IF(Q181="Previsão vencida",3,IF(Q181="Parada",2,1))*1E+13+MIN(N(O181),500)*1E+10+MIN(ROUND(N(F181),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10446,7 +10453,7 @@
         <v/>
       </c>
       <c r="R182" s="37">
-        <f>IF(OR(G182="",Q182="Fechada",Q182="Perdida"),0,IF(Q182="Previsão vencida",3000,IF(Q182="Parada",2000,1000))+MIN(N(O182),500)+N(F182)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G182="",Q182="Fechada",Q182="Perdida"),0,IF(Q182="Previsão vencida",3,IF(Q182="Parada",2,1))*1E+13+MIN(N(O182),500)*1E+10+MIN(ROUND(N(F182),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10484,7 +10491,7 @@
         <v/>
       </c>
       <c r="R183" s="37">
-        <f>IF(OR(G183="",Q183="Fechada",Q183="Perdida"),0,IF(Q183="Previsão vencida",3000,IF(Q183="Parada",2000,1000))+MIN(N(O183),500)+N(F183)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G183="",Q183="Fechada",Q183="Perdida"),0,IF(Q183="Previsão vencida",3,IF(Q183="Parada",2,1))*1E+13+MIN(N(O183),500)*1E+10+MIN(ROUND(N(F183),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10522,7 +10529,7 @@
         <v/>
       </c>
       <c r="R184" s="37">
-        <f>IF(OR(G184="",Q184="Fechada",Q184="Perdida"),0,IF(Q184="Previsão vencida",3000,IF(Q184="Parada",2000,1000))+MIN(N(O184),500)+N(F184)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G184="",Q184="Fechada",Q184="Perdida"),0,IF(Q184="Previsão vencida",3,IF(Q184="Parada",2,1))*1E+13+MIN(N(O184),500)*1E+10+MIN(ROUND(N(F184),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10560,7 +10567,7 @@
         <v/>
       </c>
       <c r="R185" s="37">
-        <f>IF(OR(G185="",Q185="Fechada",Q185="Perdida"),0,IF(Q185="Previsão vencida",3000,IF(Q185="Parada",2000,1000))+MIN(N(O185),500)+N(F185)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G185="",Q185="Fechada",Q185="Perdida"),0,IF(Q185="Previsão vencida",3,IF(Q185="Parada",2,1))*1E+13+MIN(N(O185),500)*1E+10+MIN(ROUND(N(F185),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10598,7 +10605,7 @@
         <v/>
       </c>
       <c r="R186" s="37">
-        <f>IF(OR(G186="",Q186="Fechada",Q186="Perdida"),0,IF(Q186="Previsão vencida",3000,IF(Q186="Parada",2000,1000))+MIN(N(O186),500)+N(F186)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G186="",Q186="Fechada",Q186="Perdida"),0,IF(Q186="Previsão vencida",3,IF(Q186="Parada",2,1))*1E+13+MIN(N(O186),500)*1E+10+MIN(ROUND(N(F186),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10636,7 +10643,7 @@
         <v/>
       </c>
       <c r="R187" s="37">
-        <f>IF(OR(G187="",Q187="Fechada",Q187="Perdida"),0,IF(Q187="Previsão vencida",3000,IF(Q187="Parada",2000,1000))+MIN(N(O187),500)+N(F187)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G187="",Q187="Fechada",Q187="Perdida"),0,IF(Q187="Previsão vencida",3,IF(Q187="Parada",2,1))*1E+13+MIN(N(O187),500)*1E+10+MIN(ROUND(N(F187),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10674,7 +10681,7 @@
         <v/>
       </c>
       <c r="R188" s="37">
-        <f>IF(OR(G188="",Q188="Fechada",Q188="Perdida"),0,IF(Q188="Previsão vencida",3000,IF(Q188="Parada",2000,1000))+MIN(N(O188),500)+N(F188)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G188="",Q188="Fechada",Q188="Perdida"),0,IF(Q188="Previsão vencida",3,IF(Q188="Parada",2,1))*1E+13+MIN(N(O188),500)*1E+10+MIN(ROUND(N(F188),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10712,7 +10719,7 @@
         <v/>
       </c>
       <c r="R189" s="37">
-        <f>IF(OR(G189="",Q189="Fechada",Q189="Perdida"),0,IF(Q189="Previsão vencida",3000,IF(Q189="Parada",2000,1000))+MIN(N(O189),500)+N(F189)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G189="",Q189="Fechada",Q189="Perdida"),0,IF(Q189="Previsão vencida",3,IF(Q189="Parada",2,1))*1E+13+MIN(N(O189),500)*1E+10+MIN(ROUND(N(F189),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10750,7 +10757,7 @@
         <v/>
       </c>
       <c r="R190" s="37">
-        <f>IF(OR(G190="",Q190="Fechada",Q190="Perdida"),0,IF(Q190="Previsão vencida",3000,IF(Q190="Parada",2000,1000))+MIN(N(O190),500)+N(F190)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G190="",Q190="Fechada",Q190="Perdida"),0,IF(Q190="Previsão vencida",3,IF(Q190="Parada",2,1))*1E+13+MIN(N(O190),500)*1E+10+MIN(ROUND(N(F190),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10788,7 +10795,7 @@
         <v/>
       </c>
       <c r="R191" s="37">
-        <f>IF(OR(G191="",Q191="Fechada",Q191="Perdida"),0,IF(Q191="Previsão vencida",3000,IF(Q191="Parada",2000,1000))+MIN(N(O191),500)+N(F191)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G191="",Q191="Fechada",Q191="Perdida"),0,IF(Q191="Previsão vencida",3,IF(Q191="Parada",2,1))*1E+13+MIN(N(O191),500)*1E+10+MIN(ROUND(N(F191),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10826,7 +10833,7 @@
         <v/>
       </c>
       <c r="R192" s="37">
-        <f>IF(OR(G192="",Q192="Fechada",Q192="Perdida"),0,IF(Q192="Previsão vencida",3000,IF(Q192="Parada",2000,1000))+MIN(N(O192),500)+N(F192)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G192="",Q192="Fechada",Q192="Perdida"),0,IF(Q192="Previsão vencida",3,IF(Q192="Parada",2,1))*1E+13+MIN(N(O192),500)*1E+10+MIN(ROUND(N(F192),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10864,7 +10871,7 @@
         <v/>
       </c>
       <c r="R193" s="37">
-        <f>IF(OR(G193="",Q193="Fechada",Q193="Perdida"),0,IF(Q193="Previsão vencida",3000,IF(Q193="Parada",2000,1000))+MIN(N(O193),500)+N(F193)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G193="",Q193="Fechada",Q193="Perdida"),0,IF(Q193="Previsão vencida",3,IF(Q193="Parada",2,1))*1E+13+MIN(N(O193),500)*1E+10+MIN(ROUND(N(F193),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10902,7 +10909,7 @@
         <v/>
       </c>
       <c r="R194" s="37">
-        <f>IF(OR(G194="",Q194="Fechada",Q194="Perdida"),0,IF(Q194="Previsão vencida",3000,IF(Q194="Parada",2000,1000))+MIN(N(O194),500)+N(F194)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G194="",Q194="Fechada",Q194="Perdida"),0,IF(Q194="Previsão vencida",3,IF(Q194="Parada",2,1))*1E+13+MIN(N(O194),500)*1E+10+MIN(ROUND(N(F194),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10940,7 +10947,7 @@
         <v/>
       </c>
       <c r="R195" s="37">
-        <f>IF(OR(G195="",Q195="Fechada",Q195="Perdida"),0,IF(Q195="Previsão vencida",3000,IF(Q195="Parada",2000,1000))+MIN(N(O195),500)+N(F195)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G195="",Q195="Fechada",Q195="Perdida"),0,IF(Q195="Previsão vencida",3,IF(Q195="Parada",2,1))*1E+13+MIN(N(O195),500)*1E+10+MIN(ROUND(N(F195),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10978,7 +10985,7 @@
         <v/>
       </c>
       <c r="R196" s="37">
-        <f>IF(OR(G196="",Q196="Fechada",Q196="Perdida"),0,IF(Q196="Previsão vencida",3000,IF(Q196="Parada",2000,1000))+MIN(N(O196),500)+N(F196)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G196="",Q196="Fechada",Q196="Perdida"),0,IF(Q196="Previsão vencida",3,IF(Q196="Parada",2,1))*1E+13+MIN(N(O196),500)*1E+10+MIN(ROUND(N(F196),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11016,7 +11023,7 @@
         <v/>
       </c>
       <c r="R197" s="37">
-        <f>IF(OR(G197="",Q197="Fechada",Q197="Perdida"),0,IF(Q197="Previsão vencida",3000,IF(Q197="Parada",2000,1000))+MIN(N(O197),500)+N(F197)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G197="",Q197="Fechada",Q197="Perdida"),0,IF(Q197="Previsão vencida",3,IF(Q197="Parada",2,1))*1E+13+MIN(N(O197),500)*1E+10+MIN(ROUND(N(F197),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11054,7 +11061,7 @@
         <v/>
       </c>
       <c r="R198" s="37">
-        <f>IF(OR(G198="",Q198="Fechada",Q198="Perdida"),0,IF(Q198="Previsão vencida",3000,IF(Q198="Parada",2000,1000))+MIN(N(O198),500)+N(F198)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G198="",Q198="Fechada",Q198="Perdida"),0,IF(Q198="Previsão vencida",3,IF(Q198="Parada",2,1))*1E+13+MIN(N(O198),500)*1E+10+MIN(ROUND(N(F198),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11092,7 +11099,7 @@
         <v/>
       </c>
       <c r="R199" s="37">
-        <f>IF(OR(G199="",Q199="Fechada",Q199="Perdida"),0,IF(Q199="Previsão vencida",3000,IF(Q199="Parada",2000,1000))+MIN(N(O199),500)+N(F199)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G199="",Q199="Fechada",Q199="Perdida"),0,IF(Q199="Previsão vencida",3,IF(Q199="Parada",2,1))*1E+13+MIN(N(O199),500)*1E+10+MIN(ROUND(N(F199),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11130,7 +11137,7 @@
         <v/>
       </c>
       <c r="R200" s="37">
-        <f>IF(OR(G200="",Q200="Fechada",Q200="Perdida"),0,IF(Q200="Previsão vencida",3000,IF(Q200="Parada",2000,1000))+MIN(N(O200),500)+N(F200)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G200="",Q200="Fechada",Q200="Perdida"),0,IF(Q200="Previsão vencida",3,IF(Q200="Parada",2,1))*1E+13+MIN(N(O200),500)*1E+10+MIN(ROUND(N(F200),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11168,7 +11175,7 @@
         <v/>
       </c>
       <c r="R201" s="37">
-        <f>IF(OR(G201="",Q201="Fechada",Q201="Perdida"),0,IF(Q201="Previsão vencida",3000,IF(Q201="Parada",2000,1000))+MIN(N(O201),500)+N(F201)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G201="",Q201="Fechada",Q201="Perdida"),0,IF(Q201="Previsão vencida",3,IF(Q201="Parada",2,1))*1E+13+MIN(N(O201),500)*1E+10+MIN(ROUND(N(F201),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11206,7 +11213,7 @@
         <v/>
       </c>
       <c r="R202" s="37">
-        <f>IF(OR(G202="",Q202="Fechada",Q202="Perdida"),0,IF(Q202="Previsão vencida",3000,IF(Q202="Parada",2000,1000))+MIN(N(O202),500)+N(F202)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G202="",Q202="Fechada",Q202="Perdida"),0,IF(Q202="Previsão vencida",3,IF(Q202="Parada",2,1))*1E+13+MIN(N(O202),500)*1E+10+MIN(ROUND(N(F202),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11244,7 +11251,7 @@
         <v/>
       </c>
       <c r="R203" s="37">
-        <f>IF(OR(G203="",Q203="Fechada",Q203="Perdida"),0,IF(Q203="Previsão vencida",3000,IF(Q203="Parada",2000,1000))+MIN(N(O203),500)+N(F203)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G203="",Q203="Fechada",Q203="Perdida"),0,IF(Q203="Previsão vencida",3,IF(Q203="Parada",2,1))*1E+13+MIN(N(O203),500)*1E+10+MIN(ROUND(N(F203),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11282,7 +11289,7 @@
         <v/>
       </c>
       <c r="R204" s="37">
-        <f>IF(OR(G204="",Q204="Fechada",Q204="Perdida"),0,IF(Q204="Previsão vencida",3000,IF(Q204="Parada",2000,1000))+MIN(N(O204),500)+N(F204)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G204="",Q204="Fechada",Q204="Perdida"),0,IF(Q204="Previsão vencida",3,IF(Q204="Parada",2,1))*1E+13+MIN(N(O204),500)*1E+10+MIN(ROUND(N(F204),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11320,7 +11327,7 @@
         <v/>
       </c>
       <c r="R205" s="37">
-        <f>IF(OR(G205="",Q205="Fechada",Q205="Perdida"),0,IF(Q205="Previsão vencida",3000,IF(Q205="Parada",2000,1000))+MIN(N(O205),500)+N(F205)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G205="",Q205="Fechada",Q205="Perdida"),0,IF(Q205="Previsão vencida",3,IF(Q205="Parada",2,1))*1E+13+MIN(N(O205),500)*1E+10+MIN(ROUND(N(F205),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11358,7 +11365,7 @@
         <v/>
       </c>
       <c r="R206" s="37">
-        <f>IF(OR(G206="",Q206="Fechada",Q206="Perdida"),0,IF(Q206="Previsão vencida",3000,IF(Q206="Parada",2000,1000))+MIN(N(O206),500)+N(F206)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G206="",Q206="Fechada",Q206="Perdida"),0,IF(Q206="Previsão vencida",3,IF(Q206="Parada",2,1))*1E+13+MIN(N(O206),500)*1E+10+MIN(ROUND(N(F206),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11396,7 +11403,7 @@
         <v/>
       </c>
       <c r="R207" s="37">
-        <f>IF(OR(G207="",Q207="Fechada",Q207="Perdida"),0,IF(Q207="Previsão vencida",3000,IF(Q207="Parada",2000,1000))+MIN(N(O207),500)+N(F207)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G207="",Q207="Fechada",Q207="Perdida"),0,IF(Q207="Previsão vencida",3,IF(Q207="Parada",2,1))*1E+13+MIN(N(O207),500)*1E+10+MIN(ROUND(N(F207),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11434,7 +11441,7 @@
         <v/>
       </c>
       <c r="R208" s="37">
-        <f>IF(OR(G208="",Q208="Fechada",Q208="Perdida"),0,IF(Q208="Previsão vencida",3000,IF(Q208="Parada",2000,1000))+MIN(N(O208),500)+N(F208)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G208="",Q208="Fechada",Q208="Perdida"),0,IF(Q208="Previsão vencida",3,IF(Q208="Parada",2,1))*1E+13+MIN(N(O208),500)*1E+10+MIN(ROUND(N(F208),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11472,7 +11479,7 @@
         <v/>
       </c>
       <c r="R209" s="37">
-        <f>IF(OR(G209="",Q209="Fechada",Q209="Perdida"),0,IF(Q209="Previsão vencida",3000,IF(Q209="Parada",2000,1000))+MIN(N(O209),500)+N(F209)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G209="",Q209="Fechada",Q209="Perdida"),0,IF(Q209="Previsão vencida",3,IF(Q209="Parada",2,1))*1E+13+MIN(N(O209),500)*1E+10+MIN(ROUND(N(F209),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11510,7 +11517,7 @@
         <v/>
       </c>
       <c r="R210" s="37">
-        <f>IF(OR(G210="",Q210="Fechada",Q210="Perdida"),0,IF(Q210="Previsão vencida",3000,IF(Q210="Parada",2000,1000))+MIN(N(O210),500)+N(F210)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G210="",Q210="Fechada",Q210="Perdida"),0,IF(Q210="Previsão vencida",3,IF(Q210="Parada",2,1))*1E+13+MIN(N(O210),500)*1E+10+MIN(ROUND(N(F210),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11548,7 +11555,7 @@
         <v/>
       </c>
       <c r="R211" s="37">
-        <f>IF(OR(G211="",Q211="Fechada",Q211="Perdida"),0,IF(Q211="Previsão vencida",3000,IF(Q211="Parada",2000,1000))+MIN(N(O211),500)+N(F211)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G211="",Q211="Fechada",Q211="Perdida"),0,IF(Q211="Previsão vencida",3,IF(Q211="Parada",2,1))*1E+13+MIN(N(O211),500)*1E+10+MIN(ROUND(N(F211),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11586,7 +11593,7 @@
         <v/>
       </c>
       <c r="R212" s="37">
-        <f>IF(OR(G212="",Q212="Fechada",Q212="Perdida"),0,IF(Q212="Previsão vencida",3000,IF(Q212="Parada",2000,1000))+MIN(N(O212),500)+N(F212)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G212="",Q212="Fechada",Q212="Perdida"),0,IF(Q212="Previsão vencida",3,IF(Q212="Parada",2,1))*1E+13+MIN(N(O212),500)*1E+10+MIN(ROUND(N(F212),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11624,7 +11631,7 @@
         <v/>
       </c>
       <c r="R213" s="37">
-        <f>IF(OR(G213="",Q213="Fechada",Q213="Perdida"),0,IF(Q213="Previsão vencida",3000,IF(Q213="Parada",2000,1000))+MIN(N(O213),500)+N(F213)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G213="",Q213="Fechada",Q213="Perdida"),0,IF(Q213="Previsão vencida",3,IF(Q213="Parada",2,1))*1E+13+MIN(N(O213),500)*1E+10+MIN(ROUND(N(F213),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11662,7 +11669,7 @@
         <v/>
       </c>
       <c r="R214" s="37">
-        <f>IF(OR(G214="",Q214="Fechada",Q214="Perdida"),0,IF(Q214="Previsão vencida",3000,IF(Q214="Parada",2000,1000))+MIN(N(O214),500)+N(F214)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G214="",Q214="Fechada",Q214="Perdida"),0,IF(Q214="Previsão vencida",3,IF(Q214="Parada",2,1))*1E+13+MIN(N(O214),500)*1E+10+MIN(ROUND(N(F214),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11700,7 +11707,7 @@
         <v/>
       </c>
       <c r="R215" s="37">
-        <f>IF(OR(G215="",Q215="Fechada",Q215="Perdida"),0,IF(Q215="Previsão vencida",3000,IF(Q215="Parada",2000,1000))+MIN(N(O215),500)+N(F215)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G215="",Q215="Fechada",Q215="Perdida"),0,IF(Q215="Previsão vencida",3,IF(Q215="Parada",2,1))*1E+13+MIN(N(O215),500)*1E+10+MIN(ROUND(N(F215),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11738,7 +11745,7 @@
         <v/>
       </c>
       <c r="R216" s="37">
-        <f>IF(OR(G216="",Q216="Fechada",Q216="Perdida"),0,IF(Q216="Previsão vencida",3000,IF(Q216="Parada",2000,1000))+MIN(N(O216),500)+N(F216)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G216="",Q216="Fechada",Q216="Perdida"),0,IF(Q216="Previsão vencida",3,IF(Q216="Parada",2,1))*1E+13+MIN(N(O216),500)*1E+10+MIN(ROUND(N(F216),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11776,7 +11783,7 @@
         <v/>
       </c>
       <c r="R217" s="37">
-        <f>IF(OR(G217="",Q217="Fechada",Q217="Perdida"),0,IF(Q217="Previsão vencida",3000,IF(Q217="Parada",2000,1000))+MIN(N(O217),500)+N(F217)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G217="",Q217="Fechada",Q217="Perdida"),0,IF(Q217="Previsão vencida",3,IF(Q217="Parada",2,1))*1E+13+MIN(N(O217),500)*1E+10+MIN(ROUND(N(F217),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11814,7 +11821,7 @@
         <v/>
       </c>
       <c r="R218" s="37">
-        <f>IF(OR(G218="",Q218="Fechada",Q218="Perdida"),0,IF(Q218="Previsão vencida",3000,IF(Q218="Parada",2000,1000))+MIN(N(O218),500)+N(F218)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G218="",Q218="Fechada",Q218="Perdida"),0,IF(Q218="Previsão vencida",3,IF(Q218="Parada",2,1))*1E+13+MIN(N(O218),500)*1E+10+MIN(ROUND(N(F218),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11852,7 +11859,7 @@
         <v/>
       </c>
       <c r="R219" s="37">
-        <f>IF(OR(G219="",Q219="Fechada",Q219="Perdida"),0,IF(Q219="Previsão vencida",3000,IF(Q219="Parada",2000,1000))+MIN(N(O219),500)+N(F219)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G219="",Q219="Fechada",Q219="Perdida"),0,IF(Q219="Previsão vencida",3,IF(Q219="Parada",2,1))*1E+13+MIN(N(O219),500)*1E+10+MIN(ROUND(N(F219),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11890,7 +11897,7 @@
         <v/>
       </c>
       <c r="R220" s="37">
-        <f>IF(OR(G220="",Q220="Fechada",Q220="Perdida"),0,IF(Q220="Previsão vencida",3000,IF(Q220="Parada",2000,1000))+MIN(N(O220),500)+N(F220)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G220="",Q220="Fechada",Q220="Perdida"),0,IF(Q220="Previsão vencida",3,IF(Q220="Parada",2,1))*1E+13+MIN(N(O220),500)*1E+10+MIN(ROUND(N(F220),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11928,7 +11935,7 @@
         <v/>
       </c>
       <c r="R221" s="37">
-        <f>IF(OR(G221="",Q221="Fechada",Q221="Perdida"),0,IF(Q221="Previsão vencida",3000,IF(Q221="Parada",2000,1000))+MIN(N(O221),500)+N(F221)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G221="",Q221="Fechada",Q221="Perdida"),0,IF(Q221="Previsão vencida",3,IF(Q221="Parada",2,1))*1E+13+MIN(N(O221),500)*1E+10+MIN(ROUND(N(F221),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11966,7 +11973,7 @@
         <v/>
       </c>
       <c r="R222" s="37">
-        <f>IF(OR(G222="",Q222="Fechada",Q222="Perdida"),0,IF(Q222="Previsão vencida",3000,IF(Q222="Parada",2000,1000))+MIN(N(O222),500)+N(F222)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G222="",Q222="Fechada",Q222="Perdida"),0,IF(Q222="Previsão vencida",3,IF(Q222="Parada",2,1))*1E+13+MIN(N(O222),500)*1E+10+MIN(ROUND(N(F222),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12004,7 +12011,7 @@
         <v/>
       </c>
       <c r="R223" s="37">
-        <f>IF(OR(G223="",Q223="Fechada",Q223="Perdida"),0,IF(Q223="Previsão vencida",3000,IF(Q223="Parada",2000,1000))+MIN(N(O223),500)+N(F223)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G223="",Q223="Fechada",Q223="Perdida"),0,IF(Q223="Previsão vencida",3,IF(Q223="Parada",2,1))*1E+13+MIN(N(O223),500)*1E+10+MIN(ROUND(N(F223),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12042,7 +12049,7 @@
         <v/>
       </c>
       <c r="R224" s="37">
-        <f>IF(OR(G224="",Q224="Fechada",Q224="Perdida"),0,IF(Q224="Previsão vencida",3000,IF(Q224="Parada",2000,1000))+MIN(N(O224),500)+N(F224)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G224="",Q224="Fechada",Q224="Perdida"),0,IF(Q224="Previsão vencida",3,IF(Q224="Parada",2,1))*1E+13+MIN(N(O224),500)*1E+10+MIN(ROUND(N(F224),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12080,7 +12087,7 @@
         <v/>
       </c>
       <c r="R225" s="37">
-        <f>IF(OR(G225="",Q225="Fechada",Q225="Perdida"),0,IF(Q225="Previsão vencida",3000,IF(Q225="Parada",2000,1000))+MIN(N(O225),500)+N(F225)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G225="",Q225="Fechada",Q225="Perdida"),0,IF(Q225="Previsão vencida",3,IF(Q225="Parada",2,1))*1E+13+MIN(N(O225),500)*1E+10+MIN(ROUND(N(F225),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12118,7 +12125,7 @@
         <v/>
       </c>
       <c r="R226" s="37">
-        <f>IF(OR(G226="",Q226="Fechada",Q226="Perdida"),0,IF(Q226="Previsão vencida",3000,IF(Q226="Parada",2000,1000))+MIN(N(O226),500)+N(F226)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G226="",Q226="Fechada",Q226="Perdida"),0,IF(Q226="Previsão vencida",3,IF(Q226="Parada",2,1))*1E+13+MIN(N(O226),500)*1E+10+MIN(ROUND(N(F226),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12156,7 +12163,7 @@
         <v/>
       </c>
       <c r="R227" s="37">
-        <f>IF(OR(G227="",Q227="Fechada",Q227="Perdida"),0,IF(Q227="Previsão vencida",3000,IF(Q227="Parada",2000,1000))+MIN(N(O227),500)+N(F227)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G227="",Q227="Fechada",Q227="Perdida"),0,IF(Q227="Previsão vencida",3,IF(Q227="Parada",2,1))*1E+13+MIN(N(O227),500)*1E+10+MIN(ROUND(N(F227),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12194,7 +12201,7 @@
         <v/>
       </c>
       <c r="R228" s="37">
-        <f>IF(OR(G228="",Q228="Fechada",Q228="Perdida"),0,IF(Q228="Previsão vencida",3000,IF(Q228="Parada",2000,1000))+MIN(N(O228),500)+N(F228)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G228="",Q228="Fechada",Q228="Perdida"),0,IF(Q228="Previsão vencida",3,IF(Q228="Parada",2,1))*1E+13+MIN(N(O228),500)*1E+10+MIN(ROUND(N(F228),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12232,7 +12239,7 @@
         <v/>
       </c>
       <c r="R229" s="37">
-        <f>IF(OR(G229="",Q229="Fechada",Q229="Perdida"),0,IF(Q229="Previsão vencida",3000,IF(Q229="Parada",2000,1000))+MIN(N(O229),500)+N(F229)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G229="",Q229="Fechada",Q229="Perdida"),0,IF(Q229="Previsão vencida",3,IF(Q229="Parada",2,1))*1E+13+MIN(N(O229),500)*1E+10+MIN(ROUND(N(F229),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12270,7 +12277,7 @@
         <v/>
       </c>
       <c r="R230" s="37">
-        <f>IF(OR(G230="",Q230="Fechada",Q230="Perdida"),0,IF(Q230="Previsão vencida",3000,IF(Q230="Parada",2000,1000))+MIN(N(O230),500)+N(F230)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G230="",Q230="Fechada",Q230="Perdida"),0,IF(Q230="Previsão vencida",3,IF(Q230="Parada",2,1))*1E+13+MIN(N(O230),500)*1E+10+MIN(ROUND(N(F230),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12308,7 +12315,7 @@
         <v/>
       </c>
       <c r="R231" s="37">
-        <f>IF(OR(G231="",Q231="Fechada",Q231="Perdida"),0,IF(Q231="Previsão vencida",3000,IF(Q231="Parada",2000,1000))+MIN(N(O231),500)+N(F231)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G231="",Q231="Fechada",Q231="Perdida"),0,IF(Q231="Previsão vencida",3,IF(Q231="Parada",2,1))*1E+13+MIN(N(O231),500)*1E+10+MIN(ROUND(N(F231),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12346,7 +12353,7 @@
         <v/>
       </c>
       <c r="R232" s="37">
-        <f>IF(OR(G232="",Q232="Fechada",Q232="Perdida"),0,IF(Q232="Previsão vencida",3000,IF(Q232="Parada",2000,1000))+MIN(N(O232),500)+N(F232)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G232="",Q232="Fechada",Q232="Perdida"),0,IF(Q232="Previsão vencida",3,IF(Q232="Parada",2,1))*1E+13+MIN(N(O232),500)*1E+10+MIN(ROUND(N(F232),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12384,7 +12391,7 @@
         <v/>
       </c>
       <c r="R233" s="37">
-        <f>IF(OR(G233="",Q233="Fechada",Q233="Perdida"),0,IF(Q233="Previsão vencida",3000,IF(Q233="Parada",2000,1000))+MIN(N(O233),500)+N(F233)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G233="",Q233="Fechada",Q233="Perdida"),0,IF(Q233="Previsão vencida",3,IF(Q233="Parada",2,1))*1E+13+MIN(N(O233),500)*1E+10+MIN(ROUND(N(F233),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12422,7 +12429,7 @@
         <v/>
       </c>
       <c r="R234" s="37">
-        <f>IF(OR(G234="",Q234="Fechada",Q234="Perdida"),0,IF(Q234="Previsão vencida",3000,IF(Q234="Parada",2000,1000))+MIN(N(O234),500)+N(F234)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G234="",Q234="Fechada",Q234="Perdida"),0,IF(Q234="Previsão vencida",3,IF(Q234="Parada",2,1))*1E+13+MIN(N(O234),500)*1E+10+MIN(ROUND(N(F234),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12460,7 +12467,7 @@
         <v/>
       </c>
       <c r="R235" s="37">
-        <f>IF(OR(G235="",Q235="Fechada",Q235="Perdida"),0,IF(Q235="Previsão vencida",3000,IF(Q235="Parada",2000,1000))+MIN(N(O235),500)+N(F235)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G235="",Q235="Fechada",Q235="Perdida"),0,IF(Q235="Previsão vencida",3,IF(Q235="Parada",2,1))*1E+13+MIN(N(O235),500)*1E+10+MIN(ROUND(N(F235),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12498,7 +12505,7 @@
         <v/>
       </c>
       <c r="R236" s="37">
-        <f>IF(OR(G236="",Q236="Fechada",Q236="Perdida"),0,IF(Q236="Previsão vencida",3000,IF(Q236="Parada",2000,1000))+MIN(N(O236),500)+N(F236)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G236="",Q236="Fechada",Q236="Perdida"),0,IF(Q236="Previsão vencida",3,IF(Q236="Parada",2,1))*1E+13+MIN(N(O236),500)*1E+10+MIN(ROUND(N(F236),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12536,7 +12543,7 @@
         <v/>
       </c>
       <c r="R237" s="37">
-        <f>IF(OR(G237="",Q237="Fechada",Q237="Perdida"),0,IF(Q237="Previsão vencida",3000,IF(Q237="Parada",2000,1000))+MIN(N(O237),500)+N(F237)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G237="",Q237="Fechada",Q237="Perdida"),0,IF(Q237="Previsão vencida",3,IF(Q237="Parada",2,1))*1E+13+MIN(N(O237),500)*1E+10+MIN(ROUND(N(F237),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12574,7 +12581,7 @@
         <v/>
       </c>
       <c r="R238" s="37">
-        <f>IF(OR(G238="",Q238="Fechada",Q238="Perdida"),0,IF(Q238="Previsão vencida",3000,IF(Q238="Parada",2000,1000))+MIN(N(O238),500)+N(F238)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G238="",Q238="Fechada",Q238="Perdida"),0,IF(Q238="Previsão vencida",3,IF(Q238="Parada",2,1))*1E+13+MIN(N(O238),500)*1E+10+MIN(ROUND(N(F238),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12612,7 +12619,7 @@
         <v/>
       </c>
       <c r="R239" s="37">
-        <f>IF(OR(G239="",Q239="Fechada",Q239="Perdida"),0,IF(Q239="Previsão vencida",3000,IF(Q239="Parada",2000,1000))+MIN(N(O239),500)+N(F239)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G239="",Q239="Fechada",Q239="Perdida"),0,IF(Q239="Previsão vencida",3,IF(Q239="Parada",2,1))*1E+13+MIN(N(O239),500)*1E+10+MIN(ROUND(N(F239),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12650,7 +12657,7 @@
         <v/>
       </c>
       <c r="R240" s="37">
-        <f>IF(OR(G240="",Q240="Fechada",Q240="Perdida"),0,IF(Q240="Previsão vencida",3000,IF(Q240="Parada",2000,1000))+MIN(N(O240),500)+N(F240)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G240="",Q240="Fechada",Q240="Perdida"),0,IF(Q240="Previsão vencida",3,IF(Q240="Parada",2,1))*1E+13+MIN(N(O240),500)*1E+10+MIN(ROUND(N(F240),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12688,7 +12695,7 @@
         <v/>
       </c>
       <c r="R241" s="37">
-        <f>IF(OR(G241="",Q241="Fechada",Q241="Perdida"),0,IF(Q241="Previsão vencida",3000,IF(Q241="Parada",2000,1000))+MIN(N(O241),500)+N(F241)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G241="",Q241="Fechada",Q241="Perdida"),0,IF(Q241="Previsão vencida",3,IF(Q241="Parada",2,1))*1E+13+MIN(N(O241),500)*1E+10+MIN(ROUND(N(F241),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12726,7 +12733,7 @@
         <v/>
       </c>
       <c r="R242" s="37">
-        <f>IF(OR(G242="",Q242="Fechada",Q242="Perdida"),0,IF(Q242="Previsão vencida",3000,IF(Q242="Parada",2000,1000))+MIN(N(O242),500)+N(F242)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G242="",Q242="Fechada",Q242="Perdida"),0,IF(Q242="Previsão vencida",3,IF(Q242="Parada",2,1))*1E+13+MIN(N(O242),500)*1E+10+MIN(ROUND(N(F242),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12764,7 +12771,7 @@
         <v/>
       </c>
       <c r="R243" s="37">
-        <f>IF(OR(G243="",Q243="Fechada",Q243="Perdida"),0,IF(Q243="Previsão vencida",3000,IF(Q243="Parada",2000,1000))+MIN(N(O243),500)+N(F243)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G243="",Q243="Fechada",Q243="Perdida"),0,IF(Q243="Previsão vencida",3,IF(Q243="Parada",2,1))*1E+13+MIN(N(O243),500)*1E+10+MIN(ROUND(N(F243),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12802,7 +12809,7 @@
         <v/>
       </c>
       <c r="R244" s="37">
-        <f>IF(OR(G244="",Q244="Fechada",Q244="Perdida"),0,IF(Q244="Previsão vencida",3000,IF(Q244="Parada",2000,1000))+MIN(N(O244),500)+N(F244)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G244="",Q244="Fechada",Q244="Perdida"),0,IF(Q244="Previsão vencida",3,IF(Q244="Parada",2,1))*1E+13+MIN(N(O244),500)*1E+10+MIN(ROUND(N(F244),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12840,7 +12847,7 @@
         <v/>
       </c>
       <c r="R245" s="37">
-        <f>IF(OR(G245="",Q245="Fechada",Q245="Perdida"),0,IF(Q245="Previsão vencida",3000,IF(Q245="Parada",2000,1000))+MIN(N(O245),500)+N(F245)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G245="",Q245="Fechada",Q245="Perdida"),0,IF(Q245="Previsão vencida",3,IF(Q245="Parada",2,1))*1E+13+MIN(N(O245),500)*1E+10+MIN(ROUND(N(F245),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12878,7 +12885,7 @@
         <v/>
       </c>
       <c r="R246" s="37">
-        <f>IF(OR(G246="",Q246="Fechada",Q246="Perdida"),0,IF(Q246="Previsão vencida",3000,IF(Q246="Parada",2000,1000))+MIN(N(O246),500)+N(F246)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G246="",Q246="Fechada",Q246="Perdida"),0,IF(Q246="Previsão vencida",3,IF(Q246="Parada",2,1))*1E+13+MIN(N(O246),500)*1E+10+MIN(ROUND(N(F246),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12916,7 +12923,7 @@
         <v/>
       </c>
       <c r="R247" s="37">
-        <f>IF(OR(G247="",Q247="Fechada",Q247="Perdida"),0,IF(Q247="Previsão vencida",3000,IF(Q247="Parada",2000,1000))+MIN(N(O247),500)+N(F247)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G247="",Q247="Fechada",Q247="Perdida"),0,IF(Q247="Previsão vencida",3,IF(Q247="Parada",2,1))*1E+13+MIN(N(O247),500)*1E+10+MIN(ROUND(N(F247),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12954,7 +12961,7 @@
         <v/>
       </c>
       <c r="R248" s="37">
-        <f>IF(OR(G248="",Q248="Fechada",Q248="Perdida"),0,IF(Q248="Previsão vencida",3000,IF(Q248="Parada",2000,1000))+MIN(N(O248),500)+N(F248)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G248="",Q248="Fechada",Q248="Perdida"),0,IF(Q248="Previsão vencida",3,IF(Q248="Parada",2,1))*1E+13+MIN(N(O248),500)*1E+10+MIN(ROUND(N(F248),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12992,7 +12999,7 @@
         <v/>
       </c>
       <c r="R249" s="37">
-        <f>IF(OR(G249="",Q249="Fechada",Q249="Perdida"),0,IF(Q249="Previsão vencida",3000,IF(Q249="Parada",2000,1000))+MIN(N(O249),500)+N(F249)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G249="",Q249="Fechada",Q249="Perdida"),0,IF(Q249="Previsão vencida",3,IF(Q249="Parada",2,1))*1E+13+MIN(N(O249),500)*1E+10+MIN(ROUND(N(F249),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13030,7 +13037,7 @@
         <v/>
       </c>
       <c r="R250" s="37">
-        <f>IF(OR(G250="",Q250="Fechada",Q250="Perdida"),0,IF(Q250="Previsão vencida",3000,IF(Q250="Parada",2000,1000))+MIN(N(O250),500)+N(F250)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G250="",Q250="Fechada",Q250="Perdida"),0,IF(Q250="Previsão vencida",3,IF(Q250="Parada",2,1))*1E+13+MIN(N(O250),500)*1E+10+MIN(ROUND(N(F250),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13068,7 +13075,7 @@
         <v/>
       </c>
       <c r="R251" s="37">
-        <f>IF(OR(G251="",Q251="Fechada",Q251="Perdida"),0,IF(Q251="Previsão vencida",3000,IF(Q251="Parada",2000,1000))+MIN(N(O251),500)+N(F251)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G251="",Q251="Fechada",Q251="Perdida"),0,IF(Q251="Previsão vencida",3,IF(Q251="Parada",2,1))*1E+13+MIN(N(O251),500)*1E+10+MIN(ROUND(N(F251),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13106,7 +13113,7 @@
         <v/>
       </c>
       <c r="R252" s="37">
-        <f>IF(OR(G252="",Q252="Fechada",Q252="Perdida"),0,IF(Q252="Previsão vencida",3000,IF(Q252="Parada",2000,1000))+MIN(N(O252),500)+N(F252)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G252="",Q252="Fechada",Q252="Perdida"),0,IF(Q252="Previsão vencida",3,IF(Q252="Parada",2,1))*1E+13+MIN(N(O252),500)*1E+10+MIN(ROUND(N(F252),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13144,7 +13151,7 @@
         <v/>
       </c>
       <c r="R253" s="37">
-        <f>IF(OR(G253="",Q253="Fechada",Q253="Perdida"),0,IF(Q253="Previsão vencida",3000,IF(Q253="Parada",2000,1000))+MIN(N(O253),500)+N(F253)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G253="",Q253="Fechada",Q253="Perdida"),0,IF(Q253="Previsão vencida",3,IF(Q253="Parada",2,1))*1E+13+MIN(N(O253),500)*1E+10+MIN(ROUND(N(F253),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13182,7 +13189,7 @@
         <v/>
       </c>
       <c r="R254" s="37">
-        <f>IF(OR(G254="",Q254="Fechada",Q254="Perdida"),0,IF(Q254="Previsão vencida",3000,IF(Q254="Parada",2000,1000))+MIN(N(O254),500)+N(F254)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G254="",Q254="Fechada",Q254="Perdida"),0,IF(Q254="Previsão vencida",3,IF(Q254="Parada",2,1))*1E+13+MIN(N(O254),500)*1E+10+MIN(ROUND(N(F254),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13220,7 +13227,7 @@
         <v/>
       </c>
       <c r="R255" s="37">
-        <f>IF(OR(G255="",Q255="Fechada",Q255="Perdida"),0,IF(Q255="Previsão vencida",3000,IF(Q255="Parada",2000,1000))+MIN(N(O255),500)+N(F255)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G255="",Q255="Fechada",Q255="Perdida"),0,IF(Q255="Previsão vencida",3,IF(Q255="Parada",2,1))*1E+13+MIN(N(O255),500)*1E+10+MIN(ROUND(N(F255),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13258,7 +13265,7 @@
         <v/>
       </c>
       <c r="R256" s="37">
-        <f>IF(OR(G256="",Q256="Fechada",Q256="Perdida"),0,IF(Q256="Previsão vencida",3000,IF(Q256="Parada",2000,1000))+MIN(N(O256),500)+N(F256)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G256="",Q256="Fechada",Q256="Perdida"),0,IF(Q256="Previsão vencida",3,IF(Q256="Parada",2,1))*1E+13+MIN(N(O256),500)*1E+10+MIN(ROUND(N(F256),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13296,7 +13303,7 @@
         <v/>
       </c>
       <c r="R257" s="37">
-        <f>IF(OR(G257="",Q257="Fechada",Q257="Perdida"),0,IF(Q257="Previsão vencida",3000,IF(Q257="Parada",2000,1000))+MIN(N(O257),500)+N(F257)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G257="",Q257="Fechada",Q257="Perdida"),0,IF(Q257="Previsão vencida",3,IF(Q257="Parada",2,1))*1E+13+MIN(N(O257),500)*1E+10+MIN(ROUND(N(F257),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13334,7 +13341,7 @@
         <v/>
       </c>
       <c r="R258" s="37">
-        <f>IF(OR(G258="",Q258="Fechada",Q258="Perdida"),0,IF(Q258="Previsão vencida",3000,IF(Q258="Parada",2000,1000))+MIN(N(O258),500)+N(F258)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G258="",Q258="Fechada",Q258="Perdida"),0,IF(Q258="Previsão vencida",3,IF(Q258="Parada",2,1))*1E+13+MIN(N(O258),500)*1E+10+MIN(ROUND(N(F258),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13372,7 +13379,7 @@
         <v/>
       </c>
       <c r="R259" s="37">
-        <f>IF(OR(G259="",Q259="Fechada",Q259="Perdida"),0,IF(Q259="Previsão vencida",3000,IF(Q259="Parada",2000,1000))+MIN(N(O259),500)+N(F259)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G259="",Q259="Fechada",Q259="Perdida"),0,IF(Q259="Previsão vencida",3,IF(Q259="Parada",2,1))*1E+13+MIN(N(O259),500)*1E+10+MIN(ROUND(N(F259),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13410,7 +13417,7 @@
         <v/>
       </c>
       <c r="R260" s="37">
-        <f>IF(OR(G260="",Q260="Fechada",Q260="Perdida"),0,IF(Q260="Previsão vencida",3000,IF(Q260="Parada",2000,1000))+MIN(N(O260),500)+N(F260)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G260="",Q260="Fechada",Q260="Perdida"),0,IF(Q260="Previsão vencida",3,IF(Q260="Parada",2,1))*1E+13+MIN(N(O260),500)*1E+10+MIN(ROUND(N(F260),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13448,7 +13455,7 @@
         <v/>
       </c>
       <c r="R261" s="37">
-        <f>IF(OR(G261="",Q261="Fechada",Q261="Perdida"),0,IF(Q261="Previsão vencida",3000,IF(Q261="Parada",2000,1000))+MIN(N(O261),500)+N(F261)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G261="",Q261="Fechada",Q261="Perdida"),0,IF(Q261="Previsão vencida",3,IF(Q261="Parada",2,1))*1E+13+MIN(N(O261),500)*1E+10+MIN(ROUND(N(F261),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13486,7 +13493,7 @@
         <v/>
       </c>
       <c r="R262" s="37">
-        <f>IF(OR(G262="",Q262="Fechada",Q262="Perdida"),0,IF(Q262="Previsão vencida",3000,IF(Q262="Parada",2000,1000))+MIN(N(O262),500)+N(F262)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G262="",Q262="Fechada",Q262="Perdida"),0,IF(Q262="Previsão vencida",3,IF(Q262="Parada",2,1))*1E+13+MIN(N(O262),500)*1E+10+MIN(ROUND(N(F262),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13524,7 +13531,7 @@
         <v/>
       </c>
       <c r="R263" s="37">
-        <f>IF(OR(G263="",Q263="Fechada",Q263="Perdida"),0,IF(Q263="Previsão vencida",3000,IF(Q263="Parada",2000,1000))+MIN(N(O263),500)+N(F263)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G263="",Q263="Fechada",Q263="Perdida"),0,IF(Q263="Previsão vencida",3,IF(Q263="Parada",2,1))*1E+13+MIN(N(O263),500)*1E+10+MIN(ROUND(N(F263),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13562,7 +13569,7 @@
         <v/>
       </c>
       <c r="R264" s="37">
-        <f>IF(OR(G264="",Q264="Fechada",Q264="Perdida"),0,IF(Q264="Previsão vencida",3000,IF(Q264="Parada",2000,1000))+MIN(N(O264),500)+N(F264)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G264="",Q264="Fechada",Q264="Perdida"),0,IF(Q264="Previsão vencida",3,IF(Q264="Parada",2,1))*1E+13+MIN(N(O264),500)*1E+10+MIN(ROUND(N(F264),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13600,7 +13607,7 @@
         <v/>
       </c>
       <c r="R265" s="37">
-        <f>IF(OR(G265="",Q265="Fechada",Q265="Perdida"),0,IF(Q265="Previsão vencida",3000,IF(Q265="Parada",2000,1000))+MIN(N(O265),500)+N(F265)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G265="",Q265="Fechada",Q265="Perdida"),0,IF(Q265="Previsão vencida",3,IF(Q265="Parada",2,1))*1E+13+MIN(N(O265),500)*1E+10+MIN(ROUND(N(F265),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13638,7 +13645,7 @@
         <v/>
       </c>
       <c r="R266" s="37">
-        <f>IF(OR(G266="",Q266="Fechada",Q266="Perdida"),0,IF(Q266="Previsão vencida",3000,IF(Q266="Parada",2000,1000))+MIN(N(O266),500)+N(F266)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G266="",Q266="Fechada",Q266="Perdida"),0,IF(Q266="Previsão vencida",3,IF(Q266="Parada",2,1))*1E+13+MIN(N(O266),500)*1E+10+MIN(ROUND(N(F266),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13676,7 +13683,7 @@
         <v/>
       </c>
       <c r="R267" s="37">
-        <f>IF(OR(G267="",Q267="Fechada",Q267="Perdida"),0,IF(Q267="Previsão vencida",3000,IF(Q267="Parada",2000,1000))+MIN(N(O267),500)+N(F267)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G267="",Q267="Fechada",Q267="Perdida"),0,IF(Q267="Previsão vencida",3,IF(Q267="Parada",2,1))*1E+13+MIN(N(O267),500)*1E+10+MIN(ROUND(N(F267),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13714,7 +13721,7 @@
         <v/>
       </c>
       <c r="R268" s="37">
-        <f>IF(OR(G268="",Q268="Fechada",Q268="Perdida"),0,IF(Q268="Previsão vencida",3000,IF(Q268="Parada",2000,1000))+MIN(N(O268),500)+N(F268)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G268="",Q268="Fechada",Q268="Perdida"),0,IF(Q268="Previsão vencida",3,IF(Q268="Parada",2,1))*1E+13+MIN(N(O268),500)*1E+10+MIN(ROUND(N(F268),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13752,7 +13759,7 @@
         <v/>
       </c>
       <c r="R269" s="37">
-        <f>IF(OR(G269="",Q269="Fechada",Q269="Perdida"),0,IF(Q269="Previsão vencida",3000,IF(Q269="Parada",2000,1000))+MIN(N(O269),500)+N(F269)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G269="",Q269="Fechada",Q269="Perdida"),0,IF(Q269="Previsão vencida",3,IF(Q269="Parada",2,1))*1E+13+MIN(N(O269),500)*1E+10+MIN(ROUND(N(F269),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13790,7 +13797,7 @@
         <v/>
       </c>
       <c r="R270" s="37">
-        <f>IF(OR(G270="",Q270="Fechada",Q270="Perdida"),0,IF(Q270="Previsão vencida",3000,IF(Q270="Parada",2000,1000))+MIN(N(O270),500)+N(F270)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G270="",Q270="Fechada",Q270="Perdida"),0,IF(Q270="Previsão vencida",3,IF(Q270="Parada",2,1))*1E+13+MIN(N(O270),500)*1E+10+MIN(ROUND(N(F270),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13828,7 +13835,7 @@
         <v/>
       </c>
       <c r="R271" s="37">
-        <f>IF(OR(G271="",Q271="Fechada",Q271="Perdida"),0,IF(Q271="Previsão vencida",3000,IF(Q271="Parada",2000,1000))+MIN(N(O271),500)+N(F271)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G271="",Q271="Fechada",Q271="Perdida"),0,IF(Q271="Previsão vencida",3,IF(Q271="Parada",2,1))*1E+13+MIN(N(O271),500)*1E+10+MIN(ROUND(N(F271),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13866,7 +13873,7 @@
         <v/>
       </c>
       <c r="R272" s="37">
-        <f>IF(OR(G272="",Q272="Fechada",Q272="Perdida"),0,IF(Q272="Previsão vencida",3000,IF(Q272="Parada",2000,1000))+MIN(N(O272),500)+N(F272)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G272="",Q272="Fechada",Q272="Perdida"),0,IF(Q272="Previsão vencida",3,IF(Q272="Parada",2,1))*1E+13+MIN(N(O272),500)*1E+10+MIN(ROUND(N(F272),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13904,7 +13911,7 @@
         <v/>
       </c>
       <c r="R273" s="37">
-        <f>IF(OR(G273="",Q273="Fechada",Q273="Perdida"),0,IF(Q273="Previsão vencida",3000,IF(Q273="Parada",2000,1000))+MIN(N(O273),500)+N(F273)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G273="",Q273="Fechada",Q273="Perdida"),0,IF(Q273="Previsão vencida",3,IF(Q273="Parada",2,1))*1E+13+MIN(N(O273),500)*1E+10+MIN(ROUND(N(F273),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13942,7 +13949,7 @@
         <v/>
       </c>
       <c r="R274" s="37">
-        <f>IF(OR(G274="",Q274="Fechada",Q274="Perdida"),0,IF(Q274="Previsão vencida",3000,IF(Q274="Parada",2000,1000))+MIN(N(O274),500)+N(F274)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G274="",Q274="Fechada",Q274="Perdida"),0,IF(Q274="Previsão vencida",3,IF(Q274="Parada",2,1))*1E+13+MIN(N(O274),500)*1E+10+MIN(ROUND(N(F274),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13980,7 +13987,7 @@
         <v/>
       </c>
       <c r="R275" s="37">
-        <f>IF(OR(G275="",Q275="Fechada",Q275="Perdida"),0,IF(Q275="Previsão vencida",3000,IF(Q275="Parada",2000,1000))+MIN(N(O275),500)+N(F275)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G275="",Q275="Fechada",Q275="Perdida"),0,IF(Q275="Previsão vencida",3,IF(Q275="Parada",2,1))*1E+13+MIN(N(O275),500)*1E+10+MIN(ROUND(N(F275),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14018,7 +14025,7 @@
         <v/>
       </c>
       <c r="R276" s="37">
-        <f>IF(OR(G276="",Q276="Fechada",Q276="Perdida"),0,IF(Q276="Previsão vencida",3000,IF(Q276="Parada",2000,1000))+MIN(N(O276),500)+N(F276)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G276="",Q276="Fechada",Q276="Perdida"),0,IF(Q276="Previsão vencida",3,IF(Q276="Parada",2,1))*1E+13+MIN(N(O276),500)*1E+10+MIN(ROUND(N(F276),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14056,7 +14063,7 @@
         <v/>
       </c>
       <c r="R277" s="37">
-        <f>IF(OR(G277="",Q277="Fechada",Q277="Perdida"),0,IF(Q277="Previsão vencida",3000,IF(Q277="Parada",2000,1000))+MIN(N(O277),500)+N(F277)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G277="",Q277="Fechada",Q277="Perdida"),0,IF(Q277="Previsão vencida",3,IF(Q277="Parada",2,1))*1E+13+MIN(N(O277),500)*1E+10+MIN(ROUND(N(F277),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14094,7 +14101,7 @@
         <v/>
       </c>
       <c r="R278" s="37">
-        <f>IF(OR(G278="",Q278="Fechada",Q278="Perdida"),0,IF(Q278="Previsão vencida",3000,IF(Q278="Parada",2000,1000))+MIN(N(O278),500)+N(F278)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G278="",Q278="Fechada",Q278="Perdida"),0,IF(Q278="Previsão vencida",3,IF(Q278="Parada",2,1))*1E+13+MIN(N(O278),500)*1E+10+MIN(ROUND(N(F278),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14132,7 +14139,7 @@
         <v/>
       </c>
       <c r="R279" s="37">
-        <f>IF(OR(G279="",Q279="Fechada",Q279="Perdida"),0,IF(Q279="Previsão vencida",3000,IF(Q279="Parada",2000,1000))+MIN(N(O279),500)+N(F279)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G279="",Q279="Fechada",Q279="Perdida"),0,IF(Q279="Previsão vencida",3,IF(Q279="Parada",2,1))*1E+13+MIN(N(O279),500)*1E+10+MIN(ROUND(N(F279),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14170,7 +14177,7 @@
         <v/>
       </c>
       <c r="R280" s="37">
-        <f>IF(OR(G280="",Q280="Fechada",Q280="Perdida"),0,IF(Q280="Previsão vencida",3000,IF(Q280="Parada",2000,1000))+MIN(N(O280),500)+N(F280)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G280="",Q280="Fechada",Q280="Perdida"),0,IF(Q280="Previsão vencida",3,IF(Q280="Parada",2,1))*1E+13+MIN(N(O280),500)*1E+10+MIN(ROUND(N(F280),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14208,7 +14215,7 @@
         <v/>
       </c>
       <c r="R281" s="37">
-        <f>IF(OR(G281="",Q281="Fechada",Q281="Perdida"),0,IF(Q281="Previsão vencida",3000,IF(Q281="Parada",2000,1000))+MIN(N(O281),500)+N(F281)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G281="",Q281="Fechada",Q281="Perdida"),0,IF(Q281="Previsão vencida",3,IF(Q281="Parada",2,1))*1E+13+MIN(N(O281),500)*1E+10+MIN(ROUND(N(F281),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14246,7 +14253,7 @@
         <v/>
       </c>
       <c r="R282" s="37">
-        <f>IF(OR(G282="",Q282="Fechada",Q282="Perdida"),0,IF(Q282="Previsão vencida",3000,IF(Q282="Parada",2000,1000))+MIN(N(O282),500)+N(F282)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G282="",Q282="Fechada",Q282="Perdida"),0,IF(Q282="Previsão vencida",3,IF(Q282="Parada",2,1))*1E+13+MIN(N(O282),500)*1E+10+MIN(ROUND(N(F282),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14284,7 +14291,7 @@
         <v/>
       </c>
       <c r="R283" s="37">
-        <f>IF(OR(G283="",Q283="Fechada",Q283="Perdida"),0,IF(Q283="Previsão vencida",3000,IF(Q283="Parada",2000,1000))+MIN(N(O283),500)+N(F283)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G283="",Q283="Fechada",Q283="Perdida"),0,IF(Q283="Previsão vencida",3,IF(Q283="Parada",2,1))*1E+13+MIN(N(O283),500)*1E+10+MIN(ROUND(N(F283),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14322,7 +14329,7 @@
         <v/>
       </c>
       <c r="R284" s="37">
-        <f>IF(OR(G284="",Q284="Fechada",Q284="Perdida"),0,IF(Q284="Previsão vencida",3000,IF(Q284="Parada",2000,1000))+MIN(N(O284),500)+N(F284)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G284="",Q284="Fechada",Q284="Perdida"),0,IF(Q284="Previsão vencida",3,IF(Q284="Parada",2,1))*1E+13+MIN(N(O284),500)*1E+10+MIN(ROUND(N(F284),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14360,7 +14367,7 @@
         <v/>
       </c>
       <c r="R285" s="37">
-        <f>IF(OR(G285="",Q285="Fechada",Q285="Perdida"),0,IF(Q285="Previsão vencida",3000,IF(Q285="Parada",2000,1000))+MIN(N(O285),500)+N(F285)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G285="",Q285="Fechada",Q285="Perdida"),0,IF(Q285="Previsão vencida",3,IF(Q285="Parada",2,1))*1E+13+MIN(N(O285),500)*1E+10+MIN(ROUND(N(F285),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14398,7 +14405,7 @@
         <v/>
       </c>
       <c r="R286" s="37">
-        <f>IF(OR(G286="",Q286="Fechada",Q286="Perdida"),0,IF(Q286="Previsão vencida",3000,IF(Q286="Parada",2000,1000))+MIN(N(O286),500)+N(F286)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G286="",Q286="Fechada",Q286="Perdida"),0,IF(Q286="Previsão vencida",3,IF(Q286="Parada",2,1))*1E+13+MIN(N(O286),500)*1E+10+MIN(ROUND(N(F286),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14436,7 +14443,7 @@
         <v/>
       </c>
       <c r="R287" s="37">
-        <f>IF(OR(G287="",Q287="Fechada",Q287="Perdida"),0,IF(Q287="Previsão vencida",3000,IF(Q287="Parada",2000,1000))+MIN(N(O287),500)+N(F287)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G287="",Q287="Fechada",Q287="Perdida"),0,IF(Q287="Previsão vencida",3,IF(Q287="Parada",2,1))*1E+13+MIN(N(O287),500)*1E+10+MIN(ROUND(N(F287),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14474,7 +14481,7 @@
         <v/>
       </c>
       <c r="R288" s="37">
-        <f>IF(OR(G288="",Q288="Fechada",Q288="Perdida"),0,IF(Q288="Previsão vencida",3000,IF(Q288="Parada",2000,1000))+MIN(N(O288),500)+N(F288)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G288="",Q288="Fechada",Q288="Perdida"),0,IF(Q288="Previsão vencida",3,IF(Q288="Parada",2,1))*1E+13+MIN(N(O288),500)*1E+10+MIN(ROUND(N(F288),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14512,7 +14519,7 @@
         <v/>
       </c>
       <c r="R289" s="37">
-        <f>IF(OR(G289="",Q289="Fechada",Q289="Perdida"),0,IF(Q289="Previsão vencida",3000,IF(Q289="Parada",2000,1000))+MIN(N(O289),500)+N(F289)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G289="",Q289="Fechada",Q289="Perdida"),0,IF(Q289="Previsão vencida",3,IF(Q289="Parada",2,1))*1E+13+MIN(N(O289),500)*1E+10+MIN(ROUND(N(F289),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14550,7 +14557,7 @@
         <v/>
       </c>
       <c r="R290" s="37">
-        <f>IF(OR(G290="",Q290="Fechada",Q290="Perdida"),0,IF(Q290="Previsão vencida",3000,IF(Q290="Parada",2000,1000))+MIN(N(O290),500)+N(F290)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G290="",Q290="Fechada",Q290="Perdida"),0,IF(Q290="Previsão vencida",3,IF(Q290="Parada",2,1))*1E+13+MIN(N(O290),500)*1E+10+MIN(ROUND(N(F290),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14588,7 +14595,7 @@
         <v/>
       </c>
       <c r="R291" s="37">
-        <f>IF(OR(G291="",Q291="Fechada",Q291="Perdida"),0,IF(Q291="Previsão vencida",3000,IF(Q291="Parada",2000,1000))+MIN(N(O291),500)+N(F291)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G291="",Q291="Fechada",Q291="Perdida"),0,IF(Q291="Previsão vencida",3,IF(Q291="Parada",2,1))*1E+13+MIN(N(O291),500)*1E+10+MIN(ROUND(N(F291),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14626,7 +14633,7 @@
         <v/>
       </c>
       <c r="R292" s="37">
-        <f>IF(OR(G292="",Q292="Fechada",Q292="Perdida"),0,IF(Q292="Previsão vencida",3000,IF(Q292="Parada",2000,1000))+MIN(N(O292),500)+N(F292)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G292="",Q292="Fechada",Q292="Perdida"),0,IF(Q292="Previsão vencida",3,IF(Q292="Parada",2,1))*1E+13+MIN(N(O292),500)*1E+10+MIN(ROUND(N(F292),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14664,7 +14671,7 @@
         <v/>
       </c>
       <c r="R293" s="37">
-        <f>IF(OR(G293="",Q293="Fechada",Q293="Perdida"),0,IF(Q293="Previsão vencida",3000,IF(Q293="Parada",2000,1000))+MIN(N(O293),500)+N(F293)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G293="",Q293="Fechada",Q293="Perdida"),0,IF(Q293="Previsão vencida",3,IF(Q293="Parada",2,1))*1E+13+MIN(N(O293),500)*1E+10+MIN(ROUND(N(F293),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14702,7 +14709,7 @@
         <v/>
       </c>
       <c r="R294" s="37">
-        <f>IF(OR(G294="",Q294="Fechada",Q294="Perdida"),0,IF(Q294="Previsão vencida",3000,IF(Q294="Parada",2000,1000))+MIN(N(O294),500)+N(F294)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G294="",Q294="Fechada",Q294="Perdida"),0,IF(Q294="Previsão vencida",3,IF(Q294="Parada",2,1))*1E+13+MIN(N(O294),500)*1E+10+MIN(ROUND(N(F294),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14740,7 +14747,7 @@
         <v/>
       </c>
       <c r="R295" s="37">
-        <f>IF(OR(G295="",Q295="Fechada",Q295="Perdida"),0,IF(Q295="Previsão vencida",3000,IF(Q295="Parada",2000,1000))+MIN(N(O295),500)+N(F295)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G295="",Q295="Fechada",Q295="Perdida"),0,IF(Q295="Previsão vencida",3,IF(Q295="Parada",2,1))*1E+13+MIN(N(O295),500)*1E+10+MIN(ROUND(N(F295),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14778,7 +14785,7 @@
         <v/>
       </c>
       <c r="R296" s="37">
-        <f>IF(OR(G296="",Q296="Fechada",Q296="Perdida"),0,IF(Q296="Previsão vencida",3000,IF(Q296="Parada",2000,1000))+MIN(N(O296),500)+N(F296)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G296="",Q296="Fechada",Q296="Perdida"),0,IF(Q296="Previsão vencida",3,IF(Q296="Parada",2,1))*1E+13+MIN(N(O296),500)*1E+10+MIN(ROUND(N(F296),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14816,7 +14823,7 @@
         <v/>
       </c>
       <c r="R297" s="37">
-        <f>IF(OR(G297="",Q297="Fechada",Q297="Perdida"),0,IF(Q297="Previsão vencida",3000,IF(Q297="Parada",2000,1000))+MIN(N(O297),500)+N(F297)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G297="",Q297="Fechada",Q297="Perdida"),0,IF(Q297="Previsão vencida",3,IF(Q297="Parada",2,1))*1E+13+MIN(N(O297),500)*1E+10+MIN(ROUND(N(F297),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14854,7 +14861,7 @@
         <v/>
       </c>
       <c r="R298" s="37">
-        <f>IF(OR(G298="",Q298="Fechada",Q298="Perdida"),0,IF(Q298="Previsão vencida",3000,IF(Q298="Parada",2000,1000))+MIN(N(O298),500)+N(F298)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G298="",Q298="Fechada",Q298="Perdida"),0,IF(Q298="Previsão vencida",3,IF(Q298="Parada",2,1))*1E+13+MIN(N(O298),500)*1E+10+MIN(ROUND(N(F298),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14892,7 +14899,7 @@
         <v/>
       </c>
       <c r="R299" s="37">
-        <f>IF(OR(G299="",Q299="Fechada",Q299="Perdida"),0,IF(Q299="Previsão vencida",3000,IF(Q299="Parada",2000,1000))+MIN(N(O299),500)+N(F299)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G299="",Q299="Fechada",Q299="Perdida"),0,IF(Q299="Previsão vencida",3,IF(Q299="Parada",2,1))*1E+13+MIN(N(O299),500)*1E+10+MIN(ROUND(N(F299),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14930,7 +14937,7 @@
         <v/>
       </c>
       <c r="R300" s="37">
-        <f>IF(OR(G300="",Q300="Fechada",Q300="Perdida"),0,IF(Q300="Previsão vencida",3000,IF(Q300="Parada",2000,1000))+MIN(N(O300),500)+N(F300)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G300="",Q300="Fechada",Q300="Perdida"),0,IF(Q300="Previsão vencida",3,IF(Q300="Parada",2,1))*1E+13+MIN(N(O300),500)*1E+10+MIN(ROUND(N(F300),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14968,7 +14975,7 @@
         <v/>
       </c>
       <c r="R301" s="37">
-        <f>IF(OR(G301="",Q301="Fechada",Q301="Perdida"),0,IF(Q301="Previsão vencida",3000,IF(Q301="Parada",2000,1000))+MIN(N(O301),500)+N(F301)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G301="",Q301="Fechada",Q301="Perdida"),0,IF(Q301="Previsão vencida",3,IF(Q301="Parada",2,1))*1E+13+MIN(N(O301),500)*1E+10+MIN(ROUND(N(F301),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15006,7 +15013,7 @@
         <v/>
       </c>
       <c r="R302" s="37">
-        <f>IF(OR(G302="",Q302="Fechada",Q302="Perdida"),0,IF(Q302="Previsão vencida",3000,IF(Q302="Parada",2000,1000))+MIN(N(O302),500)+N(F302)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G302="",Q302="Fechada",Q302="Perdida"),0,IF(Q302="Previsão vencida",3,IF(Q302="Parada",2,1))*1E+13+MIN(N(O302),500)*1E+10+MIN(ROUND(N(F302),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15044,7 +15051,7 @@
         <v/>
       </c>
       <c r="R303" s="37">
-        <f>IF(OR(G303="",Q303="Fechada",Q303="Perdida"),0,IF(Q303="Previsão vencida",3000,IF(Q303="Parada",2000,1000))+MIN(N(O303),500)+N(F303)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G303="",Q303="Fechada",Q303="Perdida"),0,IF(Q303="Previsão vencida",3,IF(Q303="Parada",2,1))*1E+13+MIN(N(O303),500)*1E+10+MIN(ROUND(N(F303),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15082,7 +15089,7 @@
         <v/>
       </c>
       <c r="R304" s="37">
-        <f>IF(OR(G304="",Q304="Fechada",Q304="Perdida"),0,IF(Q304="Previsão vencida",3000,IF(Q304="Parada",2000,1000))+MIN(N(O304),500)+N(F304)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G304="",Q304="Fechada",Q304="Perdida"),0,IF(Q304="Previsão vencida",3,IF(Q304="Parada",2,1))*1E+13+MIN(N(O304),500)*1E+10+MIN(ROUND(N(F304),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15123,7 +15130,7 @@
     <dataValidation sqref="B5:B304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$A$18,0,0,MAX(1,COUNTA(Config!$A$18:$A$27)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$I$18,0,0,MAX(1,COUNTA(Config!$I$18:$I$27)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/15-funil-de-propostas.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2013,442 +2013,1122 @@
         <v/>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="24">
+        <f>IF(Config!$A$28="","",Config!$A$28)</f>
+        <v/>
+      </c>
+      <c r="B44" s="25">
+        <f>IF(Config!$A$28="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$28))</f>
+        <v/>
+      </c>
+      <c r="C44" s="25">
+        <f>IF(Config!$A$28="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$28,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D44" s="25">
+        <f>IF(Config!$A$28="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$28,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E44" s="27">
+        <f>IF(Config!$A$28="","",IFERROR(C44/(C44+D44),0))</f>
+        <v/>
+      </c>
+      <c r="F44" s="26">
+        <f>IF(Config!$A$28="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$28,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="26">
+        <f>IF(Config!$A$28="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$28,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="24">
+        <f>IF(Config!$A$29="","",Config!$A$29)</f>
+        <v/>
+      </c>
+      <c r="B45" s="25">
+        <f>IF(Config!$A$29="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$29))</f>
+        <v/>
+      </c>
+      <c r="C45" s="25">
+        <f>IF(Config!$A$29="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$29,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D45" s="25">
+        <f>IF(Config!$A$29="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$29,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E45" s="27">
+        <f>IF(Config!$A$29="","",IFERROR(C45/(C45+D45),0))</f>
+        <v/>
+      </c>
+      <c r="F45" s="26">
+        <f>IF(Config!$A$29="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$29,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="26">
+        <f>IF(Config!$A$29="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$29,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24">
+        <f>IF(Config!$A$30="","",Config!$A$30)</f>
+        <v/>
+      </c>
+      <c r="B46" s="25">
+        <f>IF(Config!$A$30="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$30))</f>
+        <v/>
+      </c>
+      <c r="C46" s="25">
+        <f>IF(Config!$A$30="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$30,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D46" s="25">
+        <f>IF(Config!$A$30="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$30,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E46" s="27">
+        <f>IF(Config!$A$30="","",IFERROR(C46/(C46+D46),0))</f>
+        <v/>
+      </c>
+      <c r="F46" s="26">
+        <f>IF(Config!$A$30="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$30,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="26">
+        <f>IF(Config!$A$30="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$30,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24">
+        <f>IF(Config!$A$31="","",Config!$A$31)</f>
+        <v/>
+      </c>
+      <c r="B47" s="25">
+        <f>IF(Config!$A$31="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$31))</f>
+        <v/>
+      </c>
+      <c r="C47" s="25">
+        <f>IF(Config!$A$31="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$31,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D47" s="25">
+        <f>IF(Config!$A$31="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$31,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E47" s="27">
+        <f>IF(Config!$A$31="","",IFERROR(C47/(C47+D47),0))</f>
+        <v/>
+      </c>
+      <c r="F47" s="26">
+        <f>IF(Config!$A$31="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$31,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="26">
+        <f>IF(Config!$A$31="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$31,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24">
+        <f>IF(Config!$A$32="","",Config!$A$32)</f>
+        <v/>
+      </c>
+      <c r="B48" s="25">
+        <f>IF(Config!$A$32="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$32))</f>
+        <v/>
+      </c>
+      <c r="C48" s="25">
+        <f>IF(Config!$A$32="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$32,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D48" s="25">
+        <f>IF(Config!$A$32="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$32,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E48" s="27">
+        <f>IF(Config!$A$32="","",IFERROR(C48/(C48+D48),0))</f>
+        <v/>
+      </c>
+      <c r="F48" s="26">
+        <f>IF(Config!$A$32="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$32,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="26">
+        <f>IF(Config!$A$32="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$32,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24">
+        <f>IF(Config!$A$33="","",Config!$A$33)</f>
+        <v/>
+      </c>
+      <c r="B49" s="25">
+        <f>IF(Config!$A$33="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$33))</f>
+        <v/>
+      </c>
+      <c r="C49" s="25">
+        <f>IF(Config!$A$33="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$33,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D49" s="25">
+        <f>IF(Config!$A$33="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$33,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E49" s="27">
+        <f>IF(Config!$A$33="","",IFERROR(C49/(C49+D49),0))</f>
+        <v/>
+      </c>
+      <c r="F49" s="26">
+        <f>IF(Config!$A$33="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$33,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="26">
+        <f>IF(Config!$A$33="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$33,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24">
+        <f>IF(Config!$A$34="","",Config!$A$34)</f>
+        <v/>
+      </c>
+      <c r="B50" s="25">
+        <f>IF(Config!$A$34="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$34))</f>
+        <v/>
+      </c>
+      <c r="C50" s="25">
+        <f>IF(Config!$A$34="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$34,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D50" s="25">
+        <f>IF(Config!$A$34="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$34,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E50" s="27">
+        <f>IF(Config!$A$34="","",IFERROR(C50/(C50+D50),0))</f>
+        <v/>
+      </c>
+      <c r="F50" s="26">
+        <f>IF(Config!$A$34="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$34,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="26">
+        <f>IF(Config!$A$34="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$34,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24">
+        <f>IF(Config!$A$35="","",Config!$A$35)</f>
+        <v/>
+      </c>
+      <c r="B51" s="25">
+        <f>IF(Config!$A$35="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$35))</f>
+        <v/>
+      </c>
+      <c r="C51" s="25">
+        <f>IF(Config!$A$35="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$35,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D51" s="25">
+        <f>IF(Config!$A$35="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$35,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E51" s="27">
+        <f>IF(Config!$A$35="","",IFERROR(C51/(C51+D51),0))</f>
+        <v/>
+      </c>
+      <c r="F51" s="26">
+        <f>IF(Config!$A$35="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$35,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="26">
+        <f>IF(Config!$A$35="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$35,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24">
+        <f>IF(Config!$A$36="","",Config!$A$36)</f>
+        <v/>
+      </c>
+      <c r="B52" s="25">
+        <f>IF(Config!$A$36="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$36))</f>
+        <v/>
+      </c>
+      <c r="C52" s="25">
+        <f>IF(Config!$A$36="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$36,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D52" s="25">
+        <f>IF(Config!$A$36="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$36,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E52" s="27">
+        <f>IF(Config!$A$36="","",IFERROR(C52/(C52+D52),0))</f>
+        <v/>
+      </c>
+      <c r="F52" s="26">
+        <f>IF(Config!$A$36="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$36,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="26">
+        <f>IF(Config!$A$36="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$36,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24">
+        <f>IF(Config!$A$37="","",Config!$A$37)</f>
+        <v/>
+      </c>
+      <c r="B53" s="25">
+        <f>IF(Config!$A$37="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$37))</f>
+        <v/>
+      </c>
+      <c r="C53" s="25">
+        <f>IF(Config!$A$37="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$37,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="D53" s="25">
+        <f>IF(Config!$A$37="","",COUNTIFS(Propostas!$B$5:$B$304,Config!$A$37,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="E53" s="27">
+        <f>IF(Config!$A$37="","",IFERROR(C53/(C53+D53),0))</f>
+        <v/>
+      </c>
+      <c r="F53" s="26">
+        <f>IF(Config!$A$37="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$37,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="26">
+        <f>IF(Config!$A$37="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$B$5:$B$304,Config!$A$37,Propostas!$G$5:$G$304,"&lt;&gt;Fechada",Propostas!$G$5:$G$304,"&lt;&gt;Perdida",Propostas!$G$5:$G$304,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>Motivos de perda</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>Perdidas</t>
         </is>
       </c>
-      <c r="C46" s="21" t="inlineStr">
+      <c r="C56" s="21" t="inlineStr">
         <is>
           <t>Valor perdido (R$)</t>
         </is>
       </c>
-      <c r="D46" s="21" t="inlineStr">
+      <c r="D56" s="21" t="inlineStr">
         <is>
           <t>% das perdidas</t>
         </is>
       </c>
-      <c r="F46" s="21" t="inlineStr">
+      <c r="F56" s="21" t="inlineStr">
         <is>
           <t>Origem</t>
         </is>
       </c>
-      <c r="G46" s="21" t="inlineStr">
+      <c r="G56" s="21" t="inlineStr">
         <is>
           <t>Propostas</t>
         </is>
       </c>
-      <c r="H46" s="21" t="inlineStr">
+      <c r="H56" s="21" t="inlineStr">
         <is>
           <t>Fechadas</t>
         </is>
       </c>
-      <c r="I46" s="21" t="inlineStr">
+      <c r="I56" s="21" t="inlineStr">
         <is>
           <t>Taxa de fechamento</t>
         </is>
       </c>
-      <c r="J46" s="21" t="inlineStr">
+      <c r="J56" s="21" t="inlineStr">
         <is>
           <t>Valor fechado (R$)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="24" t="str">
+    <row r="57">
+      <c r="A57" s="24" t="str">
         <f>IF(Config!$E$18="","",Config!$E$18)</f>
         <v>Preço</v>
       </c>
-      <c r="B47" s="25">
+      <c r="B57" s="25">
         <f>IF(Config!$E$18="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$18,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>2</v>
       </c>
-      <c r="C47" s="26">
+      <c r="C57" s="26">
         <f>IF(Config!$E$18="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$18,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>16200</v>
       </c>
-      <c r="D47" s="27">
-        <f>IF(Config!$E$18="","",IFERROR(B47/$B$16,0))</f>
+      <c r="D57" s="27">
+        <f>IF(Config!$E$18="","",IFERROR(B57/$B$16,0))</f>
         <v>0.5</v>
       </c>
-      <c r="F47" s="24" t="str">
+      <c r="F57" s="24" t="str">
         <f>IF(Config!$C$18="","",Config!$C$18)</f>
         <v>Indicação de cliente</v>
       </c>
-      <c r="G47" s="25">
+      <c r="G57" s="25">
         <f>IF(Config!$C$18="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$18))</f>
         <v>4</v>
       </c>
-      <c r="H47" s="25">
+      <c r="H57" s="25">
         <f>IF(Config!$C$18="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$18,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>1</v>
       </c>
-      <c r="I47" s="27">
-        <f>IF(Config!$C$18="","",IFERROR(H47/(H47+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$18,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+      <c r="I57" s="27">
+        <f>IF(Config!$C$18="","",IFERROR(H57/(H57+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$18,Propostas!$G$5:$G$304,"Perdida")),0))</f>
         <v>0.5</v>
       </c>
-      <c r="J47" s="26">
+      <c r="J57" s="26">
         <f>IF(Config!$C$18="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$18,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>6000</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="24" t="str">
+    <row r="58">
+      <c r="A58" s="24" t="str">
         <f>IF(Config!$E$19="","",Config!$E$19)</f>
         <v>Fechou com outro escritório</v>
       </c>
-      <c r="B48" s="25">
+      <c r="B58" s="25">
         <f>IF(Config!$E$19="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$19,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>1</v>
       </c>
-      <c r="C48" s="26">
+      <c r="C58" s="26">
         <f>IF(Config!$E$19="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$19,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>6500</v>
       </c>
-      <c r="D48" s="27">
-        <f>IF(Config!$E$19="","",IFERROR(B48/$B$16,0))</f>
+      <c r="D58" s="27">
+        <f>IF(Config!$E$19="","",IFERROR(B58/$B$16,0))</f>
         <v>0.25</v>
       </c>
-      <c r="F48" s="24" t="str">
+      <c r="F58" s="24" t="str">
         <f>IF(Config!$C$19="","",Config!$C$19)</f>
         <v>Site e Google</v>
       </c>
-      <c r="G48" s="25">
+      <c r="G58" s="25">
         <f>IF(Config!$C$19="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$19))</f>
         <v>3</v>
       </c>
-      <c r="H48" s="25">
+      <c r="H58" s="25">
         <f>IF(Config!$C$19="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$19,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>1</v>
       </c>
-      <c r="I48" s="27">
-        <f>IF(Config!$C$19="","",IFERROR(H48/(H48+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$19,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+      <c r="I58" s="27">
+        <f>IF(Config!$C$19="","",IFERROR(H58/(H58+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$19,Propostas!$G$5:$G$304,"Perdida")),0))</f>
         <v>0.5</v>
       </c>
-      <c r="J48" s="26">
+      <c r="J58" s="26">
         <f>IF(Config!$C$19="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$19,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>5400</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="24" t="str">
+    <row r="59">
+      <c r="A59" s="24" t="str">
         <f>IF(Config!$E$20="","",Config!$E$20)</f>
         <v>Desistiu da demanda</v>
       </c>
-      <c r="B49" s="25">
+      <c r="B59" s="25">
         <f>IF(Config!$E$20="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$20,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>0</v>
       </c>
-      <c r="C49" s="26">
+      <c r="C59" s="26">
         <f>IF(Config!$E$20="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$20,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>0</v>
       </c>
-      <c r="D49" s="27">
-        <f>IF(Config!$E$20="","",IFERROR(B49/$B$16,0))</f>
-        <v>0</v>
-      </c>
-      <c r="F49" s="24" t="str">
+      <c r="D59" s="27">
+        <f>IF(Config!$E$20="","",IFERROR(B59/$B$16,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="24" t="str">
         <f>IF(Config!$C$20="","",Config!$C$20)</f>
         <v>Instagram</v>
       </c>
-      <c r="G49" s="25">
+      <c r="G59" s="25">
         <f>IF(Config!$C$20="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$20))</f>
         <v>2</v>
       </c>
-      <c r="H49" s="25">
+      <c r="H59" s="25">
         <f>IF(Config!$C$20="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$20,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>1</v>
       </c>
-      <c r="I49" s="27">
-        <f>IF(Config!$C$20="","",IFERROR(H49/(H49+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$20,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+      <c r="I59" s="27">
+        <f>IF(Config!$C$20="","",IFERROR(H59/(H59+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$20,Propostas!$G$5:$G$304,"Perdida")),0))</f>
         <v>0.5</v>
       </c>
-      <c r="J49" s="26">
+      <c r="J59" s="26">
         <f>IF(Config!$C$20="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$20,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>4500</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="24" t="str">
+    <row r="60">
+      <c r="A60" s="24" t="str">
         <f>IF(Config!$E$21="","",Config!$E$21)</f>
         <v>Sem resposta</v>
       </c>
-      <c r="B50" s="25">
+      <c r="B60" s="25">
         <f>IF(Config!$E$21="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$21,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>1</v>
       </c>
-      <c r="C50" s="26">
+      <c r="C60" s="26">
         <f>IF(Config!$E$21="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$21,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>4400</v>
       </c>
-      <c r="D50" s="27">
-        <f>IF(Config!$E$21="","",IFERROR(B50/$B$16,0))</f>
+      <c r="D60" s="27">
+        <f>IF(Config!$E$21="","",IFERROR(B60/$B$16,0))</f>
         <v>0.25</v>
       </c>
-      <c r="F50" s="24" t="str">
+      <c r="F60" s="24" t="str">
         <f>IF(Config!$C$21="","",Config!$C$21)</f>
         <v>Cliente antigo</v>
       </c>
-      <c r="G50" s="25">
+      <c r="G60" s="25">
         <f>IF(Config!$C$21="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$21))</f>
         <v>8</v>
       </c>
-      <c r="H50" s="25">
+      <c r="H60" s="25">
         <f>IF(Config!$C$21="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$21,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>3</v>
       </c>
-      <c r="I50" s="27">
-        <f>IF(Config!$C$21="","",IFERROR(H50/(H50+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$21,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+      <c r="I60" s="27">
+        <f>IF(Config!$C$21="","",IFERROR(H60/(H60+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$21,Propostas!$G$5:$G$304,"Perdida")),0))</f>
         <v>1</v>
       </c>
-      <c r="J50" s="26">
+      <c r="J60" s="26">
         <f>IF(Config!$C$21="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$21,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>46700</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="24" t="str">
+    <row r="61">
+      <c r="A61" s="24" t="str">
         <f>IF(Config!$E$22="","",Config!$E$22)</f>
         <v>Fora da área de atuação</v>
       </c>
-      <c r="B51" s="25">
+      <c r="B61" s="25">
         <f>IF(Config!$E$22="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$22,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>0</v>
       </c>
-      <c r="C51" s="26">
+      <c r="C61" s="26">
         <f>IF(Config!$E$22="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$22,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>0</v>
       </c>
-      <c r="D51" s="27">
-        <f>IF(Config!$E$22="","",IFERROR(B51/$B$16,0))</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="24" t="str">
+      <c r="D61" s="27">
+        <f>IF(Config!$E$22="","",IFERROR(B61/$B$16,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="24" t="str">
         <f>IF(Config!$C$22="","",Config!$C$22)</f>
         <v>Parceria (contador, imobiliária)</v>
       </c>
-      <c r="G51" s="25">
+      <c r="G61" s="25">
         <f>IF(Config!$C$22="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$22))</f>
         <v>2</v>
       </c>
-      <c r="H51" s="25">
+      <c r="H61" s="25">
         <f>IF(Config!$C$22="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$22,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>1</v>
       </c>
-      <c r="I51" s="27">
-        <f>IF(Config!$C$22="","",IFERROR(H51/(H51+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$22,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+      <c r="I61" s="27">
+        <f>IF(Config!$C$22="","",IFERROR(H61/(H61+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$22,Propostas!$G$5:$G$304,"Perdida")),0))</f>
         <v>1</v>
       </c>
-      <c r="J51" s="26">
+      <c r="J61" s="26">
         <f>IF(Config!$C$22="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$22,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>8400</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="24" t="str">
+    <row r="62">
+      <c r="A62" s="24" t="str">
         <f>IF(Config!$E$23="","",Config!$E$23)</f>
         <v>Prazo de atendimento</v>
       </c>
-      <c r="B52" s="25">
+      <c r="B62" s="25">
         <f>IF(Config!$E$23="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$23,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>0</v>
       </c>
-      <c r="C52" s="26">
+      <c r="C62" s="26">
         <f>IF(Config!$E$23="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$23,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v>0</v>
       </c>
-      <c r="D52" s="27">
-        <f>IF(Config!$E$23="","",IFERROR(B52/$B$16,0))</f>
-        <v>0</v>
-      </c>
-      <c r="F52" s="24" t="str">
+      <c r="D62" s="27">
+        <f>IF(Config!$E$23="","",IFERROR(B62/$B$16,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="24" t="str">
         <f>IF(Config!$C$23="","",Config!$C$23)</f>
         <v>Evento ou palestra</v>
       </c>
-      <c r="G52" s="25">
+      <c r="G62" s="25">
         <f>IF(Config!$C$23="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$23))</f>
         <v>1</v>
       </c>
-      <c r="H52" s="25">
+      <c r="H62" s="25">
         <f>IF(Config!$C$23="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$23,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>0</v>
       </c>
-      <c r="I52" s="27">
-        <f>IF(Config!$C$23="","",IFERROR(H52/(H52+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$23,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="26">
+      <c r="I62" s="27">
+        <f>IF(Config!$C$23="","",IFERROR(H62/(H62+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$23,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="26">
         <f>IF(Config!$C$23="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$23,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="24">
+    <row r="63">
+      <c r="A63" s="24">
         <f>IF(Config!$E$24="","",Config!$E$24)</f>
         <v/>
       </c>
-      <c r="B53" s="25">
+      <c r="B63" s="25">
         <f>IF(Config!$E$24="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$24,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v/>
       </c>
-      <c r="C53" s="26">
+      <c r="C63" s="26">
         <f>IF(Config!$E$24="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$24,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v/>
       </c>
-      <c r="D53" s="27">
-        <f>IF(Config!$E$24="","",IFERROR(B53/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F53" s="24">
+      <c r="D63" s="27">
+        <f>IF(Config!$E$24="","",IFERROR(B63/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F63" s="24">
         <f>IF(Config!$C$24="","",Config!$C$24)</f>
         <v/>
       </c>
-      <c r="G53" s="25">
+      <c r="G63" s="25">
         <f>IF(Config!$C$24="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$24))</f>
         <v/>
       </c>
-      <c r="H53" s="25">
+      <c r="H63" s="25">
         <f>IF(Config!$C$24="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$24,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v/>
       </c>
-      <c r="I53" s="27">
-        <f>IF(Config!$C$24="","",IFERROR(H53/(H53+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$24,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
-      </c>
-      <c r="J53" s="26">
+      <c r="I63" s="27">
+        <f>IF(Config!$C$24="","",IFERROR(H63/(H63+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$24,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J63" s="26">
         <f>IF(Config!$C$24="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$24,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="24">
+    <row r="64">
+      <c r="A64" s="24">
         <f>IF(Config!$E$25="","",Config!$E$25)</f>
         <v/>
       </c>
-      <c r="B54" s="25">
+      <c r="B64" s="25">
         <f>IF(Config!$E$25="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$25,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v/>
       </c>
-      <c r="C54" s="26">
+      <c r="C64" s="26">
         <f>IF(Config!$E$25="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$25,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v/>
       </c>
-      <c r="D54" s="27">
-        <f>IF(Config!$E$25="","",IFERROR(B54/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F54" s="24">
+      <c r="D64" s="27">
+        <f>IF(Config!$E$25="","",IFERROR(B64/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F64" s="24">
         <f>IF(Config!$C$25="","",Config!$C$25)</f>
         <v/>
       </c>
-      <c r="G54" s="25">
+      <c r="G64" s="25">
         <f>IF(Config!$C$25="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$25))</f>
         <v/>
       </c>
-      <c r="H54" s="25">
+      <c r="H64" s="25">
         <f>IF(Config!$C$25="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$25,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v/>
       </c>
-      <c r="I54" s="27">
-        <f>IF(Config!$C$25="","",IFERROR(H54/(H54+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$25,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
-      </c>
-      <c r="J54" s="26">
+      <c r="I64" s="27">
+        <f>IF(Config!$C$25="","",IFERROR(H64/(H64+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$25,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J64" s="26">
         <f>IF(Config!$C$25="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$25,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="24">
+    <row r="65">
+      <c r="A65" s="24">
         <f>IF(Config!$E$26="","",Config!$E$26)</f>
         <v/>
       </c>
-      <c r="B55" s="25">
+      <c r="B65" s="25">
         <f>IF(Config!$E$26="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$26,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v/>
       </c>
-      <c r="C55" s="26">
+      <c r="C65" s="26">
         <f>IF(Config!$E$26="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$26,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v/>
       </c>
-      <c r="D55" s="27">
-        <f>IF(Config!$E$26="","",IFERROR(B55/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F55" s="24">
+      <c r="D65" s="27">
+        <f>IF(Config!$E$26="","",IFERROR(B65/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F65" s="24">
         <f>IF(Config!$C$26="","",Config!$C$26)</f>
         <v/>
       </c>
-      <c r="G55" s="25">
+      <c r="G65" s="25">
         <f>IF(Config!$C$26="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$26))</f>
         <v/>
       </c>
-      <c r="H55" s="25">
+      <c r="H65" s="25">
         <f>IF(Config!$C$26="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$26,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v/>
       </c>
-      <c r="I55" s="27">
-        <f>IF(Config!$C$26="","",IFERROR(H55/(H55+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$26,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
-      </c>
-      <c r="J55" s="26">
+      <c r="I65" s="27">
+        <f>IF(Config!$C$26="","",IFERROR(H65/(H65+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$26,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J65" s="26">
         <f>IF(Config!$C$26="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$26,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="24">
+    <row r="66">
+      <c r="A66" s="24">
         <f>IF(Config!$E$27="","",Config!$E$27)</f>
         <v/>
       </c>
-      <c r="B56" s="25">
+      <c r="B66" s="25">
         <f>IF(Config!$E$27="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$27,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v/>
       </c>
-      <c r="C56" s="26">
+      <c r="C66" s="26">
         <f>IF(Config!$E$27="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$27,Propostas!$G$5:$G$304,"Perdida"))</f>
         <v/>
       </c>
-      <c r="D56" s="27">
-        <f>IF(Config!$E$27="","",IFERROR(B56/$B$16,0))</f>
-        <v/>
-      </c>
-      <c r="F56" s="24">
+      <c r="D66" s="27">
+        <f>IF(Config!$E$27="","",IFERROR(B66/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F66" s="24">
         <f>IF(Config!$C$27="","",Config!$C$27)</f>
         <v/>
       </c>
-      <c r="G56" s="25">
+      <c r="G66" s="25">
         <f>IF(Config!$C$27="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$27))</f>
         <v/>
       </c>
-      <c r="H56" s="25">
+      <c r="H66" s="25">
         <f>IF(Config!$C$27="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$27,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v/>
       </c>
-      <c r="I56" s="27">
-        <f>IF(Config!$C$27="","",IFERROR(H56/(H56+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$27,Propostas!$G$5:$G$304,"Perdida")),0))</f>
-        <v/>
-      </c>
-      <c r="J56" s="26">
+      <c r="I66" s="27">
+        <f>IF(Config!$C$27="","",IFERROR(H66/(H66+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$27,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J66" s="26">
         <f>IF(Config!$C$27="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$27,Propostas!$G$5:$G$304,"Fechada"))</f>
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="19" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="24">
+        <f>IF(Config!$E$28="","",Config!$E$28)</f>
+        <v/>
+      </c>
+      <c r="B67" s="25">
+        <f>IF(Config!$E$28="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$28,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C67" s="26">
+        <f>IF(Config!$E$28="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$28,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D67" s="27">
+        <f>IF(Config!$E$28="","",IFERROR(B67/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F67" s="24">
+        <f>IF(Config!$C$28="","",Config!$C$28)</f>
+        <v/>
+      </c>
+      <c r="G67" s="25">
+        <f>IF(Config!$C$28="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$28))</f>
+        <v/>
+      </c>
+      <c r="H67" s="25">
+        <f>IF(Config!$C$28="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$28,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I67" s="27">
+        <f>IF(Config!$C$28="","",IFERROR(H67/(H67+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$28,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J67" s="26">
+        <f>IF(Config!$C$28="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$28,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="24">
+        <f>IF(Config!$E$29="","",Config!$E$29)</f>
+        <v/>
+      </c>
+      <c r="B68" s="25">
+        <f>IF(Config!$E$29="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$29,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C68" s="26">
+        <f>IF(Config!$E$29="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$29,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D68" s="27">
+        <f>IF(Config!$E$29="","",IFERROR(B68/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F68" s="24">
+        <f>IF(Config!$C$29="","",Config!$C$29)</f>
+        <v/>
+      </c>
+      <c r="G68" s="25">
+        <f>IF(Config!$C$29="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$29))</f>
+        <v/>
+      </c>
+      <c r="H68" s="25">
+        <f>IF(Config!$C$29="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$29,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I68" s="27">
+        <f>IF(Config!$C$29="","",IFERROR(H68/(H68+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$29,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J68" s="26">
+        <f>IF(Config!$C$29="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$29,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="24">
+        <f>IF(Config!$E$30="","",Config!$E$30)</f>
+        <v/>
+      </c>
+      <c r="B69" s="25">
+        <f>IF(Config!$E$30="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$30,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C69" s="26">
+        <f>IF(Config!$E$30="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$30,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D69" s="27">
+        <f>IF(Config!$E$30="","",IFERROR(B69/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F69" s="24">
+        <f>IF(Config!$C$30="","",Config!$C$30)</f>
+        <v/>
+      </c>
+      <c r="G69" s="25">
+        <f>IF(Config!$C$30="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$30))</f>
+        <v/>
+      </c>
+      <c r="H69" s="25">
+        <f>IF(Config!$C$30="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$30,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I69" s="27">
+        <f>IF(Config!$C$30="","",IFERROR(H69/(H69+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$30,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J69" s="26">
+        <f>IF(Config!$C$30="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$30,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="24">
+        <f>IF(Config!$E$31="","",Config!$E$31)</f>
+        <v/>
+      </c>
+      <c r="B70" s="25">
+        <f>IF(Config!$E$31="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$31,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C70" s="26">
+        <f>IF(Config!$E$31="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$31,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D70" s="27">
+        <f>IF(Config!$E$31="","",IFERROR(B70/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F70" s="24">
+        <f>IF(Config!$C$31="","",Config!$C$31)</f>
+        <v/>
+      </c>
+      <c r="G70" s="25">
+        <f>IF(Config!$C$31="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$31))</f>
+        <v/>
+      </c>
+      <c r="H70" s="25">
+        <f>IF(Config!$C$31="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$31,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I70" s="27">
+        <f>IF(Config!$C$31="","",IFERROR(H70/(H70+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$31,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J70" s="26">
+        <f>IF(Config!$C$31="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$31,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24">
+        <f>IF(Config!$E$32="","",Config!$E$32)</f>
+        <v/>
+      </c>
+      <c r="B71" s="25">
+        <f>IF(Config!$E$32="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$32,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C71" s="26">
+        <f>IF(Config!$E$32="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$32,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D71" s="27">
+        <f>IF(Config!$E$32="","",IFERROR(B71/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F71" s="24">
+        <f>IF(Config!$C$32="","",Config!$C$32)</f>
+        <v/>
+      </c>
+      <c r="G71" s="25">
+        <f>IF(Config!$C$32="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$32))</f>
+        <v/>
+      </c>
+      <c r="H71" s="25">
+        <f>IF(Config!$C$32="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$32,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I71" s="27">
+        <f>IF(Config!$C$32="","",IFERROR(H71/(H71+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$32,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J71" s="26">
+        <f>IF(Config!$C$32="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$32,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24">
+        <f>IF(Config!$E$33="","",Config!$E$33)</f>
+        <v/>
+      </c>
+      <c r="B72" s="25">
+        <f>IF(Config!$E$33="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$33,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C72" s="26">
+        <f>IF(Config!$E$33="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$33,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D72" s="27">
+        <f>IF(Config!$E$33="","",IFERROR(B72/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F72" s="24">
+        <f>IF(Config!$C$33="","",Config!$C$33)</f>
+        <v/>
+      </c>
+      <c r="G72" s="25">
+        <f>IF(Config!$C$33="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$33))</f>
+        <v/>
+      </c>
+      <c r="H72" s="25">
+        <f>IF(Config!$C$33="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$33,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I72" s="27">
+        <f>IF(Config!$C$33="","",IFERROR(H72/(H72+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$33,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J72" s="26">
+        <f>IF(Config!$C$33="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$33,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="24">
+        <f>IF(Config!$E$34="","",Config!$E$34)</f>
+        <v/>
+      </c>
+      <c r="B73" s="25">
+        <f>IF(Config!$E$34="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$34,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C73" s="26">
+        <f>IF(Config!$E$34="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$34,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D73" s="27">
+        <f>IF(Config!$E$34="","",IFERROR(B73/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F73" s="24">
+        <f>IF(Config!$C$34="","",Config!$C$34)</f>
+        <v/>
+      </c>
+      <c r="G73" s="25">
+        <f>IF(Config!$C$34="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$34))</f>
+        <v/>
+      </c>
+      <c r="H73" s="25">
+        <f>IF(Config!$C$34="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$34,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I73" s="27">
+        <f>IF(Config!$C$34="","",IFERROR(H73/(H73+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$34,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J73" s="26">
+        <f>IF(Config!$C$34="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$34,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="24">
+        <f>IF(Config!$E$35="","",Config!$E$35)</f>
+        <v/>
+      </c>
+      <c r="B74" s="25">
+        <f>IF(Config!$E$35="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$35,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C74" s="26">
+        <f>IF(Config!$E$35="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$35,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D74" s="27">
+        <f>IF(Config!$E$35="","",IFERROR(B74/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F74" s="24">
+        <f>IF(Config!$C$35="","",Config!$C$35)</f>
+        <v/>
+      </c>
+      <c r="G74" s="25">
+        <f>IF(Config!$C$35="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$35))</f>
+        <v/>
+      </c>
+      <c r="H74" s="25">
+        <f>IF(Config!$C$35="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$35,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I74" s="27">
+        <f>IF(Config!$C$35="","",IFERROR(H74/(H74+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$35,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J74" s="26">
+        <f>IF(Config!$C$35="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$35,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="24">
+        <f>IF(Config!$E$36="","",Config!$E$36)</f>
+        <v/>
+      </c>
+      <c r="B75" s="25">
+        <f>IF(Config!$E$36="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$36,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C75" s="26">
+        <f>IF(Config!$E$36="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$36,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D75" s="27">
+        <f>IF(Config!$E$36="","",IFERROR(B75/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F75" s="24">
+        <f>IF(Config!$C$36="","",Config!$C$36)</f>
+        <v/>
+      </c>
+      <c r="G75" s="25">
+        <f>IF(Config!$C$36="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$36))</f>
+        <v/>
+      </c>
+      <c r="H75" s="25">
+        <f>IF(Config!$C$36="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$36,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I75" s="27">
+        <f>IF(Config!$C$36="","",IFERROR(H75/(H75+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$36,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J75" s="26">
+        <f>IF(Config!$C$36="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$36,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="24">
+        <f>IF(Config!$E$37="","",Config!$E$37)</f>
+        <v/>
+      </c>
+      <c r="B76" s="25">
+        <f>IF(Config!$E$37="","",COUNTIFS(Propostas!$L$5:$L$304,Config!$E$37,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="C76" s="26">
+        <f>IF(Config!$E$37="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$L$5:$L$304,Config!$E$37,Propostas!$G$5:$G$304,"Perdida"))</f>
+        <v/>
+      </c>
+      <c r="D76" s="27">
+        <f>IF(Config!$E$37="","",IFERROR(B76/$B$16,0))</f>
+        <v/>
+      </c>
+      <c r="F76" s="24">
+        <f>IF(Config!$C$37="","",Config!$C$37)</f>
+        <v/>
+      </c>
+      <c r="G76" s="25">
+        <f>IF(Config!$C$37="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$37))</f>
+        <v/>
+      </c>
+      <c r="H76" s="25">
+        <f>IF(Config!$C$37="","",COUNTIFS(Propostas!$D$5:$D$304,Config!$C$37,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+      <c r="I76" s="27">
+        <f>IF(Config!$C$37="","",IFERROR(H76/(H76+COUNTIFS(Propostas!$D$5:$D$304,Config!$C$37,Propostas!$G$5:$G$304,"Perdida")),0))</f>
+        <v/>
+      </c>
+      <c r="J76" s="26">
+        <f>IF(Config!$C$37="","",SUMIFS(Propostas!$F$5:$F$304,Propostas!$D$5:$D$304,Config!$C$37,Propostas!$G$5:$G$304,"Fechada"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>Fonte: aba Propostas. Uma proposta perdida com o motivo anotado vale mais que três sem: é o que mostra o que ajustar no preço, no prazo ou na abordagem.</t>
         </is>
@@ -2498,7 +3178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2862,16 +3542,83 @@
       </c>
     </row>
     <row r="28">
-      <c r="I28" t="inlineStr">
+      <c r="A28" s="31" t="n"/>
+      <c r="C28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="I28" s="31" t="inlineStr">
         <is>
           <t>Discussão de contrato de prestação de serviços</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>Preencha cada lista de cima para baixo, sem pular linha: as listas suspensas de Propostas param na primeira célula vazia. Até 10 itens por lista. Serviço é texto livre; a lista só sugere.</t>
+      <c r="A29" s="31" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="G29" s="31" t="n"/>
+      <c r="I29" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="n"/>
+      <c r="C31" s="31" t="n"/>
+      <c r="E31" s="31" t="n"/>
+      <c r="G31" s="31" t="n"/>
+      <c r="I31" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="31" t="n"/>
+      <c r="C32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="I32" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="E33" s="31" t="n"/>
+      <c r="G33" s="31" t="n"/>
+      <c r="I33" s="31" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="n"/>
+      <c r="C34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="E35" s="31" t="n"/>
+      <c r="G35" s="31" t="n"/>
+      <c r="I35" s="31" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="n"/>
+      <c r="C36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n"/>
+      <c r="C37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="I37" s="31" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>Preencha cada lista de cima para baixo, sem pular linha: as listas suspensas de Propostas param na primeira célula vazia. Até 20 itens por lista. Serviço é texto livre; a lista só sugere.</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3830,7 @@
         <v>Fechada</v>
       </c>
       <c r="R5" s="37">
-        <f>IF(OR(G5="",Q5="Fechada",Q5="Perdida"),0,IF(Q5="Previsão vencida",3,IF(Q5="Parada",2,1))*1E+13+MIN(N(O5),500)*1E+10+MIN(ROUND(N(F5),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G5="",Q5="Fechada",Q5="Perdida"),0,IF(Q5="Previsão vencida",3,IF(Q5="Parada",2,1))*1E+15+MIN(N(O5),500)*1E+12+MIN(ROUND(N(F5)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3155,7 +3902,7 @@
         <v>Fechada</v>
       </c>
       <c r="R6" s="37">
-        <f>IF(OR(G6="",Q6="Fechada",Q6="Perdida"),0,IF(Q6="Previsão vencida",3,IF(Q6="Parada",2,1))*1E+13+MIN(N(O6),500)*1E+10+MIN(ROUND(N(F6),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G6="",Q6="Fechada",Q6="Perdida"),0,IF(Q6="Previsão vencida",3,IF(Q6="Parada",2,1))*1E+15+MIN(N(O6),500)*1E+12+MIN(ROUND(N(F6)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3227,7 +3974,7 @@
         <v>Fechada</v>
       </c>
       <c r="R7" s="37">
-        <f>IF(OR(G7="",Q7="Fechada",Q7="Perdida"),0,IF(Q7="Previsão vencida",3,IF(Q7="Parada",2,1))*1E+13+MIN(N(O7),500)*1E+10+MIN(ROUND(N(F7),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G7="",Q7="Fechada",Q7="Perdida"),0,IF(Q7="Previsão vencida",3,IF(Q7="Parada",2,1))*1E+15+MIN(N(O7),500)*1E+12+MIN(ROUND(N(F7)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3299,7 +4046,7 @@
         <v>Fechada</v>
       </c>
       <c r="R8" s="37">
-        <f>IF(OR(G8="",Q8="Fechada",Q8="Perdida"),0,IF(Q8="Previsão vencida",3,IF(Q8="Parada",2,1))*1E+13+MIN(N(O8),500)*1E+10+MIN(ROUND(N(F8),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G8="",Q8="Fechada",Q8="Perdida"),0,IF(Q8="Previsão vencida",3,IF(Q8="Parada",2,1))*1E+15+MIN(N(O8),500)*1E+12+MIN(ROUND(N(F8)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3371,7 +4118,7 @@
         <v>Fechada</v>
       </c>
       <c r="R9" s="37">
-        <f>IF(OR(G9="",Q9="Fechada",Q9="Perdida"),0,IF(Q9="Previsão vencida",3,IF(Q9="Parada",2,1))*1E+13+MIN(N(O9),500)*1E+10+MIN(ROUND(N(F9),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G9="",Q9="Fechada",Q9="Perdida"),0,IF(Q9="Previsão vencida",3,IF(Q9="Parada",2,1))*1E+15+MIN(N(O9),500)*1E+12+MIN(ROUND(N(F9)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3447,7 +4194,7 @@
         <v>Perdida</v>
       </c>
       <c r="R10" s="37">
-        <f>IF(OR(G10="",Q10="Fechada",Q10="Perdida"),0,IF(Q10="Previsão vencida",3,IF(Q10="Parada",2,1))*1E+13+MIN(N(O10),500)*1E+10+MIN(ROUND(N(F10),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G10="",Q10="Fechada",Q10="Perdida"),0,IF(Q10="Previsão vencida",3,IF(Q10="Parada",2,1))*1E+15+MIN(N(O10),500)*1E+12+MIN(ROUND(N(F10)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3523,7 +4270,7 @@
         <v>Perdida</v>
       </c>
       <c r="R11" s="37">
-        <f>IF(OR(G11="",Q11="Fechada",Q11="Perdida"),0,IF(Q11="Previsão vencida",3,IF(Q11="Parada",2,1))*1E+13+MIN(N(O11),500)*1E+10+MIN(ROUND(N(F11),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G11="",Q11="Fechada",Q11="Perdida"),0,IF(Q11="Previsão vencida",3,IF(Q11="Parada",2,1))*1E+15+MIN(N(O11),500)*1E+12+MIN(ROUND(N(F11)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3595,7 +4342,7 @@
         <v>Fechada</v>
       </c>
       <c r="R12" s="37">
-        <f>IF(OR(G12="",Q12="Fechada",Q12="Perdida"),0,IF(Q12="Previsão vencida",3,IF(Q12="Parada",2,1))*1E+13+MIN(N(O12),500)*1E+10+MIN(ROUND(N(F12),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G12="",Q12="Fechada",Q12="Perdida"),0,IF(Q12="Previsão vencida",3,IF(Q12="Parada",2,1))*1E+15+MIN(N(O12),500)*1E+12+MIN(ROUND(N(F12)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3667,7 +4414,7 @@
         <v>Fechada</v>
       </c>
       <c r="R13" s="37">
-        <f>IF(OR(G13="",Q13="Fechada",Q13="Perdida"),0,IF(Q13="Previsão vencida",3,IF(Q13="Parada",2,1))*1E+13+MIN(N(O13),500)*1E+10+MIN(ROUND(N(F13),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G13="",Q13="Fechada",Q13="Perdida"),0,IF(Q13="Previsão vencida",3,IF(Q13="Parada",2,1))*1E+15+MIN(N(O13),500)*1E+12+MIN(ROUND(N(F13)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3743,7 +4490,7 @@
         <v>Perdida</v>
       </c>
       <c r="R14" s="37">
-        <f>IF(OR(G14="",Q14="Fechada",Q14="Perdida"),0,IF(Q14="Previsão vencida",3,IF(Q14="Parada",2,1))*1E+13+MIN(N(O14),500)*1E+10+MIN(ROUND(N(F14),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G14="",Q14="Fechada",Q14="Perdida"),0,IF(Q14="Previsão vencida",3,IF(Q14="Parada",2,1))*1E+15+MIN(N(O14),500)*1E+12+MIN(ROUND(N(F14)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3819,7 +4566,7 @@
         <v>Perdida</v>
       </c>
       <c r="R15" s="37">
-        <f>IF(OR(G15="",Q15="Fechada",Q15="Perdida"),0,IF(Q15="Previsão vencida",3,IF(Q15="Parada",2,1))*1E+13+MIN(N(O15),500)*1E+10+MIN(ROUND(N(F15),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G15="",Q15="Fechada",Q15="Perdida"),0,IF(Q15="Previsão vencida",3,IF(Q15="Parada",2,1))*1E+15+MIN(N(O15),500)*1E+12+MIN(ROUND(N(F15)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3889,8 +4636,8 @@
         <v>Ativa</v>
       </c>
       <c r="R16" s="37">
-        <f>IF(OR(G16="",Q16="Fechada",Q16="Perdida"),0,IF(Q16="Previsão vencida",3,IF(Q16="Parada",2,1))*1E+13+MIN(N(O16),500)*1E+10+MIN(ROUND(N(F16),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10040144000289</v>
+        <f>IF(OR(G16="",Q16="Fechada",Q16="Perdida"),0,IF(Q16="Previsão vencida",3,IF(Q16="Parada",2,1))*1E+15+MIN(N(O16),500)*1E+12+MIN(ROUND(N(F16)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1004014400000289</v>
       </c>
     </row>
     <row r="17">
@@ -3959,8 +4706,8 @@
         <v>Previsão vencida</v>
       </c>
       <c r="R17" s="37">
-        <f>IF(OR(G17="",Q17="Fechada",Q17="Perdida"),0,IF(Q17="Previsão vencida",3,IF(Q17="Parada",2,1))*1E+13+MIN(N(O17),500)*1E+10+MIN(ROUND(N(F17),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>30170068000288</v>
+        <f>IF(OR(G17="",Q17="Fechada",Q17="Perdida"),0,IF(Q17="Previsão vencida",3,IF(Q17="Parada",2,1))*1E+15+MIN(N(O17),500)*1E+12+MIN(ROUND(N(F17)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>3017006800000288</v>
       </c>
     </row>
     <row r="18">
@@ -4029,8 +4776,8 @@
         <v>Parada</v>
       </c>
       <c r="R18" s="37">
-        <f>IF(OR(G18="",Q18="Fechada",Q18="Perdida"),0,IF(Q18="Previsão vencida",3,IF(Q18="Parada",2,1))*1E+13+MIN(N(O18),500)*1E+10+MIN(ROUND(N(F18),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>20160105000287</v>
+        <f>IF(OR(G18="",Q18="Fechada",Q18="Perdida"),0,IF(Q18="Previsão vencida",3,IF(Q18="Parada",2,1))*1E+15+MIN(N(O18),500)*1E+12+MIN(ROUND(N(F18)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>2016010500000287</v>
       </c>
     </row>
     <row r="19">
@@ -4099,8 +4846,8 @@
         <v>Previsão vencida</v>
       </c>
       <c r="R19" s="37">
-        <f>IF(OR(G19="",Q19="Fechada",Q19="Perdida"),0,IF(Q19="Previsão vencida",3,IF(Q19="Parada",2,1))*1E+13+MIN(N(O19),500)*1E+10+MIN(ROUND(N(F19),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>30140042000286</v>
+        <f>IF(OR(G19="",Q19="Fechada",Q19="Perdida"),0,IF(Q19="Previsão vencida",3,IF(Q19="Parada",2,1))*1E+15+MIN(N(O19),500)*1E+12+MIN(ROUND(N(F19)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>3014004200000286</v>
       </c>
     </row>
     <row r="20">
@@ -4169,8 +4916,8 @@
         <v>Ativa</v>
       </c>
       <c r="R20" s="37">
-        <f>IF(OR(G20="",Q20="Fechada",Q20="Perdida"),0,IF(Q20="Previsão vencida",3,IF(Q20="Parada",2,1))*1E+13+MIN(N(O20),500)*1E+10+MIN(ROUND(N(F20),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10030058000285</v>
+        <f>IF(OR(G20="",Q20="Fechada",Q20="Perdida"),0,IF(Q20="Previsão vencida",3,IF(Q20="Parada",2,1))*1E+15+MIN(N(O20),500)*1E+12+MIN(ROUND(N(F20)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1003005800000285</v>
       </c>
     </row>
     <row r="21">
@@ -4239,8 +4986,8 @@
         <v>Ativa</v>
       </c>
       <c r="R21" s="37">
-        <f>IF(OR(G21="",Q21="Fechada",Q21="Perdida"),0,IF(Q21="Previsão vencida",3,IF(Q21="Parada",2,1))*1E+13+MIN(N(O21),500)*1E+10+MIN(ROUND(N(F21),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10020079000284</v>
+        <f>IF(OR(G21="",Q21="Fechada",Q21="Perdida"),0,IF(Q21="Previsão vencida",3,IF(Q21="Parada",2,1))*1E+15+MIN(N(O21),500)*1E+12+MIN(ROUND(N(F21)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1002007900000284</v>
       </c>
     </row>
     <row r="22">
@@ -4309,8 +5056,8 @@
         <v>Ativa</v>
       </c>
       <c r="R22" s="37">
-        <f>IF(OR(G22="",Q22="Fechada",Q22="Perdida"),0,IF(Q22="Previsão vencida",3,IF(Q22="Parada",2,1))*1E+13+MIN(N(O22),500)*1E+10+MIN(ROUND(N(F22),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10010132000283</v>
+        <f>IF(OR(G22="",Q22="Fechada",Q22="Perdida"),0,IF(Q22="Previsão vencida",3,IF(Q22="Parada",2,1))*1E+15+MIN(N(O22),500)*1E+12+MIN(ROUND(N(F22)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1001013200000283</v>
       </c>
     </row>
     <row r="23">
@@ -4379,8 +5126,8 @@
         <v>Ativa</v>
       </c>
       <c r="R23" s="37">
-        <f>IF(OR(G23="",Q23="Fechada",Q23="Perdida"),0,IF(Q23="Previsão vencida",3,IF(Q23="Parada",2,1))*1E+13+MIN(N(O23),500)*1E+10+MIN(ROUND(N(F23),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10000045000282</v>
+        <f>IF(OR(G23="",Q23="Fechada",Q23="Perdida"),0,IF(Q23="Previsão vencida",3,IF(Q23="Parada",2,1))*1E+15+MIN(N(O23),500)*1E+12+MIN(ROUND(N(F23)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1000004500000282</v>
       </c>
     </row>
     <row r="24">
@@ -4449,8 +5196,8 @@
         <v>Ativa</v>
       </c>
       <c r="R24" s="37">
-        <f>IF(OR(G24="",Q24="Fechada",Q24="Perdida"),0,IF(Q24="Previsão vencida",3,IF(Q24="Parada",2,1))*1E+13+MIN(N(O24),500)*1E+10+MIN(ROUND(N(F24),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10030056000281</v>
+        <f>IF(OR(G24="",Q24="Fechada",Q24="Perdida"),0,IF(Q24="Previsão vencida",3,IF(Q24="Parada",2,1))*1E+15+MIN(N(O24),500)*1E+12+MIN(ROUND(N(F24)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1003005600000281</v>
       </c>
     </row>
     <row r="25">
@@ -4487,7 +5234,7 @@
         <v/>
       </c>
       <c r="R25" s="37">
-        <f>IF(OR(G25="",Q25="Fechada",Q25="Perdida"),0,IF(Q25="Previsão vencida",3,IF(Q25="Parada",2,1))*1E+13+MIN(N(O25),500)*1E+10+MIN(ROUND(N(F25),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G25="",Q25="Fechada",Q25="Perdida"),0,IF(Q25="Previsão vencida",3,IF(Q25="Parada",2,1))*1E+15+MIN(N(O25),500)*1E+12+MIN(ROUND(N(F25)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4525,7 +5272,7 @@
         <v/>
       </c>
       <c r="R26" s="37">
-        <f>IF(OR(G26="",Q26="Fechada",Q26="Perdida"),0,IF(Q26="Previsão vencida",3,IF(Q26="Parada",2,1))*1E+13+MIN(N(O26),500)*1E+10+MIN(ROUND(N(F26),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G26="",Q26="Fechada",Q26="Perdida"),0,IF(Q26="Previsão vencida",3,IF(Q26="Parada",2,1))*1E+15+MIN(N(O26),500)*1E+12+MIN(ROUND(N(F26)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4563,7 +5310,7 @@
         <v/>
       </c>
       <c r="R27" s="37">
-        <f>IF(OR(G27="",Q27="Fechada",Q27="Perdida"),0,IF(Q27="Previsão vencida",3,IF(Q27="Parada",2,1))*1E+13+MIN(N(O27),500)*1E+10+MIN(ROUND(N(F27),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G27="",Q27="Fechada",Q27="Perdida"),0,IF(Q27="Previsão vencida",3,IF(Q27="Parada",2,1))*1E+15+MIN(N(O27),500)*1E+12+MIN(ROUND(N(F27)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4601,7 +5348,7 @@
         <v/>
       </c>
       <c r="R28" s="37">
-        <f>IF(OR(G28="",Q28="Fechada",Q28="Perdida"),0,IF(Q28="Previsão vencida",3,IF(Q28="Parada",2,1))*1E+13+MIN(N(O28),500)*1E+10+MIN(ROUND(N(F28),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G28="",Q28="Fechada",Q28="Perdida"),0,IF(Q28="Previsão vencida",3,IF(Q28="Parada",2,1))*1E+15+MIN(N(O28),500)*1E+12+MIN(ROUND(N(F28)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4639,7 +5386,7 @@
         <v/>
       </c>
       <c r="R29" s="37">
-        <f>IF(OR(G29="",Q29="Fechada",Q29="Perdida"),0,IF(Q29="Previsão vencida",3,IF(Q29="Parada",2,1))*1E+13+MIN(N(O29),500)*1E+10+MIN(ROUND(N(F29),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G29="",Q29="Fechada",Q29="Perdida"),0,IF(Q29="Previsão vencida",3,IF(Q29="Parada",2,1))*1E+15+MIN(N(O29),500)*1E+12+MIN(ROUND(N(F29)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4677,7 +5424,7 @@
         <v/>
       </c>
       <c r="R30" s="37">
-        <f>IF(OR(G30="",Q30="Fechada",Q30="Perdida"),0,IF(Q30="Previsão vencida",3,IF(Q30="Parada",2,1))*1E+13+MIN(N(O30),500)*1E+10+MIN(ROUND(N(F30),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G30="",Q30="Fechada",Q30="Perdida"),0,IF(Q30="Previsão vencida",3,IF(Q30="Parada",2,1))*1E+15+MIN(N(O30),500)*1E+12+MIN(ROUND(N(F30)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4715,7 +5462,7 @@
         <v/>
       </c>
       <c r="R31" s="37">
-        <f>IF(OR(G31="",Q31="Fechada",Q31="Perdida"),0,IF(Q31="Previsão vencida",3,IF(Q31="Parada",2,1))*1E+13+MIN(N(O31),500)*1E+10+MIN(ROUND(N(F31),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G31="",Q31="Fechada",Q31="Perdida"),0,IF(Q31="Previsão vencida",3,IF(Q31="Parada",2,1))*1E+15+MIN(N(O31),500)*1E+12+MIN(ROUND(N(F31)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4753,7 +5500,7 @@
         <v/>
       </c>
       <c r="R32" s="37">
-        <f>IF(OR(G32="",Q32="Fechada",Q32="Perdida"),0,IF(Q32="Previsão vencida",3,IF(Q32="Parada",2,1))*1E+13+MIN(N(O32),500)*1E+10+MIN(ROUND(N(F32),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G32="",Q32="Fechada",Q32="Perdida"),0,IF(Q32="Previsão vencida",3,IF(Q32="Parada",2,1))*1E+15+MIN(N(O32),500)*1E+12+MIN(ROUND(N(F32)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4791,7 +5538,7 @@
         <v/>
       </c>
       <c r="R33" s="37">
-        <f>IF(OR(G33="",Q33="Fechada",Q33="Perdida"),0,IF(Q33="Previsão vencida",3,IF(Q33="Parada",2,1))*1E+13+MIN(N(O33),500)*1E+10+MIN(ROUND(N(F33),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G33="",Q33="Fechada",Q33="Perdida"),0,IF(Q33="Previsão vencida",3,IF(Q33="Parada",2,1))*1E+15+MIN(N(O33),500)*1E+12+MIN(ROUND(N(F33)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4829,7 +5576,7 @@
         <v/>
       </c>
       <c r="R34" s="37">
-        <f>IF(OR(G34="",Q34="Fechada",Q34="Perdida"),0,IF(Q34="Previsão vencida",3,IF(Q34="Parada",2,1))*1E+13+MIN(N(O34),500)*1E+10+MIN(ROUND(N(F34),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G34="",Q34="Fechada",Q34="Perdida"),0,IF(Q34="Previsão vencida",3,IF(Q34="Parada",2,1))*1E+15+MIN(N(O34),500)*1E+12+MIN(ROUND(N(F34)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4867,7 +5614,7 @@
         <v/>
       </c>
       <c r="R35" s="37">
-        <f>IF(OR(G35="",Q35="Fechada",Q35="Perdida"),0,IF(Q35="Previsão vencida",3,IF(Q35="Parada",2,1))*1E+13+MIN(N(O35),500)*1E+10+MIN(ROUND(N(F35),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G35="",Q35="Fechada",Q35="Perdida"),0,IF(Q35="Previsão vencida",3,IF(Q35="Parada",2,1))*1E+15+MIN(N(O35),500)*1E+12+MIN(ROUND(N(F35)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4905,7 +5652,7 @@
         <v/>
       </c>
       <c r="R36" s="37">
-        <f>IF(OR(G36="",Q36="Fechada",Q36="Perdida"),0,IF(Q36="Previsão vencida",3,IF(Q36="Parada",2,1))*1E+13+MIN(N(O36),500)*1E+10+MIN(ROUND(N(F36),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G36="",Q36="Fechada",Q36="Perdida"),0,IF(Q36="Previsão vencida",3,IF(Q36="Parada",2,1))*1E+15+MIN(N(O36),500)*1E+12+MIN(ROUND(N(F36)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4943,7 +5690,7 @@
         <v/>
       </c>
       <c r="R37" s="37">
-        <f>IF(OR(G37="",Q37="Fechada",Q37="Perdida"),0,IF(Q37="Previsão vencida",3,IF(Q37="Parada",2,1))*1E+13+MIN(N(O37),500)*1E+10+MIN(ROUND(N(F37),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G37="",Q37="Fechada",Q37="Perdida"),0,IF(Q37="Previsão vencida",3,IF(Q37="Parada",2,1))*1E+15+MIN(N(O37),500)*1E+12+MIN(ROUND(N(F37)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4981,7 +5728,7 @@
         <v/>
       </c>
       <c r="R38" s="37">
-        <f>IF(OR(G38="",Q38="Fechada",Q38="Perdida"),0,IF(Q38="Previsão vencida",3,IF(Q38="Parada",2,1))*1E+13+MIN(N(O38),500)*1E+10+MIN(ROUND(N(F38),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G38="",Q38="Fechada",Q38="Perdida"),0,IF(Q38="Previsão vencida",3,IF(Q38="Parada",2,1))*1E+15+MIN(N(O38),500)*1E+12+MIN(ROUND(N(F38)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5019,7 +5766,7 @@
         <v/>
       </c>
       <c r="R39" s="37">
-        <f>IF(OR(G39="",Q39="Fechada",Q39="Perdida"),0,IF(Q39="Previsão vencida",3,IF(Q39="Parada",2,1))*1E+13+MIN(N(O39),500)*1E+10+MIN(ROUND(N(F39),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G39="",Q39="Fechada",Q39="Perdida"),0,IF(Q39="Previsão vencida",3,IF(Q39="Parada",2,1))*1E+15+MIN(N(O39),500)*1E+12+MIN(ROUND(N(F39)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5057,7 +5804,7 @@
         <v/>
       </c>
       <c r="R40" s="37">
-        <f>IF(OR(G40="",Q40="Fechada",Q40="Perdida"),0,IF(Q40="Previsão vencida",3,IF(Q40="Parada",2,1))*1E+13+MIN(N(O40),500)*1E+10+MIN(ROUND(N(F40),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G40="",Q40="Fechada",Q40="Perdida"),0,IF(Q40="Previsão vencida",3,IF(Q40="Parada",2,1))*1E+15+MIN(N(O40),500)*1E+12+MIN(ROUND(N(F40)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5095,7 +5842,7 @@
         <v/>
       </c>
       <c r="R41" s="37">
-        <f>IF(OR(G41="",Q41="Fechada",Q41="Perdida"),0,IF(Q41="Previsão vencida",3,IF(Q41="Parada",2,1))*1E+13+MIN(N(O41),500)*1E+10+MIN(ROUND(N(F41),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G41="",Q41="Fechada",Q41="Perdida"),0,IF(Q41="Previsão vencida",3,IF(Q41="Parada",2,1))*1E+15+MIN(N(O41),500)*1E+12+MIN(ROUND(N(F41)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5133,7 +5880,7 @@
         <v/>
       </c>
       <c r="R42" s="37">
-        <f>IF(OR(G42="",Q42="Fechada",Q42="Perdida"),0,IF(Q42="Previsão vencida",3,IF(Q42="Parada",2,1))*1E+13+MIN(N(O42),500)*1E+10+MIN(ROUND(N(F42),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G42="",Q42="Fechada",Q42="Perdida"),0,IF(Q42="Previsão vencida",3,IF(Q42="Parada",2,1))*1E+15+MIN(N(O42),500)*1E+12+MIN(ROUND(N(F42)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5171,7 +5918,7 @@
         <v/>
       </c>
       <c r="R43" s="37">
-        <f>IF(OR(G43="",Q43="Fechada",Q43="Perdida"),0,IF(Q43="Previsão vencida",3,IF(Q43="Parada",2,1))*1E+13+MIN(N(O43),500)*1E+10+MIN(ROUND(N(F43),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G43="",Q43="Fechada",Q43="Perdida"),0,IF(Q43="Previsão vencida",3,IF(Q43="Parada",2,1))*1E+15+MIN(N(O43),500)*1E+12+MIN(ROUND(N(F43)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5209,7 +5956,7 @@
         <v/>
       </c>
       <c r="R44" s="37">
-        <f>IF(OR(G44="",Q44="Fechada",Q44="Perdida"),0,IF(Q44="Previsão vencida",3,IF(Q44="Parada",2,1))*1E+13+MIN(N(O44),500)*1E+10+MIN(ROUND(N(F44),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G44="",Q44="Fechada",Q44="Perdida"),0,IF(Q44="Previsão vencida",3,IF(Q44="Parada",2,1))*1E+15+MIN(N(O44),500)*1E+12+MIN(ROUND(N(F44)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5247,7 +5994,7 @@
         <v/>
       </c>
       <c r="R45" s="37">
-        <f>IF(OR(G45="",Q45="Fechada",Q45="Perdida"),0,IF(Q45="Previsão vencida",3,IF(Q45="Parada",2,1))*1E+13+MIN(N(O45),500)*1E+10+MIN(ROUND(N(F45),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G45="",Q45="Fechada",Q45="Perdida"),0,IF(Q45="Previsão vencida",3,IF(Q45="Parada",2,1))*1E+15+MIN(N(O45),500)*1E+12+MIN(ROUND(N(F45)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5285,7 +6032,7 @@
         <v/>
       </c>
       <c r="R46" s="37">
-        <f>IF(OR(G46="",Q46="Fechada",Q46="Perdida"),0,IF(Q46="Previsão vencida",3,IF(Q46="Parada",2,1))*1E+13+MIN(N(O46),500)*1E+10+MIN(ROUND(N(F46),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G46="",Q46="Fechada",Q46="Perdida"),0,IF(Q46="Previsão vencida",3,IF(Q46="Parada",2,1))*1E+15+MIN(N(O46),500)*1E+12+MIN(ROUND(N(F46)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5323,7 +6070,7 @@
         <v/>
       </c>
       <c r="R47" s="37">
-        <f>IF(OR(G47="",Q47="Fechada",Q47="Perdida"),0,IF(Q47="Previsão vencida",3,IF(Q47="Parada",2,1))*1E+13+MIN(N(O47),500)*1E+10+MIN(ROUND(N(F47),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G47="",Q47="Fechada",Q47="Perdida"),0,IF(Q47="Previsão vencida",3,IF(Q47="Parada",2,1))*1E+15+MIN(N(O47),500)*1E+12+MIN(ROUND(N(F47)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5361,7 +6108,7 @@
         <v/>
       </c>
       <c r="R48" s="37">
-        <f>IF(OR(G48="",Q48="Fechada",Q48="Perdida"),0,IF(Q48="Previsão vencida",3,IF(Q48="Parada",2,1))*1E+13+MIN(N(O48),500)*1E+10+MIN(ROUND(N(F48),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G48="",Q48="Fechada",Q48="Perdida"),0,IF(Q48="Previsão vencida",3,IF(Q48="Parada",2,1))*1E+15+MIN(N(O48),500)*1E+12+MIN(ROUND(N(F48)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5399,7 +6146,7 @@
         <v/>
       </c>
       <c r="R49" s="37">
-        <f>IF(OR(G49="",Q49="Fechada",Q49="Perdida"),0,IF(Q49="Previsão vencida",3,IF(Q49="Parada",2,1))*1E+13+MIN(N(O49),500)*1E+10+MIN(ROUND(N(F49),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G49="",Q49="Fechada",Q49="Perdida"),0,IF(Q49="Previsão vencida",3,IF(Q49="Parada",2,1))*1E+15+MIN(N(O49),500)*1E+12+MIN(ROUND(N(F49)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5437,7 +6184,7 @@
         <v/>
       </c>
       <c r="R50" s="37">
-        <f>IF(OR(G50="",Q50="Fechada",Q50="Perdida"),0,IF(Q50="Previsão vencida",3,IF(Q50="Parada",2,1))*1E+13+MIN(N(O50),500)*1E+10+MIN(ROUND(N(F50),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G50="",Q50="Fechada",Q50="Perdida"),0,IF(Q50="Previsão vencida",3,IF(Q50="Parada",2,1))*1E+15+MIN(N(O50),500)*1E+12+MIN(ROUND(N(F50)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5475,7 +6222,7 @@
         <v/>
       </c>
       <c r="R51" s="37">
-        <f>IF(OR(G51="",Q51="Fechada",Q51="Perdida"),0,IF(Q51="Previsão vencida",3,IF(Q51="Parada",2,1))*1E+13+MIN(N(O51),500)*1E+10+MIN(ROUND(N(F51),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G51="",Q51="Fechada",Q51="Perdida"),0,IF(Q51="Previsão vencida",3,IF(Q51="Parada",2,1))*1E+15+MIN(N(O51),500)*1E+12+MIN(ROUND(N(F51)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5513,7 +6260,7 @@
         <v/>
       </c>
       <c r="R52" s="37">
-        <f>IF(OR(G52="",Q52="Fechada",Q52="Perdida"),0,IF(Q52="Previsão vencida",3,IF(Q52="Parada",2,1))*1E+13+MIN(N(O52),500)*1E+10+MIN(ROUND(N(F52),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G52="",Q52="Fechada",Q52="Perdida"),0,IF(Q52="Previsão vencida",3,IF(Q52="Parada",2,1))*1E+15+MIN(N(O52),500)*1E+12+MIN(ROUND(N(F52)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5551,7 +6298,7 @@
         <v/>
       </c>
       <c r="R53" s="37">
-        <f>IF(OR(G53="",Q53="Fechada",Q53="Perdida"),0,IF(Q53="Previsão vencida",3,IF(Q53="Parada",2,1))*1E+13+MIN(N(O53),500)*1E+10+MIN(ROUND(N(F53),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G53="",Q53="Fechada",Q53="Perdida"),0,IF(Q53="Previsão vencida",3,IF(Q53="Parada",2,1))*1E+15+MIN(N(O53),500)*1E+12+MIN(ROUND(N(F53)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5589,7 +6336,7 @@
         <v/>
       </c>
       <c r="R54" s="37">
-        <f>IF(OR(G54="",Q54="Fechada",Q54="Perdida"),0,IF(Q54="Previsão vencida",3,IF(Q54="Parada",2,1))*1E+13+MIN(N(O54),500)*1E+10+MIN(ROUND(N(F54),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G54="",Q54="Fechada",Q54="Perdida"),0,IF(Q54="Previsão vencida",3,IF(Q54="Parada",2,1))*1E+15+MIN(N(O54),500)*1E+12+MIN(ROUND(N(F54)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5627,7 +6374,7 @@
         <v/>
       </c>
       <c r="R55" s="37">
-        <f>IF(OR(G55="",Q55="Fechada",Q55="Perdida"),0,IF(Q55="Previsão vencida",3,IF(Q55="Parada",2,1))*1E+13+MIN(N(O55),500)*1E+10+MIN(ROUND(N(F55),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G55="",Q55="Fechada",Q55="Perdida"),0,IF(Q55="Previsão vencida",3,IF(Q55="Parada",2,1))*1E+15+MIN(N(O55),500)*1E+12+MIN(ROUND(N(F55)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5665,7 +6412,7 @@
         <v/>
       </c>
       <c r="R56" s="37">
-        <f>IF(OR(G56="",Q56="Fechada",Q56="Perdida"),0,IF(Q56="Previsão vencida",3,IF(Q56="Parada",2,1))*1E+13+MIN(N(O56),500)*1E+10+MIN(ROUND(N(F56),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G56="",Q56="Fechada",Q56="Perdida"),0,IF(Q56="Previsão vencida",3,IF(Q56="Parada",2,1))*1E+15+MIN(N(O56),500)*1E+12+MIN(ROUND(N(F56)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5703,7 +6450,7 @@
         <v/>
       </c>
       <c r="R57" s="37">
-        <f>IF(OR(G57="",Q57="Fechada",Q57="Perdida"),0,IF(Q57="Previsão vencida",3,IF(Q57="Parada",2,1))*1E+13+MIN(N(O57),500)*1E+10+MIN(ROUND(N(F57),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G57="",Q57="Fechada",Q57="Perdida"),0,IF(Q57="Previsão vencida",3,IF(Q57="Parada",2,1))*1E+15+MIN(N(O57),500)*1E+12+MIN(ROUND(N(F57)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5741,7 +6488,7 @@
         <v/>
       </c>
       <c r="R58" s="37">
-        <f>IF(OR(G58="",Q58="Fechada",Q58="Perdida"),0,IF(Q58="Previsão vencida",3,IF(Q58="Parada",2,1))*1E+13+MIN(N(O58),500)*1E+10+MIN(ROUND(N(F58),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G58="",Q58="Fechada",Q58="Perdida"),0,IF(Q58="Previsão vencida",3,IF(Q58="Parada",2,1))*1E+15+MIN(N(O58),500)*1E+12+MIN(ROUND(N(F58)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5779,7 +6526,7 @@
         <v/>
       </c>
       <c r="R59" s="37">
-        <f>IF(OR(G59="",Q59="Fechada",Q59="Perdida"),0,IF(Q59="Previsão vencida",3,IF(Q59="Parada",2,1))*1E+13+MIN(N(O59),500)*1E+10+MIN(ROUND(N(F59),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G59="",Q59="Fechada",Q59="Perdida"),0,IF(Q59="Previsão vencida",3,IF(Q59="Parada",2,1))*1E+15+MIN(N(O59),500)*1E+12+MIN(ROUND(N(F59)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5817,7 +6564,7 @@
         <v/>
       </c>
       <c r="R60" s="37">
-        <f>IF(OR(G60="",Q60="Fechada",Q60="Perdida"),0,IF(Q60="Previsão vencida",3,IF(Q60="Parada",2,1))*1E+13+MIN(N(O60),500)*1E+10+MIN(ROUND(N(F60),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G60="",Q60="Fechada",Q60="Perdida"),0,IF(Q60="Previsão vencida",3,IF(Q60="Parada",2,1))*1E+15+MIN(N(O60),500)*1E+12+MIN(ROUND(N(F60)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5855,7 +6602,7 @@
         <v/>
       </c>
       <c r="R61" s="37">
-        <f>IF(OR(G61="",Q61="Fechada",Q61="Perdida"),0,IF(Q61="Previsão vencida",3,IF(Q61="Parada",2,1))*1E+13+MIN(N(O61),500)*1E+10+MIN(ROUND(N(F61),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G61="",Q61="Fechada",Q61="Perdida"),0,IF(Q61="Previsão vencida",3,IF(Q61="Parada",2,1))*1E+15+MIN(N(O61),500)*1E+12+MIN(ROUND(N(F61)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5893,7 +6640,7 @@
         <v/>
       </c>
       <c r="R62" s="37">
-        <f>IF(OR(G62="",Q62="Fechada",Q62="Perdida"),0,IF(Q62="Previsão vencida",3,IF(Q62="Parada",2,1))*1E+13+MIN(N(O62),500)*1E+10+MIN(ROUND(N(F62),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G62="",Q62="Fechada",Q62="Perdida"),0,IF(Q62="Previsão vencida",3,IF(Q62="Parada",2,1))*1E+15+MIN(N(O62),500)*1E+12+MIN(ROUND(N(F62)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5931,7 +6678,7 @@
         <v/>
       </c>
       <c r="R63" s="37">
-        <f>IF(OR(G63="",Q63="Fechada",Q63="Perdida"),0,IF(Q63="Previsão vencida",3,IF(Q63="Parada",2,1))*1E+13+MIN(N(O63),500)*1E+10+MIN(ROUND(N(F63),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G63="",Q63="Fechada",Q63="Perdida"),0,IF(Q63="Previsão vencida",3,IF(Q63="Parada",2,1))*1E+15+MIN(N(O63),500)*1E+12+MIN(ROUND(N(F63)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5969,7 +6716,7 @@
         <v/>
       </c>
       <c r="R64" s="37">
-        <f>IF(OR(G64="",Q64="Fechada",Q64="Perdida"),0,IF(Q64="Previsão vencida",3,IF(Q64="Parada",2,1))*1E+13+MIN(N(O64),500)*1E+10+MIN(ROUND(N(F64),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G64="",Q64="Fechada",Q64="Perdida"),0,IF(Q64="Previsão vencida",3,IF(Q64="Parada",2,1))*1E+15+MIN(N(O64),500)*1E+12+MIN(ROUND(N(F64)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6007,7 +6754,7 @@
         <v/>
       </c>
       <c r="R65" s="37">
-        <f>IF(OR(G65="",Q65="Fechada",Q65="Perdida"),0,IF(Q65="Previsão vencida",3,IF(Q65="Parada",2,1))*1E+13+MIN(N(O65),500)*1E+10+MIN(ROUND(N(F65),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G65="",Q65="Fechada",Q65="Perdida"),0,IF(Q65="Previsão vencida",3,IF(Q65="Parada",2,1))*1E+15+MIN(N(O65),500)*1E+12+MIN(ROUND(N(F65)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6045,7 +6792,7 @@
         <v/>
       </c>
       <c r="R66" s="37">
-        <f>IF(OR(G66="",Q66="Fechada",Q66="Perdida"),0,IF(Q66="Previsão vencida",3,IF(Q66="Parada",2,1))*1E+13+MIN(N(O66),500)*1E+10+MIN(ROUND(N(F66),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G66="",Q66="Fechada",Q66="Perdida"),0,IF(Q66="Previsão vencida",3,IF(Q66="Parada",2,1))*1E+15+MIN(N(O66),500)*1E+12+MIN(ROUND(N(F66)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6083,7 +6830,7 @@
         <v/>
       </c>
       <c r="R67" s="37">
-        <f>IF(OR(G67="",Q67="Fechada",Q67="Perdida"),0,IF(Q67="Previsão vencida",3,IF(Q67="Parada",2,1))*1E+13+MIN(N(O67),500)*1E+10+MIN(ROUND(N(F67),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G67="",Q67="Fechada",Q67="Perdida"),0,IF(Q67="Previsão vencida",3,IF(Q67="Parada",2,1))*1E+15+MIN(N(O67),500)*1E+12+MIN(ROUND(N(F67)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6121,7 +6868,7 @@
         <v/>
       </c>
       <c r="R68" s="37">
-        <f>IF(OR(G68="",Q68="Fechada",Q68="Perdida"),0,IF(Q68="Previsão vencida",3,IF(Q68="Parada",2,1))*1E+13+MIN(N(O68),500)*1E+10+MIN(ROUND(N(F68),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G68="",Q68="Fechada",Q68="Perdida"),0,IF(Q68="Previsão vencida",3,IF(Q68="Parada",2,1))*1E+15+MIN(N(O68),500)*1E+12+MIN(ROUND(N(F68)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6159,7 +6906,7 @@
         <v/>
       </c>
       <c r="R69" s="37">
-        <f>IF(OR(G69="",Q69="Fechada",Q69="Perdida"),0,IF(Q69="Previsão vencida",3,IF(Q69="Parada",2,1))*1E+13+MIN(N(O69),500)*1E+10+MIN(ROUND(N(F69),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G69="",Q69="Fechada",Q69="Perdida"),0,IF(Q69="Previsão vencida",3,IF(Q69="Parada",2,1))*1E+15+MIN(N(O69),500)*1E+12+MIN(ROUND(N(F69)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6197,7 +6944,7 @@
         <v/>
       </c>
       <c r="R70" s="37">
-        <f>IF(OR(G70="",Q70="Fechada",Q70="Perdida"),0,IF(Q70="Previsão vencida",3,IF(Q70="Parada",2,1))*1E+13+MIN(N(O70),500)*1E+10+MIN(ROUND(N(F70),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G70="",Q70="Fechada",Q70="Perdida"),0,IF(Q70="Previsão vencida",3,IF(Q70="Parada",2,1))*1E+15+MIN(N(O70),500)*1E+12+MIN(ROUND(N(F70)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6235,7 +6982,7 @@
         <v/>
       </c>
       <c r="R71" s="37">
-        <f>IF(OR(G71="",Q71="Fechada",Q71="Perdida"),0,IF(Q71="Previsão vencida",3,IF(Q71="Parada",2,1))*1E+13+MIN(N(O71),500)*1E+10+MIN(ROUND(N(F71),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G71="",Q71="Fechada",Q71="Perdida"),0,IF(Q71="Previsão vencida",3,IF(Q71="Parada",2,1))*1E+15+MIN(N(O71),500)*1E+12+MIN(ROUND(N(F71)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6273,7 +7020,7 @@
         <v/>
       </c>
       <c r="R72" s="37">
-        <f>IF(OR(G72="",Q72="Fechada",Q72="Perdida"),0,IF(Q72="Previsão vencida",3,IF(Q72="Parada",2,1))*1E+13+MIN(N(O72),500)*1E+10+MIN(ROUND(N(F72),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G72="",Q72="Fechada",Q72="Perdida"),0,IF(Q72="Previsão vencida",3,IF(Q72="Parada",2,1))*1E+15+MIN(N(O72),500)*1E+12+MIN(ROUND(N(F72)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6311,7 +7058,7 @@
         <v/>
       </c>
       <c r="R73" s="37">
-        <f>IF(OR(G73="",Q73="Fechada",Q73="Perdida"),0,IF(Q73="Previsão vencida",3,IF(Q73="Parada",2,1))*1E+13+MIN(N(O73),500)*1E+10+MIN(ROUND(N(F73),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G73="",Q73="Fechada",Q73="Perdida"),0,IF(Q73="Previsão vencida",3,IF(Q73="Parada",2,1))*1E+15+MIN(N(O73),500)*1E+12+MIN(ROUND(N(F73)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6349,7 +7096,7 @@
         <v/>
       </c>
       <c r="R74" s="37">
-        <f>IF(OR(G74="",Q74="Fechada",Q74="Perdida"),0,IF(Q74="Previsão vencida",3,IF(Q74="Parada",2,1))*1E+13+MIN(N(O74),500)*1E+10+MIN(ROUND(N(F74),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G74="",Q74="Fechada",Q74="Perdida"),0,IF(Q74="Previsão vencida",3,IF(Q74="Parada",2,1))*1E+15+MIN(N(O74),500)*1E+12+MIN(ROUND(N(F74)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6387,7 +7134,7 @@
         <v/>
       </c>
       <c r="R75" s="37">
-        <f>IF(OR(G75="",Q75="Fechada",Q75="Perdida"),0,IF(Q75="Previsão vencida",3,IF(Q75="Parada",2,1))*1E+13+MIN(N(O75),500)*1E+10+MIN(ROUND(N(F75),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G75="",Q75="Fechada",Q75="Perdida"),0,IF(Q75="Previsão vencida",3,IF(Q75="Parada",2,1))*1E+15+MIN(N(O75),500)*1E+12+MIN(ROUND(N(F75)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6425,7 +7172,7 @@
         <v/>
       </c>
       <c r="R76" s="37">
-        <f>IF(OR(G76="",Q76="Fechada",Q76="Perdida"),0,IF(Q76="Previsão vencida",3,IF(Q76="Parada",2,1))*1E+13+MIN(N(O76),500)*1E+10+MIN(ROUND(N(F76),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G76="",Q76="Fechada",Q76="Perdida"),0,IF(Q76="Previsão vencida",3,IF(Q76="Parada",2,1))*1E+15+MIN(N(O76),500)*1E+12+MIN(ROUND(N(F76)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6463,7 +7210,7 @@
         <v/>
       </c>
       <c r="R77" s="37">
-        <f>IF(OR(G77="",Q77="Fechada",Q77="Perdida"),0,IF(Q77="Previsão vencida",3,IF(Q77="Parada",2,1))*1E+13+MIN(N(O77),500)*1E+10+MIN(ROUND(N(F77),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G77="",Q77="Fechada",Q77="Perdida"),0,IF(Q77="Previsão vencida",3,IF(Q77="Parada",2,1))*1E+15+MIN(N(O77),500)*1E+12+MIN(ROUND(N(F77)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6501,7 +7248,7 @@
         <v/>
       </c>
       <c r="R78" s="37">
-        <f>IF(OR(G78="",Q78="Fechada",Q78="Perdida"),0,IF(Q78="Previsão vencida",3,IF(Q78="Parada",2,1))*1E+13+MIN(N(O78),500)*1E+10+MIN(ROUND(N(F78),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G78="",Q78="Fechada",Q78="Perdida"),0,IF(Q78="Previsão vencida",3,IF(Q78="Parada",2,1))*1E+15+MIN(N(O78),500)*1E+12+MIN(ROUND(N(F78)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6539,7 +7286,7 @@
         <v/>
       </c>
       <c r="R79" s="37">
-        <f>IF(OR(G79="",Q79="Fechada",Q79="Perdida"),0,IF(Q79="Previsão vencida",3,IF(Q79="Parada",2,1))*1E+13+MIN(N(O79),500)*1E+10+MIN(ROUND(N(F79),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G79="",Q79="Fechada",Q79="Perdida"),0,IF(Q79="Previsão vencida",3,IF(Q79="Parada",2,1))*1E+15+MIN(N(O79),500)*1E+12+MIN(ROUND(N(F79)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6577,7 +7324,7 @@
         <v/>
       </c>
       <c r="R80" s="37">
-        <f>IF(OR(G80="",Q80="Fechada",Q80="Perdida"),0,IF(Q80="Previsão vencida",3,IF(Q80="Parada",2,1))*1E+13+MIN(N(O80),500)*1E+10+MIN(ROUND(N(F80),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G80="",Q80="Fechada",Q80="Perdida"),0,IF(Q80="Previsão vencida",3,IF(Q80="Parada",2,1))*1E+15+MIN(N(O80),500)*1E+12+MIN(ROUND(N(F80)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6615,7 +7362,7 @@
         <v/>
       </c>
       <c r="R81" s="37">
-        <f>IF(OR(G81="",Q81="Fechada",Q81="Perdida"),0,IF(Q81="Previsão vencida",3,IF(Q81="Parada",2,1))*1E+13+MIN(N(O81),500)*1E+10+MIN(ROUND(N(F81),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G81="",Q81="Fechada",Q81="Perdida"),0,IF(Q81="Previsão vencida",3,IF(Q81="Parada",2,1))*1E+15+MIN(N(O81),500)*1E+12+MIN(ROUND(N(F81)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6653,7 +7400,7 @@
         <v/>
       </c>
       <c r="R82" s="37">
-        <f>IF(OR(G82="",Q82="Fechada",Q82="Perdida"),0,IF(Q82="Previsão vencida",3,IF(Q82="Parada",2,1))*1E+13+MIN(N(O82),500)*1E+10+MIN(ROUND(N(F82),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G82="",Q82="Fechada",Q82="Perdida"),0,IF(Q82="Previsão vencida",3,IF(Q82="Parada",2,1))*1E+15+MIN(N(O82),500)*1E+12+MIN(ROUND(N(F82)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6691,7 +7438,7 @@
         <v/>
       </c>
       <c r="R83" s="37">
-        <f>IF(OR(G83="",Q83="Fechada",Q83="Perdida"),0,IF(Q83="Previsão vencida",3,IF(Q83="Parada",2,1))*1E+13+MIN(N(O83),500)*1E+10+MIN(ROUND(N(F83),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G83="",Q83="Fechada",Q83="Perdida"),0,IF(Q83="Previsão vencida",3,IF(Q83="Parada",2,1))*1E+15+MIN(N(O83),500)*1E+12+MIN(ROUND(N(F83)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6729,7 +7476,7 @@
         <v/>
       </c>
       <c r="R84" s="37">
-        <f>IF(OR(G84="",Q84="Fechada",Q84="Perdida"),0,IF(Q84="Previsão vencida",3,IF(Q84="Parada",2,1))*1E+13+MIN(N(O84),500)*1E+10+MIN(ROUND(N(F84),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G84="",Q84="Fechada",Q84="Perdida"),0,IF(Q84="Previsão vencida",3,IF(Q84="Parada",2,1))*1E+15+MIN(N(O84),500)*1E+12+MIN(ROUND(N(F84)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6767,7 +7514,7 @@
         <v/>
       </c>
       <c r="R85" s="37">
-        <f>IF(OR(G85="",Q85="Fechada",Q85="Perdida"),0,IF(Q85="Previsão vencida",3,IF(Q85="Parada",2,1))*1E+13+MIN(N(O85),500)*1E+10+MIN(ROUND(N(F85),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G85="",Q85="Fechada",Q85="Perdida"),0,IF(Q85="Previsão vencida",3,IF(Q85="Parada",2,1))*1E+15+MIN(N(O85),500)*1E+12+MIN(ROUND(N(F85)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6805,7 +7552,7 @@
         <v/>
       </c>
       <c r="R86" s="37">
-        <f>IF(OR(G86="",Q86="Fechada",Q86="Perdida"),0,IF(Q86="Previsão vencida",3,IF(Q86="Parada",2,1))*1E+13+MIN(N(O86),500)*1E+10+MIN(ROUND(N(F86),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G86="",Q86="Fechada",Q86="Perdida"),0,IF(Q86="Previsão vencida",3,IF(Q86="Parada",2,1))*1E+15+MIN(N(O86),500)*1E+12+MIN(ROUND(N(F86)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6843,7 +7590,7 @@
         <v/>
       </c>
       <c r="R87" s="37">
-        <f>IF(OR(G87="",Q87="Fechada",Q87="Perdida"),0,IF(Q87="Previsão vencida",3,IF(Q87="Parada",2,1))*1E+13+MIN(N(O87),500)*1E+10+MIN(ROUND(N(F87),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G87="",Q87="Fechada",Q87="Perdida"),0,IF(Q87="Previsão vencida",3,IF(Q87="Parada",2,1))*1E+15+MIN(N(O87),500)*1E+12+MIN(ROUND(N(F87)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6881,7 +7628,7 @@
         <v/>
       </c>
       <c r="R88" s="37">
-        <f>IF(OR(G88="",Q88="Fechada",Q88="Perdida"),0,IF(Q88="Previsão vencida",3,IF(Q88="Parada",2,1))*1E+13+MIN(N(O88),500)*1E+10+MIN(ROUND(N(F88),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G88="",Q88="Fechada",Q88="Perdida"),0,IF(Q88="Previsão vencida",3,IF(Q88="Parada",2,1))*1E+15+MIN(N(O88),500)*1E+12+MIN(ROUND(N(F88)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6919,7 +7666,7 @@
         <v/>
       </c>
       <c r="R89" s="37">
-        <f>IF(OR(G89="",Q89="Fechada",Q89="Perdida"),0,IF(Q89="Previsão vencida",3,IF(Q89="Parada",2,1))*1E+13+MIN(N(O89),500)*1E+10+MIN(ROUND(N(F89),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G89="",Q89="Fechada",Q89="Perdida"),0,IF(Q89="Previsão vencida",3,IF(Q89="Parada",2,1))*1E+15+MIN(N(O89),500)*1E+12+MIN(ROUND(N(F89)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6957,7 +7704,7 @@
         <v/>
       </c>
       <c r="R90" s="37">
-        <f>IF(OR(G90="",Q90="Fechada",Q90="Perdida"),0,IF(Q90="Previsão vencida",3,IF(Q90="Parada",2,1))*1E+13+MIN(N(O90),500)*1E+10+MIN(ROUND(N(F90),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G90="",Q90="Fechada",Q90="Perdida"),0,IF(Q90="Previsão vencida",3,IF(Q90="Parada",2,1))*1E+15+MIN(N(O90),500)*1E+12+MIN(ROUND(N(F90)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6995,7 +7742,7 @@
         <v/>
       </c>
       <c r="R91" s="37">
-        <f>IF(OR(G91="",Q91="Fechada",Q91="Perdida"),0,IF(Q91="Previsão vencida",3,IF(Q91="Parada",2,1))*1E+13+MIN(N(O91),500)*1E+10+MIN(ROUND(N(F91),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G91="",Q91="Fechada",Q91="Perdida"),0,IF(Q91="Previsão vencida",3,IF(Q91="Parada",2,1))*1E+15+MIN(N(O91),500)*1E+12+MIN(ROUND(N(F91)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7033,7 +7780,7 @@
         <v/>
       </c>
       <c r="R92" s="37">
-        <f>IF(OR(G92="",Q92="Fechada",Q92="Perdida"),0,IF(Q92="Previsão vencida",3,IF(Q92="Parada",2,1))*1E+13+MIN(N(O92),500)*1E+10+MIN(ROUND(N(F92),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G92="",Q92="Fechada",Q92="Perdida"),0,IF(Q92="Previsão vencida",3,IF(Q92="Parada",2,1))*1E+15+MIN(N(O92),500)*1E+12+MIN(ROUND(N(F92)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7071,7 +7818,7 @@
         <v/>
       </c>
       <c r="R93" s="37">
-        <f>IF(OR(G93="",Q93="Fechada",Q93="Perdida"),0,IF(Q93="Previsão vencida",3,IF(Q93="Parada",2,1))*1E+13+MIN(N(O93),500)*1E+10+MIN(ROUND(N(F93),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G93="",Q93="Fechada",Q93="Perdida"),0,IF(Q93="Previsão vencida",3,IF(Q93="Parada",2,1))*1E+15+MIN(N(O93),500)*1E+12+MIN(ROUND(N(F93)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7109,7 +7856,7 @@
         <v/>
       </c>
       <c r="R94" s="37">
-        <f>IF(OR(G94="",Q94="Fechada",Q94="Perdida"),0,IF(Q94="Previsão vencida",3,IF(Q94="Parada",2,1))*1E+13+MIN(N(O94),500)*1E+10+MIN(ROUND(N(F94),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G94="",Q94="Fechada",Q94="Perdida"),0,IF(Q94="Previsão vencida",3,IF(Q94="Parada",2,1))*1E+15+MIN(N(O94),500)*1E+12+MIN(ROUND(N(F94)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7147,7 +7894,7 @@
         <v/>
       </c>
       <c r="R95" s="37">
-        <f>IF(OR(G95="",Q95="Fechada",Q95="Perdida"),0,IF(Q95="Previsão vencida",3,IF(Q95="Parada",2,1))*1E+13+MIN(N(O95),500)*1E+10+MIN(ROUND(N(F95),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G95="",Q95="Fechada",Q95="Perdida"),0,IF(Q95="Previsão vencida",3,IF(Q95="Parada",2,1))*1E+15+MIN(N(O95),500)*1E+12+MIN(ROUND(N(F95)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7185,7 +7932,7 @@
         <v/>
       </c>
       <c r="R96" s="37">
-        <f>IF(OR(G96="",Q96="Fechada",Q96="Perdida"),0,IF(Q96="Previsão vencida",3,IF(Q96="Parada",2,1))*1E+13+MIN(N(O96),500)*1E+10+MIN(ROUND(N(F96),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G96="",Q96="Fechada",Q96="Perdida"),0,IF(Q96="Previsão vencida",3,IF(Q96="Parada",2,1))*1E+15+MIN(N(O96),500)*1E+12+MIN(ROUND(N(F96)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7223,7 +7970,7 @@
         <v/>
       </c>
       <c r="R97" s="37">
-        <f>IF(OR(G97="",Q97="Fechada",Q97="Perdida"),0,IF(Q97="Previsão vencida",3,IF(Q97="Parada",2,1))*1E+13+MIN(N(O97),500)*1E+10+MIN(ROUND(N(F97),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G97="",Q97="Fechada",Q97="Perdida"),0,IF(Q97="Previsão vencida",3,IF(Q97="Parada",2,1))*1E+15+MIN(N(O97),500)*1E+12+MIN(ROUND(N(F97)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7261,7 +8008,7 @@
         <v/>
       </c>
       <c r="R98" s="37">
-        <f>IF(OR(G98="",Q98="Fechada",Q98="Perdida"),0,IF(Q98="Previsão vencida",3,IF(Q98="Parada",2,1))*1E+13+MIN(N(O98),500)*1E+10+MIN(ROUND(N(F98),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G98="",Q98="Fechada",Q98="Perdida"),0,IF(Q98="Previsão vencida",3,IF(Q98="Parada",2,1))*1E+15+MIN(N(O98),500)*1E+12+MIN(ROUND(N(F98)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7299,7 +8046,7 @@
         <v/>
       </c>
       <c r="R99" s="37">
-        <f>IF(OR(G99="",Q99="Fechada",Q99="Perdida"),0,IF(Q99="Previsão vencida",3,IF(Q99="Parada",2,1))*1E+13+MIN(N(O99),500)*1E+10+MIN(ROUND(N(F99),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G99="",Q99="Fechada",Q99="Perdida"),0,IF(Q99="Previsão vencida",3,IF(Q99="Parada",2,1))*1E+15+MIN(N(O99),500)*1E+12+MIN(ROUND(N(F99)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7337,7 +8084,7 @@
         <v/>
       </c>
       <c r="R100" s="37">
-        <f>IF(OR(G100="",Q100="Fechada",Q100="Perdida"),0,IF(Q100="Previsão vencida",3,IF(Q100="Parada",2,1))*1E+13+MIN(N(O100),500)*1E+10+MIN(ROUND(N(F100),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G100="",Q100="Fechada",Q100="Perdida"),0,IF(Q100="Previsão vencida",3,IF(Q100="Parada",2,1))*1E+15+MIN(N(O100),500)*1E+12+MIN(ROUND(N(F100)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7375,7 +8122,7 @@
         <v/>
       </c>
       <c r="R101" s="37">
-        <f>IF(OR(G101="",Q101="Fechada",Q101="Perdida"),0,IF(Q101="Previsão vencida",3,IF(Q101="Parada",2,1))*1E+13+MIN(N(O101),500)*1E+10+MIN(ROUND(N(F101),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G101="",Q101="Fechada",Q101="Perdida"),0,IF(Q101="Previsão vencida",3,IF(Q101="Parada",2,1))*1E+15+MIN(N(O101),500)*1E+12+MIN(ROUND(N(F101)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7413,7 +8160,7 @@
         <v/>
       </c>
       <c r="R102" s="37">
-        <f>IF(OR(G102="",Q102="Fechada",Q102="Perdida"),0,IF(Q102="Previsão vencida",3,IF(Q102="Parada",2,1))*1E+13+MIN(N(O102),500)*1E+10+MIN(ROUND(N(F102),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G102="",Q102="Fechada",Q102="Perdida"),0,IF(Q102="Previsão vencida",3,IF(Q102="Parada",2,1))*1E+15+MIN(N(O102),500)*1E+12+MIN(ROUND(N(F102)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7451,7 +8198,7 @@
         <v/>
       </c>
       <c r="R103" s="37">
-        <f>IF(OR(G103="",Q103="Fechada",Q103="Perdida"),0,IF(Q103="Previsão vencida",3,IF(Q103="Parada",2,1))*1E+13+MIN(N(O103),500)*1E+10+MIN(ROUND(N(F103),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G103="",Q103="Fechada",Q103="Perdida"),0,IF(Q103="Previsão vencida",3,IF(Q103="Parada",2,1))*1E+15+MIN(N(O103),500)*1E+12+MIN(ROUND(N(F103)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7489,7 +8236,7 @@
         <v/>
       </c>
       <c r="R104" s="37">
-        <f>IF(OR(G104="",Q104="Fechada",Q104="Perdida"),0,IF(Q104="Previsão vencida",3,IF(Q104="Parada",2,1))*1E+13+MIN(N(O104),500)*1E+10+MIN(ROUND(N(F104),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G104="",Q104="Fechada",Q104="Perdida"),0,IF(Q104="Previsão vencida",3,IF(Q104="Parada",2,1))*1E+15+MIN(N(O104),500)*1E+12+MIN(ROUND(N(F104)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7527,7 +8274,7 @@
         <v/>
       </c>
       <c r="R105" s="37">
-        <f>IF(OR(G105="",Q105="Fechada",Q105="Perdida"),0,IF(Q105="Previsão vencida",3,IF(Q105="Parada",2,1))*1E+13+MIN(N(O105),500)*1E+10+MIN(ROUND(N(F105),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G105="",Q105="Fechada",Q105="Perdida"),0,IF(Q105="Previsão vencida",3,IF(Q105="Parada",2,1))*1E+15+MIN(N(O105),500)*1E+12+MIN(ROUND(N(F105)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7565,7 +8312,7 @@
         <v/>
       </c>
       <c r="R106" s="37">
-        <f>IF(OR(G106="",Q106="Fechada",Q106="Perdida"),0,IF(Q106="Previsão vencida",3,IF(Q106="Parada",2,1))*1E+13+MIN(N(O106),500)*1E+10+MIN(ROUND(N(F106),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G106="",Q106="Fechada",Q106="Perdida"),0,IF(Q106="Previsão vencida",3,IF(Q106="Parada",2,1))*1E+15+MIN(N(O106),500)*1E+12+MIN(ROUND(N(F106)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7603,7 +8350,7 @@
         <v/>
       </c>
       <c r="R107" s="37">
-        <f>IF(OR(G107="",Q107="Fechada",Q107="Perdida"),0,IF(Q107="Previsão vencida",3,IF(Q107="Parada",2,1))*1E+13+MIN(N(O107),500)*1E+10+MIN(ROUND(N(F107),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G107="",Q107="Fechada",Q107="Perdida"),0,IF(Q107="Previsão vencida",3,IF(Q107="Parada",2,1))*1E+15+MIN(N(O107),500)*1E+12+MIN(ROUND(N(F107)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7641,7 +8388,7 @@
         <v/>
       </c>
       <c r="R108" s="37">
-        <f>IF(OR(G108="",Q108="Fechada",Q108="Perdida"),0,IF(Q108="Previsão vencida",3,IF(Q108="Parada",2,1))*1E+13+MIN(N(O108),500)*1E+10+MIN(ROUND(N(F108),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G108="",Q108="Fechada",Q108="Perdida"),0,IF(Q108="Previsão vencida",3,IF(Q108="Parada",2,1))*1E+15+MIN(N(O108),500)*1E+12+MIN(ROUND(N(F108)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7679,7 +8426,7 @@
         <v/>
       </c>
       <c r="R109" s="37">
-        <f>IF(OR(G109="",Q109="Fechada",Q109="Perdida"),0,IF(Q109="Previsão vencida",3,IF(Q109="Parada",2,1))*1E+13+MIN(N(O109),500)*1E+10+MIN(ROUND(N(F109),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G109="",Q109="Fechada",Q109="Perdida"),0,IF(Q109="Previsão vencida",3,IF(Q109="Parada",2,1))*1E+15+MIN(N(O109),500)*1E+12+MIN(ROUND(N(F109)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7717,7 +8464,7 @@
         <v/>
       </c>
       <c r="R110" s="37">
-        <f>IF(OR(G110="",Q110="Fechada",Q110="Perdida"),0,IF(Q110="Previsão vencida",3,IF(Q110="Parada",2,1))*1E+13+MIN(N(O110),500)*1E+10+MIN(ROUND(N(F110),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G110="",Q110="Fechada",Q110="Perdida"),0,IF(Q110="Previsão vencida",3,IF(Q110="Parada",2,1))*1E+15+MIN(N(O110),500)*1E+12+MIN(ROUND(N(F110)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7755,7 +8502,7 @@
         <v/>
       </c>
       <c r="R111" s="37">
-        <f>IF(OR(G111="",Q111="Fechada",Q111="Perdida"),0,IF(Q111="Previsão vencida",3,IF(Q111="Parada",2,1))*1E+13+MIN(N(O111),500)*1E+10+MIN(ROUND(N(F111),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G111="",Q111="Fechada",Q111="Perdida"),0,IF(Q111="Previsão vencida",3,IF(Q111="Parada",2,1))*1E+15+MIN(N(O111),500)*1E+12+MIN(ROUND(N(F111)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7793,7 +8540,7 @@
         <v/>
       </c>
       <c r="R112" s="37">
-        <f>IF(OR(G112="",Q112="Fechada",Q112="Perdida"),0,IF(Q112="Previsão vencida",3,IF(Q112="Parada",2,1))*1E+13+MIN(N(O112),500)*1E+10+MIN(ROUND(N(F112),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G112="",Q112="Fechada",Q112="Perdida"),0,IF(Q112="Previsão vencida",3,IF(Q112="Parada",2,1))*1E+15+MIN(N(O112),500)*1E+12+MIN(ROUND(N(F112)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7831,7 +8578,7 @@
         <v/>
       </c>
       <c r="R113" s="37">
-        <f>IF(OR(G113="",Q113="Fechada",Q113="Perdida"),0,IF(Q113="Previsão vencida",3,IF(Q113="Parada",2,1))*1E+13+MIN(N(O113),500)*1E+10+MIN(ROUND(N(F113),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G113="",Q113="Fechada",Q113="Perdida"),0,IF(Q113="Previsão vencida",3,IF(Q113="Parada",2,1))*1E+15+MIN(N(O113),500)*1E+12+MIN(ROUND(N(F113)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7869,7 +8616,7 @@
         <v/>
       </c>
       <c r="R114" s="37">
-        <f>IF(OR(G114="",Q114="Fechada",Q114="Perdida"),0,IF(Q114="Previsão vencida",3,IF(Q114="Parada",2,1))*1E+13+MIN(N(O114),500)*1E+10+MIN(ROUND(N(F114),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G114="",Q114="Fechada",Q114="Perdida"),0,IF(Q114="Previsão vencida",3,IF(Q114="Parada",2,1))*1E+15+MIN(N(O114),500)*1E+12+MIN(ROUND(N(F114)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7907,7 +8654,7 @@
         <v/>
       </c>
       <c r="R115" s="37">
-        <f>IF(OR(G115="",Q115="Fechada",Q115="Perdida"),0,IF(Q115="Previsão vencida",3,IF(Q115="Parada",2,1))*1E+13+MIN(N(O115),500)*1E+10+MIN(ROUND(N(F115),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G115="",Q115="Fechada",Q115="Perdida"),0,IF(Q115="Previsão vencida",3,IF(Q115="Parada",2,1))*1E+15+MIN(N(O115),500)*1E+12+MIN(ROUND(N(F115)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7945,7 +8692,7 @@
         <v/>
       </c>
       <c r="R116" s="37">
-        <f>IF(OR(G116="",Q116="Fechada",Q116="Perdida"),0,IF(Q116="Previsão vencida",3,IF(Q116="Parada",2,1))*1E+13+MIN(N(O116),500)*1E+10+MIN(ROUND(N(F116),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G116="",Q116="Fechada",Q116="Perdida"),0,IF(Q116="Previsão vencida",3,IF(Q116="Parada",2,1))*1E+15+MIN(N(O116),500)*1E+12+MIN(ROUND(N(F116)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7983,7 +8730,7 @@
         <v/>
       </c>
       <c r="R117" s="37">
-        <f>IF(OR(G117="",Q117="Fechada",Q117="Perdida"),0,IF(Q117="Previsão vencida",3,IF(Q117="Parada",2,1))*1E+13+MIN(N(O117),500)*1E+10+MIN(ROUND(N(F117),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G117="",Q117="Fechada",Q117="Perdida"),0,IF(Q117="Previsão vencida",3,IF(Q117="Parada",2,1))*1E+15+MIN(N(O117),500)*1E+12+MIN(ROUND(N(F117)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8021,7 +8768,7 @@
         <v/>
       </c>
       <c r="R118" s="37">
-        <f>IF(OR(G118="",Q118="Fechada",Q118="Perdida"),0,IF(Q118="Previsão vencida",3,IF(Q118="Parada",2,1))*1E+13+MIN(N(O118),500)*1E+10+MIN(ROUND(N(F118),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G118="",Q118="Fechada",Q118="Perdida"),0,IF(Q118="Previsão vencida",3,IF(Q118="Parada",2,1))*1E+15+MIN(N(O118),500)*1E+12+MIN(ROUND(N(F118)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8059,7 +8806,7 @@
         <v/>
       </c>
       <c r="R119" s="37">
-        <f>IF(OR(G119="",Q119="Fechada",Q119="Perdida"),0,IF(Q119="Previsão vencida",3,IF(Q119="Parada",2,1))*1E+13+MIN(N(O119),500)*1E+10+MIN(ROUND(N(F119),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G119="",Q119="Fechada",Q119="Perdida"),0,IF(Q119="Previsão vencida",3,IF(Q119="Parada",2,1))*1E+15+MIN(N(O119),500)*1E+12+MIN(ROUND(N(F119)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8097,7 +8844,7 @@
         <v/>
       </c>
       <c r="R120" s="37">
-        <f>IF(OR(G120="",Q120="Fechada",Q120="Perdida"),0,IF(Q120="Previsão vencida",3,IF(Q120="Parada",2,1))*1E+13+MIN(N(O120),500)*1E+10+MIN(ROUND(N(F120),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G120="",Q120="Fechada",Q120="Perdida"),0,IF(Q120="Previsão vencida",3,IF(Q120="Parada",2,1))*1E+15+MIN(N(O120),500)*1E+12+MIN(ROUND(N(F120)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8135,7 +8882,7 @@
         <v/>
       </c>
       <c r="R121" s="37">
-        <f>IF(OR(G121="",Q121="Fechada",Q121="Perdida"),0,IF(Q121="Previsão vencida",3,IF(Q121="Parada",2,1))*1E+13+MIN(N(O121),500)*1E+10+MIN(ROUND(N(F121),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G121="",Q121="Fechada",Q121="Perdida"),0,IF(Q121="Previsão vencida",3,IF(Q121="Parada",2,1))*1E+15+MIN(N(O121),500)*1E+12+MIN(ROUND(N(F121)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8173,7 +8920,7 @@
         <v/>
       </c>
       <c r="R122" s="37">
-        <f>IF(OR(G122="",Q122="Fechada",Q122="Perdida"),0,IF(Q122="Previsão vencida",3,IF(Q122="Parada",2,1))*1E+13+MIN(N(O122),500)*1E+10+MIN(ROUND(N(F122),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G122="",Q122="Fechada",Q122="Perdida"),0,IF(Q122="Previsão vencida",3,IF(Q122="Parada",2,1))*1E+15+MIN(N(O122),500)*1E+12+MIN(ROUND(N(F122)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8211,7 +8958,7 @@
         <v/>
       </c>
       <c r="R123" s="37">
-        <f>IF(OR(G123="",Q123="Fechada",Q123="Perdida"),0,IF(Q123="Previsão vencida",3,IF(Q123="Parada",2,1))*1E+13+MIN(N(O123),500)*1E+10+MIN(ROUND(N(F123),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G123="",Q123="Fechada",Q123="Perdida"),0,IF(Q123="Previsão vencida",3,IF(Q123="Parada",2,1))*1E+15+MIN(N(O123),500)*1E+12+MIN(ROUND(N(F123)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8249,7 +8996,7 @@
         <v/>
       </c>
       <c r="R124" s="37">
-        <f>IF(OR(G124="",Q124="Fechada",Q124="Perdida"),0,IF(Q124="Previsão vencida",3,IF(Q124="Parada",2,1))*1E+13+MIN(N(O124),500)*1E+10+MIN(ROUND(N(F124),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G124="",Q124="Fechada",Q124="Perdida"),0,IF(Q124="Previsão vencida",3,IF(Q124="Parada",2,1))*1E+15+MIN(N(O124),500)*1E+12+MIN(ROUND(N(F124)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8287,7 +9034,7 @@
         <v/>
       </c>
       <c r="R125" s="37">
-        <f>IF(OR(G125="",Q125="Fechada",Q125="Perdida"),0,IF(Q125="Previsão vencida",3,IF(Q125="Parada",2,1))*1E+13+MIN(N(O125),500)*1E+10+MIN(ROUND(N(F125),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G125="",Q125="Fechada",Q125="Perdida"),0,IF(Q125="Previsão vencida",3,IF(Q125="Parada",2,1))*1E+15+MIN(N(O125),500)*1E+12+MIN(ROUND(N(F125)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8325,7 +9072,7 @@
         <v/>
       </c>
       <c r="R126" s="37">
-        <f>IF(OR(G126="",Q126="Fechada",Q126="Perdida"),0,IF(Q126="Previsão vencida",3,IF(Q126="Parada",2,1))*1E+13+MIN(N(O126),500)*1E+10+MIN(ROUND(N(F126),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G126="",Q126="Fechada",Q126="Perdida"),0,IF(Q126="Previsão vencida",3,IF(Q126="Parada",2,1))*1E+15+MIN(N(O126),500)*1E+12+MIN(ROUND(N(F126)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8363,7 +9110,7 @@
         <v/>
       </c>
       <c r="R127" s="37">
-        <f>IF(OR(G127="",Q127="Fechada",Q127="Perdida"),0,IF(Q127="Previsão vencida",3,IF(Q127="Parada",2,1))*1E+13+MIN(N(O127),500)*1E+10+MIN(ROUND(N(F127),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G127="",Q127="Fechada",Q127="Perdida"),0,IF(Q127="Previsão vencida",3,IF(Q127="Parada",2,1))*1E+15+MIN(N(O127),500)*1E+12+MIN(ROUND(N(F127)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8401,7 +9148,7 @@
         <v/>
       </c>
       <c r="R128" s="37">
-        <f>IF(OR(G128="",Q128="Fechada",Q128="Perdida"),0,IF(Q128="Previsão vencida",3,IF(Q128="Parada",2,1))*1E+13+MIN(N(O128),500)*1E+10+MIN(ROUND(N(F128),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G128="",Q128="Fechada",Q128="Perdida"),0,IF(Q128="Previsão vencida",3,IF(Q128="Parada",2,1))*1E+15+MIN(N(O128),500)*1E+12+MIN(ROUND(N(F128)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8439,7 +9186,7 @@
         <v/>
       </c>
       <c r="R129" s="37">
-        <f>IF(OR(G129="",Q129="Fechada",Q129="Perdida"),0,IF(Q129="Previsão vencida",3,IF(Q129="Parada",2,1))*1E+13+MIN(N(O129),500)*1E+10+MIN(ROUND(N(F129),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G129="",Q129="Fechada",Q129="Perdida"),0,IF(Q129="Previsão vencida",3,IF(Q129="Parada",2,1))*1E+15+MIN(N(O129),500)*1E+12+MIN(ROUND(N(F129)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8477,7 +9224,7 @@
         <v/>
       </c>
       <c r="R130" s="37">
-        <f>IF(OR(G130="",Q130="Fechada",Q130="Perdida"),0,IF(Q130="Previsão vencida",3,IF(Q130="Parada",2,1))*1E+13+MIN(N(O130),500)*1E+10+MIN(ROUND(N(F130),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G130="",Q130="Fechada",Q130="Perdida"),0,IF(Q130="Previsão vencida",3,IF(Q130="Parada",2,1))*1E+15+MIN(N(O130),500)*1E+12+MIN(ROUND(N(F130)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8515,7 +9262,7 @@
         <v/>
       </c>
       <c r="R131" s="37">
-        <f>IF(OR(G131="",Q131="Fechada",Q131="Perdida"),0,IF(Q131="Previsão vencida",3,IF(Q131="Parada",2,1))*1E+13+MIN(N(O131),500)*1E+10+MIN(ROUND(N(F131),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G131="",Q131="Fechada",Q131="Perdida"),0,IF(Q131="Previsão vencida",3,IF(Q131="Parada",2,1))*1E+15+MIN(N(O131),500)*1E+12+MIN(ROUND(N(F131)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8553,7 +9300,7 @@
         <v/>
       </c>
       <c r="R132" s="37">
-        <f>IF(OR(G132="",Q132="Fechada",Q132="Perdida"),0,IF(Q132="Previsão vencida",3,IF(Q132="Parada",2,1))*1E+13+MIN(N(O132),500)*1E+10+MIN(ROUND(N(F132),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G132="",Q132="Fechada",Q132="Perdida"),0,IF(Q132="Previsão vencida",3,IF(Q132="Parada",2,1))*1E+15+MIN(N(O132),500)*1E+12+MIN(ROUND(N(F132)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8591,7 +9338,7 @@
         <v/>
       </c>
       <c r="R133" s="37">
-        <f>IF(OR(G133="",Q133="Fechada",Q133="Perdida"),0,IF(Q133="Previsão vencida",3,IF(Q133="Parada",2,1))*1E+13+MIN(N(O133),500)*1E+10+MIN(ROUND(N(F133),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G133="",Q133="Fechada",Q133="Perdida"),0,IF(Q133="Previsão vencida",3,IF(Q133="Parada",2,1))*1E+15+MIN(N(O133),500)*1E+12+MIN(ROUND(N(F133)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8629,7 +9376,7 @@
         <v/>
       </c>
       <c r="R134" s="37">
-        <f>IF(OR(G134="",Q134="Fechada",Q134="Perdida"),0,IF(Q134="Previsão vencida",3,IF(Q134="Parada",2,1))*1E+13+MIN(N(O134),500)*1E+10+MIN(ROUND(N(F134),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G134="",Q134="Fechada",Q134="Perdida"),0,IF(Q134="Previsão vencida",3,IF(Q134="Parada",2,1))*1E+15+MIN(N(O134),500)*1E+12+MIN(ROUND(N(F134)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8667,7 +9414,7 @@
         <v/>
       </c>
       <c r="R135" s="37">
-        <f>IF(OR(G135="",Q135="Fechada",Q135="Perdida"),0,IF(Q135="Previsão vencida",3,IF(Q135="Parada",2,1))*1E+13+MIN(N(O135),500)*1E+10+MIN(ROUND(N(F135),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G135="",Q135="Fechada",Q135="Perdida"),0,IF(Q135="Previsão vencida",3,IF(Q135="Parada",2,1))*1E+15+MIN(N(O135),500)*1E+12+MIN(ROUND(N(F135)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8705,7 +9452,7 @@
         <v/>
       </c>
       <c r="R136" s="37">
-        <f>IF(OR(G136="",Q136="Fechada",Q136="Perdida"),0,IF(Q136="Previsão vencida",3,IF(Q136="Parada",2,1))*1E+13+MIN(N(O136),500)*1E+10+MIN(ROUND(N(F136),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G136="",Q136="Fechada",Q136="Perdida"),0,IF(Q136="Previsão vencida",3,IF(Q136="Parada",2,1))*1E+15+MIN(N(O136),500)*1E+12+MIN(ROUND(N(F136)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8743,7 +9490,7 @@
         <v/>
       </c>
       <c r="R137" s="37">
-        <f>IF(OR(G137="",Q137="Fechada",Q137="Perdida"),0,IF(Q137="Previsão vencida",3,IF(Q137="Parada",2,1))*1E+13+MIN(N(O137),500)*1E+10+MIN(ROUND(N(F137),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G137="",Q137="Fechada",Q137="Perdida"),0,IF(Q137="Previsão vencida",3,IF(Q137="Parada",2,1))*1E+15+MIN(N(O137),500)*1E+12+MIN(ROUND(N(F137)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8781,7 +9528,7 @@
         <v/>
       </c>
       <c r="R138" s="37">
-        <f>IF(OR(G138="",Q138="Fechada",Q138="Perdida"),0,IF(Q138="Previsão vencida",3,IF(Q138="Parada",2,1))*1E+13+MIN(N(O138),500)*1E+10+MIN(ROUND(N(F138),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G138="",Q138="Fechada",Q138="Perdida"),0,IF(Q138="Previsão vencida",3,IF(Q138="Parada",2,1))*1E+15+MIN(N(O138),500)*1E+12+MIN(ROUND(N(F138)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8819,7 +9566,7 @@
         <v/>
       </c>
       <c r="R139" s="37">
-        <f>IF(OR(G139="",Q139="Fechada",Q139="Perdida"),0,IF(Q139="Previsão vencida",3,IF(Q139="Parada",2,1))*1E+13+MIN(N(O139),500)*1E+10+MIN(ROUND(N(F139),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G139="",Q139="Fechada",Q139="Perdida"),0,IF(Q139="Previsão vencida",3,IF(Q139="Parada",2,1))*1E+15+MIN(N(O139),500)*1E+12+MIN(ROUND(N(F139)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8857,7 +9604,7 @@
         <v/>
       </c>
       <c r="R140" s="37">
-        <f>IF(OR(G140="",Q140="Fechada",Q140="Perdida"),0,IF(Q140="Previsão vencida",3,IF(Q140="Parada",2,1))*1E+13+MIN(N(O140),500)*1E+10+MIN(ROUND(N(F140),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G140="",Q140="Fechada",Q140="Perdida"),0,IF(Q140="Previsão vencida",3,IF(Q140="Parada",2,1))*1E+15+MIN(N(O140),500)*1E+12+MIN(ROUND(N(F140)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8895,7 +9642,7 @@
         <v/>
       </c>
       <c r="R141" s="37">
-        <f>IF(OR(G141="",Q141="Fechada",Q141="Perdida"),0,IF(Q141="Previsão vencida",3,IF(Q141="Parada",2,1))*1E+13+MIN(N(O141),500)*1E+10+MIN(ROUND(N(F141),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G141="",Q141="Fechada",Q141="Perdida"),0,IF(Q141="Previsão vencida",3,IF(Q141="Parada",2,1))*1E+15+MIN(N(O141),500)*1E+12+MIN(ROUND(N(F141)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8933,7 +9680,7 @@
         <v/>
       </c>
       <c r="R142" s="37">
-        <f>IF(OR(G142="",Q142="Fechada",Q142="Perdida"),0,IF(Q142="Previsão vencida",3,IF(Q142="Parada",2,1))*1E+13+MIN(N(O142),500)*1E+10+MIN(ROUND(N(F142),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G142="",Q142="Fechada",Q142="Perdida"),0,IF(Q142="Previsão vencida",3,IF(Q142="Parada",2,1))*1E+15+MIN(N(O142),500)*1E+12+MIN(ROUND(N(F142)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8971,7 +9718,7 @@
         <v/>
       </c>
       <c r="R143" s="37">
-        <f>IF(OR(G143="",Q143="Fechada",Q143="Perdida"),0,IF(Q143="Previsão vencida",3,IF(Q143="Parada",2,1))*1E+13+MIN(N(O143),500)*1E+10+MIN(ROUND(N(F143),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G143="",Q143="Fechada",Q143="Perdida"),0,IF(Q143="Previsão vencida",3,IF(Q143="Parada",2,1))*1E+15+MIN(N(O143),500)*1E+12+MIN(ROUND(N(F143)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9009,7 +9756,7 @@
         <v/>
       </c>
       <c r="R144" s="37">
-        <f>IF(OR(G144="",Q144="Fechada",Q144="Perdida"),0,IF(Q144="Previsão vencida",3,IF(Q144="Parada",2,1))*1E+13+MIN(N(O144),500)*1E+10+MIN(ROUND(N(F144),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G144="",Q144="Fechada",Q144="Perdida"),0,IF(Q144="Previsão vencida",3,IF(Q144="Parada",2,1))*1E+15+MIN(N(O144),500)*1E+12+MIN(ROUND(N(F144)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9047,7 +9794,7 @@
         <v/>
       </c>
       <c r="R145" s="37">
-        <f>IF(OR(G145="",Q145="Fechada",Q145="Perdida"),0,IF(Q145="Previsão vencida",3,IF(Q145="Parada",2,1))*1E+13+MIN(N(O145),500)*1E+10+MIN(ROUND(N(F145),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G145="",Q145="Fechada",Q145="Perdida"),0,IF(Q145="Previsão vencida",3,IF(Q145="Parada",2,1))*1E+15+MIN(N(O145),500)*1E+12+MIN(ROUND(N(F145)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9085,7 +9832,7 @@
         <v/>
       </c>
       <c r="R146" s="37">
-        <f>IF(OR(G146="",Q146="Fechada",Q146="Perdida"),0,IF(Q146="Previsão vencida",3,IF(Q146="Parada",2,1))*1E+13+MIN(N(O146),500)*1E+10+MIN(ROUND(N(F146),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G146="",Q146="Fechada",Q146="Perdida"),0,IF(Q146="Previsão vencida",3,IF(Q146="Parada",2,1))*1E+15+MIN(N(O146),500)*1E+12+MIN(ROUND(N(F146)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9123,7 +9870,7 @@
         <v/>
       </c>
       <c r="R147" s="37">
-        <f>IF(OR(G147="",Q147="Fechada",Q147="Perdida"),0,IF(Q147="Previsão vencida",3,IF(Q147="Parada",2,1))*1E+13+MIN(N(O147),500)*1E+10+MIN(ROUND(N(F147),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G147="",Q147="Fechada",Q147="Perdida"),0,IF(Q147="Previsão vencida",3,IF(Q147="Parada",2,1))*1E+15+MIN(N(O147),500)*1E+12+MIN(ROUND(N(F147)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9161,7 +9908,7 @@
         <v/>
       </c>
       <c r="R148" s="37">
-        <f>IF(OR(G148="",Q148="Fechada",Q148="Perdida"),0,IF(Q148="Previsão vencida",3,IF(Q148="Parada",2,1))*1E+13+MIN(N(O148),500)*1E+10+MIN(ROUND(N(F148),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G148="",Q148="Fechada",Q148="Perdida"),0,IF(Q148="Previsão vencida",3,IF(Q148="Parada",2,1))*1E+15+MIN(N(O148),500)*1E+12+MIN(ROUND(N(F148)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9199,7 +9946,7 @@
         <v/>
       </c>
       <c r="R149" s="37">
-        <f>IF(OR(G149="",Q149="Fechada",Q149="Perdida"),0,IF(Q149="Previsão vencida",3,IF(Q149="Parada",2,1))*1E+13+MIN(N(O149),500)*1E+10+MIN(ROUND(N(F149),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G149="",Q149="Fechada",Q149="Perdida"),0,IF(Q149="Previsão vencida",3,IF(Q149="Parada",2,1))*1E+15+MIN(N(O149),500)*1E+12+MIN(ROUND(N(F149)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9237,7 +9984,7 @@
         <v/>
       </c>
       <c r="R150" s="37">
-        <f>IF(OR(G150="",Q150="Fechada",Q150="Perdida"),0,IF(Q150="Previsão vencida",3,IF(Q150="Parada",2,1))*1E+13+MIN(N(O150),500)*1E+10+MIN(ROUND(N(F150),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G150="",Q150="Fechada",Q150="Perdida"),0,IF(Q150="Previsão vencida",3,IF(Q150="Parada",2,1))*1E+15+MIN(N(O150),500)*1E+12+MIN(ROUND(N(F150)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9275,7 +10022,7 @@
         <v/>
       </c>
       <c r="R151" s="37">
-        <f>IF(OR(G151="",Q151="Fechada",Q151="Perdida"),0,IF(Q151="Previsão vencida",3,IF(Q151="Parada",2,1))*1E+13+MIN(N(O151),500)*1E+10+MIN(ROUND(N(F151),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G151="",Q151="Fechada",Q151="Perdida"),0,IF(Q151="Previsão vencida",3,IF(Q151="Parada",2,1))*1E+15+MIN(N(O151),500)*1E+12+MIN(ROUND(N(F151)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9313,7 +10060,7 @@
         <v/>
       </c>
       <c r="R152" s="37">
-        <f>IF(OR(G152="",Q152="Fechada",Q152="Perdida"),0,IF(Q152="Previsão vencida",3,IF(Q152="Parada",2,1))*1E+13+MIN(N(O152),500)*1E+10+MIN(ROUND(N(F152),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G152="",Q152="Fechada",Q152="Perdida"),0,IF(Q152="Previsão vencida",3,IF(Q152="Parada",2,1))*1E+15+MIN(N(O152),500)*1E+12+MIN(ROUND(N(F152)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9351,7 +10098,7 @@
         <v/>
       </c>
       <c r="R153" s="37">
-        <f>IF(OR(G153="",Q153="Fechada",Q153="Perdida"),0,IF(Q153="Previsão vencida",3,IF(Q153="Parada",2,1))*1E+13+MIN(N(O153),500)*1E+10+MIN(ROUND(N(F153),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G153="",Q153="Fechada",Q153="Perdida"),0,IF(Q153="Previsão vencida",3,IF(Q153="Parada",2,1))*1E+15+MIN(N(O153),500)*1E+12+MIN(ROUND(N(F153)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9389,7 +10136,7 @@
         <v/>
       </c>
       <c r="R154" s="37">
-        <f>IF(OR(G154="",Q154="Fechada",Q154="Perdida"),0,IF(Q154="Previsão vencida",3,IF(Q154="Parada",2,1))*1E+13+MIN(N(O154),500)*1E+10+MIN(ROUND(N(F154),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G154="",Q154="Fechada",Q154="Perdida"),0,IF(Q154="Previsão vencida",3,IF(Q154="Parada",2,1))*1E+15+MIN(N(O154),500)*1E+12+MIN(ROUND(N(F154)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9427,7 +10174,7 @@
         <v/>
       </c>
       <c r="R155" s="37">
-        <f>IF(OR(G155="",Q155="Fechada",Q155="Perdida"),0,IF(Q155="Previsão vencida",3,IF(Q155="Parada",2,1))*1E+13+MIN(N(O155),500)*1E+10+MIN(ROUND(N(F155),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G155="",Q155="Fechada",Q155="Perdida"),0,IF(Q155="Previsão vencida",3,IF(Q155="Parada",2,1))*1E+15+MIN(N(O155),500)*1E+12+MIN(ROUND(N(F155)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9465,7 +10212,7 @@
         <v/>
       </c>
       <c r="R156" s="37">
-        <f>IF(OR(G156="",Q156="Fechada",Q156="Perdida"),0,IF(Q156="Previsão vencida",3,IF(Q156="Parada",2,1))*1E+13+MIN(N(O156),500)*1E+10+MIN(ROUND(N(F156),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G156="",Q156="Fechada",Q156="Perdida"),0,IF(Q156="Previsão vencida",3,IF(Q156="Parada",2,1))*1E+15+MIN(N(O156),500)*1E+12+MIN(ROUND(N(F156)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9503,7 +10250,7 @@
         <v/>
       </c>
       <c r="R157" s="37">
-        <f>IF(OR(G157="",Q157="Fechada",Q157="Perdida"),0,IF(Q157="Previsão vencida",3,IF(Q157="Parada",2,1))*1E+13+MIN(N(O157),500)*1E+10+MIN(ROUND(N(F157),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G157="",Q157="Fechada",Q157="Perdida"),0,IF(Q157="Previsão vencida",3,IF(Q157="Parada",2,1))*1E+15+MIN(N(O157),500)*1E+12+MIN(ROUND(N(F157)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9541,7 +10288,7 @@
         <v/>
       </c>
       <c r="R158" s="37">
-        <f>IF(OR(G158="",Q158="Fechada",Q158="Perdida"),0,IF(Q158="Previsão vencida",3,IF(Q158="Parada",2,1))*1E+13+MIN(N(O158),500)*1E+10+MIN(ROUND(N(F158),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G158="",Q158="Fechada",Q158="Perdida"),0,IF(Q158="Previsão vencida",3,IF(Q158="Parada",2,1))*1E+15+MIN(N(O158),500)*1E+12+MIN(ROUND(N(F158)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9579,7 +10326,7 @@
         <v/>
       </c>
       <c r="R159" s="37">
-        <f>IF(OR(G159="",Q159="Fechada",Q159="Perdida"),0,IF(Q159="Previsão vencida",3,IF(Q159="Parada",2,1))*1E+13+MIN(N(O159),500)*1E+10+MIN(ROUND(N(F159),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G159="",Q159="Fechada",Q159="Perdida"),0,IF(Q159="Previsão vencida",3,IF(Q159="Parada",2,1))*1E+15+MIN(N(O159),500)*1E+12+MIN(ROUND(N(F159)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9617,7 +10364,7 @@
         <v/>
       </c>
       <c r="R160" s="37">
-        <f>IF(OR(G160="",Q160="Fechada",Q160="Perdida"),0,IF(Q160="Previsão vencida",3,IF(Q160="Parada",2,1))*1E+13+MIN(N(O160),500)*1E+10+MIN(ROUND(N(F160),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G160="",Q160="Fechada",Q160="Perdida"),0,IF(Q160="Previsão vencida",3,IF(Q160="Parada",2,1))*1E+15+MIN(N(O160),500)*1E+12+MIN(ROUND(N(F160)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9655,7 +10402,7 @@
         <v/>
       </c>
       <c r="R161" s="37">
-        <f>IF(OR(G161="",Q161="Fechada",Q161="Perdida"),0,IF(Q161="Previsão vencida",3,IF(Q161="Parada",2,1))*1E+13+MIN(N(O161),500)*1E+10+MIN(ROUND(N(F161),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G161="",Q161="Fechada",Q161="Perdida"),0,IF(Q161="Previsão vencida",3,IF(Q161="Parada",2,1))*1E+15+MIN(N(O161),500)*1E+12+MIN(ROUND(N(F161)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9693,7 +10440,7 @@
         <v/>
       </c>
       <c r="R162" s="37">
-        <f>IF(OR(G162="",Q162="Fechada",Q162="Perdida"),0,IF(Q162="Previsão vencida",3,IF(Q162="Parada",2,1))*1E+13+MIN(N(O162),500)*1E+10+MIN(ROUND(N(F162),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G162="",Q162="Fechada",Q162="Perdida"),0,IF(Q162="Previsão vencida",3,IF(Q162="Parada",2,1))*1E+15+MIN(N(O162),500)*1E+12+MIN(ROUND(N(F162)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9731,7 +10478,7 @@
         <v/>
       </c>
       <c r="R163" s="37">
-        <f>IF(OR(G163="",Q163="Fechada",Q163="Perdida"),0,IF(Q163="Previsão vencida",3,IF(Q163="Parada",2,1))*1E+13+MIN(N(O163),500)*1E+10+MIN(ROUND(N(F163),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G163="",Q163="Fechada",Q163="Perdida"),0,IF(Q163="Previsão vencida",3,IF(Q163="Parada",2,1))*1E+15+MIN(N(O163),500)*1E+12+MIN(ROUND(N(F163)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9769,7 +10516,7 @@
         <v/>
       </c>
       <c r="R164" s="37">
-        <f>IF(OR(G164="",Q164="Fechada",Q164="Perdida"),0,IF(Q164="Previsão vencida",3,IF(Q164="Parada",2,1))*1E+13+MIN(N(O164),500)*1E+10+MIN(ROUND(N(F164),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G164="",Q164="Fechada",Q164="Perdida"),0,IF(Q164="Previsão vencida",3,IF(Q164="Parada",2,1))*1E+15+MIN(N(O164),500)*1E+12+MIN(ROUND(N(F164)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9807,7 +10554,7 @@
         <v/>
       </c>
       <c r="R165" s="37">
-        <f>IF(OR(G165="",Q165="Fechada",Q165="Perdida"),0,IF(Q165="Previsão vencida",3,IF(Q165="Parada",2,1))*1E+13+MIN(N(O165),500)*1E+10+MIN(ROUND(N(F165),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G165="",Q165="Fechada",Q165="Perdida"),0,IF(Q165="Previsão vencida",3,IF(Q165="Parada",2,1))*1E+15+MIN(N(O165),500)*1E+12+MIN(ROUND(N(F165)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9845,7 +10592,7 @@
         <v/>
       </c>
       <c r="R166" s="37">
-        <f>IF(OR(G166="",Q166="Fechada",Q166="Perdida"),0,IF(Q166="Previsão vencida",3,IF(Q166="Parada",2,1))*1E+13+MIN(N(O166),500)*1E+10+MIN(ROUND(N(F166),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G166="",Q166="Fechada",Q166="Perdida"),0,IF(Q166="Previsão vencida",3,IF(Q166="Parada",2,1))*1E+15+MIN(N(O166),500)*1E+12+MIN(ROUND(N(F166)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9883,7 +10630,7 @@
         <v/>
       </c>
       <c r="R167" s="37">
-        <f>IF(OR(G167="",Q167="Fechada",Q167="Perdida"),0,IF(Q167="Previsão vencida",3,IF(Q167="Parada",2,1))*1E+13+MIN(N(O167),500)*1E+10+MIN(ROUND(N(F167),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G167="",Q167="Fechada",Q167="Perdida"),0,IF(Q167="Previsão vencida",3,IF(Q167="Parada",2,1))*1E+15+MIN(N(O167),500)*1E+12+MIN(ROUND(N(F167)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9921,7 +10668,7 @@
         <v/>
       </c>
       <c r="R168" s="37">
-        <f>IF(OR(G168="",Q168="Fechada",Q168="Perdida"),0,IF(Q168="Previsão vencida",3,IF(Q168="Parada",2,1))*1E+13+MIN(N(O168),500)*1E+10+MIN(ROUND(N(F168),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G168="",Q168="Fechada",Q168="Perdida"),0,IF(Q168="Previsão vencida",3,IF(Q168="Parada",2,1))*1E+15+MIN(N(O168),500)*1E+12+MIN(ROUND(N(F168)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9959,7 +10706,7 @@
         <v/>
       </c>
       <c r="R169" s="37">
-        <f>IF(OR(G169="",Q169="Fechada",Q169="Perdida"),0,IF(Q169="Previsão vencida",3,IF(Q169="Parada",2,1))*1E+13+MIN(N(O169),500)*1E+10+MIN(ROUND(N(F169),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G169="",Q169="Fechada",Q169="Perdida"),0,IF(Q169="Previsão vencida",3,IF(Q169="Parada",2,1))*1E+15+MIN(N(O169),500)*1E+12+MIN(ROUND(N(F169)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9997,7 +10744,7 @@
         <v/>
       </c>
       <c r="R170" s="37">
-        <f>IF(OR(G170="",Q170="Fechada",Q170="Perdida"),0,IF(Q170="Previsão vencida",3,IF(Q170="Parada",2,1))*1E+13+MIN(N(O170),500)*1E+10+MIN(ROUND(N(F170),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G170="",Q170="Fechada",Q170="Perdida"),0,IF(Q170="Previsão vencida",3,IF(Q170="Parada",2,1))*1E+15+MIN(N(O170),500)*1E+12+MIN(ROUND(N(F170)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10035,7 +10782,7 @@
         <v/>
       </c>
       <c r="R171" s="37">
-        <f>IF(OR(G171="",Q171="Fechada",Q171="Perdida"),0,IF(Q171="Previsão vencida",3,IF(Q171="Parada",2,1))*1E+13+MIN(N(O171),500)*1E+10+MIN(ROUND(N(F171),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G171="",Q171="Fechada",Q171="Perdida"),0,IF(Q171="Previsão vencida",3,IF(Q171="Parada",2,1))*1E+15+MIN(N(O171),500)*1E+12+MIN(ROUND(N(F171)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10073,7 +10820,7 @@
         <v/>
       </c>
       <c r="R172" s="37">
-        <f>IF(OR(G172="",Q172="Fechada",Q172="Perdida"),0,IF(Q172="Previsão vencida",3,IF(Q172="Parada",2,1))*1E+13+MIN(N(O172),500)*1E+10+MIN(ROUND(N(F172),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G172="",Q172="Fechada",Q172="Perdida"),0,IF(Q172="Previsão vencida",3,IF(Q172="Parada",2,1))*1E+15+MIN(N(O172),500)*1E+12+MIN(ROUND(N(F172)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10111,7 +10858,7 @@
         <v/>
       </c>
       <c r="R173" s="37">
-        <f>IF(OR(G173="",Q173="Fechada",Q173="Perdida"),0,IF(Q173="Previsão vencida",3,IF(Q173="Parada",2,1))*1E+13+MIN(N(O173),500)*1E+10+MIN(ROUND(N(F173),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G173="",Q173="Fechada",Q173="Perdida"),0,IF(Q173="Previsão vencida",3,IF(Q173="Parada",2,1))*1E+15+MIN(N(O173),500)*1E+12+MIN(ROUND(N(F173)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10149,7 +10896,7 @@
         <v/>
       </c>
       <c r="R174" s="37">
-        <f>IF(OR(G174="",Q174="Fechada",Q174="Perdida"),0,IF(Q174="Previsão vencida",3,IF(Q174="Parada",2,1))*1E+13+MIN(N(O174),500)*1E+10+MIN(ROUND(N(F174),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G174="",Q174="Fechada",Q174="Perdida"),0,IF(Q174="Previsão vencida",3,IF(Q174="Parada",2,1))*1E+15+MIN(N(O174),500)*1E+12+MIN(ROUND(N(F174)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10187,7 +10934,7 @@
         <v/>
       </c>
       <c r="R175" s="37">
-        <f>IF(OR(G175="",Q175="Fechada",Q175="Perdida"),0,IF(Q175="Previsão vencida",3,IF(Q175="Parada",2,1))*1E+13+MIN(N(O175),500)*1E+10+MIN(ROUND(N(F175),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G175="",Q175="Fechada",Q175="Perdida"),0,IF(Q175="Previsão vencida",3,IF(Q175="Parada",2,1))*1E+15+MIN(N(O175),500)*1E+12+MIN(ROUND(N(F175)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10225,7 +10972,7 @@
         <v/>
       </c>
       <c r="R176" s="37">
-        <f>IF(OR(G176="",Q176="Fechada",Q176="Perdida"),0,IF(Q176="Previsão vencida",3,IF(Q176="Parada",2,1))*1E+13+MIN(N(O176),500)*1E+10+MIN(ROUND(N(F176),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G176="",Q176="Fechada",Q176="Perdida"),0,IF(Q176="Previsão vencida",3,IF(Q176="Parada",2,1))*1E+15+MIN(N(O176),500)*1E+12+MIN(ROUND(N(F176)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10263,7 +11010,7 @@
         <v/>
       </c>
       <c r="R177" s="37">
-        <f>IF(OR(G177="",Q177="Fechada",Q177="Perdida"),0,IF(Q177="Previsão vencida",3,IF(Q177="Parada",2,1))*1E+13+MIN(N(O177),500)*1E+10+MIN(ROUND(N(F177),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G177="",Q177="Fechada",Q177="Perdida"),0,IF(Q177="Previsão vencida",3,IF(Q177="Parada",2,1))*1E+15+MIN(N(O177),500)*1E+12+MIN(ROUND(N(F177)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10301,7 +11048,7 @@
         <v/>
       </c>
       <c r="R178" s="37">
-        <f>IF(OR(G178="",Q178="Fechada",Q178="Perdida"),0,IF(Q178="Previsão vencida",3,IF(Q178="Parada",2,1))*1E+13+MIN(N(O178),500)*1E+10+MIN(ROUND(N(F178),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G178="",Q178="Fechada",Q178="Perdida"),0,IF(Q178="Previsão vencida",3,IF(Q178="Parada",2,1))*1E+15+MIN(N(O178),500)*1E+12+MIN(ROUND(N(F178)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10339,7 +11086,7 @@
         <v/>
       </c>
       <c r="R179" s="37">
-        <f>IF(OR(G179="",Q179="Fechada",Q179="Perdida"),0,IF(Q179="Previsão vencida",3,IF(Q179="Parada",2,1))*1E+13+MIN(N(O179),500)*1E+10+MIN(ROUND(N(F179),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G179="",Q179="Fechada",Q179="Perdida"),0,IF(Q179="Previsão vencida",3,IF(Q179="Parada",2,1))*1E+15+MIN(N(O179),500)*1E+12+MIN(ROUND(N(F179)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10377,7 +11124,7 @@
         <v/>
       </c>
       <c r="R180" s="37">
-        <f>IF(OR(G180="",Q180="Fechada",Q180="Perdida"),0,IF(Q180="Previsão vencida",3,IF(Q180="Parada",2,1))*1E+13+MIN(N(O180),500)*1E+10+MIN(ROUND(N(F180),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G180="",Q180="Fechada",Q180="Perdida"),0,IF(Q180="Previsão vencida",3,IF(Q180="Parada",2,1))*1E+15+MIN(N(O180),500)*1E+12+MIN(ROUND(N(F180)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10415,7 +11162,7 @@
         <v/>
       </c>
       <c r="R181" s="37">
-        <f>IF(OR(G181="",Q181="Fechada",Q181="Perdida"),0,IF(Q181="Previsão vencida",3,IF(Q181="Parada",2,1))*1E+13+MIN(N(O181),500)*1E+10+MIN(ROUND(N(F181),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G181="",Q181="Fechada",Q181="Perdida"),0,IF(Q181="Previsão vencida",3,IF(Q181="Parada",2,1))*1E+15+MIN(N(O181),500)*1E+12+MIN(ROUND(N(F181)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10453,7 +11200,7 @@
         <v/>
       </c>
       <c r="R182" s="37">
-        <f>IF(OR(G182="",Q182="Fechada",Q182="Perdida"),0,IF(Q182="Previsão vencida",3,IF(Q182="Parada",2,1))*1E+13+MIN(N(O182),500)*1E+10+MIN(ROUND(N(F182),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G182="",Q182="Fechada",Q182="Perdida"),0,IF(Q182="Previsão vencida",3,IF(Q182="Parada",2,1))*1E+15+MIN(N(O182),500)*1E+12+MIN(ROUND(N(F182)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10491,7 +11238,7 @@
         <v/>
       </c>
       <c r="R183" s="37">
-        <f>IF(OR(G183="",Q183="Fechada",Q183="Perdida"),0,IF(Q183="Previsão vencida",3,IF(Q183="Parada",2,1))*1E+13+MIN(N(O183),500)*1E+10+MIN(ROUND(N(F183),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G183="",Q183="Fechada",Q183="Perdida"),0,IF(Q183="Previsão vencida",3,IF(Q183="Parada",2,1))*1E+15+MIN(N(O183),500)*1E+12+MIN(ROUND(N(F183)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10529,7 +11276,7 @@
         <v/>
       </c>
       <c r="R184" s="37">
-        <f>IF(OR(G184="",Q184="Fechada",Q184="Perdida"),0,IF(Q184="Previsão vencida",3,IF(Q184="Parada",2,1))*1E+13+MIN(N(O184),500)*1E+10+MIN(ROUND(N(F184),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G184="",Q184="Fechada",Q184="Perdida"),0,IF(Q184="Previsão vencida",3,IF(Q184="Parada",2,1))*1E+15+MIN(N(O184),500)*1E+12+MIN(ROUND(N(F184)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10567,7 +11314,7 @@
         <v/>
       </c>
       <c r="R185" s="37">
-        <f>IF(OR(G185="",Q185="Fechada",Q185="Perdida"),0,IF(Q185="Previsão vencida",3,IF(Q185="Parada",2,1))*1E+13+MIN(N(O185),500)*1E+10+MIN(ROUND(N(F185),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G185="",Q185="Fechada",Q185="Perdida"),0,IF(Q185="Previsão vencida",3,IF(Q185="Parada",2,1))*1E+15+MIN(N(O185),500)*1E+12+MIN(ROUND(N(F185)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10605,7 +11352,7 @@
         <v/>
       </c>
       <c r="R186" s="37">
-        <f>IF(OR(G186="",Q186="Fechada",Q186="Perdida"),0,IF(Q186="Previsão vencida",3,IF(Q186="Parada",2,1))*1E+13+MIN(N(O186),500)*1E+10+MIN(ROUND(N(F186),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G186="",Q186="Fechada",Q186="Perdida"),0,IF(Q186="Previsão vencida",3,IF(Q186="Parada",2,1))*1E+15+MIN(N(O186),500)*1E+12+MIN(ROUND(N(F186)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10643,7 +11390,7 @@
         <v/>
       </c>
       <c r="R187" s="37">
-        <f>IF(OR(G187="",Q187="Fechada",Q187="Perdida"),0,IF(Q187="Previsão vencida",3,IF(Q187="Parada",2,1))*1E+13+MIN(N(O187),500)*1E+10+MIN(ROUND(N(F187),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G187="",Q187="Fechada",Q187="Perdida"),0,IF(Q187="Previsão vencida",3,IF(Q187="Parada",2,1))*1E+15+MIN(N(O187),500)*1E+12+MIN(ROUND(N(F187)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10681,7 +11428,7 @@
         <v/>
       </c>
       <c r="R188" s="37">
-        <f>IF(OR(G188="",Q188="Fechada",Q188="Perdida"),0,IF(Q188="Previsão vencida",3,IF(Q188="Parada",2,1))*1E+13+MIN(N(O188),500)*1E+10+MIN(ROUND(N(F188),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G188="",Q188="Fechada",Q188="Perdida"),0,IF(Q188="Previsão vencida",3,IF(Q188="Parada",2,1))*1E+15+MIN(N(O188),500)*1E+12+MIN(ROUND(N(F188)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10719,7 +11466,7 @@
         <v/>
       </c>
       <c r="R189" s="37">
-        <f>IF(OR(G189="",Q189="Fechada",Q189="Perdida"),0,IF(Q189="Previsão vencida",3,IF(Q189="Parada",2,1))*1E+13+MIN(N(O189),500)*1E+10+MIN(ROUND(N(F189),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G189="",Q189="Fechada",Q189="Perdida"),0,IF(Q189="Previsão vencida",3,IF(Q189="Parada",2,1))*1E+15+MIN(N(O189),500)*1E+12+MIN(ROUND(N(F189)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10757,7 +11504,7 @@
         <v/>
       </c>
       <c r="R190" s="37">
-        <f>IF(OR(G190="",Q190="Fechada",Q190="Perdida"),0,IF(Q190="Previsão vencida",3,IF(Q190="Parada",2,1))*1E+13+MIN(N(O190),500)*1E+10+MIN(ROUND(N(F190),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G190="",Q190="Fechada",Q190="Perdida"),0,IF(Q190="Previsão vencida",3,IF(Q190="Parada",2,1))*1E+15+MIN(N(O190),500)*1E+12+MIN(ROUND(N(F190)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10795,7 +11542,7 @@
         <v/>
       </c>
       <c r="R191" s="37">
-        <f>IF(OR(G191="",Q191="Fechada",Q191="Perdida"),0,IF(Q191="Previsão vencida",3,IF(Q191="Parada",2,1))*1E+13+MIN(N(O191),500)*1E+10+MIN(ROUND(N(F191),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G191="",Q191="Fechada",Q191="Perdida"),0,IF(Q191="Previsão vencida",3,IF(Q191="Parada",2,1))*1E+15+MIN(N(O191),500)*1E+12+MIN(ROUND(N(F191)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10833,7 +11580,7 @@
         <v/>
       </c>
       <c r="R192" s="37">
-        <f>IF(OR(G192="",Q192="Fechada",Q192="Perdida"),0,IF(Q192="Previsão vencida",3,IF(Q192="Parada",2,1))*1E+13+MIN(N(O192),500)*1E+10+MIN(ROUND(N(F192),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G192="",Q192="Fechada",Q192="Perdida"),0,IF(Q192="Previsão vencida",3,IF(Q192="Parada",2,1))*1E+15+MIN(N(O192),500)*1E+12+MIN(ROUND(N(F192)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10871,7 +11618,7 @@
         <v/>
       </c>
       <c r="R193" s="37">
-        <f>IF(OR(G193="",Q193="Fechada",Q193="Perdida"),0,IF(Q193="Previsão vencida",3,IF(Q193="Parada",2,1))*1E+13+MIN(N(O193),500)*1E+10+MIN(ROUND(N(F193),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G193="",Q193="Fechada",Q193="Perdida"),0,IF(Q193="Previsão vencida",3,IF(Q193="Parada",2,1))*1E+15+MIN(N(O193),500)*1E+12+MIN(ROUND(N(F193)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10909,7 +11656,7 @@
         <v/>
       </c>
       <c r="R194" s="37">
-        <f>IF(OR(G194="",Q194="Fechada",Q194="Perdida"),0,IF(Q194="Previsão vencida",3,IF(Q194="Parada",2,1))*1E+13+MIN(N(O194),500)*1E+10+MIN(ROUND(N(F194),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G194="",Q194="Fechada",Q194="Perdida"),0,IF(Q194="Previsão vencida",3,IF(Q194="Parada",2,1))*1E+15+MIN(N(O194),500)*1E+12+MIN(ROUND(N(F194)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10947,7 +11694,7 @@
         <v/>
       </c>
       <c r="R195" s="37">
-        <f>IF(OR(G195="",Q195="Fechada",Q195="Perdida"),0,IF(Q195="Previsão vencida",3,IF(Q195="Parada",2,1))*1E+13+MIN(N(O195),500)*1E+10+MIN(ROUND(N(F195),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G195="",Q195="Fechada",Q195="Perdida"),0,IF(Q195="Previsão vencida",3,IF(Q195="Parada",2,1))*1E+15+MIN(N(O195),500)*1E+12+MIN(ROUND(N(F195)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10985,7 +11732,7 @@
         <v/>
       </c>
       <c r="R196" s="37">
-        <f>IF(OR(G196="",Q196="Fechada",Q196="Perdida"),0,IF(Q196="Previsão vencida",3,IF(Q196="Parada",2,1))*1E+13+MIN(N(O196),500)*1E+10+MIN(ROUND(N(F196),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G196="",Q196="Fechada",Q196="Perdida"),0,IF(Q196="Previsão vencida",3,IF(Q196="Parada",2,1))*1E+15+MIN(N(O196),500)*1E+12+MIN(ROUND(N(F196)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11023,7 +11770,7 @@
         <v/>
       </c>
       <c r="R197" s="37">
-        <f>IF(OR(G197="",Q197="Fechada",Q197="Perdida"),0,IF(Q197="Previsão vencida",3,IF(Q197="Parada",2,1))*1E+13+MIN(N(O197),500)*1E+10+MIN(ROUND(N(F197),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G197="",Q197="Fechada",Q197="Perdida"),0,IF(Q197="Previsão vencida",3,IF(Q197="Parada",2,1))*1E+15+MIN(N(O197),500)*1E+12+MIN(ROUND(N(F197)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11061,7 +11808,7 @@
         <v/>
       </c>
       <c r="R198" s="37">
-        <f>IF(OR(G198="",Q198="Fechada",Q198="Perdida"),0,IF(Q198="Previsão vencida",3,IF(Q198="Parada",2,1))*1E+13+MIN(N(O198),500)*1E+10+MIN(ROUND(N(F198),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G198="",Q198="Fechada",Q198="Perdida"),0,IF(Q198="Previsão vencida",3,IF(Q198="Parada",2,1))*1E+15+MIN(N(O198),500)*1E+12+MIN(ROUND(N(F198)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11099,7 +11846,7 @@
         <v/>
       </c>
       <c r="R199" s="37">
-        <f>IF(OR(G199="",Q199="Fechada",Q199="Perdida"),0,IF(Q199="Previsão vencida",3,IF(Q199="Parada",2,1))*1E+13+MIN(N(O199),500)*1E+10+MIN(ROUND(N(F199),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G199="",Q199="Fechada",Q199="Perdida"),0,IF(Q199="Previsão vencida",3,IF(Q199="Parada",2,1))*1E+15+MIN(N(O199),500)*1E+12+MIN(ROUND(N(F199)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11137,7 +11884,7 @@
         <v/>
       </c>
       <c r="R200" s="37">
-        <f>IF(OR(G200="",Q200="Fechada",Q200="Perdida"),0,IF(Q200="Previsão vencida",3,IF(Q200="Parada",2,1))*1E+13+MIN(N(O200),500)*1E+10+MIN(ROUND(N(F200),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G200="",Q200="Fechada",Q200="Perdida"),0,IF(Q200="Previsão vencida",3,IF(Q200="Parada",2,1))*1E+15+MIN(N(O200),500)*1E+12+MIN(ROUND(N(F200)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11175,7 +11922,7 @@
         <v/>
       </c>
       <c r="R201" s="37">
-        <f>IF(OR(G201="",Q201="Fechada",Q201="Perdida"),0,IF(Q201="Previsão vencida",3,IF(Q201="Parada",2,1))*1E+13+MIN(N(O201),500)*1E+10+MIN(ROUND(N(F201),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G201="",Q201="Fechada",Q201="Perdida"),0,IF(Q201="Previsão vencida",3,IF(Q201="Parada",2,1))*1E+15+MIN(N(O201),500)*1E+12+MIN(ROUND(N(F201)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11213,7 +11960,7 @@
         <v/>
       </c>
       <c r="R202" s="37">
-        <f>IF(OR(G202="",Q202="Fechada",Q202="Perdida"),0,IF(Q202="Previsão vencida",3,IF(Q202="Parada",2,1))*1E+13+MIN(N(O202),500)*1E+10+MIN(ROUND(N(F202),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G202="",Q202="Fechada",Q202="Perdida"),0,IF(Q202="Previsão vencida",3,IF(Q202="Parada",2,1))*1E+15+MIN(N(O202),500)*1E+12+MIN(ROUND(N(F202)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11251,7 +11998,7 @@
         <v/>
       </c>
       <c r="R203" s="37">
-        <f>IF(OR(G203="",Q203="Fechada",Q203="Perdida"),0,IF(Q203="Previsão vencida",3,IF(Q203="Parada",2,1))*1E+13+MIN(N(O203),500)*1E+10+MIN(ROUND(N(F203),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G203="",Q203="Fechada",Q203="Perdida"),0,IF(Q203="Previsão vencida",3,IF(Q203="Parada",2,1))*1E+15+MIN(N(O203),500)*1E+12+MIN(ROUND(N(F203)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11289,7 +12036,7 @@
         <v/>
       </c>
       <c r="R204" s="37">
-        <f>IF(OR(G204="",Q204="Fechada",Q204="Perdida"),0,IF(Q204="Previsão vencida",3,IF(Q204="Parada",2,1))*1E+13+MIN(N(O204),500)*1E+10+MIN(ROUND(N(F204),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G204="",Q204="Fechada",Q204="Perdida"),0,IF(Q204="Previsão vencida",3,IF(Q204="Parada",2,1))*1E+15+MIN(N(O204),500)*1E+12+MIN(ROUND(N(F204)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11327,7 +12074,7 @@
         <v/>
       </c>
       <c r="R205" s="37">
-        <f>IF(OR(G205="",Q205="Fechada",Q205="Perdida"),0,IF(Q205="Previsão vencida",3,IF(Q205="Parada",2,1))*1E+13+MIN(N(O205),500)*1E+10+MIN(ROUND(N(F205),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G205="",Q205="Fechada",Q205="Perdida"),0,IF(Q205="Previsão vencida",3,IF(Q205="Parada",2,1))*1E+15+MIN(N(O205),500)*1E+12+MIN(ROUND(N(F205)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11365,7 +12112,7 @@
         <v/>
       </c>
       <c r="R206" s="37">
-        <f>IF(OR(G206="",Q206="Fechada",Q206="Perdida"),0,IF(Q206="Previsão vencida",3,IF(Q206="Parada",2,1))*1E+13+MIN(N(O206),500)*1E+10+MIN(ROUND(N(F206),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G206="",Q206="Fechada",Q206="Perdida"),0,IF(Q206="Previsão vencida",3,IF(Q206="Parada",2,1))*1E+15+MIN(N(O206),500)*1E+12+MIN(ROUND(N(F206)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11403,7 +12150,7 @@
         <v/>
       </c>
       <c r="R207" s="37">
-        <f>IF(OR(G207="",Q207="Fechada",Q207="Perdida"),0,IF(Q207="Previsão vencida",3,IF(Q207="Parada",2,1))*1E+13+MIN(N(O207),500)*1E+10+MIN(ROUND(N(F207),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G207="",Q207="Fechada",Q207="Perdida"),0,IF(Q207="Previsão vencida",3,IF(Q207="Parada",2,1))*1E+15+MIN(N(O207),500)*1E+12+MIN(ROUND(N(F207)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11441,7 +12188,7 @@
         <v/>
       </c>
       <c r="R208" s="37">
-        <f>IF(OR(G208="",Q208="Fechada",Q208="Perdida"),0,IF(Q208="Previsão vencida",3,IF(Q208="Parada",2,1))*1E+13+MIN(N(O208),500)*1E+10+MIN(ROUND(N(F208),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G208="",Q208="Fechada",Q208="Perdida"),0,IF(Q208="Previsão vencida",3,IF(Q208="Parada",2,1))*1E+15+MIN(N(O208),500)*1E+12+MIN(ROUND(N(F208)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11479,7 +12226,7 @@
         <v/>
       </c>
       <c r="R209" s="37">
-        <f>IF(OR(G209="",Q209="Fechada",Q209="Perdida"),0,IF(Q209="Previsão vencida",3,IF(Q209="Parada",2,1))*1E+13+MIN(N(O209),500)*1E+10+MIN(ROUND(N(F209),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G209="",Q209="Fechada",Q209="Perdida"),0,IF(Q209="Previsão vencida",3,IF(Q209="Parada",2,1))*1E+15+MIN(N(O209),500)*1E+12+MIN(ROUND(N(F209)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11517,7 +12264,7 @@
         <v/>
       </c>
       <c r="R210" s="37">
-        <f>IF(OR(G210="",Q210="Fechada",Q210="Perdida"),0,IF(Q210="Previsão vencida",3,IF(Q210="Parada",2,1))*1E+13+MIN(N(O210),500)*1E+10+MIN(ROUND(N(F210),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G210="",Q210="Fechada",Q210="Perdida"),0,IF(Q210="Previsão vencida",3,IF(Q210="Parada",2,1))*1E+15+MIN(N(O210),500)*1E+12+MIN(ROUND(N(F210)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11555,7 +12302,7 @@
         <v/>
       </c>
       <c r="R211" s="37">
-        <f>IF(OR(G211="",Q211="Fechada",Q211="Perdida"),0,IF(Q211="Previsão vencida",3,IF(Q211="Parada",2,1))*1E+13+MIN(N(O211),500)*1E+10+MIN(ROUND(N(F211),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G211="",Q211="Fechada",Q211="Perdida"),0,IF(Q211="Previsão vencida",3,IF(Q211="Parada",2,1))*1E+15+MIN(N(O211),500)*1E+12+MIN(ROUND(N(F211)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11593,7 +12340,7 @@
         <v/>
       </c>
       <c r="R212" s="37">
-        <f>IF(OR(G212="",Q212="Fechada",Q212="Perdida"),0,IF(Q212="Previsão vencida",3,IF(Q212="Parada",2,1))*1E+13+MIN(N(O212),500)*1E+10+MIN(ROUND(N(F212),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G212="",Q212="Fechada",Q212="Perdida"),0,IF(Q212="Previsão vencida",3,IF(Q212="Parada",2,1))*1E+15+MIN(N(O212),500)*1E+12+MIN(ROUND(N(F212)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11631,7 +12378,7 @@
         <v/>
       </c>
       <c r="R213" s="37">
-        <f>IF(OR(G213="",Q213="Fechada",Q213="Perdida"),0,IF(Q213="Previsão vencida",3,IF(Q213="Parada",2,1))*1E+13+MIN(N(O213),500)*1E+10+MIN(ROUND(N(F213),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G213="",Q213="Fechada",Q213="Perdida"),0,IF(Q213="Previsão vencida",3,IF(Q213="Parada",2,1))*1E+15+MIN(N(O213),500)*1E+12+MIN(ROUND(N(F213)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11669,7 +12416,7 @@
         <v/>
       </c>
       <c r="R214" s="37">
-        <f>IF(OR(G214="",Q214="Fechada",Q214="Perdida"),0,IF(Q214="Previsão vencida",3,IF(Q214="Parada",2,1))*1E+13+MIN(N(O214),500)*1E+10+MIN(ROUND(N(F214),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G214="",Q214="Fechada",Q214="Perdida"),0,IF(Q214="Previsão vencida",3,IF(Q214="Parada",2,1))*1E+15+MIN(N(O214),500)*1E+12+MIN(ROUND(N(F214)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11707,7 +12454,7 @@
         <v/>
       </c>
       <c r="R215" s="37">
-        <f>IF(OR(G215="",Q215="Fechada",Q215="Perdida"),0,IF(Q215="Previsão vencida",3,IF(Q215="Parada",2,1))*1E+13+MIN(N(O215),500)*1E+10+MIN(ROUND(N(F215),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G215="",Q215="Fechada",Q215="Perdida"),0,IF(Q215="Previsão vencida",3,IF(Q215="Parada",2,1))*1E+15+MIN(N(O215),500)*1E+12+MIN(ROUND(N(F215)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11745,7 +12492,7 @@
         <v/>
       </c>
       <c r="R216" s="37">
-        <f>IF(OR(G216="",Q216="Fechada",Q216="Perdida"),0,IF(Q216="Previsão vencida",3,IF(Q216="Parada",2,1))*1E+13+MIN(N(O216),500)*1E+10+MIN(ROUND(N(F216),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G216="",Q216="Fechada",Q216="Perdida"),0,IF(Q216="Previsão vencida",3,IF(Q216="Parada",2,1))*1E+15+MIN(N(O216),500)*1E+12+MIN(ROUND(N(F216)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11783,7 +12530,7 @@
         <v/>
       </c>
       <c r="R217" s="37">
-        <f>IF(OR(G217="",Q217="Fechada",Q217="Perdida"),0,IF(Q217="Previsão vencida",3,IF(Q217="Parada",2,1))*1E+13+MIN(N(O217),500)*1E+10+MIN(ROUND(N(F217),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G217="",Q217="Fechada",Q217="Perdida"),0,IF(Q217="Previsão vencida",3,IF(Q217="Parada",2,1))*1E+15+MIN(N(O217),500)*1E+12+MIN(ROUND(N(F217)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11821,7 +12568,7 @@
         <v/>
       </c>
       <c r="R218" s="37">
-        <f>IF(OR(G218="",Q218="Fechada",Q218="Perdida"),0,IF(Q218="Previsão vencida",3,IF(Q218="Parada",2,1))*1E+13+MIN(N(O218),500)*1E+10+MIN(ROUND(N(F218),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G218="",Q218="Fechada",Q218="Perdida"),0,IF(Q218="Previsão vencida",3,IF(Q218="Parada",2,1))*1E+15+MIN(N(O218),500)*1E+12+MIN(ROUND(N(F218)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11859,7 +12606,7 @@
         <v/>
       </c>
       <c r="R219" s="37">
-        <f>IF(OR(G219="",Q219="Fechada",Q219="Perdida"),0,IF(Q219="Previsão vencida",3,IF(Q219="Parada",2,1))*1E+13+MIN(N(O219),500)*1E+10+MIN(ROUND(N(F219),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G219="",Q219="Fechada",Q219="Perdida"),0,IF(Q219="Previsão vencida",3,IF(Q219="Parada",2,1))*1E+15+MIN(N(O219),500)*1E+12+MIN(ROUND(N(F219)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11897,7 +12644,7 @@
         <v/>
       </c>
       <c r="R220" s="37">
-        <f>IF(OR(G220="",Q220="Fechada",Q220="Perdida"),0,IF(Q220="Previsão vencida",3,IF(Q220="Parada",2,1))*1E+13+MIN(N(O220),500)*1E+10+MIN(ROUND(N(F220),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G220="",Q220="Fechada",Q220="Perdida"),0,IF(Q220="Previsão vencida",3,IF(Q220="Parada",2,1))*1E+15+MIN(N(O220),500)*1E+12+MIN(ROUND(N(F220)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11935,7 +12682,7 @@
         <v/>
       </c>
       <c r="R221" s="37">
-        <f>IF(OR(G221="",Q221="Fechada",Q221="Perdida"),0,IF(Q221="Previsão vencida",3,IF(Q221="Parada",2,1))*1E+13+MIN(N(O221),500)*1E+10+MIN(ROUND(N(F221),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G221="",Q221="Fechada",Q221="Perdida"),0,IF(Q221="Previsão vencida",3,IF(Q221="Parada",2,1))*1E+15+MIN(N(O221),500)*1E+12+MIN(ROUND(N(F221)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11973,7 +12720,7 @@
         <v/>
       </c>
       <c r="R222" s="37">
-        <f>IF(OR(G222="",Q222="Fechada",Q222="Perdida"),0,IF(Q222="Previsão vencida",3,IF(Q222="Parada",2,1))*1E+13+MIN(N(O222),500)*1E+10+MIN(ROUND(N(F222),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G222="",Q222="Fechada",Q222="Perdida"),0,IF(Q222="Previsão vencida",3,IF(Q222="Parada",2,1))*1E+15+MIN(N(O222),500)*1E+12+MIN(ROUND(N(F222)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12011,7 +12758,7 @@
         <v/>
       </c>
       <c r="R223" s="37">
-        <f>IF(OR(G223="",Q223="Fechada",Q223="Perdida"),0,IF(Q223="Previsão vencida",3,IF(Q223="Parada",2,1))*1E+13+MIN(N(O223),500)*1E+10+MIN(ROUND(N(F223),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G223="",Q223="Fechada",Q223="Perdida"),0,IF(Q223="Previsão vencida",3,IF(Q223="Parada",2,1))*1E+15+MIN(N(O223),500)*1E+12+MIN(ROUND(N(F223)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12049,7 +12796,7 @@
         <v/>
       </c>
       <c r="R224" s="37">
-        <f>IF(OR(G224="",Q224="Fechada",Q224="Perdida"),0,IF(Q224="Previsão vencida",3,IF(Q224="Parada",2,1))*1E+13+MIN(N(O224),500)*1E+10+MIN(ROUND(N(F224),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G224="",Q224="Fechada",Q224="Perdida"),0,IF(Q224="Previsão vencida",3,IF(Q224="Parada",2,1))*1E+15+MIN(N(O224),500)*1E+12+MIN(ROUND(N(F224)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12087,7 +12834,7 @@
         <v/>
       </c>
       <c r="R225" s="37">
-        <f>IF(OR(G225="",Q225="Fechada",Q225="Perdida"),0,IF(Q225="Previsão vencida",3,IF(Q225="Parada",2,1))*1E+13+MIN(N(O225),500)*1E+10+MIN(ROUND(N(F225),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G225="",Q225="Fechada",Q225="Perdida"),0,IF(Q225="Previsão vencida",3,IF(Q225="Parada",2,1))*1E+15+MIN(N(O225),500)*1E+12+MIN(ROUND(N(F225)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12125,7 +12872,7 @@
         <v/>
       </c>
       <c r="R226" s="37">
-        <f>IF(OR(G226="",Q226="Fechada",Q226="Perdida"),0,IF(Q226="Previsão vencida",3,IF(Q226="Parada",2,1))*1E+13+MIN(N(O226),500)*1E+10+MIN(ROUND(N(F226),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G226="",Q226="Fechada",Q226="Perdida"),0,IF(Q226="Previsão vencida",3,IF(Q226="Parada",2,1))*1E+15+MIN(N(O226),500)*1E+12+MIN(ROUND(N(F226)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12163,7 +12910,7 @@
         <v/>
       </c>
       <c r="R227" s="37">
-        <f>IF(OR(G227="",Q227="Fechada",Q227="Perdida"),0,IF(Q227="Previsão vencida",3,IF(Q227="Parada",2,1))*1E+13+MIN(N(O227),500)*1E+10+MIN(ROUND(N(F227),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G227="",Q227="Fechada",Q227="Perdida"),0,IF(Q227="Previsão vencida",3,IF(Q227="Parada",2,1))*1E+15+MIN(N(O227),500)*1E+12+MIN(ROUND(N(F227)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12201,7 +12948,7 @@
         <v/>
       </c>
       <c r="R228" s="37">
-        <f>IF(OR(G228="",Q228="Fechada",Q228="Perdida"),0,IF(Q228="Previsão vencida",3,IF(Q228="Parada",2,1))*1E+13+MIN(N(O228),500)*1E+10+MIN(ROUND(N(F228),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G228="",Q228="Fechada",Q228="Perdida"),0,IF(Q228="Previsão vencida",3,IF(Q228="Parada",2,1))*1E+15+MIN(N(O228),500)*1E+12+MIN(ROUND(N(F228)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12239,7 +12986,7 @@
         <v/>
       </c>
       <c r="R229" s="37">
-        <f>IF(OR(G229="",Q229="Fechada",Q229="Perdida"),0,IF(Q229="Previsão vencida",3,IF(Q229="Parada",2,1))*1E+13+MIN(N(O229),500)*1E+10+MIN(ROUND(N(F229),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G229="",Q229="Fechada",Q229="Perdida"),0,IF(Q229="Previsão vencida",3,IF(Q229="Parada",2,1))*1E+15+MIN(N(O229),500)*1E+12+MIN(ROUND(N(F229)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12277,7 +13024,7 @@
         <v/>
       </c>
       <c r="R230" s="37">
-        <f>IF(OR(G230="",Q230="Fechada",Q230="Perdida"),0,IF(Q230="Previsão vencida",3,IF(Q230="Parada",2,1))*1E+13+MIN(N(O230),500)*1E+10+MIN(ROUND(N(F230),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G230="",Q230="Fechada",Q230="Perdida"),0,IF(Q230="Previsão vencida",3,IF(Q230="Parada",2,1))*1E+15+MIN(N(O230),500)*1E+12+MIN(ROUND(N(F230)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12315,7 +13062,7 @@
         <v/>
       </c>
       <c r="R231" s="37">
-        <f>IF(OR(G231="",Q231="Fechada",Q231="Perdida"),0,IF(Q231="Previsão vencida",3,IF(Q231="Parada",2,1))*1E+13+MIN(N(O231),500)*1E+10+MIN(ROUND(N(F231),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G231="",Q231="Fechada",Q231="Perdida"),0,IF(Q231="Previsão vencida",3,IF(Q231="Parada",2,1))*1E+15+MIN(N(O231),500)*1E+12+MIN(ROUND(N(F231)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12353,7 +13100,7 @@
         <v/>
       </c>
       <c r="R232" s="37">
-        <f>IF(OR(G232="",Q232="Fechada",Q232="Perdida"),0,IF(Q232="Previsão vencida",3,IF(Q232="Parada",2,1))*1E+13+MIN(N(O232),500)*1E+10+MIN(ROUND(N(F232),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G232="",Q232="Fechada",Q232="Perdida"),0,IF(Q232="Previsão vencida",3,IF(Q232="Parada",2,1))*1E+15+MIN(N(O232),500)*1E+12+MIN(ROUND(N(F232)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12391,7 +13138,7 @@
         <v/>
       </c>
       <c r="R233" s="37">
-        <f>IF(OR(G233="",Q233="Fechada",Q233="Perdida"),0,IF(Q233="Previsão vencida",3,IF(Q233="Parada",2,1))*1E+13+MIN(N(O233),500)*1E+10+MIN(ROUND(N(F233),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G233="",Q233="Fechada",Q233="Perdida"),0,IF(Q233="Previsão vencida",3,IF(Q233="Parada",2,1))*1E+15+MIN(N(O233),500)*1E+12+MIN(ROUND(N(F233)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12429,7 +13176,7 @@
         <v/>
       </c>
       <c r="R234" s="37">
-        <f>IF(OR(G234="",Q234="Fechada",Q234="Perdida"),0,IF(Q234="Previsão vencida",3,IF(Q234="Parada",2,1))*1E+13+MIN(N(O234),500)*1E+10+MIN(ROUND(N(F234),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G234="",Q234="Fechada",Q234="Perdida"),0,IF(Q234="Previsão vencida",3,IF(Q234="Parada",2,1))*1E+15+MIN(N(O234),500)*1E+12+MIN(ROUND(N(F234)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12467,7 +13214,7 @@
         <v/>
       </c>
       <c r="R235" s="37">
-        <f>IF(OR(G235="",Q235="Fechada",Q235="Perdida"),0,IF(Q235="Previsão vencida",3,IF(Q235="Parada",2,1))*1E+13+MIN(N(O235),500)*1E+10+MIN(ROUND(N(F235),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G235="",Q235="Fechada",Q235="Perdida"),0,IF(Q235="Previsão vencida",3,IF(Q235="Parada",2,1))*1E+15+MIN(N(O235),500)*1E+12+MIN(ROUND(N(F235)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12505,7 +13252,7 @@
         <v/>
       </c>
       <c r="R236" s="37">
-        <f>IF(OR(G236="",Q236="Fechada",Q236="Perdida"),0,IF(Q236="Previsão vencida",3,IF(Q236="Parada",2,1))*1E+13+MIN(N(O236),500)*1E+10+MIN(ROUND(N(F236),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G236="",Q236="Fechada",Q236="Perdida"),0,IF(Q236="Previsão vencida",3,IF(Q236="Parada",2,1))*1E+15+MIN(N(O236),500)*1E+12+MIN(ROUND(N(F236)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12543,7 +13290,7 @@
         <v/>
       </c>
       <c r="R237" s="37">
-        <f>IF(OR(G237="",Q237="Fechada",Q237="Perdida"),0,IF(Q237="Previsão vencida",3,IF(Q237="Parada",2,1))*1E+13+MIN(N(O237),500)*1E+10+MIN(ROUND(N(F237),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G237="",Q237="Fechada",Q237="Perdida"),0,IF(Q237="Previsão vencida",3,IF(Q237="Parada",2,1))*1E+15+MIN(N(O237),500)*1E+12+MIN(ROUND(N(F237)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12581,7 +13328,7 @@
         <v/>
       </c>
       <c r="R238" s="37">
-        <f>IF(OR(G238="",Q238="Fechada",Q238="Perdida"),0,IF(Q238="Previsão vencida",3,IF(Q238="Parada",2,1))*1E+13+MIN(N(O238),500)*1E+10+MIN(ROUND(N(F238),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G238="",Q238="Fechada",Q238="Perdida"),0,IF(Q238="Previsão vencida",3,IF(Q238="Parada",2,1))*1E+15+MIN(N(O238),500)*1E+12+MIN(ROUND(N(F238)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12619,7 +13366,7 @@
         <v/>
       </c>
       <c r="R239" s="37">
-        <f>IF(OR(G239="",Q239="Fechada",Q239="Perdida"),0,IF(Q239="Previsão vencida",3,IF(Q239="Parada",2,1))*1E+13+MIN(N(O239),500)*1E+10+MIN(ROUND(N(F239),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G239="",Q239="Fechada",Q239="Perdida"),0,IF(Q239="Previsão vencida",3,IF(Q239="Parada",2,1))*1E+15+MIN(N(O239),500)*1E+12+MIN(ROUND(N(F239)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12657,7 +13404,7 @@
         <v/>
       </c>
       <c r="R240" s="37">
-        <f>IF(OR(G240="",Q240="Fechada",Q240="Perdida"),0,IF(Q240="Previsão vencida",3,IF(Q240="Parada",2,1))*1E+13+MIN(N(O240),500)*1E+10+MIN(ROUND(N(F240),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G240="",Q240="Fechada",Q240="Perdida"),0,IF(Q240="Previsão vencida",3,IF(Q240="Parada",2,1))*1E+15+MIN(N(O240),500)*1E+12+MIN(ROUND(N(F240)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12695,7 +13442,7 @@
         <v/>
       </c>
       <c r="R241" s="37">
-        <f>IF(OR(G241="",Q241="Fechada",Q241="Perdida"),0,IF(Q241="Previsão vencida",3,IF(Q241="Parada",2,1))*1E+13+MIN(N(O241),500)*1E+10+MIN(ROUND(N(F241),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G241="",Q241="Fechada",Q241="Perdida"),0,IF(Q241="Previsão vencida",3,IF(Q241="Parada",2,1))*1E+15+MIN(N(O241),500)*1E+12+MIN(ROUND(N(F241)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12733,7 +13480,7 @@
         <v/>
       </c>
       <c r="R242" s="37">
-        <f>IF(OR(G242="",Q242="Fechada",Q242="Perdida"),0,IF(Q242="Previsão vencida",3,IF(Q242="Parada",2,1))*1E+13+MIN(N(O242),500)*1E+10+MIN(ROUND(N(F242),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G242="",Q242="Fechada",Q242="Perdida"),0,IF(Q242="Previsão vencida",3,IF(Q242="Parada",2,1))*1E+15+MIN(N(O242),500)*1E+12+MIN(ROUND(N(F242)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12771,7 +13518,7 @@
         <v/>
       </c>
       <c r="R243" s="37">
-        <f>IF(OR(G243="",Q243="Fechada",Q243="Perdida"),0,IF(Q243="Previsão vencida",3,IF(Q243="Parada",2,1))*1E+13+MIN(N(O243),500)*1E+10+MIN(ROUND(N(F243),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G243="",Q243="Fechada",Q243="Perdida"),0,IF(Q243="Previsão vencida",3,IF(Q243="Parada",2,1))*1E+15+MIN(N(O243),500)*1E+12+MIN(ROUND(N(F243)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12809,7 +13556,7 @@
         <v/>
       </c>
       <c r="R244" s="37">
-        <f>IF(OR(G244="",Q244="Fechada",Q244="Perdida"),0,IF(Q244="Previsão vencida",3,IF(Q244="Parada",2,1))*1E+13+MIN(N(O244),500)*1E+10+MIN(ROUND(N(F244),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G244="",Q244="Fechada",Q244="Perdida"),0,IF(Q244="Previsão vencida",3,IF(Q244="Parada",2,1))*1E+15+MIN(N(O244),500)*1E+12+MIN(ROUND(N(F244)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12847,7 +13594,7 @@
         <v/>
       </c>
       <c r="R245" s="37">
-        <f>IF(OR(G245="",Q245="Fechada",Q245="Perdida"),0,IF(Q245="Previsão vencida",3,IF(Q245="Parada",2,1))*1E+13+MIN(N(O245),500)*1E+10+MIN(ROUND(N(F245),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G245="",Q245="Fechada",Q245="Perdida"),0,IF(Q245="Previsão vencida",3,IF(Q245="Parada",2,1))*1E+15+MIN(N(O245),500)*1E+12+MIN(ROUND(N(F245)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12885,7 +13632,7 @@
         <v/>
       </c>
       <c r="R246" s="37">
-        <f>IF(OR(G246="",Q246="Fechada",Q246="Perdida"),0,IF(Q246="Previsão vencida",3,IF(Q246="Parada",2,1))*1E+13+MIN(N(O246),500)*1E+10+MIN(ROUND(N(F246),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G246="",Q246="Fechada",Q246="Perdida"),0,IF(Q246="Previsão vencida",3,IF(Q246="Parada",2,1))*1E+15+MIN(N(O246),500)*1E+12+MIN(ROUND(N(F246)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12923,7 +13670,7 @@
         <v/>
       </c>
       <c r="R247" s="37">
-        <f>IF(OR(G247="",Q247="Fechada",Q247="Perdida"),0,IF(Q247="Previsão vencida",3,IF(Q247="Parada",2,1))*1E+13+MIN(N(O247),500)*1E+10+MIN(ROUND(N(F247),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G247="",Q247="Fechada",Q247="Perdida"),0,IF(Q247="Previsão vencida",3,IF(Q247="Parada",2,1))*1E+15+MIN(N(O247),500)*1E+12+MIN(ROUND(N(F247)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12961,7 +13708,7 @@
         <v/>
       </c>
       <c r="R248" s="37">
-        <f>IF(OR(G248="",Q248="Fechada",Q248="Perdida"),0,IF(Q248="Previsão vencida",3,IF(Q248="Parada",2,1))*1E+13+MIN(N(O248),500)*1E+10+MIN(ROUND(N(F248),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G248="",Q248="Fechada",Q248="Perdida"),0,IF(Q248="Previsão vencida",3,IF(Q248="Parada",2,1))*1E+15+MIN(N(O248),500)*1E+12+MIN(ROUND(N(F248)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12999,7 +13746,7 @@
         <v/>
       </c>
       <c r="R249" s="37">
-        <f>IF(OR(G249="",Q249="Fechada",Q249="Perdida"),0,IF(Q249="Previsão vencida",3,IF(Q249="Parada",2,1))*1E+13+MIN(N(O249),500)*1E+10+MIN(ROUND(N(F249),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G249="",Q249="Fechada",Q249="Perdida"),0,IF(Q249="Previsão vencida",3,IF(Q249="Parada",2,1))*1E+15+MIN(N(O249),500)*1E+12+MIN(ROUND(N(F249)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13037,7 +13784,7 @@
         <v/>
       </c>
       <c r="R250" s="37">
-        <f>IF(OR(G250="",Q250="Fechada",Q250="Perdida"),0,IF(Q250="Previsão vencida",3,IF(Q250="Parada",2,1))*1E+13+MIN(N(O250),500)*1E+10+MIN(ROUND(N(F250),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G250="",Q250="Fechada",Q250="Perdida"),0,IF(Q250="Previsão vencida",3,IF(Q250="Parada",2,1))*1E+15+MIN(N(O250),500)*1E+12+MIN(ROUND(N(F250)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13075,7 +13822,7 @@
         <v/>
       </c>
       <c r="R251" s="37">
-        <f>IF(OR(G251="",Q251="Fechada",Q251="Perdida"),0,IF(Q251="Previsão vencida",3,IF(Q251="Parada",2,1))*1E+13+MIN(N(O251),500)*1E+10+MIN(ROUND(N(F251),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G251="",Q251="Fechada",Q251="Perdida"),0,IF(Q251="Previsão vencida",3,IF(Q251="Parada",2,1))*1E+15+MIN(N(O251),500)*1E+12+MIN(ROUND(N(F251)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13113,7 +13860,7 @@
         <v/>
       </c>
       <c r="R252" s="37">
-        <f>IF(OR(G252="",Q252="Fechada",Q252="Perdida"),0,IF(Q252="Previsão vencida",3,IF(Q252="Parada",2,1))*1E+13+MIN(N(O252),500)*1E+10+MIN(ROUND(N(F252),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G252="",Q252="Fechada",Q252="Perdida"),0,IF(Q252="Previsão vencida",3,IF(Q252="Parada",2,1))*1E+15+MIN(N(O252),500)*1E+12+MIN(ROUND(N(F252)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13151,7 +13898,7 @@
         <v/>
       </c>
       <c r="R253" s="37">
-        <f>IF(OR(G253="",Q253="Fechada",Q253="Perdida"),0,IF(Q253="Previsão vencida",3,IF(Q253="Parada",2,1))*1E+13+MIN(N(O253),500)*1E+10+MIN(ROUND(N(F253),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G253="",Q253="Fechada",Q253="Perdida"),0,IF(Q253="Previsão vencida",3,IF(Q253="Parada",2,1))*1E+15+MIN(N(O253),500)*1E+12+MIN(ROUND(N(F253)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13189,7 +13936,7 @@
         <v/>
       </c>
       <c r="R254" s="37">
-        <f>IF(OR(G254="",Q254="Fechada",Q254="Perdida"),0,IF(Q254="Previsão vencida",3,IF(Q254="Parada",2,1))*1E+13+MIN(N(O254),500)*1E+10+MIN(ROUND(N(F254),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G254="",Q254="Fechada",Q254="Perdida"),0,IF(Q254="Previsão vencida",3,IF(Q254="Parada",2,1))*1E+15+MIN(N(O254),500)*1E+12+MIN(ROUND(N(F254)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13227,7 +13974,7 @@
         <v/>
       </c>
       <c r="R255" s="37">
-        <f>IF(OR(G255="",Q255="Fechada",Q255="Perdida"),0,IF(Q255="Previsão vencida",3,IF(Q255="Parada",2,1))*1E+13+MIN(N(O255),500)*1E+10+MIN(ROUND(N(F255),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G255="",Q255="Fechada",Q255="Perdida"),0,IF(Q255="Previsão vencida",3,IF(Q255="Parada",2,1))*1E+15+MIN(N(O255),500)*1E+12+MIN(ROUND(N(F255)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13265,7 +14012,7 @@
         <v/>
       </c>
       <c r="R256" s="37">
-        <f>IF(OR(G256="",Q256="Fechada",Q256="Perdida"),0,IF(Q256="Previsão vencida",3,IF(Q256="Parada",2,1))*1E+13+MIN(N(O256),500)*1E+10+MIN(ROUND(N(F256),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G256="",Q256="Fechada",Q256="Perdida"),0,IF(Q256="Previsão vencida",3,IF(Q256="Parada",2,1))*1E+15+MIN(N(O256),500)*1E+12+MIN(ROUND(N(F256)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13303,7 +14050,7 @@
         <v/>
       </c>
       <c r="R257" s="37">
-        <f>IF(OR(G257="",Q257="Fechada",Q257="Perdida"),0,IF(Q257="Previsão vencida",3,IF(Q257="Parada",2,1))*1E+13+MIN(N(O257),500)*1E+10+MIN(ROUND(N(F257),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G257="",Q257="Fechada",Q257="Perdida"),0,IF(Q257="Previsão vencida",3,IF(Q257="Parada",2,1))*1E+15+MIN(N(O257),500)*1E+12+MIN(ROUND(N(F257)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13341,7 +14088,7 @@
         <v/>
       </c>
       <c r="R258" s="37">
-        <f>IF(OR(G258="",Q258="Fechada",Q258="Perdida"),0,IF(Q258="Previsão vencida",3,IF(Q258="Parada",2,1))*1E+13+MIN(N(O258),500)*1E+10+MIN(ROUND(N(F258),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G258="",Q258="Fechada",Q258="Perdida"),0,IF(Q258="Previsão vencida",3,IF(Q258="Parada",2,1))*1E+15+MIN(N(O258),500)*1E+12+MIN(ROUND(N(F258)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13379,7 +14126,7 @@
         <v/>
       </c>
       <c r="R259" s="37">
-        <f>IF(OR(G259="",Q259="Fechada",Q259="Perdida"),0,IF(Q259="Previsão vencida",3,IF(Q259="Parada",2,1))*1E+13+MIN(N(O259),500)*1E+10+MIN(ROUND(N(F259),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G259="",Q259="Fechada",Q259="Perdida"),0,IF(Q259="Previsão vencida",3,IF(Q259="Parada",2,1))*1E+15+MIN(N(O259),500)*1E+12+MIN(ROUND(N(F259)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13417,7 +14164,7 @@
         <v/>
       </c>
       <c r="R260" s="37">
-        <f>IF(OR(G260="",Q260="Fechada",Q260="Perdida"),0,IF(Q260="Previsão vencida",3,IF(Q260="Parada",2,1))*1E+13+MIN(N(O260),500)*1E+10+MIN(ROUND(N(F260),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G260="",Q260="Fechada",Q260="Perdida"),0,IF(Q260="Previsão vencida",3,IF(Q260="Parada",2,1))*1E+15+MIN(N(O260),500)*1E+12+MIN(ROUND(N(F260)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13455,7 +14202,7 @@
         <v/>
       </c>
       <c r="R261" s="37">
-        <f>IF(OR(G261="",Q261="Fechada",Q261="Perdida"),0,IF(Q261="Previsão vencida",3,IF(Q261="Parada",2,1))*1E+13+MIN(N(O261),500)*1E+10+MIN(ROUND(N(F261),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G261="",Q261="Fechada",Q261="Perdida"),0,IF(Q261="Previsão vencida",3,IF(Q261="Parada",2,1))*1E+15+MIN(N(O261),500)*1E+12+MIN(ROUND(N(F261)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13493,7 +14240,7 @@
         <v/>
       </c>
       <c r="R262" s="37">
-        <f>IF(OR(G262="",Q262="Fechada",Q262="Perdida"),0,IF(Q262="Previsão vencida",3,IF(Q262="Parada",2,1))*1E+13+MIN(N(O262),500)*1E+10+MIN(ROUND(N(F262),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G262="",Q262="Fechada",Q262="Perdida"),0,IF(Q262="Previsão vencida",3,IF(Q262="Parada",2,1))*1E+15+MIN(N(O262),500)*1E+12+MIN(ROUND(N(F262)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13531,7 +14278,7 @@
         <v/>
       </c>
       <c r="R263" s="37">
-        <f>IF(OR(G263="",Q263="Fechada",Q263="Perdida"),0,IF(Q263="Previsão vencida",3,IF(Q263="Parada",2,1))*1E+13+MIN(N(O263),500)*1E+10+MIN(ROUND(N(F263),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G263="",Q263="Fechada",Q263="Perdida"),0,IF(Q263="Previsão vencida",3,IF(Q263="Parada",2,1))*1E+15+MIN(N(O263),500)*1E+12+MIN(ROUND(N(F263)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13569,7 +14316,7 @@
         <v/>
       </c>
       <c r="R264" s="37">
-        <f>IF(OR(G264="",Q264="Fechada",Q264="Perdida"),0,IF(Q264="Previsão vencida",3,IF(Q264="Parada",2,1))*1E+13+MIN(N(O264),500)*1E+10+MIN(ROUND(N(F264),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G264="",Q264="Fechada",Q264="Perdida"),0,IF(Q264="Previsão vencida",3,IF(Q264="Parada",2,1))*1E+15+MIN(N(O264),500)*1E+12+MIN(ROUND(N(F264)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13607,7 +14354,7 @@
         <v/>
       </c>
       <c r="R265" s="37">
-        <f>IF(OR(G265="",Q265="Fechada",Q265="Perdida"),0,IF(Q265="Previsão vencida",3,IF(Q265="Parada",2,1))*1E+13+MIN(N(O265),500)*1E+10+MIN(ROUND(N(F265),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G265="",Q265="Fechada",Q265="Perdida"),0,IF(Q265="Previsão vencida",3,IF(Q265="Parada",2,1))*1E+15+MIN(N(O265),500)*1E+12+MIN(ROUND(N(F265)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13645,7 +14392,7 @@
         <v/>
       </c>
       <c r="R266" s="37">
-        <f>IF(OR(G266="",Q266="Fechada",Q266="Perdida"),0,IF(Q266="Previsão vencida",3,IF(Q266="Parada",2,1))*1E+13+MIN(N(O266),500)*1E+10+MIN(ROUND(N(F266),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G266="",Q266="Fechada",Q266="Perdida"),0,IF(Q266="Previsão vencida",3,IF(Q266="Parada",2,1))*1E+15+MIN(N(O266),500)*1E+12+MIN(ROUND(N(F266)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13683,7 +14430,7 @@
         <v/>
       </c>
       <c r="R267" s="37">
-        <f>IF(OR(G267="",Q267="Fechada",Q267="Perdida"),0,IF(Q267="Previsão vencida",3,IF(Q267="Parada",2,1))*1E+13+MIN(N(O267),500)*1E+10+MIN(ROUND(N(F267),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G267="",Q267="Fechada",Q267="Perdida"),0,IF(Q267="Previsão vencida",3,IF(Q267="Parada",2,1))*1E+15+MIN(N(O267),500)*1E+12+MIN(ROUND(N(F267)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13721,7 +14468,7 @@
         <v/>
       </c>
       <c r="R268" s="37">
-        <f>IF(OR(G268="",Q268="Fechada",Q268="Perdida"),0,IF(Q268="Previsão vencida",3,IF(Q268="Parada",2,1))*1E+13+MIN(N(O268),500)*1E+10+MIN(ROUND(N(F268),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G268="",Q268="Fechada",Q268="Perdida"),0,IF(Q268="Previsão vencida",3,IF(Q268="Parada",2,1))*1E+15+MIN(N(O268),500)*1E+12+MIN(ROUND(N(F268)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13759,7 +14506,7 @@
         <v/>
       </c>
       <c r="R269" s="37">
-        <f>IF(OR(G269="",Q269="Fechada",Q269="Perdida"),0,IF(Q269="Previsão vencida",3,IF(Q269="Parada",2,1))*1E+13+MIN(N(O269),500)*1E+10+MIN(ROUND(N(F269),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G269="",Q269="Fechada",Q269="Perdida"),0,IF(Q269="Previsão vencida",3,IF(Q269="Parada",2,1))*1E+15+MIN(N(O269),500)*1E+12+MIN(ROUND(N(F269)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13797,7 +14544,7 @@
         <v/>
       </c>
       <c r="R270" s="37">
-        <f>IF(OR(G270="",Q270="Fechada",Q270="Perdida"),0,IF(Q270="Previsão vencida",3,IF(Q270="Parada",2,1))*1E+13+MIN(N(O270),500)*1E+10+MIN(ROUND(N(F270),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G270="",Q270="Fechada",Q270="Perdida"),0,IF(Q270="Previsão vencida",3,IF(Q270="Parada",2,1))*1E+15+MIN(N(O270),500)*1E+12+MIN(ROUND(N(F270)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13835,7 +14582,7 @@
         <v/>
       </c>
       <c r="R271" s="37">
-        <f>IF(OR(G271="",Q271="Fechada",Q271="Perdida"),0,IF(Q271="Previsão vencida",3,IF(Q271="Parada",2,1))*1E+13+MIN(N(O271),500)*1E+10+MIN(ROUND(N(F271),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G271="",Q271="Fechada",Q271="Perdida"),0,IF(Q271="Previsão vencida",3,IF(Q271="Parada",2,1))*1E+15+MIN(N(O271),500)*1E+12+MIN(ROUND(N(F271)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13873,7 +14620,7 @@
         <v/>
       </c>
       <c r="R272" s="37">
-        <f>IF(OR(G272="",Q272="Fechada",Q272="Perdida"),0,IF(Q272="Previsão vencida",3,IF(Q272="Parada",2,1))*1E+13+MIN(N(O272),500)*1E+10+MIN(ROUND(N(F272),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G272="",Q272="Fechada",Q272="Perdida"),0,IF(Q272="Previsão vencida",3,IF(Q272="Parada",2,1))*1E+15+MIN(N(O272),500)*1E+12+MIN(ROUND(N(F272)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13911,7 +14658,7 @@
         <v/>
       </c>
       <c r="R273" s="37">
-        <f>IF(OR(G273="",Q273="Fechada",Q273="Perdida"),0,IF(Q273="Previsão vencida",3,IF(Q273="Parada",2,1))*1E+13+MIN(N(O273),500)*1E+10+MIN(ROUND(N(F273),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G273="",Q273="Fechada",Q273="Perdida"),0,IF(Q273="Previsão vencida",3,IF(Q273="Parada",2,1))*1E+15+MIN(N(O273),500)*1E+12+MIN(ROUND(N(F273)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13949,7 +14696,7 @@
         <v/>
       </c>
       <c r="R274" s="37">
-        <f>IF(OR(G274="",Q274="Fechada",Q274="Perdida"),0,IF(Q274="Previsão vencida",3,IF(Q274="Parada",2,1))*1E+13+MIN(N(O274),500)*1E+10+MIN(ROUND(N(F274),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G274="",Q274="Fechada",Q274="Perdida"),0,IF(Q274="Previsão vencida",3,IF(Q274="Parada",2,1))*1E+15+MIN(N(O274),500)*1E+12+MIN(ROUND(N(F274)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13987,7 +14734,7 @@
         <v/>
       </c>
       <c r="R275" s="37">
-        <f>IF(OR(G275="",Q275="Fechada",Q275="Perdida"),0,IF(Q275="Previsão vencida",3,IF(Q275="Parada",2,1))*1E+13+MIN(N(O275),500)*1E+10+MIN(ROUND(N(F275),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G275="",Q275="Fechada",Q275="Perdida"),0,IF(Q275="Previsão vencida",3,IF(Q275="Parada",2,1))*1E+15+MIN(N(O275),500)*1E+12+MIN(ROUND(N(F275)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14025,7 +14772,7 @@
         <v/>
       </c>
       <c r="R276" s="37">
-        <f>IF(OR(G276="",Q276="Fechada",Q276="Perdida"),0,IF(Q276="Previsão vencida",3,IF(Q276="Parada",2,1))*1E+13+MIN(N(O276),500)*1E+10+MIN(ROUND(N(F276),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G276="",Q276="Fechada",Q276="Perdida"),0,IF(Q276="Previsão vencida",3,IF(Q276="Parada",2,1))*1E+15+MIN(N(O276),500)*1E+12+MIN(ROUND(N(F276)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14063,7 +14810,7 @@
         <v/>
       </c>
       <c r="R277" s="37">
-        <f>IF(OR(G277="",Q277="Fechada",Q277="Perdida"),0,IF(Q277="Previsão vencida",3,IF(Q277="Parada",2,1))*1E+13+MIN(N(O277),500)*1E+10+MIN(ROUND(N(F277),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G277="",Q277="Fechada",Q277="Perdida"),0,IF(Q277="Previsão vencida",3,IF(Q277="Parada",2,1))*1E+15+MIN(N(O277),500)*1E+12+MIN(ROUND(N(F277)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14101,7 +14848,7 @@
         <v/>
       </c>
       <c r="R278" s="37">
-        <f>IF(OR(G278="",Q278="Fechada",Q278="Perdida"),0,IF(Q278="Previsão vencida",3,IF(Q278="Parada",2,1))*1E+13+MIN(N(O278),500)*1E+10+MIN(ROUND(N(F278),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G278="",Q278="Fechada",Q278="Perdida"),0,IF(Q278="Previsão vencida",3,IF(Q278="Parada",2,1))*1E+15+MIN(N(O278),500)*1E+12+MIN(ROUND(N(F278)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14139,7 +14886,7 @@
         <v/>
       </c>
       <c r="R279" s="37">
-        <f>IF(OR(G279="",Q279="Fechada",Q279="Perdida"),0,IF(Q279="Previsão vencida",3,IF(Q279="Parada",2,1))*1E+13+MIN(N(O279),500)*1E+10+MIN(ROUND(N(F279),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G279="",Q279="Fechada",Q279="Perdida"),0,IF(Q279="Previsão vencida",3,IF(Q279="Parada",2,1))*1E+15+MIN(N(O279),500)*1E+12+MIN(ROUND(N(F279)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14177,7 +14924,7 @@
         <v/>
       </c>
       <c r="R280" s="37">
-        <f>IF(OR(G280="",Q280="Fechada",Q280="Perdida"),0,IF(Q280="Previsão vencida",3,IF(Q280="Parada",2,1))*1E+13+MIN(N(O280),500)*1E+10+MIN(ROUND(N(F280),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G280="",Q280="Fechada",Q280="Perdida"),0,IF(Q280="Previsão vencida",3,IF(Q280="Parada",2,1))*1E+15+MIN(N(O280),500)*1E+12+MIN(ROUND(N(F280)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14215,7 +14962,7 @@
         <v/>
       </c>
       <c r="R281" s="37">
-        <f>IF(OR(G281="",Q281="Fechada",Q281="Perdida"),0,IF(Q281="Previsão vencida",3,IF(Q281="Parada",2,1))*1E+13+MIN(N(O281),500)*1E+10+MIN(ROUND(N(F281),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G281="",Q281="Fechada",Q281="Perdida"),0,IF(Q281="Previsão vencida",3,IF(Q281="Parada",2,1))*1E+15+MIN(N(O281),500)*1E+12+MIN(ROUND(N(F281)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14253,7 +15000,7 @@
         <v/>
       </c>
       <c r="R282" s="37">
-        <f>IF(OR(G282="",Q282="Fechada",Q282="Perdida"),0,IF(Q282="Previsão vencida",3,IF(Q282="Parada",2,1))*1E+13+MIN(N(O282),500)*1E+10+MIN(ROUND(N(F282),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G282="",Q282="Fechada",Q282="Perdida"),0,IF(Q282="Previsão vencida",3,IF(Q282="Parada",2,1))*1E+15+MIN(N(O282),500)*1E+12+MIN(ROUND(N(F282)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14291,7 +15038,7 @@
         <v/>
       </c>
       <c r="R283" s="37">
-        <f>IF(OR(G283="",Q283="Fechada",Q283="Perdida"),0,IF(Q283="Previsão vencida",3,IF(Q283="Parada",2,1))*1E+13+MIN(N(O283),500)*1E+10+MIN(ROUND(N(F283),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G283="",Q283="Fechada",Q283="Perdida"),0,IF(Q283="Previsão vencida",3,IF(Q283="Parada",2,1))*1E+15+MIN(N(O283),500)*1E+12+MIN(ROUND(N(F283)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14329,7 +15076,7 @@
         <v/>
       </c>
       <c r="R284" s="37">
-        <f>IF(OR(G284="",Q284="Fechada",Q284="Perdida"),0,IF(Q284="Previsão vencida",3,IF(Q284="Parada",2,1))*1E+13+MIN(N(O284),500)*1E+10+MIN(ROUND(N(F284),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G284="",Q284="Fechada",Q284="Perdida"),0,IF(Q284="Previsão vencida",3,IF(Q284="Parada",2,1))*1E+15+MIN(N(O284),500)*1E+12+MIN(ROUND(N(F284)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14367,7 +15114,7 @@
         <v/>
       </c>
       <c r="R285" s="37">
-        <f>IF(OR(G285="",Q285="Fechada",Q285="Perdida"),0,IF(Q285="Previsão vencida",3,IF(Q285="Parada",2,1))*1E+13+MIN(N(O285),500)*1E+10+MIN(ROUND(N(F285),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G285="",Q285="Fechada",Q285="Perdida"),0,IF(Q285="Previsão vencida",3,IF(Q285="Parada",2,1))*1E+15+MIN(N(O285),500)*1E+12+MIN(ROUND(N(F285)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14405,7 +15152,7 @@
         <v/>
       </c>
       <c r="R286" s="37">
-        <f>IF(OR(G286="",Q286="Fechada",Q286="Perdida"),0,IF(Q286="Previsão vencida",3,IF(Q286="Parada",2,1))*1E+13+MIN(N(O286),500)*1E+10+MIN(ROUND(N(F286),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G286="",Q286="Fechada",Q286="Perdida"),0,IF(Q286="Previsão vencida",3,IF(Q286="Parada",2,1))*1E+15+MIN(N(O286),500)*1E+12+MIN(ROUND(N(F286)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14443,7 +15190,7 @@
         <v/>
       </c>
       <c r="R287" s="37">
-        <f>IF(OR(G287="",Q287="Fechada",Q287="Perdida"),0,IF(Q287="Previsão vencida",3,IF(Q287="Parada",2,1))*1E+13+MIN(N(O287),500)*1E+10+MIN(ROUND(N(F287),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G287="",Q287="Fechada",Q287="Perdida"),0,IF(Q287="Previsão vencida",3,IF(Q287="Parada",2,1))*1E+15+MIN(N(O287),500)*1E+12+MIN(ROUND(N(F287)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14481,7 +15228,7 @@
         <v/>
       </c>
       <c r="R288" s="37">
-        <f>IF(OR(G288="",Q288="Fechada",Q288="Perdida"),0,IF(Q288="Previsão vencida",3,IF(Q288="Parada",2,1))*1E+13+MIN(N(O288),500)*1E+10+MIN(ROUND(N(F288),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G288="",Q288="Fechada",Q288="Perdida"),0,IF(Q288="Previsão vencida",3,IF(Q288="Parada",2,1))*1E+15+MIN(N(O288),500)*1E+12+MIN(ROUND(N(F288)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14519,7 +15266,7 @@
         <v/>
       </c>
       <c r="R289" s="37">
-        <f>IF(OR(G289="",Q289="Fechada",Q289="Perdida"),0,IF(Q289="Previsão vencida",3,IF(Q289="Parada",2,1))*1E+13+MIN(N(O289),500)*1E+10+MIN(ROUND(N(F289),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G289="",Q289="Fechada",Q289="Perdida"),0,IF(Q289="Previsão vencida",3,IF(Q289="Parada",2,1))*1E+15+MIN(N(O289),500)*1E+12+MIN(ROUND(N(F289)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14557,7 +15304,7 @@
         <v/>
       </c>
       <c r="R290" s="37">
-        <f>IF(OR(G290="",Q290="Fechada",Q290="Perdida"),0,IF(Q290="Previsão vencida",3,IF(Q290="Parada",2,1))*1E+13+MIN(N(O290),500)*1E+10+MIN(ROUND(N(F290),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G290="",Q290="Fechada",Q290="Perdida"),0,IF(Q290="Previsão vencida",3,IF(Q290="Parada",2,1))*1E+15+MIN(N(O290),500)*1E+12+MIN(ROUND(N(F290)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14595,7 +15342,7 @@
         <v/>
       </c>
       <c r="R291" s="37">
-        <f>IF(OR(G291="",Q291="Fechada",Q291="Perdida"),0,IF(Q291="Previsão vencida",3,IF(Q291="Parada",2,1))*1E+13+MIN(N(O291),500)*1E+10+MIN(ROUND(N(F291),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G291="",Q291="Fechada",Q291="Perdida"),0,IF(Q291="Previsão vencida",3,IF(Q291="Parada",2,1))*1E+15+MIN(N(O291),500)*1E+12+MIN(ROUND(N(F291)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14633,7 +15380,7 @@
         <v/>
       </c>
       <c r="R292" s="37">
-        <f>IF(OR(G292="",Q292="Fechada",Q292="Perdida"),0,IF(Q292="Previsão vencida",3,IF(Q292="Parada",2,1))*1E+13+MIN(N(O292),500)*1E+10+MIN(ROUND(N(F292),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G292="",Q292="Fechada",Q292="Perdida"),0,IF(Q292="Previsão vencida",3,IF(Q292="Parada",2,1))*1E+15+MIN(N(O292),500)*1E+12+MIN(ROUND(N(F292)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14671,7 +15418,7 @@
         <v/>
       </c>
       <c r="R293" s="37">
-        <f>IF(OR(G293="",Q293="Fechada",Q293="Perdida"),0,IF(Q293="Previsão vencida",3,IF(Q293="Parada",2,1))*1E+13+MIN(N(O293),500)*1E+10+MIN(ROUND(N(F293),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G293="",Q293="Fechada",Q293="Perdida"),0,IF(Q293="Previsão vencida",3,IF(Q293="Parada",2,1))*1E+15+MIN(N(O293),500)*1E+12+MIN(ROUND(N(F293)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14709,7 +15456,7 @@
         <v/>
       </c>
       <c r="R294" s="37">
-        <f>IF(OR(G294="",Q294="Fechada",Q294="Perdida"),0,IF(Q294="Previsão vencida",3,IF(Q294="Parada",2,1))*1E+13+MIN(N(O294),500)*1E+10+MIN(ROUND(N(F294),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G294="",Q294="Fechada",Q294="Perdida"),0,IF(Q294="Previsão vencida",3,IF(Q294="Parada",2,1))*1E+15+MIN(N(O294),500)*1E+12+MIN(ROUND(N(F294)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14747,7 +15494,7 @@
         <v/>
       </c>
       <c r="R295" s="37">
-        <f>IF(OR(G295="",Q295="Fechada",Q295="Perdida"),0,IF(Q295="Previsão vencida",3,IF(Q295="Parada",2,1))*1E+13+MIN(N(O295),500)*1E+10+MIN(ROUND(N(F295),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G295="",Q295="Fechada",Q295="Perdida"),0,IF(Q295="Previsão vencida",3,IF(Q295="Parada",2,1))*1E+15+MIN(N(O295),500)*1E+12+MIN(ROUND(N(F295)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14785,7 +15532,7 @@
         <v/>
       </c>
       <c r="R296" s="37">
-        <f>IF(OR(G296="",Q296="Fechada",Q296="Perdida"),0,IF(Q296="Previsão vencida",3,IF(Q296="Parada",2,1))*1E+13+MIN(N(O296),500)*1E+10+MIN(ROUND(N(F296),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G296="",Q296="Fechada",Q296="Perdida"),0,IF(Q296="Previsão vencida",3,IF(Q296="Parada",2,1))*1E+15+MIN(N(O296),500)*1E+12+MIN(ROUND(N(F296)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14823,7 +15570,7 @@
         <v/>
       </c>
       <c r="R297" s="37">
-        <f>IF(OR(G297="",Q297="Fechada",Q297="Perdida"),0,IF(Q297="Previsão vencida",3,IF(Q297="Parada",2,1))*1E+13+MIN(N(O297),500)*1E+10+MIN(ROUND(N(F297),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G297="",Q297="Fechada",Q297="Perdida"),0,IF(Q297="Previsão vencida",3,IF(Q297="Parada",2,1))*1E+15+MIN(N(O297),500)*1E+12+MIN(ROUND(N(F297)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14861,7 +15608,7 @@
         <v/>
       </c>
       <c r="R298" s="37">
-        <f>IF(OR(G298="",Q298="Fechada",Q298="Perdida"),0,IF(Q298="Previsão vencida",3,IF(Q298="Parada",2,1))*1E+13+MIN(N(O298),500)*1E+10+MIN(ROUND(N(F298),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G298="",Q298="Fechada",Q298="Perdida"),0,IF(Q298="Previsão vencida",3,IF(Q298="Parada",2,1))*1E+15+MIN(N(O298),500)*1E+12+MIN(ROUND(N(F298)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14899,7 +15646,7 @@
         <v/>
       </c>
       <c r="R299" s="37">
-        <f>IF(OR(G299="",Q299="Fechada",Q299="Perdida"),0,IF(Q299="Previsão vencida",3,IF(Q299="Parada",2,1))*1E+13+MIN(N(O299),500)*1E+10+MIN(ROUND(N(F299),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G299="",Q299="Fechada",Q299="Perdida"),0,IF(Q299="Previsão vencida",3,IF(Q299="Parada",2,1))*1E+15+MIN(N(O299),500)*1E+12+MIN(ROUND(N(F299)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14937,7 +15684,7 @@
         <v/>
       </c>
       <c r="R300" s="37">
-        <f>IF(OR(G300="",Q300="Fechada",Q300="Perdida"),0,IF(Q300="Previsão vencida",3,IF(Q300="Parada",2,1))*1E+13+MIN(N(O300),500)*1E+10+MIN(ROUND(N(F300),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G300="",Q300="Fechada",Q300="Perdida"),0,IF(Q300="Previsão vencida",3,IF(Q300="Parada",2,1))*1E+15+MIN(N(O300),500)*1E+12+MIN(ROUND(N(F300)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14975,7 +15722,7 @@
         <v/>
       </c>
       <c r="R301" s="37">
-        <f>IF(OR(G301="",Q301="Fechada",Q301="Perdida"),0,IF(Q301="Previsão vencida",3,IF(Q301="Parada",2,1))*1E+13+MIN(N(O301),500)*1E+10+MIN(ROUND(N(F301),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G301="",Q301="Fechada",Q301="Perdida"),0,IF(Q301="Previsão vencida",3,IF(Q301="Parada",2,1))*1E+15+MIN(N(O301),500)*1E+12+MIN(ROUND(N(F301)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15013,7 +15760,7 @@
         <v/>
       </c>
       <c r="R302" s="37">
-        <f>IF(OR(G302="",Q302="Fechada",Q302="Perdida"),0,IF(Q302="Previsão vencida",3,IF(Q302="Parada",2,1))*1E+13+MIN(N(O302),500)*1E+10+MIN(ROUND(N(F302),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G302="",Q302="Fechada",Q302="Perdida"),0,IF(Q302="Previsão vencida",3,IF(Q302="Parada",2,1))*1E+15+MIN(N(O302),500)*1E+12+MIN(ROUND(N(F302)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15051,7 +15798,7 @@
         <v/>
       </c>
       <c r="R303" s="37">
-        <f>IF(OR(G303="",Q303="Fechada",Q303="Perdida"),0,IF(Q303="Previsão vencida",3,IF(Q303="Parada",2,1))*1E+13+MIN(N(O303),500)*1E+10+MIN(ROUND(N(F303),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G303="",Q303="Fechada",Q303="Perdida"),0,IF(Q303="Previsão vencida",3,IF(Q303="Parada",2,1))*1E+15+MIN(N(O303),500)*1E+12+MIN(ROUND(N(F303)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15089,7 +15836,7 @@
         <v/>
       </c>
       <c r="R304" s="37">
-        <f>IF(OR(G304="",Q304="Fechada",Q304="Perdida"),0,IF(Q304="Previsão vencida",3,IF(Q304="Parada",2,1))*1E+13+MIN(N(O304),500)*1E+10+MIN(ROUND(N(F304),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G304="",Q304="Fechada",Q304="Perdida"),0,IF(Q304="Previsão vencida",3,IF(Q304="Parada",2,1))*1E+15+MIN(N(O304),500)*1E+12+MIN(ROUND(N(F304)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15128,22 +15875,22 @@
   </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation sqref="B5:B304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=OFFSET(Config!$A$18,0,0,MAX(1,COUNTA(Config!$A$18:$A$27)),1)</formula1>
+      <formula1>=OFFSET(Config!$A$18,0,0,MAX(1,COUNTA(Config!$A$18:$A$37)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=OFFSET(Config!$I$18,0,0,MAX(1,COUNTA(Config!$I$18:$I$27)),1)</formula1>
+      <formula1>=OFFSET(Config!$I$18,0,0,MAX(1,COUNTA(Config!$I$18:$I$37)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=OFFSET(Config!$C$18,0,0,MAX(1,COUNTA(Config!$C$18:$C$27)),1)</formula1>
+      <formula1>=OFFSET(Config!$C$18,0,0,MAX(1,COUNTA(Config!$C$18:$C$37)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=OFFSET(Config!$G$18,0,0,MAX(1,COUNTA(Config!$G$18:$G$27)),1)</formula1>
+      <formula1>=OFFSET(Config!$G$18,0,0,MAX(1,COUNTA(Config!$G$18:$G$37)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="G5:G304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$A$10:$A$15</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=OFFSET(Config!$E$18,0,0,MAX(1,COUNTA(Config!$E$18:$E$27)),1)</formula1>
+      <formula1>=OFFSET(Config!$E$18,0,0,MAX(1,COUNTA(Config!$E$18:$E$37)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="H5:K304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
